--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D18" s="343" t="n">
-        <v>2858.4</v>
+        <v>2125.2</v>
       </c>
       <c r="E18" s="344" t="n">
         <v>17.5</v>
@@ -5070,7 +5070,7 @@
         <v/>
       </c>
       <c r="G18" s="340" t="n">
-        <v>81.67</v>
+        <v>60.72</v>
       </c>
       <c r="H18" s="340" t="n">
         <v>2</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D24" s="343" t="n">
-        <v>1334.6</v>
+        <v>1006.6</v>
       </c>
       <c r="E24" s="344" t="n">
         <v>17.5</v>
@@ -5340,7 +5340,7 @@
         <v/>
       </c>
       <c r="G24" s="340" t="n">
-        <v>38.13</v>
+        <v>28.76</v>
       </c>
       <c r="H24" s="340" t="n">
         <v>1</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="D55" s="348" t="n">
-        <v>1594.6</v>
+        <v>1586.9</v>
       </c>
       <c r="E55" s="349" t="n">
         <v>17.5</v>
@@ -6711,7 +6711,7 @@
         <v/>
       </c>
       <c r="G55" s="345" t="n">
-        <v>45.56</v>
+        <v>45.34</v>
       </c>
       <c r="H55" s="345" t="n">
         <v>1</v>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="D56" s="348" t="n">
-        <v>2847.9</v>
+        <v>2443.7</v>
       </c>
       <c r="E56" s="349" t="n">
         <v>17.5</v>
@@ -6756,7 +6756,7 @@
         <v/>
       </c>
       <c r="G56" s="345" t="n">
-        <v>81.37</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="H56" s="345" t="n">
         <v>2</v>
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="D63" s="348" t="n">
-        <v>2652.3</v>
+        <v>1210.3</v>
       </c>
       <c r="E63" s="349" t="n">
         <v>17.5</v>
@@ -7071,7 +7071,7 @@
         <v/>
       </c>
       <c r="G63" s="345" t="n">
-        <v>75.78</v>
+        <v>34.58</v>
       </c>
       <c r="H63" s="345" t="n">
         <v>2</v>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 37157 W</t>
+          <t>TOPLAM ISI = 36095 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -13952,10 +13952,10 @@
         <v>7.87</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>6.98</v>
+        <v>6.92</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="R12" s="397" t="n">
         <v>8.73</v>
@@ -14040,10 +14040,10 @@
         <v>1694</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>1480.5</v>
+        <v>1091.3</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>1377.9</v>
+        <v>1033.9</v>
       </c>
       <c r="R13" s="398" t="n">
         <v>1365.3</v>
@@ -14064,7 +14064,7 @@
         <v>385.7</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>1334.6</v>
+        <v>1006.6</v>
       </c>
       <c r="Y13" s="398" t="n">
         <v>949.5</v>
@@ -16052,10 +16052,10 @@
         <v>9141</v>
       </c>
       <c r="P32" s="407" t="n">
-        <v>6311</v>
+        <v>2728</v>
       </c>
       <c r="Q32" s="407" t="n">
-        <v>5180</v>
+        <v>2351</v>
       </c>
       <c r="R32" s="407" t="n">
         <v>5051</v>
@@ -16076,7 +16076,7 @@
         <v>131</v>
       </c>
       <c r="X32" s="407" t="n">
-        <v>4745</v>
+        <v>2185</v>
       </c>
       <c r="Y32" s="407" t="n">
         <v>1861</v>
@@ -20704,7 +20704,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 36764 W</t>
+          <t>TOPLAM ISI = 34910 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -21500,10 +21500,10 @@
         <v>7.57</v>
       </c>
       <c r="G12" s="397" t="n">
-        <v>6.98</v>
+        <v>6.05</v>
       </c>
       <c r="H12" s="397" t="n">
-        <v>6.46</v>
+        <v>7.39</v>
       </c>
       <c r="I12" s="397" t="n">
         <v>8.73</v>
@@ -21527,10 +21527,10 @@
         <v>6.92</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>7.56</v>
+        <v>6.75</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>6.46</v>
+        <v>7.27</v>
       </c>
       <c r="R12" s="397" t="n">
         <v>8.66</v>
@@ -21602,13 +21602,13 @@
       <c r="D13" s="261" t="n"/>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>1594.6</v>
+        <v>1586.9</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>1478</v>
+        <v>1100</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>1369.9</v>
+        <v>1343.7</v>
       </c>
       <c r="I13" s="398" t="n">
         <v>1361.2</v>
@@ -21632,10 +21632,10 @@
         <v>1189.3</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>1429.8</v>
+        <v>583.1</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>1222.5</v>
+        <v>627.2</v>
       </c>
       <c r="R13" s="398" t="n">
         <v>1539</v>
@@ -23930,13 +23930,13 @@
       </c>
       <c r="E32" s="259" t="n"/>
       <c r="F32" s="407" t="n">
-        <v>7741</v>
+        <v>7639</v>
       </c>
       <c r="G32" s="407" t="n">
-        <v>6282</v>
+        <v>2788</v>
       </c>
       <c r="H32" s="407" t="n">
-        <v>5098</v>
+        <v>4834</v>
       </c>
       <c r="I32" s="407" t="n">
         <v>5009</v>
@@ -23960,10 +23960,10 @@
         <v>3456</v>
       </c>
       <c r="P32" s="407" t="n">
-        <v>5734</v>
+        <v>300</v>
       </c>
       <c r="Q32" s="407" t="n">
-        <v>3728</v>
+        <v>595</v>
       </c>
       <c r="R32" s="407" t="n">
         <v>7021</v>

--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="D10" s="343" t="n">
-        <v>1604.4</v>
+        <v>802.2</v>
       </c>
       <c r="E10" s="344" t="n">
         <v>17.5</v>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="D11" s="343" t="n">
-        <v>2551.9</v>
+        <v>1275.9</v>
       </c>
       <c r="E11" s="344" t="n">
         <v>17.5</v>
@@ -4790,7 +4790,7 @@
         </is>
       </c>
       <c r="D12" s="343" t="n">
-        <v>1365.3</v>
+        <v>682.7</v>
       </c>
       <c r="E12" s="344" t="n">
         <v>17.5</v>
@@ -4835,7 +4835,7 @@
         </is>
       </c>
       <c r="D13" s="343" t="n">
-        <v>1544.2</v>
+        <v>772.1</v>
       </c>
       <c r="E13" s="344" t="n">
         <v>17.5</v>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="D14" s="343" t="n">
-        <v>3600.5</v>
+        <v>1800.2</v>
       </c>
       <c r="E14" s="344" t="n">
         <v>17.5</v>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="D15" s="343" t="n">
-        <v>1519.3</v>
+        <v>759.7</v>
       </c>
       <c r="E15" s="344" t="n">
         <v>17.5</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D16" s="343" t="n">
-        <v>391.6</v>
+        <v>195.8</v>
       </c>
       <c r="E16" s="344" t="n">
         <v>17.5</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="D17" s="343" t="n">
-        <v>1694</v>
+        <v>847</v>
       </c>
       <c r="E17" s="344" t="n">
         <v>17.5</v>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D18" s="343" t="n">
-        <v>2125.2</v>
+        <v>1062.6</v>
       </c>
       <c r="E18" s="344" t="n">
         <v>17.5</v>
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="D19" s="343" t="n">
-        <v>1365.3</v>
+        <v>682.7</v>
       </c>
       <c r="E19" s="344" t="n">
         <v>17.5</v>
@@ -5150,7 +5150,7 @@
         </is>
       </c>
       <c r="D20" s="343" t="n">
-        <v>1481.9</v>
+        <v>741</v>
       </c>
       <c r="E20" s="344" t="n">
         <v>17.5</v>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="D21" s="343" t="n">
-        <v>3933.3</v>
+        <v>1966.6</v>
       </c>
       <c r="E21" s="344" t="n">
         <v>17.5</v>
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="D22" s="343" t="n">
-        <v>1521.8</v>
+        <v>760.9</v>
       </c>
       <c r="E22" s="344" t="n">
         <v>17.5</v>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="D23" s="343" t="n">
-        <v>385.7</v>
+        <v>192.8</v>
       </c>
       <c r="E23" s="344" t="n">
         <v>17.5</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D24" s="343" t="n">
-        <v>1006.6</v>
+        <v>503.3</v>
       </c>
       <c r="E24" s="344" t="n">
         <v>17.5</v>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="D25" s="348" t="n">
-        <v>2011</v>
+        <v>1005.5</v>
       </c>
       <c r="E25" s="349" t="n">
         <v>17.5</v>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="D26" s="348" t="n">
-        <v>1504.7</v>
+        <v>752.3</v>
       </c>
       <c r="E26" s="349" t="n">
         <v>17.5</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="D27" s="348" t="n">
-        <v>3407</v>
+        <v>1703.5</v>
       </c>
       <c r="E27" s="349" t="n">
         <v>17.5</v>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="D28" s="348" t="n">
-        <v>1254.4</v>
+        <v>627.2</v>
       </c>
       <c r="E28" s="349" t="n">
         <v>17.5</v>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="D29" s="348" t="n">
-        <v>1577.8</v>
+        <v>788.9</v>
       </c>
       <c r="E29" s="349" t="n">
         <v>17.5</v>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="D30" s="348" t="n">
-        <v>249.5</v>
+        <v>124.8</v>
       </c>
       <c r="E30" s="349" t="n">
         <v>17.5</v>
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="D32" s="348" t="n">
-        <v>1695.4</v>
+        <v>847.7</v>
       </c>
       <c r="E32" s="349" t="n">
         <v>17.5</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="D33" s="348" t="n">
-        <v>2538.2</v>
+        <v>1269.1</v>
       </c>
       <c r="E33" s="349" t="n">
         <v>17.5</v>
@@ -5768,7 +5768,7 @@
         </is>
       </c>
       <c r="D34" s="348" t="n">
-        <v>1365.3</v>
+        <v>682.7</v>
       </c>
       <c r="E34" s="349" t="n">
         <v>17.5</v>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="D35" s="348" t="n">
-        <v>1481.9</v>
+        <v>741</v>
       </c>
       <c r="E35" s="349" t="n">
         <v>17.5</v>
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="D36" s="348" t="n">
-        <v>3919.3</v>
+        <v>1959.7</v>
       </c>
       <c r="E36" s="349" t="n">
         <v>17.5</v>
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="D37" s="348" t="n">
-        <v>1521.8</v>
+        <v>760.9</v>
       </c>
       <c r="E37" s="349" t="n">
         <v>17.5</v>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="D38" s="348" t="n">
-        <v>385</v>
+        <v>192.5</v>
       </c>
       <c r="E38" s="349" t="n">
         <v>17.5</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="D39" s="348" t="n">
-        <v>1176.7</v>
+        <v>588.3</v>
       </c>
       <c r="E39" s="349" t="n">
         <v>17.5</v>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="D40" s="348" t="n">
-        <v>2112.3</v>
+        <v>1056.1</v>
       </c>
       <c r="E40" s="349" t="n">
         <v>17.5</v>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="D41" s="348" t="n">
-        <v>1504.7</v>
+        <v>752.3</v>
       </c>
       <c r="E41" s="349" t="n">
         <v>17.5</v>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="D42" s="348" t="n">
-        <v>3226.3</v>
+        <v>1613.2</v>
       </c>
       <c r="E42" s="349" t="n">
         <v>17.5</v>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="D43" s="348" t="n">
-        <v>1086.8</v>
+        <v>543.4</v>
       </c>
       <c r="E43" s="349" t="n">
         <v>17.5</v>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="D44" s="348" t="n">
-        <v>1577.5</v>
+        <v>788.7</v>
       </c>
       <c r="E44" s="349" t="n">
         <v>17.5</v>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="D45" s="348" t="n">
-        <v>249.9</v>
+        <v>124.9</v>
       </c>
       <c r="E45" s="349" t="n">
         <v>17.5</v>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="D46" s="348" t="n">
-        <v>1688.4</v>
+        <v>844.2</v>
       </c>
       <c r="E46" s="349" t="n">
         <v>17.5</v>
@@ -6353,7 +6353,7 @@
         </is>
       </c>
       <c r="D47" s="348" t="n">
-        <v>2557.5</v>
+        <v>1278.7</v>
       </c>
       <c r="E47" s="349" t="n">
         <v>17.5</v>
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="D48" s="348" t="n">
-        <v>1421.3</v>
+        <v>710.7</v>
       </c>
       <c r="E48" s="349" t="n">
         <v>17.5</v>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="D49" s="348" t="n">
-        <v>1499.4</v>
+        <v>749.7</v>
       </c>
       <c r="E49" s="349" t="n">
         <v>17.5</v>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="D50" s="348" t="n">
-        <v>3606.1</v>
+        <v>1803</v>
       </c>
       <c r="E50" s="349" t="n">
         <v>17.5</v>
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="D51" s="348" t="n">
-        <v>1519.3</v>
+        <v>759.7</v>
       </c>
       <c r="E51" s="349" t="n">
         <v>17.5</v>
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="D52" s="348" t="n">
-        <v>58.1</v>
+        <v>29</v>
       </c>
       <c r="E52" s="349" t="n">
         <v>17.5</v>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="D53" s="348" t="n">
-        <v>249.5</v>
+        <v>124.8</v>
       </c>
       <c r="E53" s="349" t="n">
         <v>17.5</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="D55" s="348" t="n">
-        <v>1586.9</v>
+        <v>793.5</v>
       </c>
       <c r="E55" s="349" t="n">
         <v>17.5</v>
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="D56" s="348" t="n">
-        <v>2443.7</v>
+        <v>1221.8</v>
       </c>
       <c r="E56" s="349" t="n">
         <v>17.5</v>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="D57" s="348" t="n">
-        <v>1361.2</v>
+        <v>680.6</v>
       </c>
       <c r="E57" s="349" t="n">
         <v>17.5</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="D58" s="348" t="n">
-        <v>1490.3</v>
+        <v>745.1</v>
       </c>
       <c r="E58" s="349" t="n">
         <v>17.5</v>
@@ -6881,7 +6881,7 @@
         </is>
       </c>
       <c r="D59" s="348" t="n">
-        <v>3576.6</v>
+        <v>1788.3</v>
       </c>
       <c r="E59" s="349" t="n">
         <v>17.5</v>
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="D60" s="348" t="n">
-        <v>1505.3</v>
+        <v>752.7</v>
       </c>
       <c r="E60" s="349" t="n">
         <v>17.5</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="D61" s="348" t="n">
-        <v>389.2</v>
+        <v>194.6</v>
       </c>
       <c r="E61" s="349" t="n">
         <v>17.5</v>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="D62" s="348" t="n">
-        <v>1189.3</v>
+        <v>594.6</v>
       </c>
       <c r="E62" s="349" t="n">
         <v>17.5</v>
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="D63" s="348" t="n">
-        <v>1210.3</v>
+        <v>605.1</v>
       </c>
       <c r="E63" s="349" t="n">
         <v>17.5</v>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="D64" s="348" t="n">
-        <v>1539</v>
+        <v>769.5</v>
       </c>
       <c r="E64" s="349" t="n">
         <v>17.5</v>
@@ -7151,7 +7151,7 @@
         </is>
       </c>
       <c r="D65" s="348" t="n">
-        <v>2985.5</v>
+        <v>1492.8</v>
       </c>
       <c r="E65" s="349" t="n">
         <v>17.5</v>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="D66" s="348" t="n">
-        <v>1244.6</v>
+        <v>622.3</v>
       </c>
       <c r="E66" s="349" t="n">
         <v>17.5</v>
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="D67" s="348" t="n">
-        <v>1575.7</v>
+        <v>787.9</v>
       </c>
       <c r="E67" s="349" t="n">
         <v>17.5</v>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="D68" s="348" t="n">
-        <v>247.5</v>
+        <v>123.7</v>
       </c>
       <c r="E68" s="349" t="n">
         <v>17.5</v>
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="D69" s="348" t="n">
-        <v>1677.9</v>
+        <v>838.9</v>
       </c>
       <c r="E69" s="349" t="n">
         <v>17.5</v>
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="D70" s="348" t="n">
-        <v>2544.2</v>
+        <v>1272.1</v>
       </c>
       <c r="E70" s="349" t="n">
         <v>17.5</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="D71" s="348" t="n">
-        <v>1372.4</v>
+        <v>686.2</v>
       </c>
       <c r="E71" s="349" t="n">
         <v>17.5</v>
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="D72" s="348" t="n">
-        <v>1542.8</v>
+        <v>771.4</v>
       </c>
       <c r="E72" s="349" t="n">
         <v>17.5</v>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="D73" s="348" t="n">
-        <v>3559.8</v>
+        <v>1779.9</v>
       </c>
       <c r="E73" s="349" t="n">
         <v>17.5</v>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="D74" s="348" t="n">
-        <v>1505.7</v>
+        <v>752.9</v>
       </c>
       <c r="E74" s="349" t="n">
         <v>17.5</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="D75" s="348" t="n">
-        <v>362.6</v>
+        <v>181.3</v>
       </c>
       <c r="E75" s="349" t="n">
         <v>17.5</v>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 36095 W</t>
+          <t>TOPLAM ISI = 18048 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 16935 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 5035 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -14010,85 +14010,85 @@
       <c r="D13" s="261" t="n"/>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>1604.4</v>
+        <v>802.2</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>1180.9</v>
+        <v>590.5</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>1371</v>
+        <v>685.5</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>1365.3</v>
+        <v>682.7</v>
       </c>
       <c r="J13" s="398" t="n">
-        <v>1544.2</v>
+        <v>772.1</v>
       </c>
       <c r="K13" s="398" t="n">
-        <v>1749.7</v>
+        <v>874.8</v>
       </c>
       <c r="L13" s="398" t="n">
-        <v>1850.8</v>
+        <v>925.4</v>
       </c>
       <c r="M13" s="398" t="n">
-        <v>1519.3</v>
+        <v>759.7</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>391.6</v>
+        <v>195.8</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>1694</v>
+        <v>847</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>1091.3</v>
+        <v>545.6</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>1033.9</v>
+        <v>516.9</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>1365.3</v>
+        <v>682.7</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>1481.9</v>
+        <v>741</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>2082.5</v>
+        <v>1041.2</v>
       </c>
       <c r="U13" s="398" t="n">
-        <v>1850.8</v>
+        <v>925.4</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>1521.8</v>
+        <v>760.9</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>385.7</v>
+        <v>192.8</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>1006.6</v>
+        <v>503.3</v>
       </c>
       <c r="Y13" s="398" t="n">
-        <v>949.5</v>
+        <v>474.8</v>
       </c>
       <c r="Z13" s="398" t="n">
-        <v>1061.5</v>
+        <v>530.8</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>1504.7</v>
+        <v>752.3</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>1808.5</v>
+        <v>904.2</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>1598.5</v>
+        <v>799.2</v>
       </c>
       <c r="AD13" s="398" t="n">
-        <v>1254.4</v>
+        <v>627.2</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>1577.8</v>
+        <v>788.9</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>249.5</v>
+        <v>124.8</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1" s="244">
@@ -16022,85 +16022,85 @@
       </c>
       <c r="E32" s="259" t="n"/>
       <c r="F32" s="407" t="n">
-        <v>7872</v>
+        <v>2340</v>
       </c>
       <c r="G32" s="407" t="n">
-        <v>3389</v>
+        <v>615</v>
       </c>
       <c r="H32" s="407" t="n">
-        <v>5109</v>
+        <v>1519</v>
       </c>
       <c r="I32" s="407" t="n">
-        <v>5051</v>
+        <v>1502</v>
       </c>
       <c r="J32" s="407" t="n">
-        <v>7087</v>
+        <v>2107</v>
       </c>
       <c r="K32" s="407" t="n">
-        <v>9992</v>
+        <v>2970</v>
       </c>
       <c r="L32" s="407" t="n">
-        <v>11661</v>
+        <v>3467</v>
       </c>
       <c r="M32" s="407" t="n">
-        <v>6777</v>
+        <v>2015</v>
       </c>
       <c r="N32" s="407" t="n">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="O32" s="407" t="n">
-        <v>9141</v>
+        <v>2718</v>
       </c>
       <c r="P32" s="407" t="n">
-        <v>2728</v>
+        <v>525</v>
       </c>
       <c r="Q32" s="407" t="n">
-        <v>2351</v>
+        <v>472</v>
       </c>
       <c r="R32" s="407" t="n">
-        <v>5051</v>
+        <v>1502</v>
       </c>
       <c r="S32" s="407" t="n">
-        <v>6328</v>
+        <v>1881</v>
       </c>
       <c r="T32" s="407" t="n">
-        <v>16129</v>
+        <v>4795</v>
       </c>
       <c r="U32" s="407" t="n">
-        <v>11661</v>
+        <v>3467</v>
       </c>
       <c r="V32" s="407" t="n">
-        <v>6807</v>
+        <v>2024</v>
       </c>
       <c r="W32" s="407" t="n">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="X32" s="407" t="n">
-        <v>2185</v>
+        <v>447</v>
       </c>
       <c r="Y32" s="407" t="n">
-        <v>1861</v>
+        <v>398</v>
       </c>
       <c r="Z32" s="407" t="n">
-        <v>2528</v>
+        <v>497</v>
       </c>
       <c r="AA32" s="407" t="n">
-        <v>6599</v>
+        <v>1962</v>
       </c>
       <c r="AB32" s="407" t="n">
-        <v>10942</v>
+        <v>3253</v>
       </c>
       <c r="AC32" s="407" t="n">
-        <v>7793</v>
+        <v>2317</v>
       </c>
       <c r="AD32" s="407" t="n">
-        <v>4001</v>
+        <v>1190</v>
       </c>
       <c r="AE32" s="407" t="n">
-        <v>7519</v>
+        <v>2235</v>
       </c>
       <c r="AF32" s="407" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1" s="244">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="B43" s="243" t="inlineStr">
         <is>
-          <t>Alta geçen ısı 0,2 q" olarak alınmıştır.</t>
+          <t>Alta geçen ısı 0,2 q" olarak alınmıştır. qh = 17,5 W/m × devre boyu (şablon birim verimi); ısı kaybı hesabı ayrıca yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 36441 W</t>
+          <t>TOPLAM ISI = 18220 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 16624 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 4942 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -17585,88 +17585,88 @@
       <c r="D13" s="261" t="n"/>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>1695.4</v>
+        <v>847.7</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>1480.5</v>
+        <v>740.2</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>1057.7</v>
+        <v>528.9</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>1365.3</v>
+        <v>682.7</v>
       </c>
       <c r="J13" s="398" t="n">
-        <v>1481.9</v>
+        <v>741</v>
       </c>
       <c r="K13" s="398" t="n">
-        <v>2068.5</v>
+        <v>1034.2</v>
       </c>
       <c r="L13" s="398" t="n">
-        <v>1850.8</v>
+        <v>925.4</v>
       </c>
       <c r="M13" s="398" t="n">
-        <v>1521.8</v>
+        <v>760.9</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>385</v>
+        <v>192.5</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>1176.7</v>
+        <v>588.3</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>981.8</v>
+        <v>490.9</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>1130.5</v>
+        <v>565.2</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>1504.7</v>
+        <v>752.3</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>1708</v>
+        <v>854</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>1518.3</v>
+        <v>759.2</v>
       </c>
       <c r="U13" s="398" t="n">
-        <v>1086.8</v>
+        <v>543.4</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>1577.5</v>
+        <v>788.7</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>249.9</v>
+        <v>124.9</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>1688.4</v>
+        <v>844.2</v>
       </c>
       <c r="Y13" s="398" t="n">
-        <v>1185.1</v>
+        <v>592.5</v>
       </c>
       <c r="Z13" s="398" t="n">
-        <v>1372.4</v>
+        <v>686.2</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>1421.3</v>
+        <v>710.7</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>1499.4</v>
+        <v>749.7</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>1752.5</v>
+        <v>876.2</v>
       </c>
       <c r="AD13" s="398" t="n">
-        <v>1853.6</v>
+        <v>926.8</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>1519.3</v>
+        <v>759.7</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>58.1</v>
+        <v>29</v>
       </c>
       <c r="AG13" s="398" t="n">
-        <v>249.5</v>
+        <v>124.8</v>
       </c>
       <c r="AH13" s="425" t="n"/>
       <c r="AI13" s="425" t="n"/>
@@ -19963,88 +19963,88 @@
       </c>
       <c r="E32" s="259" t="n"/>
       <c r="F32" s="407" t="n">
-        <v>9162</v>
+        <v>2724</v>
       </c>
       <c r="G32" s="407" t="n">
-        <v>6311</v>
+        <v>1876</v>
       </c>
       <c r="H32" s="407" t="n">
-        <v>2503</v>
+        <v>494</v>
       </c>
       <c r="I32" s="407" t="n">
-        <v>5051</v>
+        <v>1502</v>
       </c>
       <c r="J32" s="407" t="n">
-        <v>6328</v>
+        <v>1881</v>
       </c>
       <c r="K32" s="407" t="n">
-        <v>15833</v>
+        <v>4707</v>
       </c>
       <c r="L32" s="407" t="n">
-        <v>11661</v>
+        <v>3467</v>
       </c>
       <c r="M32" s="407" t="n">
-        <v>6807</v>
+        <v>2024</v>
       </c>
       <c r="N32" s="407" t="n">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="O32" s="407" t="n">
-        <v>3356</v>
+        <v>611</v>
       </c>
       <c r="P32" s="407" t="n">
-        <v>2040</v>
+        <v>425</v>
       </c>
       <c r="Q32" s="407" t="n">
-        <v>3006</v>
+        <v>564</v>
       </c>
       <c r="R32" s="407" t="n">
-        <v>6599</v>
+        <v>1962</v>
       </c>
       <c r="S32" s="407" t="n">
-        <v>9351</v>
+        <v>2780</v>
       </c>
       <c r="T32" s="407" t="n">
-        <v>6764</v>
+        <v>2011</v>
       </c>
       <c r="U32" s="407" t="n">
-        <v>2697</v>
+        <v>521</v>
       </c>
       <c r="V32" s="407" t="n">
-        <v>7515</v>
+        <v>2234</v>
       </c>
       <c r="W32" s="407" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="X32" s="407" t="n">
-        <v>9058</v>
+        <v>2693</v>
       </c>
       <c r="Y32" s="407" t="n">
-        <v>3422</v>
+        <v>1017</v>
       </c>
       <c r="Z32" s="407" t="n">
-        <v>5123</v>
+        <v>1523</v>
       </c>
       <c r="AA32" s="407" t="n">
-        <v>5642</v>
+        <v>1677</v>
       </c>
       <c r="AB32" s="407" t="n">
-        <v>6535</v>
+        <v>1943</v>
       </c>
       <c r="AC32" s="407" t="n">
-        <v>10036</v>
+        <v>2983</v>
       </c>
       <c r="AD32" s="407" t="n">
-        <v>11710</v>
+        <v>3481</v>
       </c>
       <c r="AE32" s="407" t="n">
-        <v>6777</v>
+        <v>2015</v>
       </c>
       <c r="AF32" s="407" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG32" s="407" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="AH32" s="431" t="n"/>
       <c r="AI32" s="431" t="n"/>
@@ -20568,7 +20568,7 @@
       </c>
       <c r="B43" s="243" t="inlineStr">
         <is>
-          <t>Alta geçen ısı 0,2 q" olarak alınmıştır.</t>
+          <t>Alta geçen ısı 0,2 q" olarak alınmıştır. qh = 17,5 W/m × devre boyu (şablon birim verimi); ısı kaybı hesabı ayrıca yapılmalıdır.</t>
         </is>
       </c>
     </row>
@@ -20704,7 +20704,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 34910 W</t>
+          <t>TOPLAM ISI = 17455 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 12168 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 3618 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -21602,85 +21602,85 @@
       <c r="D13" s="261" t="n"/>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>1586.9</v>
+        <v>793.5</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>1343.7</v>
+        <v>671.8</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>1361.2</v>
+        <v>680.6</v>
       </c>
       <c r="J13" s="398" t="n">
-        <v>1490.3</v>
+        <v>745.1</v>
       </c>
       <c r="K13" s="398" t="n">
-        <v>1730</v>
+        <v>865</v>
       </c>
       <c r="L13" s="398" t="n">
-        <v>1846.6</v>
+        <v>923.3</v>
       </c>
       <c r="M13" s="398" t="n">
-        <v>1505.3</v>
+        <v>752.7</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>389.2</v>
+        <v>194.6</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>1189.3</v>
+        <v>594.6</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>583.1</v>
+        <v>291.6</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>627.2</v>
+        <v>313.6</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>1539</v>
+        <v>769.5</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>1571.2</v>
+        <v>785.6</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>1414.3</v>
+        <v>707.2</v>
       </c>
       <c r="U13" s="398" t="n">
-        <v>1244.6</v>
+        <v>622.3</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>1575.7</v>
+        <v>787.9</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>247.5</v>
+        <v>123.7</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>1677.9</v>
+        <v>838.9</v>
       </c>
       <c r="Y13" s="398" t="n">
-        <v>1177.8</v>
+        <v>588.9</v>
       </c>
       <c r="Z13" s="398" t="n">
-        <v>1366.4</v>
+        <v>683.2</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>1372.4</v>
+        <v>686.2</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>1542.8</v>
+        <v>771.4</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>1713.2</v>
+        <v>856.6</v>
       </c>
       <c r="AD13" s="398" t="n">
-        <v>1846.6</v>
+        <v>923.3</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>1505.7</v>
+        <v>752.9</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>362.6</v>
+        <v>181.3</v>
       </c>
       <c r="AG13" s="425" t="n"/>
       <c r="AH13" s="425" t="n"/>
@@ -23930,85 +23930,85 @@
       </c>
       <c r="E32" s="259" t="n"/>
       <c r="F32" s="407" t="n">
-        <v>7639</v>
+        <v>2271</v>
       </c>
       <c r="G32" s="407" t="n">
-        <v>2788</v>
+        <v>534</v>
       </c>
       <c r="H32" s="407" t="n">
-        <v>4834</v>
+        <v>1437</v>
       </c>
       <c r="I32" s="407" t="n">
-        <v>5009</v>
+        <v>1489</v>
       </c>
       <c r="J32" s="407" t="n">
-        <v>6427</v>
+        <v>1911</v>
       </c>
       <c r="K32" s="407" t="n">
-        <v>9686</v>
+        <v>2880</v>
       </c>
       <c r="L32" s="407" t="n">
-        <v>11588</v>
+        <v>3445</v>
       </c>
       <c r="M32" s="407" t="n">
-        <v>6607</v>
+        <v>1964</v>
       </c>
       <c r="N32" s="407" t="n">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="O32" s="407" t="n">
-        <v>3456</v>
+        <v>1027</v>
       </c>
       <c r="P32" s="407" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="Q32" s="407" t="n">
-        <v>595</v>
+        <v>174</v>
       </c>
       <c r="R32" s="407" t="n">
-        <v>7021</v>
+        <v>2087</v>
       </c>
       <c r="S32" s="407" t="n">
-        <v>7432</v>
+        <v>2210</v>
       </c>
       <c r="T32" s="407" t="n">
-        <v>5565</v>
+        <v>1655</v>
       </c>
       <c r="U32" s="407" t="n">
-        <v>3916</v>
+        <v>1164</v>
       </c>
       <c r="V32" s="407" t="n">
-        <v>7491</v>
+        <v>2227</v>
       </c>
       <c r="W32" s="407" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="X32" s="407" t="n">
-        <v>8904</v>
+        <v>2647</v>
       </c>
       <c r="Y32" s="407" t="n">
-        <v>3365</v>
+        <v>612</v>
       </c>
       <c r="Z32" s="407" t="n">
-        <v>5062</v>
+        <v>1505</v>
       </c>
       <c r="AA32" s="407" t="n">
-        <v>5123</v>
+        <v>1523</v>
       </c>
       <c r="AB32" s="407" t="n">
-        <v>7069</v>
+        <v>2102</v>
       </c>
       <c r="AC32" s="407" t="n">
-        <v>9429</v>
+        <v>2804</v>
       </c>
       <c r="AD32" s="407" t="n">
-        <v>11588</v>
+        <v>3445</v>
       </c>
       <c r="AE32" s="407" t="n">
-        <v>6611</v>
+        <v>1966</v>
       </c>
       <c r="AF32" s="407" t="n">
-        <v>116</v>
+        <v>58</v>
       </c>
       <c r="AG32" s="431" t="n"/>
       <c r="AH32" s="431" t="n"/>
@@ -24524,7 +24524,7 @@
       </c>
       <c r="B43" s="243" t="inlineStr">
         <is>
-          <t>Alta geçen ısı 0,2 q" olarak alınmıştır.</t>
+          <t>Alta geçen ısı 0,2 q" olarak alınmıştır. qh = 17,5 W/m × devre boyu (şablon birim verimi); ısı kaybı hesabı ayrıca yapılmalıdır.</t>
         </is>
       </c>
     </row>

--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="D16" s="343" t="n">
-        <v>195.8</v>
+        <v>232.6</v>
       </c>
       <c r="E16" s="344" t="n">
         <v>17.5</v>
@@ -4980,7 +4980,7 @@
         <v/>
       </c>
       <c r="G16" s="340" t="n">
-        <v>11.19</v>
+        <v>13.29</v>
       </c>
       <c r="H16" s="340" t="n">
         <v>1</v>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D18" s="343" t="n">
-        <v>1062.6</v>
+        <v>1222.7</v>
       </c>
       <c r="E18" s="344" t="n">
         <v>17.5</v>
@@ -5070,7 +5070,7 @@
         <v/>
       </c>
       <c r="G18" s="340" t="n">
-        <v>60.72</v>
+        <v>69.87</v>
       </c>
       <c r="H18" s="340" t="n">
         <v>2</v>
@@ -5330,7 +5330,7 @@
         </is>
       </c>
       <c r="D24" s="343" t="n">
-        <v>503.3</v>
+        <v>589</v>
       </c>
       <c r="E24" s="344" t="n">
         <v>17.5</v>
@@ -5340,7 +5340,7 @@
         <v/>
       </c>
       <c r="G24" s="340" t="n">
-        <v>28.76</v>
+        <v>33.66</v>
       </c>
       <c r="H24" s="340" t="n">
         <v>1</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="D61" s="348" t="n">
-        <v>194.6</v>
+        <v>211.4</v>
       </c>
       <c r="E61" s="349" t="n">
         <v>17.5</v>
@@ -6981,7 +6981,7 @@
         <v/>
       </c>
       <c r="G61" s="345" t="n">
-        <v>11.12</v>
+        <v>12.08</v>
       </c>
       <c r="H61" s="345" t="n">
         <v>1</v>
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="D63" s="348" t="n">
-        <v>605.1</v>
+        <v>932.2</v>
       </c>
       <c r="E63" s="349" t="n">
         <v>17.5</v>
@@ -7071,7 +7071,7 @@
         <v/>
       </c>
       <c r="G63" s="345" t="n">
-        <v>34.58</v>
+        <v>53.27</v>
       </c>
       <c r="H63" s="345" t="n">
         <v>2</v>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="D75" s="348" t="n">
-        <v>181.3</v>
+        <v>233.4</v>
       </c>
       <c r="E75" s="349" t="n">
         <v>17.5</v>
@@ -7611,7 +7611,7 @@
         <v/>
       </c>
       <c r="G75" s="345" t="n">
-        <v>10.36</v>
+        <v>13.34</v>
       </c>
       <c r="H75" s="345" t="n">
         <v>1</v>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 18048 W</t>
+          <t>TOPLAM ISI = 18330 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -13952,10 +13952,10 @@
         <v>7.87</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>6.92</v>
+        <v>6.27</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>6.55</v>
+        <v>7.2</v>
       </c>
       <c r="R12" s="397" t="n">
         <v>8.73</v>
@@ -14034,16 +14034,16 @@
         <v>759.7</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>195.8</v>
+        <v>232.6</v>
       </c>
       <c r="O13" s="398" t="n">
         <v>847</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>545.6</v>
+        <v>569.3</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>516.9</v>
+        <v>653.5</v>
       </c>
       <c r="R13" s="398" t="n">
         <v>682.7</v>
@@ -14064,7 +14064,7 @@
         <v>192.8</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>503.3</v>
+        <v>589</v>
       </c>
       <c r="Y13" s="398" t="n">
         <v>474.8</v>
@@ -16046,16 +16046,16 @@
         <v>2015</v>
       </c>
       <c r="N32" s="407" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O32" s="407" t="n">
         <v>2718</v>
       </c>
       <c r="P32" s="407" t="n">
-        <v>525</v>
+        <v>572</v>
       </c>
       <c r="Q32" s="407" t="n">
-        <v>472</v>
+        <v>1332</v>
       </c>
       <c r="R32" s="407" t="n">
         <v>1502</v>
@@ -16076,7 +16076,7 @@
         <v>66</v>
       </c>
       <c r="X32" s="407" t="n">
-        <v>447</v>
+        <v>612</v>
       </c>
       <c r="Y32" s="407" t="n">
         <v>398</v>
@@ -20704,7 +20704,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 17455 W</t>
+          <t>TOPLAM ISI = 17851 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -21527,10 +21527,10 @@
         <v>6.92</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>6.75</v>
+        <v>7.39</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>7.27</v>
+        <v>6.63</v>
       </c>
       <c r="R12" s="397" t="n">
         <v>8.66</v>
@@ -21626,16 +21626,16 @@
         <v>752.7</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>194.6</v>
+        <v>211.4</v>
       </c>
       <c r="O13" s="398" t="n">
         <v>594.6</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>291.6</v>
+        <v>491.6</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>313.6</v>
+        <v>440.6</v>
       </c>
       <c r="R13" s="398" t="n">
         <v>769.5</v>
@@ -21680,7 +21680,7 @@
         <v>752.9</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>181.3</v>
+        <v>233.4</v>
       </c>
       <c r="AG13" s="425" t="n"/>
       <c r="AH13" s="425" t="n"/>
@@ -23954,16 +23954,16 @@
         <v>1964</v>
       </c>
       <c r="N32" s="407" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="O32" s="407" t="n">
         <v>1027</v>
       </c>
       <c r="P32" s="407" t="n">
-        <v>150</v>
+        <v>426</v>
       </c>
       <c r="Q32" s="407" t="n">
-        <v>174</v>
+        <v>343</v>
       </c>
       <c r="R32" s="407" t="n">
         <v>2087</v>
@@ -24008,7 +24008,7 @@
         <v>1966</v>
       </c>
       <c r="AF32" s="407" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="AG32" s="431" t="n"/>
       <c r="AH32" s="431" t="n"/>

--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -15,14 +15,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YERDEN ISITMA- DEVAMI" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YERDEN ISITMA- DEVAMI (2)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'PETEK LİST'!$A$1:$P$77</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'YERDEN ISITMA'!$A$1:$N$77</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'kapak'!$A$1:$I$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'TEKNİK RAPOR'!$A$1:$H$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'PETEK LİST'!$A$1:$P$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'YERDEN ISITMA'!$A$1:$N$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'MMO YERDEN ISITMA'!$A$1:$AF$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'YERDEN ISITMA- DEVAMI'!$A$1:$AG$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'YERDEN ISITMA- DEVAMI'!$A$1:$AF$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'YERDEN ISITMA- DEVAMI (2)'!$A$1:$AF$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001"/>
@@ -39,7 +38,7 @@
     <numFmt numFmtId="168" formatCode="#,##0&quot;  &quot;"/>
     <numFmt numFmtId="169" formatCode="&quot;  &quot;@"/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="57">
     <font>
       <name val="Arial Tur"/>
       <charset val="162"/>
@@ -400,8 +399,15 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <color rgb="00C00000"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -436,6 +442,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF99CC00"/>
         <bgColor rgb="FFFFCC00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -833,7 +844,7 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="434">
+  <cellXfs count="437">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2006,6 +2017,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2033,6 +2047,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -2540,43 +2556,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="kapak"/>
-      <sheetName val="TEKNİK RAPOR"/>
-      <sheetName val="TEKNİK RAPOR (2)"/>
-      <sheetName val="ZEMİN"/>
-      <sheetName val="1 NK"/>
-      <sheetName val="PETEK LİST"/>
-      <sheetName val="TAHHÜTNAME"/>
-      <sheetName val="FENNİ MESUL"/>
-      <sheetName val="HİDRAFOR HESABI ÜMİT"/>
-      <sheetName val="Sayfa1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="41">
-          <cell r="G41">
-            <v>44267</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -3267,7 +3246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.0546875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4.99" customWidth="1" style="243" min="1" max="1"/>
@@ -3769,7 +3748,7 @@
       </c>
       <c r="F31" s="317" t="inlineStr">
         <is>
-          <t>: balkon, yüklük, &lt; 2 m² wc-lavabo / duş, merdiven, asansör</t>
+          <t>: balkon, yüklük, wc-lavabo / duş / wc-duş (≤ 2,7 m²), merdiven, asansör</t>
         </is>
       </c>
       <c r="H31" s="321" t="n"/>
@@ -3792,7 +3771,7 @@
       </c>
       <c r="B33" s="315" t="inlineStr">
         <is>
-          <t>Isı İletim Katsayıları:</t>
+          <t>Devre Isıl Gücü Esası:</t>
         </is>
       </c>
       <c r="C33" s="317" t="n"/>
@@ -3814,536 +3793,236 @@
       <c r="A35" s="310" t="n"/>
       <c r="B35" s="313" t="inlineStr">
         <is>
-          <t>Dış Duvar                                         :</t>
-        </is>
-      </c>
-      <c r="E35" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F35" s="317" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="G35" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+          <t>Plan etiketlerindeki, kolon şemasındaki ve bu hesaptaki devre ısıl gücü aynı esastan alınmıştır:</t>
+        </is>
+      </c>
+      <c r="E35" s="243" t="n"/>
+      <c r="F35" s="317" t="n"/>
+      <c r="G35" s="323" t="n"/>
       <c r="H35" s="280" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1" s="244">
       <c r="A36" s="310" t="n"/>
       <c r="B36" s="313" t="inlineStr">
         <is>
-          <t>Kiriş 25 cm</t>
-        </is>
-      </c>
-      <c r="E36" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F36" s="317" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="G36" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+          <t xml:space="preserve">   Q (W) = 35 W/m × hat uzunluğu L (m); L = plandaki serpantinin yaylar dahil gerçek boyu.</t>
+        </is>
+      </c>
+      <c r="E36" s="243" t="n"/>
+      <c r="F36" s="317" t="n"/>
+      <c r="G36" s="323" t="n"/>
       <c r="H36" s="280" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="244">
       <c r="A37" s="310" t="n"/>
       <c r="B37" s="313" t="inlineStr">
         <is>
-          <t>Kiriş 30 cm</t>
-        </is>
-      </c>
-      <c r="E37" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F37" s="317" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="G37" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+          <t>Bu projede ayrı ısı kaybı hesabı yapılmamıştır; "ısı ihtiyacı" sütunları boru boyundan hesaplanmıştır.</t>
+        </is>
+      </c>
+      <c r="E37" s="243" t="n"/>
+      <c r="F37" s="317" t="n"/>
+      <c r="G37" s="323" t="n"/>
       <c r="H37" s="280" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1" s="244">
       <c r="A38" s="310" t="n"/>
       <c r="B38" s="313" t="inlineStr">
         <is>
-          <t>Kapı                                                  :</t>
-        </is>
-      </c>
-      <c r="E38" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F38" s="317" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G38" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+          <t>Boru PEX 16 x 2,0, boru aralığı 15 cm, duvardan kenar mesafesi 7,5 cm; devre boyu en çok 80 m.</t>
+        </is>
+      </c>
+      <c r="E38" s="243" t="n"/>
+      <c r="F38" s="317" t="n"/>
+      <c r="G38" s="323" t="n"/>
       <c r="H38" s="280" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="244">
       <c r="A39" s="310" t="n"/>
       <c r="B39" s="313" t="inlineStr">
         <is>
-          <t>Pencere                                           :</t>
-        </is>
-      </c>
-      <c r="E39" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F39" s="317" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G39" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+          <t>Döşeme yüzey sıcaklığı kontrolü MMO sayfalarındadır (sınır: oturma 29 °C, banyo 33 °C).</t>
+        </is>
+      </c>
+      <c r="E39" s="243" t="n"/>
+      <c r="F39" s="317" t="n"/>
+      <c r="G39" s="323" t="n"/>
       <c r="H39" s="280" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="244">
       <c r="A40" s="310" t="n"/>
-      <c r="B40" s="313" t="inlineStr">
-        <is>
-          <t>Döşeme      ara                              :</t>
-        </is>
-      </c>
-      <c r="E40" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F40" s="317" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="G40" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+      <c r="B40" s="313" t="n"/>
+      <c r="E40" s="243" t="n"/>
+      <c r="F40" s="317" t="n"/>
+      <c r="G40" s="323" t="n"/>
       <c r="H40" s="280" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="244">
       <c r="A41" s="310" t="n"/>
-      <c r="B41" s="313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Merdiven Duvarı </t>
-        </is>
-      </c>
-      <c r="E41" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F41" s="317" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+      <c r="B41" s="313" t="n"/>
+      <c r="E41" s="243" t="n"/>
+      <c r="F41" s="317" t="n"/>
+      <c r="G41" s="323" t="n"/>
       <c r="H41" s="280" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="244">
       <c r="A42" s="310" t="n"/>
-      <c r="B42" s="313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Merdiven Kiriş-kolon </t>
-        </is>
-      </c>
-      <c r="E42" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F42" s="317" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+      <c r="B42" s="313" t="n"/>
+      <c r="E42" s="243" t="n"/>
+      <c r="F42" s="317" t="n"/>
+      <c r="G42" s="323" t="n"/>
       <c r="H42" s="280" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="244">
       <c r="A43" s="310" t="n"/>
-      <c r="B43" s="313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Döşeme  </t>
-        </is>
-      </c>
-      <c r="E43" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F43" s="317" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="G43" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+      <c r="B43" s="313" t="n"/>
+      <c r="E43" s="243" t="n"/>
+      <c r="F43" s="317" t="n"/>
+      <c r="G43" s="323" t="n"/>
       <c r="H43" s="280" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="244">
       <c r="A44" s="310" t="n"/>
-      <c r="B44" s="313" t="inlineStr">
-        <is>
-          <t>Tavan                                               :</t>
-        </is>
-      </c>
-      <c r="E44" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F44" s="317" t="n">
-        <v>0.318</v>
-      </c>
-      <c r="G44" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+      <c r="B44" s="313" t="n"/>
+      <c r="E44" s="243" t="n"/>
+      <c r="F44" s="317" t="n"/>
+      <c r="G44" s="323" t="n"/>
       <c r="H44" s="280" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="244">
       <c r="A45" s="310" t="n"/>
-      <c r="B45" s="313" t="inlineStr">
-        <is>
-          <t>Döşeme  Açık Geçit</t>
-        </is>
-      </c>
-      <c r="E45" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F45" s="317" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="G45" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+      <c r="B45" s="313" t="n"/>
+      <c r="E45" s="243" t="n"/>
+      <c r="F45" s="317" t="n"/>
+      <c r="G45" s="323" t="n"/>
       <c r="H45" s="280" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="244">
       <c r="A46" s="310" t="n"/>
-      <c r="B46" s="313" t="inlineStr">
-        <is>
-          <t>Bağımsız bölüm</t>
-        </is>
-      </c>
+      <c r="B46" s="313" t="n"/>
       <c r="C46" s="324" t="n"/>
       <c r="D46" s="323" t="n"/>
-      <c r="E46" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F46" s="317" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+      <c r="E46" s="243" t="n"/>
+      <c r="F46" s="317" t="n"/>
+      <c r="G46" s="323" t="n"/>
       <c r="H46" s="280" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="244">
       <c r="A47" s="310" t="n"/>
-      <c r="B47" s="313" t="inlineStr">
-        <is>
-          <t>Bağımsız bölüm kolon kiriş</t>
-        </is>
-      </c>
+      <c r="B47" s="313" t="n"/>
       <c r="C47" s="324" t="n"/>
       <c r="D47" s="323" t="n"/>
-      <c r="E47" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F47" s="317" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+      <c r="E47" s="243" t="n"/>
+      <c r="F47" s="317" t="n"/>
+      <c r="G47" s="323" t="n"/>
       <c r="H47" s="280" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="244">
       <c r="A48" s="310" t="n"/>
-      <c r="B48" s="313" t="inlineStr">
-        <is>
-          <t>İç Duvar</t>
-        </is>
-      </c>
+      <c r="B48" s="313" t="n"/>
       <c r="C48" s="324" t="n"/>
       <c r="D48" s="323" t="n"/>
-      <c r="E48" s="243" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="F48" s="317" t="n">
-        <v>0.8139999999999999</v>
-      </c>
-      <c r="G48" s="323" t="inlineStr">
-        <is>
-          <t>W/M²k</t>
-        </is>
-      </c>
+      <c r="E48" s="243" t="n"/>
+      <c r="F48" s="317" t="n"/>
+      <c r="G48" s="323" t="n"/>
       <c r="H48" s="280" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="244">
       <c r="A49" s="310" t="n"/>
-      <c r="B49" s="315" t="inlineStr">
-        <is>
-          <t>Kullanılan Kısaltmalar:</t>
-        </is>
-      </c>
+      <c r="B49" s="315" t="n"/>
       <c r="D49" s="323" t="n"/>
       <c r="H49" s="280" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1" s="244">
       <c r="A50" s="310" t="n"/>
-      <c r="B50" s="313" t="inlineStr">
-        <is>
-          <t>Dış Duvar</t>
-        </is>
-      </c>
+      <c r="B50" s="313" t="n"/>
       <c r="D50" s="323" t="n"/>
-      <c r="E50" s="317" t="inlineStr">
-        <is>
-          <t>:DD</t>
-        </is>
-      </c>
+      <c r="E50" s="317" t="n"/>
       <c r="H50" s="280" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1" s="244">
       <c r="A51" s="310" t="n"/>
-      <c r="B51" s="313" t="inlineStr">
-        <is>
-          <t>Pencere</t>
-        </is>
-      </c>
+      <c r="B51" s="313" t="n"/>
       <c r="D51" s="323" t="n"/>
-      <c r="E51" s="317" t="inlineStr">
-        <is>
-          <t>:ÇP</t>
-        </is>
-      </c>
+      <c r="E51" s="317" t="n"/>
       <c r="H51" s="280" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1" s="244">
       <c r="A52" s="310" t="n"/>
-      <c r="B52" s="313" t="inlineStr">
-        <is>
-          <t>İç Kapı</t>
-        </is>
-      </c>
-      <c r="E52" s="317" t="inlineStr">
-        <is>
-          <t>:İK</t>
-        </is>
-      </c>
+      <c r="B52" s="313" t="n"/>
+      <c r="E52" s="317" t="n"/>
       <c r="H52" s="280" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="244">
       <c r="A53" s="310" t="n"/>
-      <c r="B53" s="313" t="inlineStr">
-        <is>
-          <t>Dış Kapı</t>
-        </is>
-      </c>
-      <c r="E53" s="317" t="inlineStr">
-        <is>
-          <t>:DK</t>
-        </is>
-      </c>
+      <c r="B53" s="313" t="n"/>
+      <c r="E53" s="317" t="n"/>
       <c r="H53" s="280" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="244">
       <c r="A54" s="310" t="n"/>
-      <c r="B54" s="313" t="inlineStr">
-        <is>
-          <t>Balkon Kapısı</t>
-        </is>
-      </c>
-      <c r="E54" s="317" t="inlineStr">
-        <is>
-          <t>:BK</t>
-        </is>
-      </c>
+      <c r="B54" s="313" t="n"/>
+      <c r="E54" s="317" t="n"/>
       <c r="H54" s="280" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="244">
       <c r="A55" s="310" t="n"/>
-      <c r="B55" s="313" t="inlineStr">
-        <is>
-          <t>Döşeme</t>
-        </is>
-      </c>
-      <c r="E55" s="317" t="inlineStr">
-        <is>
-          <t>:Dö</t>
-        </is>
-      </c>
+      <c r="B55" s="313" t="n"/>
+      <c r="E55" s="317" t="n"/>
       <c r="H55" s="280" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1" s="244">
       <c r="A56" s="310" t="n"/>
-      <c r="B56" s="313" t="inlineStr">
-        <is>
-          <t>Tavan</t>
-        </is>
-      </c>
-      <c r="E56" s="317" t="inlineStr">
-        <is>
-          <t>:Ta</t>
-        </is>
-      </c>
+      <c r="B56" s="313" t="n"/>
+      <c r="E56" s="317" t="n"/>
       <c r="H56" s="280" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1" s="244">
       <c r="A57" s="310" t="n"/>
-      <c r="B57" s="313" t="inlineStr">
-        <is>
-          <t>Dükkan</t>
-        </is>
-      </c>
-      <c r="E57" s="317" t="inlineStr">
-        <is>
-          <t>:DÜK</t>
-        </is>
-      </c>
+      <c r="B57" s="313" t="n"/>
+      <c r="E57" s="317" t="n"/>
       <c r="H57" s="280" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="244">
       <c r="A58" s="310" t="n"/>
-      <c r="B58" s="313" t="inlineStr">
-        <is>
-          <t>Bodrum</t>
-        </is>
-      </c>
-      <c r="E58" s="317" t="inlineStr">
-        <is>
-          <t>:B</t>
-        </is>
-      </c>
+      <c r="B58" s="313" t="n"/>
+      <c r="E58" s="317" t="n"/>
       <c r="H58" s="280" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" s="244">
       <c r="A59" s="310" t="n"/>
-      <c r="B59" s="313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sürgülü  kapı                                </t>
-        </is>
-      </c>
-      <c r="E59" s="317" t="inlineStr">
-        <is>
-          <t>:SK</t>
-        </is>
-      </c>
+      <c r="B59" s="313" t="n"/>
+      <c r="E59" s="317" t="n"/>
       <c r="H59" s="280" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="244">
       <c r="A60" s="310" t="n"/>
-      <c r="B60" s="313" t="inlineStr">
-        <is>
-          <t>Kiriş - Kolon</t>
-        </is>
-      </c>
-      <c r="E60" s="317" t="inlineStr">
-        <is>
-          <t>: DD2</t>
-        </is>
-      </c>
+      <c r="B60" s="313" t="n"/>
+      <c r="E60" s="317" t="n"/>
       <c r="H60" s="280" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1" s="244">
       <c r="A61" s="310" t="n"/>
-      <c r="B61" s="313" t="inlineStr">
-        <is>
-          <t>İç Taban</t>
-        </is>
-      </c>
-      <c r="E61" s="317" t="inlineStr">
-        <is>
-          <t>:Dö</t>
-        </is>
-      </c>
+      <c r="B61" s="313" t="n"/>
+      <c r="E61" s="317" t="n"/>
       <c r="H61" s="280" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1" s="244">
       <c r="A62" s="310" t="n"/>
-      <c r="B62" s="313" t="inlineStr">
-        <is>
-          <t>İç Duvar</t>
-        </is>
-      </c>
-      <c r="E62" s="317" t="inlineStr">
-        <is>
-          <t>: İD</t>
-        </is>
-      </c>
+      <c r="B62" s="313" t="n"/>
+      <c r="E62" s="317" t="n"/>
       <c r="H62" s="280" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1" s="244">
       <c r="A63" s="279" t="n"/>
-      <c r="B63" s="313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Merdiven Duvarı </t>
-        </is>
-      </c>
-      <c r="E63" s="317" t="inlineStr">
-        <is>
-          <t>: İDM</t>
-        </is>
-      </c>
+      <c r="B63" s="313" t="n"/>
+      <c r="E63" s="317" t="n"/>
       <c r="H63" s="280" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1" s="244">
       <c r="A64" s="279" t="n"/>
-      <c r="B64" s="313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Merdiven Kiriş-kolon </t>
-        </is>
-      </c>
-      <c r="E64" s="317" t="inlineStr">
-        <is>
-          <t>: İDMK</t>
-        </is>
-      </c>
+      <c r="B64" s="313" t="n"/>
+      <c r="E64" s="317" t="n"/>
       <c r="H64" s="280" t="n"/>
     </row>
     <row r="65" ht="13.5" customHeight="1" s="244">
@@ -4357,6 +4036,9 @@
       <c r="H65" s="327" t="n"/>
     </row>
     <row r="66" ht="13.5" customHeight="1" s="244"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A4:B4"/>
@@ -4535,8 +4217,8 @@
       </c>
       <c r="D6" s="330" t="inlineStr">
         <is>
-          <t>ISI
-KAYBI</t>
+          <t>ISIL GÜÇ
+35 W/m × L</t>
         </is>
       </c>
       <c r="E6" s="330" t="inlineStr">
@@ -4655,17 +4337,17 @@
       </c>
       <c r="D9" s="331" t="inlineStr">
         <is>
-          <t>W/h</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E9" s="331" t="inlineStr">
         <is>
-          <t>W/m2K</t>
+          <t>W/m</t>
         </is>
       </c>
       <c r="F9" s="331" t="inlineStr">
         <is>
-          <t>W/m2K</t>
+          <t>W</t>
         </is>
       </c>
       <c r="G9" s="331" t="inlineStr">
@@ -4700,17 +4382,17 @@
         </is>
       </c>
       <c r="D10" s="343" t="n">
-        <v>802.2</v>
+        <v>1688.4</v>
       </c>
       <c r="E10" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F10" s="343">
         <f>'YERDEN ISITMA'!N10</f>
         <v/>
       </c>
       <c r="G10" s="340" t="n">
-        <v>45.84</v>
+        <v>48.24</v>
       </c>
       <c r="H10" s="340" t="n">
         <v>1</v>
@@ -4745,17 +4427,17 @@
         </is>
       </c>
       <c r="D11" s="343" t="n">
-        <v>1275.9</v>
+        <v>2872.1</v>
       </c>
       <c r="E11" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F11" s="343">
         <f>'YERDEN ISITMA'!N11</f>
         <v/>
       </c>
       <c r="G11" s="340" t="n">
-        <v>72.91</v>
+        <v>82.06</v>
       </c>
       <c r="H11" s="340" t="n">
         <v>2</v>
@@ -4790,17 +4472,17 @@
         </is>
       </c>
       <c r="D12" s="343" t="n">
-        <v>682.7</v>
+        <v>1850.8</v>
       </c>
       <c r="E12" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F12" s="343">
         <f>'YERDEN ISITMA'!N12</f>
         <v/>
       </c>
       <c r="G12" s="340" t="n">
-        <v>39.01</v>
+        <v>52.88</v>
       </c>
       <c r="H12" s="340" t="n">
         <v>1</v>
@@ -4835,17 +4517,17 @@
         </is>
       </c>
       <c r="D13" s="343" t="n">
-        <v>772.1</v>
+        <v>1866.2</v>
       </c>
       <c r="E13" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F13" s="343">
         <f>'YERDEN ISITMA'!N13</f>
         <v/>
       </c>
       <c r="G13" s="340" t="n">
-        <v>44.12</v>
+        <v>53.32</v>
       </c>
       <c r="H13" s="340" t="n">
         <v>1</v>
@@ -4880,17 +4562,17 @@
         </is>
       </c>
       <c r="D14" s="343" t="n">
-        <v>1800.2</v>
+        <v>4240.9</v>
       </c>
       <c r="E14" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F14" s="343">
         <f>'YERDEN ISITMA'!N14</f>
         <v/>
       </c>
       <c r="G14" s="340" t="n">
-        <v>102.87</v>
+        <v>121.17</v>
       </c>
       <c r="H14" s="340" t="n">
         <v>2</v>
@@ -4925,17 +4607,17 @@
         </is>
       </c>
       <c r="D15" s="343" t="n">
-        <v>759.7</v>
+        <v>1522.5</v>
       </c>
       <c r="E15" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F15" s="343">
         <f>'YERDEN ISITMA'!N15</f>
         <v/>
       </c>
       <c r="G15" s="340" t="n">
-        <v>43.41</v>
+        <v>43.5</v>
       </c>
       <c r="H15" s="340" t="n">
         <v>1</v>
@@ -4970,17 +4652,17 @@
         </is>
       </c>
       <c r="D16" s="343" t="n">
-        <v>232.6</v>
+        <v>596.1</v>
       </c>
       <c r="E16" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F16" s="343">
         <f>'YERDEN ISITMA'!N16</f>
         <v/>
       </c>
       <c r="G16" s="340" t="n">
-        <v>13.29</v>
+        <v>17.03</v>
       </c>
       <c r="H16" s="340" t="n">
         <v>1</v>
@@ -5015,10 +4697,10 @@
         </is>
       </c>
       <c r="D17" s="343" t="n">
-        <v>847</v>
+        <v>1694</v>
       </c>
       <c r="E17" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F17" s="343">
         <f>'YERDEN ISITMA'!N17</f>
@@ -5060,17 +4742,17 @@
         </is>
       </c>
       <c r="D18" s="343" t="n">
-        <v>1222.7</v>
+        <v>2845.1</v>
       </c>
       <c r="E18" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F18" s="343">
         <f>'YERDEN ISITMA'!N18</f>
         <v/>
       </c>
       <c r="G18" s="340" t="n">
-        <v>69.87</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="H18" s="340" t="n">
         <v>2</v>
@@ -5105,17 +4787,17 @@
         </is>
       </c>
       <c r="D19" s="343" t="n">
-        <v>682.7</v>
+        <v>1850.8</v>
       </c>
       <c r="E19" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F19" s="343">
         <f>'YERDEN ISITMA'!N19</f>
         <v/>
       </c>
       <c r="G19" s="340" t="n">
-        <v>39.01</v>
+        <v>52.88</v>
       </c>
       <c r="H19" s="340" t="n">
         <v>1</v>
@@ -5150,17 +4832,17 @@
         </is>
       </c>
       <c r="D20" s="343" t="n">
-        <v>741</v>
+        <v>1860.6</v>
       </c>
       <c r="E20" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F20" s="343">
         <f>'YERDEN ISITMA'!N20</f>
         <v/>
       </c>
       <c r="G20" s="340" t="n">
-        <v>42.34</v>
+        <v>53.16</v>
       </c>
       <c r="H20" s="340" t="n">
         <v>1</v>
@@ -5195,17 +4877,17 @@
         </is>
       </c>
       <c r="D21" s="343" t="n">
-        <v>1966.6</v>
+        <v>4253.6</v>
       </c>
       <c r="E21" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F21" s="343">
         <f>'YERDEN ISITMA'!N21</f>
         <v/>
       </c>
       <c r="G21" s="340" t="n">
-        <v>112.38</v>
+        <v>121.53</v>
       </c>
       <c r="H21" s="340" t="n">
         <v>2</v>
@@ -5240,17 +4922,17 @@
         </is>
       </c>
       <c r="D22" s="343" t="n">
-        <v>760.9</v>
+        <v>1533</v>
       </c>
       <c r="E22" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F22" s="343">
         <f>'YERDEN ISITMA'!N22</f>
         <v/>
       </c>
       <c r="G22" s="340" t="n">
-        <v>43.48</v>
+        <v>43.8</v>
       </c>
       <c r="H22" s="340" t="n">
         <v>1</v>
@@ -5285,17 +4967,17 @@
         </is>
       </c>
       <c r="D23" s="343" t="n">
-        <v>192.8</v>
+        <v>561.1</v>
       </c>
       <c r="E23" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F23" s="343">
         <f>'YERDEN ISITMA'!N23</f>
         <v/>
       </c>
       <c r="G23" s="340" t="n">
-        <v>11.02</v>
+        <v>16.03</v>
       </c>
       <c r="H23" s="340" t="n">
         <v>1</v>
@@ -5330,17 +5012,17 @@
         </is>
       </c>
       <c r="D24" s="343" t="n">
-        <v>589</v>
+        <v>1370.6</v>
       </c>
       <c r="E24" s="344" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F24" s="343">
         <f>'YERDEN ISITMA'!N24</f>
         <v/>
       </c>
       <c r="G24" s="340" t="n">
-        <v>33.66</v>
+        <v>39.16</v>
       </c>
       <c r="H24" s="340" t="n">
         <v>1</v>
@@ -5375,17 +5057,17 @@
         </is>
       </c>
       <c r="D25" s="348" t="n">
-        <v>1005.5</v>
+        <v>3031.7</v>
       </c>
       <c r="E25" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F25" s="348">
         <f>'YERDEN ISITMA'!N25</f>
         <v/>
       </c>
       <c r="G25" s="345" t="n">
-        <v>57.46</v>
+        <v>86.62</v>
       </c>
       <c r="H25" s="345" t="n">
         <v>2</v>
@@ -5420,17 +5102,17 @@
         </is>
       </c>
       <c r="D26" s="348" t="n">
-        <v>752.3</v>
+        <v>1859.2</v>
       </c>
       <c r="E26" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F26" s="348">
         <f>'YERDEN ISITMA'!N26</f>
         <v/>
       </c>
       <c r="G26" s="345" t="n">
-        <v>42.99</v>
+        <v>53.12</v>
       </c>
       <c r="H26" s="345" t="n">
         <v>1</v>
@@ -5465,17 +5147,17 @@
         </is>
       </c>
       <c r="D27" s="348" t="n">
-        <v>1703.5</v>
+        <v>4437.3</v>
       </c>
       <c r="E27" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F27" s="348">
         <f>'YERDEN ISITMA'!N27</f>
         <v/>
       </c>
       <c r="G27" s="345" t="n">
-        <v>97.34</v>
+        <v>126.78</v>
       </c>
       <c r="H27" s="345" t="n">
         <v>2</v>
@@ -5510,17 +5192,17 @@
         </is>
       </c>
       <c r="D28" s="348" t="n">
-        <v>627.2</v>
+        <v>1619.1</v>
       </c>
       <c r="E28" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F28" s="348">
         <f>'YERDEN ISITMA'!N28</f>
         <v/>
       </c>
       <c r="G28" s="345" t="n">
-        <v>35.84</v>
+        <v>46.26</v>
       </c>
       <c r="H28" s="345" t="n">
         <v>1</v>
@@ -5555,17 +5237,17 @@
         </is>
       </c>
       <c r="D29" s="348" t="n">
-        <v>788.9</v>
+        <v>1998.8</v>
       </c>
       <c r="E29" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F29" s="348">
         <f>'YERDEN ISITMA'!N29</f>
         <v/>
       </c>
       <c r="G29" s="345" t="n">
-        <v>45.08</v>
+        <v>57.11</v>
       </c>
       <c r="H29" s="345" t="n">
         <v>1</v>
@@ -5600,17 +5282,17 @@
         </is>
       </c>
       <c r="D30" s="348" t="n">
-        <v>124.8</v>
+        <v>419.7</v>
       </c>
       <c r="E30" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F30" s="348">
         <f>'YERDEN ISITMA'!N30</f>
         <v/>
       </c>
       <c r="G30" s="345" t="n">
-        <v>7.13</v>
+        <v>11.99</v>
       </c>
       <c r="H30" s="345" t="n">
         <v>1</v>
@@ -5678,10 +5360,10 @@
         </is>
       </c>
       <c r="D32" s="348" t="n">
-        <v>847.7</v>
+        <v>1695.4</v>
       </c>
       <c r="E32" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F32" s="348">
         <f>'YERDEN ISITMA'!N32</f>
@@ -5723,17 +5405,17 @@
         </is>
       </c>
       <c r="D33" s="348" t="n">
-        <v>1269.1</v>
+        <v>3069.5</v>
       </c>
       <c r="E33" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F33" s="348">
         <f>'YERDEN ISITMA'!N33</f>
         <v/>
       </c>
       <c r="G33" s="345" t="n">
-        <v>72.52</v>
+        <v>87.7</v>
       </c>
       <c r="H33" s="345" t="n">
         <v>2</v>
@@ -5768,17 +5450,17 @@
         </is>
       </c>
       <c r="D34" s="348" t="n">
-        <v>682.7</v>
+        <v>1850.8</v>
       </c>
       <c r="E34" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F34" s="348">
         <f>'YERDEN ISITMA'!N34</f>
         <v/>
       </c>
       <c r="G34" s="345" t="n">
-        <v>39.01</v>
+        <v>52.88</v>
       </c>
       <c r="H34" s="345" t="n">
         <v>1</v>
@@ -5813,17 +5495,17 @@
         </is>
       </c>
       <c r="D35" s="348" t="n">
-        <v>741</v>
+        <v>1860.6</v>
       </c>
       <c r="E35" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F35" s="348">
         <f>'YERDEN ISITMA'!N35</f>
         <v/>
       </c>
       <c r="G35" s="345" t="n">
-        <v>42.34</v>
+        <v>53.16</v>
       </c>
       <c r="H35" s="345" t="n">
         <v>1</v>
@@ -5858,17 +5540,17 @@
         </is>
       </c>
       <c r="D36" s="348" t="n">
-        <v>1959.7</v>
+        <v>4235.7</v>
       </c>
       <c r="E36" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F36" s="348">
         <f>'YERDEN ISITMA'!N36</f>
         <v/>
       </c>
       <c r="G36" s="345" t="n">
-        <v>111.98</v>
+        <v>121.02</v>
       </c>
       <c r="H36" s="345" t="n">
         <v>2</v>
@@ -5903,17 +5585,17 @@
         </is>
       </c>
       <c r="D37" s="348" t="n">
-        <v>760.9</v>
+        <v>1533</v>
       </c>
       <c r="E37" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F37" s="348">
         <f>'YERDEN ISITMA'!N37</f>
         <v/>
       </c>
       <c r="G37" s="345" t="n">
-        <v>43.48</v>
+        <v>43.8</v>
       </c>
       <c r="H37" s="345" t="n">
         <v>1</v>
@@ -5948,17 +5630,17 @@
         </is>
       </c>
       <c r="D38" s="348" t="n">
-        <v>192.5</v>
+        <v>560.7</v>
       </c>
       <c r="E38" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F38" s="348">
         <f>'YERDEN ISITMA'!N38</f>
         <v/>
       </c>
       <c r="G38" s="345" t="n">
-        <v>11</v>
+        <v>16.02</v>
       </c>
       <c r="H38" s="345" t="n">
         <v>1</v>
@@ -5993,17 +5675,17 @@
         </is>
       </c>
       <c r="D39" s="348" t="n">
-        <v>588.3</v>
+        <v>1341.2</v>
       </c>
       <c r="E39" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F39" s="348">
         <f>'YERDEN ISITMA'!N39</f>
         <v/>
       </c>
       <c r="G39" s="345" t="n">
-        <v>33.62</v>
+        <v>38.32</v>
       </c>
       <c r="H39" s="345" t="n">
         <v>1</v>
@@ -6038,17 +5720,17 @@
         </is>
       </c>
       <c r="D40" s="348" t="n">
-        <v>1056.1</v>
+        <v>3031.7</v>
       </c>
       <c r="E40" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F40" s="348">
         <f>'YERDEN ISITMA'!N40</f>
         <v/>
       </c>
       <c r="G40" s="345" t="n">
-        <v>60.35</v>
+        <v>86.62</v>
       </c>
       <c r="H40" s="345" t="n">
         <v>2</v>
@@ -6083,17 +5765,17 @@
         </is>
       </c>
       <c r="D41" s="348" t="n">
-        <v>752.3</v>
+        <v>1859.2</v>
       </c>
       <c r="E41" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F41" s="348">
         <f>'YERDEN ISITMA'!N41</f>
         <v/>
       </c>
       <c r="G41" s="345" t="n">
-        <v>42.99</v>
+        <v>53.12</v>
       </c>
       <c r="H41" s="345" t="n">
         <v>1</v>
@@ -6128,17 +5810,17 @@
         </is>
       </c>
       <c r="D42" s="348" t="n">
-        <v>1613.2</v>
+        <v>4299.8</v>
       </c>
       <c r="E42" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F42" s="348">
         <f>'YERDEN ISITMA'!N42</f>
         <v/>
       </c>
       <c r="G42" s="345" t="n">
-        <v>92.18000000000001</v>
+        <v>122.85</v>
       </c>
       <c r="H42" s="345" t="n">
         <v>2</v>
@@ -6173,17 +5855,17 @@
         </is>
       </c>
       <c r="D43" s="348" t="n">
-        <v>543.4</v>
+        <v>1614.9</v>
       </c>
       <c r="E43" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F43" s="348">
         <f>'YERDEN ISITMA'!N43</f>
         <v/>
       </c>
       <c r="G43" s="345" t="n">
-        <v>31.05</v>
+        <v>46.14</v>
       </c>
       <c r="H43" s="345" t="n">
         <v>1</v>
@@ -6218,17 +5900,17 @@
         </is>
       </c>
       <c r="D44" s="348" t="n">
-        <v>788.7</v>
+        <v>2005.1</v>
       </c>
       <c r="E44" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F44" s="348">
         <f>'YERDEN ISITMA'!N44</f>
         <v/>
       </c>
       <c r="G44" s="345" t="n">
-        <v>45.07</v>
+        <v>57.29</v>
       </c>
       <c r="H44" s="345" t="n">
         <v>1</v>
@@ -6263,17 +5945,17 @@
         </is>
       </c>
       <c r="D45" s="348" t="n">
-        <v>124.9</v>
+        <v>419.7</v>
       </c>
       <c r="E45" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F45" s="348">
         <f>'YERDEN ISITMA'!N45</f>
         <v/>
       </c>
       <c r="G45" s="345" t="n">
-        <v>7.14</v>
+        <v>11.99</v>
       </c>
       <c r="H45" s="345" t="n">
         <v>1</v>
@@ -6308,10 +5990,10 @@
         </is>
       </c>
       <c r="D46" s="348" t="n">
-        <v>844.2</v>
+        <v>1688.4</v>
       </c>
       <c r="E46" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F46" s="348">
         <f>'YERDEN ISITMA'!N46</f>
@@ -6353,17 +6035,17 @@
         </is>
       </c>
       <c r="D47" s="348" t="n">
-        <v>1278.7</v>
+        <v>2877.7</v>
       </c>
       <c r="E47" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F47" s="348">
         <f>'YERDEN ISITMA'!N47</f>
         <v/>
       </c>
       <c r="G47" s="345" t="n">
-        <v>73.06999999999999</v>
+        <v>82.22</v>
       </c>
       <c r="H47" s="345" t="n">
         <v>2</v>
@@ -6398,17 +6080,17 @@
         </is>
       </c>
       <c r="D48" s="348" t="n">
-        <v>710.7</v>
+        <v>1856.4</v>
       </c>
       <c r="E48" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F48" s="348">
         <f>'YERDEN ISITMA'!N48</f>
         <v/>
       </c>
       <c r="G48" s="345" t="n">
-        <v>40.61</v>
+        <v>53.04</v>
       </c>
       <c r="H48" s="345" t="n">
         <v>1</v>
@@ -6443,17 +6125,17 @@
         </is>
       </c>
       <c r="D49" s="348" t="n">
-        <v>749.7</v>
+        <v>1872.8</v>
       </c>
       <c r="E49" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F49" s="348">
         <f>'YERDEN ISITMA'!N49</f>
         <v/>
       </c>
       <c r="G49" s="345" t="n">
-        <v>42.84</v>
+        <v>53.51</v>
       </c>
       <c r="H49" s="345" t="n">
         <v>1</v>
@@ -6488,17 +6170,17 @@
         </is>
       </c>
       <c r="D50" s="348" t="n">
-        <v>1803</v>
+        <v>4246.6</v>
       </c>
       <c r="E50" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F50" s="348">
         <f>'YERDEN ISITMA'!N50</f>
         <v/>
       </c>
       <c r="G50" s="345" t="n">
-        <v>103.03</v>
+        <v>121.33</v>
       </c>
       <c r="H50" s="345" t="n">
         <v>2</v>
@@ -6533,17 +6215,17 @@
         </is>
       </c>
       <c r="D51" s="348" t="n">
-        <v>759.7</v>
+        <v>1522.5</v>
       </c>
       <c r="E51" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F51" s="348">
         <f>'YERDEN ISITMA'!N51</f>
         <v/>
       </c>
       <c r="G51" s="345" t="n">
-        <v>43.41</v>
+        <v>43.5</v>
       </c>
       <c r="H51" s="345" t="n">
         <v>1</v>
@@ -6569,7 +6251,7 @@
       </c>
       <c r="B52" s="346" t="inlineStr">
         <is>
-          <t>D6 WC-DUŞ</t>
+          <t>D6 BANYO</t>
         </is>
       </c>
       <c r="C52" s="347" t="inlineStr">
@@ -6578,17 +6260,17 @@
         </is>
       </c>
       <c r="D52" s="348" t="n">
-        <v>29</v>
+        <v>425.9</v>
       </c>
       <c r="E52" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F52" s="348">
         <f>'YERDEN ISITMA'!N52</f>
         <v/>
       </c>
       <c r="G52" s="345" t="n">
-        <v>1.66</v>
+        <v>12.17</v>
       </c>
       <c r="H52" s="345" t="n">
         <v>1</v>
@@ -6607,92 +6289,92 @@
       <c r="P52" s="260" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="345" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="B53" s="346" t="inlineStr">
-        <is>
-          <t>D6 BANYO</t>
-        </is>
-      </c>
-      <c r="C53" s="347" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D53" s="348" t="n">
-        <v>124.8</v>
-      </c>
-      <c r="E53" s="349" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F53" s="348">
-        <f>'YERDEN ISITMA'!N53</f>
-        <v/>
-      </c>
-      <c r="G53" s="345" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="H53" s="345" t="n">
+      <c r="A53" s="345" t="n"/>
+      <c r="B53" s="345" t="inlineStr">
+        <is>
+          <t>1. KAT</t>
+        </is>
+      </c>
+      <c r="C53" s="347" t="n"/>
+      <c r="D53" s="348" t="n"/>
+      <c r="E53" s="350" t="inlineStr">
+        <is>
+          <t>TOPLAM =</t>
+        </is>
+      </c>
+      <c r="F53" s="351">
+        <f>SUM(F32:F52)</f>
+        <v/>
+      </c>
+      <c r="G53" s="345" t="inlineStr">
+        <is>
+          <t>watt</t>
+        </is>
+      </c>
+      <c r="H53" s="345" t="n"/>
+      <c r="I53" s="345" t="n"/>
+      <c r="J53" s="345" t="n"/>
+      <c r="K53" s="345" t="n"/>
+      <c r="L53" s="345" t="n"/>
+      <c r="M53" s="345" t="n"/>
+      <c r="N53" s="345" t="n"/>
+      <c r="O53" s="345" t="n"/>
+      <c r="P53" s="345" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="345" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="B54" s="346" t="inlineStr">
+        <is>
+          <t>D7 MUTFAK</t>
+        </is>
+      </c>
+      <c r="C54" s="347" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D54" s="348" t="n">
+        <v>1597.8</v>
+      </c>
+      <c r="E54" s="349" t="n">
+        <v>35</v>
+      </c>
+      <c r="F54" s="348">
+        <f>'YERDEN ISITMA'!N54</f>
+        <v/>
+      </c>
+      <c r="G54" s="345" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="H54" s="345" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="345" t="inlineStr">
+      <c r="I54" s="345" t="inlineStr">
         <is>
           <t>ZEMİNDEN ISITMA</t>
         </is>
       </c>
-      <c r="J53" s="264" t="n"/>
-      <c r="K53" s="264" t="n"/>
-      <c r="L53" s="264" t="n"/>
-      <c r="M53" s="264" t="n"/>
-      <c r="N53" s="264" t="n"/>
-      <c r="O53" s="264" t="n"/>
-      <c r="P53" s="260" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="345" t="n"/>
-      <c r="B54" s="345" t="inlineStr">
-        <is>
-          <t>1. KAT</t>
-        </is>
-      </c>
-      <c r="C54" s="347" t="n"/>
-      <c r="D54" s="348" t="n"/>
-      <c r="E54" s="350" t="inlineStr">
-        <is>
-          <t>TOPLAM =</t>
-        </is>
-      </c>
-      <c r="F54" s="351">
-        <f>SUM(F32:F53)</f>
-        <v/>
-      </c>
-      <c r="G54" s="345" t="inlineStr">
-        <is>
-          <t>watt</t>
-        </is>
-      </c>
-      <c r="H54" s="345" t="n"/>
-      <c r="I54" s="345" t="n"/>
-      <c r="J54" s="345" t="n"/>
-      <c r="K54" s="345" t="n"/>
-      <c r="L54" s="345" t="n"/>
-      <c r="M54" s="345" t="n"/>
-      <c r="N54" s="345" t="n"/>
-      <c r="O54" s="345" t="n"/>
-      <c r="P54" s="345" t="n"/>
+      <c r="J54" s="264" t="n"/>
+      <c r="K54" s="264" t="n"/>
+      <c r="L54" s="264" t="n"/>
+      <c r="M54" s="264" t="n"/>
+      <c r="N54" s="264" t="n"/>
+      <c r="O54" s="264" t="n"/>
+      <c r="P54" s="260" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="345" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B55" s="346" t="inlineStr">
         <is>
-          <t>D7 MUTFAK</t>
+          <t>D7 YATAK OD.</t>
         </is>
       </c>
       <c r="C55" s="347" t="inlineStr">
@@ -6701,20 +6383,20 @@
         </is>
       </c>
       <c r="D55" s="348" t="n">
-        <v>793.5</v>
+        <v>3057.2</v>
       </c>
       <c r="E55" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F55" s="348">
         <f>'YERDEN ISITMA'!N55</f>
         <v/>
       </c>
       <c r="G55" s="345" t="n">
-        <v>45.34</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="H55" s="345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" s="345" t="inlineStr">
         <is>
@@ -6732,7 +6414,7 @@
     <row r="56">
       <c r="A56" s="345" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B56" s="346" t="inlineStr">
@@ -6746,20 +6428,20 @@
         </is>
       </c>
       <c r="D56" s="348" t="n">
-        <v>1221.8</v>
+        <v>1848</v>
       </c>
       <c r="E56" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F56" s="348">
         <f>'YERDEN ISITMA'!N56</f>
         <v/>
       </c>
       <c r="G56" s="345" t="n">
-        <v>69.81999999999999</v>
+        <v>52.8</v>
       </c>
       <c r="H56" s="345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I56" s="345" t="inlineStr">
         <is>
@@ -6777,7 +6459,7 @@
     <row r="57">
       <c r="A57" s="345" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B57" s="346" t="inlineStr">
@@ -6791,17 +6473,17 @@
         </is>
       </c>
       <c r="D57" s="348" t="n">
-        <v>680.6</v>
+        <v>1859.2</v>
       </c>
       <c r="E57" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F57" s="348">
         <f>'YERDEN ISITMA'!N57</f>
         <v/>
       </c>
       <c r="G57" s="345" t="n">
-        <v>38.89</v>
+        <v>53.12</v>
       </c>
       <c r="H57" s="345" t="n">
         <v>1</v>
@@ -6822,12 +6504,12 @@
     <row r="58">
       <c r="A58" s="345" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B58" s="346" t="inlineStr">
         <is>
-          <t>D7 YATAK OD.</t>
+          <t>D7 SALON</t>
         </is>
       </c>
       <c r="C58" s="347" t="inlineStr">
@@ -6836,20 +6518,20 @@
         </is>
       </c>
       <c r="D58" s="348" t="n">
-        <v>745.1</v>
+        <v>4213.3</v>
       </c>
       <c r="E58" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F58" s="348">
         <f>'YERDEN ISITMA'!N58</f>
         <v/>
       </c>
       <c r="G58" s="345" t="n">
-        <v>42.58</v>
+        <v>120.38</v>
       </c>
       <c r="H58" s="345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" s="345" t="inlineStr">
         <is>
@@ -6867,34 +6549,34 @@
     <row r="59">
       <c r="A59" s="345" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B59" s="346" t="inlineStr">
         <is>
-          <t>D7 SALON</t>
+          <t>D7 ANTRE-KOR.</t>
         </is>
       </c>
       <c r="C59" s="347" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D59" s="348" t="n">
-        <v>1788.3</v>
+        <v>1526.3</v>
       </c>
       <c r="E59" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F59" s="348">
         <f>'YERDEN ISITMA'!N59</f>
         <v/>
       </c>
       <c r="G59" s="345" t="n">
-        <v>102.19</v>
+        <v>43.61</v>
       </c>
       <c r="H59" s="345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I59" s="345" t="inlineStr">
         <is>
@@ -6912,31 +6594,31 @@
     <row r="60">
       <c r="A60" s="345" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B60" s="346" t="inlineStr">
         <is>
-          <t>D7 ANTRE-KOR.</t>
+          <t>D7 BANYO</t>
         </is>
       </c>
       <c r="C60" s="347" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D60" s="348" t="n">
-        <v>752.7</v>
+        <v>621.2</v>
       </c>
       <c r="E60" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F60" s="348">
         <f>'YERDEN ISITMA'!N60</f>
         <v/>
       </c>
       <c r="G60" s="345" t="n">
-        <v>43.01</v>
+        <v>17.75</v>
       </c>
       <c r="H60" s="345" t="n">
         <v>1</v>
@@ -6957,31 +6639,31 @@
     <row r="61">
       <c r="A61" s="345" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B61" s="346" t="inlineStr">
         <is>
-          <t>D7 BANYO</t>
+          <t>D8 MUTFAK</t>
         </is>
       </c>
       <c r="C61" s="347" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D61" s="348" t="n">
-        <v>211.4</v>
+        <v>1288.4</v>
       </c>
       <c r="E61" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F61" s="348">
         <f>'YERDEN ISITMA'!N61</f>
         <v/>
       </c>
       <c r="G61" s="345" t="n">
-        <v>12.08</v>
+        <v>36.81</v>
       </c>
       <c r="H61" s="345" t="n">
         <v>1</v>
@@ -7002,12 +6684,12 @@
     <row r="62">
       <c r="A62" s="345" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B62" s="346" t="inlineStr">
         <is>
-          <t>D8 MUTFAK</t>
+          <t>D8 YATAK OD.</t>
         </is>
       </c>
       <c r="C62" s="347" t="inlineStr">
@@ -7016,20 +6698,20 @@
         </is>
       </c>
       <c r="D62" s="348" t="n">
-        <v>594.6</v>
+        <v>2937.2</v>
       </c>
       <c r="E62" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F62" s="348">
         <f>'YERDEN ISITMA'!N62</f>
         <v/>
       </c>
       <c r="G62" s="345" t="n">
-        <v>33.98</v>
+        <v>83.92</v>
       </c>
       <c r="H62" s="345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" s="345" t="inlineStr">
         <is>
@@ -7047,7 +6729,7 @@
     <row r="63">
       <c r="A63" s="345" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B63" s="346" t="inlineStr">
@@ -7061,20 +6743,20 @@
         </is>
       </c>
       <c r="D63" s="348" t="n">
-        <v>932.2</v>
+        <v>1859.2</v>
       </c>
       <c r="E63" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F63" s="348">
         <f>'YERDEN ISITMA'!N63</f>
         <v/>
       </c>
       <c r="G63" s="345" t="n">
-        <v>53.27</v>
+        <v>53.12</v>
       </c>
       <c r="H63" s="345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" s="345" t="inlineStr">
         <is>
@@ -7092,12 +6774,12 @@
     <row r="64">
       <c r="A64" s="345" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B64" s="346" t="inlineStr">
         <is>
-          <t>D8 YATAK OD.</t>
+          <t>D8 SALON</t>
         </is>
       </c>
       <c r="C64" s="347" t="inlineStr">
@@ -7106,20 +6788,20 @@
         </is>
       </c>
       <c r="D64" s="348" t="n">
-        <v>769.5</v>
+        <v>4288.6</v>
       </c>
       <c r="E64" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F64" s="348">
         <f>'YERDEN ISITMA'!N64</f>
         <v/>
       </c>
       <c r="G64" s="345" t="n">
-        <v>43.97</v>
+        <v>122.53</v>
       </c>
       <c r="H64" s="345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" s="345" t="inlineStr">
         <is>
@@ -7137,12 +6819,12 @@
     <row r="65">
       <c r="A65" s="345" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B65" s="346" t="inlineStr">
         <is>
-          <t>D8 SALON</t>
+          <t>D8 ODA</t>
         </is>
       </c>
       <c r="C65" s="347" t="inlineStr">
@@ -7151,20 +6833,20 @@
         </is>
       </c>
       <c r="D65" s="348" t="n">
-        <v>1492.8</v>
+        <v>1610.7</v>
       </c>
       <c r="E65" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F65" s="348">
         <f>'YERDEN ISITMA'!N65</f>
         <v/>
       </c>
       <c r="G65" s="345" t="n">
-        <v>85.3</v>
+        <v>46.02</v>
       </c>
       <c r="H65" s="345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65" s="345" t="inlineStr">
         <is>
@@ -7182,31 +6864,31 @@
     <row r="66">
       <c r="A66" s="345" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B66" s="346" t="inlineStr">
         <is>
-          <t>D8 ODA</t>
+          <t>D8 ANTRE-KOR.</t>
         </is>
       </c>
       <c r="C66" s="347" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D66" s="348" t="n">
-        <v>622.3</v>
+        <v>2005.9</v>
       </c>
       <c r="E66" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F66" s="348">
         <f>'YERDEN ISITMA'!N66</f>
         <v/>
       </c>
       <c r="G66" s="345" t="n">
-        <v>35.56</v>
+        <v>57.31</v>
       </c>
       <c r="H66" s="345" t="n">
         <v>1</v>
@@ -7227,31 +6909,31 @@
     <row r="67">
       <c r="A67" s="345" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B67" s="346" t="inlineStr">
         <is>
-          <t>D8 ANTRE-KOR.</t>
+          <t>D8 WC-BANYO</t>
         </is>
       </c>
       <c r="C67" s="347" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D67" s="348" t="n">
-        <v>787.9</v>
+        <v>420.3</v>
       </c>
       <c r="E67" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F67" s="348">
         <f>'YERDEN ISITMA'!N67</f>
         <v/>
       </c>
       <c r="G67" s="345" t="n">
-        <v>45.02</v>
+        <v>12.01</v>
       </c>
       <c r="H67" s="345" t="n">
         <v>1</v>
@@ -7272,31 +6954,31 @@
     <row r="68">
       <c r="A68" s="345" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B68" s="346" t="inlineStr">
         <is>
-          <t>D8 WC-BANYO</t>
+          <t>D9 MUTFAK</t>
         </is>
       </c>
       <c r="C68" s="347" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D68" s="348" t="n">
-        <v>123.7</v>
+        <v>1679.7</v>
       </c>
       <c r="E68" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F68" s="348">
         <f>'YERDEN ISITMA'!N68</f>
         <v/>
       </c>
       <c r="G68" s="345" t="n">
-        <v>7.07</v>
+        <v>47.99</v>
       </c>
       <c r="H68" s="345" t="n">
         <v>1</v>
@@ -7317,12 +6999,12 @@
     <row r="69">
       <c r="A69" s="345" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B69" s="346" t="inlineStr">
         <is>
-          <t>D9 MUTFAK</t>
+          <t>D9 YATAK OD.</t>
         </is>
       </c>
       <c r="C69" s="347" t="inlineStr">
@@ -7331,20 +7013,20 @@
         </is>
       </c>
       <c r="D69" s="348" t="n">
-        <v>838.9</v>
+        <v>2864.4</v>
       </c>
       <c r="E69" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F69" s="348">
         <f>'YERDEN ISITMA'!N69</f>
         <v/>
       </c>
       <c r="G69" s="345" t="n">
-        <v>47.94</v>
+        <v>81.84</v>
       </c>
       <c r="H69" s="345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69" s="345" t="inlineStr">
         <is>
@@ -7362,7 +7044,7 @@
     <row r="70">
       <c r="A70" s="345" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B70" s="346" t="inlineStr">
@@ -7376,20 +7058,20 @@
         </is>
       </c>
       <c r="D70" s="348" t="n">
-        <v>1272.1</v>
+        <v>1848</v>
       </c>
       <c r="E70" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F70" s="348">
         <f>'YERDEN ISITMA'!N70</f>
         <v/>
       </c>
       <c r="G70" s="345" t="n">
-        <v>72.69</v>
+        <v>52.8</v>
       </c>
       <c r="H70" s="345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I70" s="345" t="inlineStr">
         <is>
@@ -7407,7 +7089,7 @@
     <row r="71">
       <c r="A71" s="345" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B71" s="346" t="inlineStr">
@@ -7421,17 +7103,17 @@
         </is>
       </c>
       <c r="D71" s="348" t="n">
-        <v>686.2</v>
+        <v>1864.8</v>
       </c>
       <c r="E71" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F71" s="348">
         <f>'YERDEN ISITMA'!N71</f>
         <v/>
       </c>
       <c r="G71" s="345" t="n">
-        <v>39.21</v>
+        <v>53.28</v>
       </c>
       <c r="H71" s="345" t="n">
         <v>1</v>
@@ -7452,12 +7134,12 @@
     <row r="72">
       <c r="A72" s="345" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B72" s="346" t="inlineStr">
         <is>
-          <t>D9 YATAK OD.</t>
+          <t>D9 SALON</t>
         </is>
       </c>
       <c r="C72" s="347" t="inlineStr">
@@ -7466,20 +7148,20 @@
         </is>
       </c>
       <c r="D72" s="348" t="n">
-        <v>771.4</v>
+        <v>4196.5</v>
       </c>
       <c r="E72" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F72" s="348">
         <f>'YERDEN ISITMA'!N72</f>
         <v/>
       </c>
       <c r="G72" s="345" t="n">
-        <v>44.08</v>
+        <v>119.9</v>
       </c>
       <c r="H72" s="345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="345" t="inlineStr">
         <is>
@@ -7497,34 +7179,34 @@
     <row r="73">
       <c r="A73" s="345" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B73" s="346" t="inlineStr">
         <is>
-          <t>D9 SALON</t>
+          <t>D9 ANTRE-KOR.</t>
         </is>
       </c>
       <c r="C73" s="347" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D73" s="348" t="n">
-        <v>1779.9</v>
+        <v>1545.2</v>
       </c>
       <c r="E73" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F73" s="348">
         <f>'YERDEN ISITMA'!N73</f>
         <v/>
       </c>
       <c r="G73" s="345" t="n">
-        <v>101.71</v>
+        <v>44.15</v>
       </c>
       <c r="H73" s="345" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73" s="345" t="inlineStr">
         <is>
@@ -7542,31 +7224,31 @@
     <row r="74">
       <c r="A74" s="345" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B74" s="346" t="inlineStr">
         <is>
-          <t>D9 ANTRE-KOR.</t>
+          <t>D9 BANYO</t>
         </is>
       </c>
       <c r="C74" s="347" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D74" s="348" t="n">
-        <v>752.9</v>
+        <v>627.5</v>
       </c>
       <c r="E74" s="349" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F74" s="348">
         <f>'YERDEN ISITMA'!N74</f>
         <v/>
       </c>
       <c r="G74" s="345" t="n">
-        <v>43.02</v>
+        <v>17.93</v>
       </c>
       <c r="H74" s="345" t="n">
         <v>1</v>
@@ -7585,83 +7267,39 @@
       <c r="P74" s="260" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="345" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="B75" s="346" t="inlineStr">
-        <is>
-          <t>D9 BANYO</t>
-        </is>
-      </c>
-      <c r="C75" s="347" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D75" s="348" t="n">
-        <v>233.4</v>
-      </c>
-      <c r="E75" s="349" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F75" s="348">
-        <f>'YERDEN ISITMA'!N75</f>
-        <v/>
-      </c>
-      <c r="G75" s="345" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="H75" s="345" t="n">
-        <v>1</v>
-      </c>
-      <c r="I75" s="345" t="inlineStr">
-        <is>
-          <t>ZEMİNDEN ISITMA</t>
-        </is>
-      </c>
-      <c r="J75" s="264" t="n"/>
-      <c r="K75" s="264" t="n"/>
-      <c r="L75" s="264" t="n"/>
-      <c r="M75" s="264" t="n"/>
-      <c r="N75" s="264" t="n"/>
-      <c r="O75" s="264" t="n"/>
-      <c r="P75" s="260" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="345" t="n"/>
-      <c r="B76" s="345" t="inlineStr">
+      <c r="A75" s="345" t="n"/>
+      <c r="B75" s="345" t="inlineStr">
         <is>
           <t>2. KAT</t>
         </is>
       </c>
-      <c r="C76" s="347" t="n"/>
-      <c r="D76" s="348" t="n"/>
-      <c r="E76" s="350" t="inlineStr">
+      <c r="C75" s="347" t="n"/>
+      <c r="D75" s="348" t="n"/>
+      <c r="E75" s="350" t="inlineStr">
         <is>
           <t>TOPLAM =</t>
         </is>
       </c>
-      <c r="F76" s="351">
-        <f>SUM(F55:F75)</f>
-        <v/>
-      </c>
-      <c r="G76" s="345" t="inlineStr">
+      <c r="F75" s="351">
+        <f>SUM(F54:F74)</f>
+        <v/>
+      </c>
+      <c r="G75" s="345" t="inlineStr">
         <is>
           <t>watt</t>
         </is>
       </c>
-      <c r="H76" s="345" t="n"/>
-      <c r="I76" s="345" t="n"/>
-      <c r="J76" s="345" t="n"/>
-      <c r="K76" s="345" t="n"/>
-      <c r="L76" s="345" t="n"/>
-      <c r="M76" s="345" t="n"/>
-      <c r="N76" s="345" t="n"/>
-      <c r="O76" s="345" t="n"/>
-      <c r="P76" s="345" t="n"/>
-    </row>
+      <c r="H75" s="345" t="n"/>
+      <c r="I75" s="345" t="n"/>
+      <c r="J75" s="345" t="n"/>
+      <c r="K75" s="345" t="n"/>
+      <c r="L75" s="345" t="n"/>
+      <c r="M75" s="345" t="n"/>
+      <c r="N75" s="345" t="n"/>
+      <c r="O75" s="345" t="n"/>
+      <c r="P75" s="345" t="n"/>
+    </row>
+    <row r="76"/>
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
@@ -7787,7 +7425,7 @@
     <row r="199"/>
     <row r="200"/>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="90">
     <mergeCell ref="I65:P65"/>
     <mergeCell ref="I34:P34"/>
     <mergeCell ref="I74:P74"/>
@@ -7819,8 +7457,6 @@
     <mergeCell ref="I25:P25"/>
     <mergeCell ref="I66:P66"/>
     <mergeCell ref="D6:D8"/>
-    <mergeCell ref="I75:P75"/>
-    <mergeCell ref="I53:P53"/>
     <mergeCell ref="F6:F8"/>
     <mergeCell ref="N3:P4"/>
     <mergeCell ref="I68:P68"/>
@@ -7841,6 +7477,7 @@
     <mergeCell ref="I70:P70"/>
     <mergeCell ref="I26:P26"/>
     <mergeCell ref="I57:P57"/>
+    <mergeCell ref="I54:P54"/>
     <mergeCell ref="I72:P72"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="I41:P41"/>
@@ -8853,7 +8490,7 @@
       </c>
       <c r="D8" s="360" t="inlineStr">
         <is>
-          <t>Mahal ısı ihtiyacı Q</t>
+          <t>Mahal ısı ihtiyacı Q (boru boyundan: 35 W/m × L)</t>
         </is>
       </c>
       <c r="E8" s="359" t="inlineStr">
@@ -9199,7 +8836,7 @@
       </c>
       <c r="M9" s="362" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>W/m</t>
         </is>
       </c>
       <c r="N9" s="363" t="inlineStr">
@@ -9497,7 +9134,7 @@
         <v/>
       </c>
       <c r="M10" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N10" s="373">
         <f>J10*M10</f>
@@ -9552,7 +9189,7 @@
         <v/>
       </c>
       <c r="M11" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N11" s="373">
         <f>J11*M11</f>
@@ -9607,7 +9244,7 @@
         <v/>
       </c>
       <c r="M12" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N12" s="373">
         <f>J12*M12</f>
@@ -9662,7 +9299,7 @@
         <v/>
       </c>
       <c r="M13" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N13" s="373">
         <f>J13*M13</f>
@@ -9717,7 +9354,7 @@
         <v/>
       </c>
       <c r="M14" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N14" s="373">
         <f>J14*M14</f>
@@ -9772,7 +9409,7 @@
         <v/>
       </c>
       <c r="M15" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N15" s="373">
         <f>J15*M15</f>
@@ -9827,7 +9464,7 @@
         <v/>
       </c>
       <c r="M16" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N16" s="373">
         <f>J16*M16</f>
@@ -9882,7 +9519,7 @@
         <v/>
       </c>
       <c r="M17" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N17" s="373">
         <f>J17*M17</f>
@@ -9937,7 +9574,7 @@
         <v/>
       </c>
       <c r="M18" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N18" s="373">
         <f>J18*M18</f>
@@ -9992,7 +9629,7 @@
         <v/>
       </c>
       <c r="M19" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N19" s="373">
         <f>J19*M19</f>
@@ -10047,7 +9684,7 @@
         <v/>
       </c>
       <c r="M20" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N20" s="373">
         <f>J20*M20</f>
@@ -10102,7 +9739,7 @@
         <v/>
       </c>
       <c r="M21" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N21" s="373">
         <f>J21*M21</f>
@@ -10157,7 +9794,7 @@
         <v/>
       </c>
       <c r="M22" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N22" s="373">
         <f>J22*M22</f>
@@ -10212,7 +9849,7 @@
         <v/>
       </c>
       <c r="M23" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N23" s="373">
         <f>J23*M23</f>
@@ -10267,7 +9904,7 @@
         <v/>
       </c>
       <c r="M24" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N24" s="373">
         <f>J24*M24</f>
@@ -10322,7 +9959,7 @@
         <v/>
       </c>
       <c r="M25" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N25" s="373">
         <f>J25*M25</f>
@@ -10377,7 +10014,7 @@
         <v/>
       </c>
       <c r="M26" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N26" s="373">
         <f>J26*M26</f>
@@ -10432,7 +10069,7 @@
         <v/>
       </c>
       <c r="M27" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N27" s="373">
         <f>J27*M27</f>
@@ -10487,7 +10124,7 @@
         <v/>
       </c>
       <c r="M28" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N28" s="373">
         <f>J28*M28</f>
@@ -10542,7 +10179,7 @@
         <v/>
       </c>
       <c r="M29" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N29" s="373">
         <f>J29*M29</f>
@@ -10597,7 +10234,7 @@
         <v/>
       </c>
       <c r="M30" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N30" s="373">
         <f>J30*M30</f>
@@ -10653,7 +10290,7 @@
         <v/>
       </c>
       <c r="M32" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N32" s="373">
         <f>J32*M32</f>
@@ -10708,7 +10345,7 @@
         <v/>
       </c>
       <c r="M33" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N33" s="373">
         <f>J33*M33</f>
@@ -10763,7 +10400,7 @@
         <v/>
       </c>
       <c r="M34" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N34" s="373">
         <f>J34*M34</f>
@@ -10818,7 +10455,7 @@
         <v/>
       </c>
       <c r="M35" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N35" s="373">
         <f>J35*M35</f>
@@ -10873,7 +10510,7 @@
         <v/>
       </c>
       <c r="M36" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N36" s="373">
         <f>J36*M36</f>
@@ -10928,7 +10565,7 @@
         <v/>
       </c>
       <c r="M37" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N37" s="373">
         <f>J37*M37</f>
@@ -10983,7 +10620,7 @@
         <v/>
       </c>
       <c r="M38" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N38" s="373">
         <f>J38*M38</f>
@@ -11038,7 +10675,7 @@
         <v/>
       </c>
       <c r="M39" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N39" s="373">
         <f>J39*M39</f>
@@ -11093,7 +10730,7 @@
         <v/>
       </c>
       <c r="M40" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N40" s="373">
         <f>J40*M40</f>
@@ -11148,7 +10785,7 @@
         <v/>
       </c>
       <c r="M41" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N41" s="373">
         <f>J41*M41</f>
@@ -11203,7 +10840,7 @@
         <v/>
       </c>
       <c r="M42" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N42" s="373">
         <f>J42*M42</f>
@@ -11258,7 +10895,7 @@
         <v/>
       </c>
       <c r="M43" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N43" s="373">
         <f>J43*M43</f>
@@ -11313,7 +10950,7 @@
         <v/>
       </c>
       <c r="M44" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N44" s="373">
         <f>J44*M44</f>
@@ -11368,7 +11005,7 @@
         <v/>
       </c>
       <c r="M45" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N45" s="373">
         <f>J45*M45</f>
@@ -11423,7 +11060,7 @@
         <v/>
       </c>
       <c r="M46" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N46" s="373">
         <f>J46*M46</f>
@@ -11478,7 +11115,7 @@
         <v/>
       </c>
       <c r="M47" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N47" s="373">
         <f>J47*M47</f>
@@ -11533,7 +11170,7 @@
         <v/>
       </c>
       <c r="M48" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N48" s="373">
         <f>J48*M48</f>
@@ -11588,7 +11225,7 @@
         <v/>
       </c>
       <c r="M49" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N49" s="373">
         <f>J49*M49</f>
@@ -11643,7 +11280,7 @@
         <v/>
       </c>
       <c r="M50" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N50" s="373">
         <f>J50*M50</f>
@@ -11698,7 +11335,7 @@
         <v/>
       </c>
       <c r="M51" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N51" s="373">
         <f>J51*M51</f>
@@ -11723,7 +11360,7 @@
         <v/>
       </c>
       <c r="E52" s="371" t="n">
-        <v>2.65</v>
+        <v>4.37</v>
       </c>
       <c r="F52" s="372">
         <f>D52/E52</f>
@@ -11753,69 +11390,69 @@
         <v/>
       </c>
       <c r="M52" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N52" s="373">
         <f>J52*M52</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="368">
-        <f>'PETEK LİST'!A53</f>
-        <v/>
-      </c>
-      <c r="B53" s="369">
-        <f>'PETEK LİST'!B53</f>
-        <v/>
-      </c>
-      <c r="C53" s="370">
-        <f>'PETEK LİST'!C53</f>
-        <v/>
-      </c>
-      <c r="D53" s="348">
-        <f>'PETEK LİST'!D53</f>
-        <v/>
-      </c>
-      <c r="E53" s="371" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="F53" s="372">
-        <f>D53/E53</f>
-        <v/>
-      </c>
-      <c r="G53" s="372">
-        <f>76.263-0.539*F53</f>
-        <v/>
-      </c>
-      <c r="H53" s="372">
-        <f>D53/G53</f>
-        <v/>
-      </c>
-      <c r="I53" s="368" t="n">
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="368">
+        <f>'PETEK LİST'!A54</f>
+        <v/>
+      </c>
+      <c r="B54" s="369">
+        <f>'PETEK LİST'!B54</f>
+        <v/>
+      </c>
+      <c r="C54" s="370">
+        <f>'PETEK LİST'!C54</f>
+        <v/>
+      </c>
+      <c r="D54" s="348">
+        <f>'PETEK LİST'!D54</f>
+        <v/>
+      </c>
+      <c r="E54" s="371" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="F54" s="372">
+        <f>D54/E54</f>
+        <v/>
+      </c>
+      <c r="G54" s="372">
+        <f>76.263-0.539*F54</f>
+        <v/>
+      </c>
+      <c r="H54" s="372">
+        <f>D54/G54</f>
+        <v/>
+      </c>
+      <c r="I54" s="368" t="n">
         <v>15</v>
       </c>
-      <c r="J53" s="345">
-        <f>'PETEK LİST'!G53</f>
-        <v/>
-      </c>
-      <c r="K53" s="372">
-        <f>J53/80</f>
-        <v/>
-      </c>
-      <c r="L53" s="368">
-        <f>CEILING(K53,1)</f>
-        <v/>
-      </c>
-      <c r="M53" s="368" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N53" s="373">
-        <f>J53*M53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54"/>
+      <c r="J54" s="345">
+        <f>'PETEK LİST'!G54</f>
+        <v/>
+      </c>
+      <c r="K54" s="372">
+        <f>J54/80</f>
+        <v/>
+      </c>
+      <c r="L54" s="368">
+        <f>CEILING(K54,1)</f>
+        <v/>
+      </c>
+      <c r="M54" s="368" t="n">
+        <v>35</v>
+      </c>
+      <c r="N54" s="373">
+        <f>J54*M54</f>
+        <v/>
+      </c>
+    </row>
     <row r="55">
       <c r="A55" s="368">
         <f>'PETEK LİST'!A55</f>
@@ -11834,7 +11471,7 @@
         <v/>
       </c>
       <c r="E55" s="371" t="n">
-        <v>11.07</v>
+        <v>14.25</v>
       </c>
       <c r="F55" s="372">
         <f>D55/E55</f>
@@ -11864,7 +11501,7 @@
         <v/>
       </c>
       <c r="M55" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N55" s="373">
         <f>J55*M55</f>
@@ -11889,7 +11526,7 @@
         <v/>
       </c>
       <c r="E56" s="371" t="n">
-        <v>14.25</v>
+        <v>9.31</v>
       </c>
       <c r="F56" s="372">
         <f>D56/E56</f>
@@ -11919,7 +11556,7 @@
         <v/>
       </c>
       <c r="M56" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N56" s="373">
         <f>J56*M56</f>
@@ -11974,7 +11611,7 @@
         <v/>
       </c>
       <c r="M57" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N57" s="373">
         <f>J57*M57</f>
@@ -11999,7 +11636,7 @@
         <v/>
       </c>
       <c r="E58" s="371" t="n">
-        <v>9.31</v>
+        <v>21.18</v>
       </c>
       <c r="F58" s="372">
         <f>D58/E58</f>
@@ -12029,7 +11666,7 @@
         <v/>
       </c>
       <c r="M58" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N58" s="373">
         <f>J58*M58</f>
@@ -12054,7 +11691,7 @@
         <v/>
       </c>
       <c r="E59" s="371" t="n">
-        <v>21.18</v>
+        <v>7.77</v>
       </c>
       <c r="F59" s="372">
         <f>D59/E59</f>
@@ -12084,7 +11721,7 @@
         <v/>
       </c>
       <c r="M59" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N59" s="373">
         <f>J59*M59</f>
@@ -12109,7 +11746,7 @@
         <v/>
       </c>
       <c r="E60" s="371" t="n">
-        <v>7.77</v>
+        <v>5.04</v>
       </c>
       <c r="F60" s="372">
         <f>D60/E60</f>
@@ -12139,7 +11776,7 @@
         <v/>
       </c>
       <c r="M60" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N60" s="373">
         <f>J60*M60</f>
@@ -12164,7 +11801,7 @@
         <v/>
       </c>
       <c r="E61" s="371" t="n">
-        <v>5.04</v>
+        <v>10.11</v>
       </c>
       <c r="F61" s="372">
         <f>D61/E61</f>
@@ -12194,7 +11831,7 @@
         <v/>
       </c>
       <c r="M61" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N61" s="373">
         <f>J61*M61</f>
@@ -12219,7 +11856,7 @@
         <v/>
       </c>
       <c r="E62" s="371" t="n">
-        <v>10.11</v>
+        <v>15.44</v>
       </c>
       <c r="F62" s="372">
         <f>D62/E62</f>
@@ -12249,7 +11886,7 @@
         <v/>
       </c>
       <c r="M62" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N62" s="373">
         <f>J62*M62</f>
@@ -12274,7 +11911,7 @@
         <v/>
       </c>
       <c r="E63" s="371" t="n">
-        <v>15.44</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F63" s="372">
         <f>D63/E63</f>
@@ -12304,7 +11941,7 @@
         <v/>
       </c>
       <c r="M63" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N63" s="373">
         <f>J63*M63</f>
@@ -12329,7 +11966,7 @@
         <v/>
       </c>
       <c r="E64" s="371" t="n">
-        <v>9.050000000000001</v>
+        <v>22.31</v>
       </c>
       <c r="F64" s="372">
         <f>D64/E64</f>
@@ -12359,7 +11996,7 @@
         <v/>
       </c>
       <c r="M64" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N64" s="373">
         <f>J64*M64</f>
@@ -12384,7 +12021,7 @@
         <v/>
       </c>
       <c r="E65" s="371" t="n">
-        <v>22.31</v>
+        <v>7.75</v>
       </c>
       <c r="F65" s="372">
         <f>D65/E65</f>
@@ -12414,7 +12051,7 @@
         <v/>
       </c>
       <c r="M65" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N65" s="373">
         <f>J65*M65</f>
@@ -12439,7 +12076,7 @@
         <v/>
       </c>
       <c r="E66" s="371" t="n">
-        <v>7.75</v>
+        <v>11</v>
       </c>
       <c r="F66" s="372">
         <f>D66/E66</f>
@@ -12469,7 +12106,7 @@
         <v/>
       </c>
       <c r="M66" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N66" s="373">
         <f>J66*M66</f>
@@ -12494,7 +12131,7 @@
         <v/>
       </c>
       <c r="E67" s="371" t="n">
-        <v>11</v>
+        <v>4.37</v>
       </c>
       <c r="F67" s="372">
         <f>D67/E67</f>
@@ -12524,7 +12161,7 @@
         <v/>
       </c>
       <c r="M67" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N67" s="373">
         <f>J67*M67</f>
@@ -12549,7 +12186,7 @@
         <v/>
       </c>
       <c r="E68" s="371" t="n">
-        <v>4.37</v>
+        <v>11.07</v>
       </c>
       <c r="F68" s="372">
         <f>D68/E68</f>
@@ -12579,7 +12216,7 @@
         <v/>
       </c>
       <c r="M68" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N68" s="373">
         <f>J68*M68</f>
@@ -12604,7 +12241,7 @@
         <v/>
       </c>
       <c r="E69" s="371" t="n">
-        <v>11.07</v>
+        <v>14.25</v>
       </c>
       <c r="F69" s="372">
         <f>D69/E69</f>
@@ -12634,7 +12271,7 @@
         <v/>
       </c>
       <c r="M69" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N69" s="373">
         <f>J69*M69</f>
@@ -12659,7 +12296,7 @@
         <v/>
       </c>
       <c r="E70" s="371" t="n">
-        <v>14.25</v>
+        <v>9.31</v>
       </c>
       <c r="F70" s="372">
         <f>D70/E70</f>
@@ -12689,7 +12326,7 @@
         <v/>
       </c>
       <c r="M70" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N70" s="373">
         <f>J70*M70</f>
@@ -12744,7 +12381,7 @@
         <v/>
       </c>
       <c r="M71" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N71" s="373">
         <f>J71*M71</f>
@@ -12769,7 +12406,7 @@
         <v/>
       </c>
       <c r="E72" s="371" t="n">
-        <v>9.31</v>
+        <v>21.18</v>
       </c>
       <c r="F72" s="372">
         <f>D72/E72</f>
@@ -12799,7 +12436,7 @@
         <v/>
       </c>
       <c r="M72" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N72" s="373">
         <f>J72*M72</f>
@@ -12824,7 +12461,7 @@
         <v/>
       </c>
       <c r="E73" s="371" t="n">
-        <v>21.18</v>
+        <v>7.77</v>
       </c>
       <c r="F73" s="372">
         <f>D73/E73</f>
@@ -12854,7 +12491,7 @@
         <v/>
       </c>
       <c r="M73" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N73" s="373">
         <f>J73*M73</f>
@@ -12879,7 +12516,7 @@
         <v/>
       </c>
       <c r="E74" s="371" t="n">
-        <v>7.77</v>
+        <v>5.04</v>
       </c>
       <c r="F74" s="372">
         <f>D74/E74</f>
@@ -12909,68 +12546,14 @@
         <v/>
       </c>
       <c r="M74" s="368" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="N74" s="373">
         <f>J74*M74</f>
         <v/>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="368">
-        <f>'PETEK LİST'!A75</f>
-        <v/>
-      </c>
-      <c r="B75" s="369">
-        <f>'PETEK LİST'!B75</f>
-        <v/>
-      </c>
-      <c r="C75" s="370">
-        <f>'PETEK LİST'!C75</f>
-        <v/>
-      </c>
-      <c r="D75" s="348">
-        <f>'PETEK LİST'!D75</f>
-        <v/>
-      </c>
-      <c r="E75" s="371" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="F75" s="372">
-        <f>D75/E75</f>
-        <v/>
-      </c>
-      <c r="G75" s="372">
-        <f>76.263-0.539*F75</f>
-        <v/>
-      </c>
-      <c r="H75" s="372">
-        <f>D75/G75</f>
-        <v/>
-      </c>
-      <c r="I75" s="368" t="n">
-        <v>15</v>
-      </c>
-      <c r="J75" s="345">
-        <f>'PETEK LİST'!G75</f>
-        <v/>
-      </c>
-      <c r="K75" s="372">
-        <f>J75/80</f>
-        <v/>
-      </c>
-      <c r="L75" s="368">
-        <f>CEILING(K75,1)</f>
-        <v/>
-      </c>
-      <c r="M75" s="368" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N75" s="373">
-        <f>J75*M75</f>
-        <v/>
-      </c>
-    </row>
+    <row r="75"/>
     <row r="76"/>
     <row r="77"/>
     <row r="78"/>
@@ -13241,7 +12824,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 18330 W</t>
+          <t>TOPLAM ISI = 43972 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -13272,7 +12855,7 @@
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 5035 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 22298 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -13922,173 +13505,181 @@
       <c r="D12" s="261" t="n"/>
       <c r="E12" s="259" t="n"/>
       <c r="F12" s="397" t="n">
-        <v>7.8</v>
+        <v>7.83</v>
       </c>
       <c r="G12" s="397" t="n">
-        <v>6.28</v>
+        <v>7.11</v>
       </c>
       <c r="H12" s="397" t="n">
-        <v>7.29</v>
+        <v>6.49</v>
       </c>
       <c r="I12" s="397" t="n">
-        <v>8.74</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="J12" s="397" t="n">
         <v>8.84</v>
       </c>
       <c r="K12" s="397" t="n">
-        <v>9.77</v>
+        <v>9.81</v>
       </c>
       <c r="L12" s="397" t="n">
-        <v>10.33</v>
+        <v>10.29</v>
       </c>
       <c r="M12" s="397" t="n">
         <v>7.61</v>
       </c>
       <c r="N12" s="397" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="O12" s="397" t="n">
         <v>7.87</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>6.27</v>
+        <v>7.1</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>7.2</v>
+        <v>6.74</v>
       </c>
       <c r="R12" s="397" t="n">
-        <v>8.73</v>
+        <v>8.76</v>
       </c>
       <c r="S12" s="397" t="n">
-        <v>8.800000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="T12" s="397" t="n">
-        <v>10.68</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="U12" s="397" t="n">
-        <v>9.49</v>
+        <v>10.29</v>
       </c>
       <c r="V12" s="397" t="n">
-        <v>7.63</v>
+        <v>7.67</v>
       </c>
       <c r="W12" s="397" t="n">
         <v>3.29</v>
       </c>
       <c r="X12" s="397" t="n">
-        <v>6.79</v>
+        <v>7.23</v>
       </c>
       <c r="Y12" s="397" t="n">
-        <v>6.73</v>
+        <v>7.24</v>
       </c>
       <c r="Z12" s="397" t="n">
-        <v>7.53</v>
+        <v>7.08</v>
       </c>
       <c r="AA12" s="397" t="n">
-        <v>8.619999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB12" s="397" t="n">
-        <v>11.03</v>
+        <v>10.87</v>
       </c>
       <c r="AC12" s="397" t="n">
-        <v>9.74</v>
+        <v>10.08</v>
       </c>
       <c r="AD12" s="397" t="n">
-        <v>7.14</v>
+        <v>7.31</v>
       </c>
       <c r="AE12" s="397" t="n">
-        <v>10</v>
+        <v>10.28</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="244">
       <c r="A13" s="261" t="n"/>
       <c r="B13" s="282" t="n"/>
-      <c r="C13" s="394" t="n"/>
-      <c r="D13" s="261" t="n"/>
+      <c r="C13" s="394" t="inlineStr">
+        <is>
+          <t>DEVRE ISIL GÜCÜ</t>
+        </is>
+      </c>
+      <c r="D13" s="261" t="inlineStr">
+        <is>
+          <t>35 W/m × L (planla aynı)</t>
+        </is>
+      </c>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>802.2</v>
+        <v>1688.4</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>590.5</v>
+        <v>1501.2</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>685.5</v>
+        <v>1371</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>682.7</v>
+        <v>1850.8</v>
       </c>
       <c r="J13" s="398" t="n">
-        <v>772.1</v>
+        <v>1866.2</v>
       </c>
       <c r="K13" s="398" t="n">
-        <v>874.8</v>
+        <v>2069.9</v>
       </c>
       <c r="L13" s="398" t="n">
-        <v>925.4</v>
+        <v>2171.1</v>
       </c>
       <c r="M13" s="398" t="n">
-        <v>759.7</v>
+        <v>1522.5</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>232.6</v>
+        <v>596.1</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>847</v>
+        <v>1694</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>569.3</v>
+        <v>1460.2</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>653.5</v>
+        <v>1385</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>682.7</v>
+        <v>1850.8</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>741</v>
+        <v>1860.6</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>1041.2</v>
+        <v>2082.5</v>
       </c>
       <c r="U13" s="398" t="n">
-        <v>925.4</v>
+        <v>2171.1</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>760.9</v>
+        <v>1533</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>192.8</v>
+        <v>561.1</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>589</v>
+        <v>1370.6</v>
       </c>
       <c r="Y13" s="398" t="n">
-        <v>474.8</v>
+        <v>1533</v>
       </c>
       <c r="Z13" s="398" t="n">
-        <v>530.8</v>
+        <v>1498.7</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>752.3</v>
+        <v>1859.2</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>904.2</v>
+        <v>2301.6</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>799.2</v>
+        <v>2135.7</v>
       </c>
       <c r="AD13" s="398" t="n">
-        <v>627.2</v>
+        <v>1619.1</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>788.9</v>
+        <v>1998.8</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>124.8</v>
+        <v>419.7</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1" s="244">
@@ -14618,111 +14209,111 @@
       <c r="C19" s="394" t="n"/>
       <c r="D19" s="261" t="n"/>
       <c r="E19" s="259" t="n"/>
-      <c r="F19" s="400">
+      <c r="F19" s="401">
         <f>F10+(F14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="G19" s="400">
+      <c r="G19" s="401">
         <f>G10+(G14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="H19" s="400">
+      <c r="H19" s="401">
         <f>H10+(H14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="I19" s="400">
+      <c r="I19" s="401">
         <f>I10+(I14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="J19" s="400">
+      <c r="J19" s="401">
         <f>J10+(J14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="K19" s="400">
+      <c r="K19" s="401">
         <f>K10+(K14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="L19" s="400">
+      <c r="L19" s="401">
         <f>L10+(L14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="M19" s="400">
+      <c r="M19" s="401">
         <f>M10+(M14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="N19" s="400">
+      <c r="N19" s="401">
         <f>N10+(N14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="O19" s="400">
+      <c r="O19" s="401">
         <f>O10+(O14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="P19" s="400">
+      <c r="P19" s="401">
         <f>P10+(P14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="Q19" s="400">
+      <c r="Q19" s="401">
         <f>Q10+(Q14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="R19" s="400">
+      <c r="R19" s="401">
         <f>R10+(R14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="S19" s="400">
+      <c r="S19" s="401">
         <f>S10+(S14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="T19" s="400">
+      <c r="T19" s="401">
         <f>T10+(T14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="U19" s="400">
+      <c r="U19" s="401">
         <f>U10+(U14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="V19" s="400">
+      <c r="V19" s="401">
         <f>V10+(V14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="W19" s="400">
+      <c r="W19" s="401">
         <f>W10+(W14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="X19" s="400">
+      <c r="X19" s="401">
         <f>X10+(X14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="Y19" s="400">
+      <c r="Y19" s="401">
         <f>Y10+(Y14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="Z19" s="400">
+      <c r="Z19" s="401">
         <f>Z10+(Z14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AA19" s="400">
+      <c r="AA19" s="401">
         <f>AA10+(AA14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AB19" s="400">
+      <c r="AB19" s="401">
         <f>AB10+(AB14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AC19" s="400">
+      <c r="AC19" s="401">
         <f>AC10+(AC14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AD19" s="400">
+      <c r="AD19" s="401">
         <f>AD10+(AD14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AE19" s="400">
+      <c r="AE19" s="401">
         <f>AE10+(AE14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AF19" s="400">
+      <c r="AF19" s="401">
         <f>AF10+(AF14/8.92)^0.91</f>
         <v/>
       </c>
@@ -14817,7 +14408,7 @@
     </row>
     <row r="21" ht="12" customHeight="1" s="244">
       <c r="A21" s="261" t="n"/>
-      <c r="B21" s="401" t="n"/>
+      <c r="B21" s="402" t="n"/>
       <c r="C21" s="394" t="n"/>
       <c r="D21" s="261" t="n"/>
       <c r="E21" s="259" t="n"/>
@@ -14932,7 +14523,7 @@
     </row>
     <row r="22" ht="12" customHeight="1" s="244">
       <c r="A22" s="261" t="n"/>
-      <c r="B22" s="402" t="n"/>
+      <c r="B22" s="403" t="n"/>
       <c r="C22" s="394" t="n"/>
       <c r="D22" s="261" t="n"/>
       <c r="E22" s="259" t="n"/>
@@ -15020,95 +14611,95 @@
     </row>
     <row r="23" ht="12" customHeight="1" s="244">
       <c r="A23" s="261" t="n"/>
-      <c r="B23" s="402" t="n"/>
+      <c r="B23" s="403" t="n"/>
       <c r="C23" s="394" t="n"/>
       <c r="D23" s="261" t="n"/>
       <c r="E23" s="259" t="n"/>
-      <c r="F23" s="403" t="n">
+      <c r="F23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="G23" s="403" t="n">
+      <c r="G23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="H23" s="403" t="n">
+      <c r="H23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="I23" s="403" t="n">
+      <c r="I23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="J23" s="403" t="n">
+      <c r="J23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="K23" s="403" t="n">
+      <c r="K23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="L23" s="403" t="n">
+      <c r="L23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="M23" s="403" t="n">
+      <c r="M23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="N23" s="403" t="n">
+      <c r="N23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="O23" s="403" t="n">
+      <c r="O23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="P23" s="403" t="n">
+      <c r="P23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="Q23" s="403" t="n">
+      <c r="Q23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="R23" s="403" t="n">
+      <c r="R23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="S23" s="403" t="n">
+      <c r="S23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="T23" s="403" t="n">
+      <c r="T23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="U23" s="403" t="n">
+      <c r="U23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="V23" s="403" t="n">
+      <c r="V23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="W23" s="403" t="n">
+      <c r="W23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="X23" s="403" t="n">
+      <c r="X23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="Y23" s="403" t="n">
+      <c r="Y23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="Z23" s="403" t="n">
+      <c r="Z23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AA23" s="403" t="n">
+      <c r="AA23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AB23" s="403" t="n">
+      <c r="AB23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AC23" s="403" t="n">
+      <c r="AC23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AD23" s="403" t="n">
+      <c r="AD23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AE23" s="403" t="n">
+      <c r="AE23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AF23" s="403" t="n">
+      <c r="AF23" s="404" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="24" ht="12" customHeight="1" s="244">
       <c r="A24" s="261" t="n"/>
-      <c r="B24" s="401" t="n"/>
+      <c r="B24" s="402" t="n"/>
       <c r="C24" s="394" t="n"/>
       <c r="D24" s="261" t="n"/>
       <c r="E24" s="259" t="n"/>
@@ -15223,7 +14814,7 @@
     </row>
     <row r="25" ht="12" customHeight="1" s="244">
       <c r="A25" s="261" t="n"/>
-      <c r="B25" s="401" t="n"/>
+      <c r="B25" s="402" t="n"/>
       <c r="C25" s="394" t="n"/>
       <c r="D25" s="261" t="n"/>
       <c r="E25" s="259" t="n"/>
@@ -15338,9 +14929,9 @@
     </row>
     <row r="26" ht="12" customHeight="1" s="244">
       <c r="A26" s="261" t="n"/>
-      <c r="B26" s="402" t="n"/>
+      <c r="B26" s="403" t="n"/>
       <c r="C26" s="394" t="n"/>
-      <c r="D26" s="404" t="n"/>
+      <c r="D26" s="405" t="n"/>
       <c r="E26" s="259" t="n"/>
       <c r="F26" s="400">
         <f>0.2*F14</f>
@@ -15453,352 +15044,352 @@
     </row>
     <row r="27" ht="12" customHeight="1" s="244">
       <c r="A27" s="261" t="n"/>
-      <c r="B27" s="402" t="n"/>
+      <c r="B27" s="403" t="n"/>
       <c r="C27" s="394" t="n"/>
       <c r="D27" s="261" t="n"/>
       <c r="E27" s="259" t="n"/>
-      <c r="F27" s="405">
+      <c r="F27" s="406">
         <f>F17*(F14+F26)</f>
         <v/>
       </c>
-      <c r="G27" s="405">
+      <c r="G27" s="406">
         <f>G17*(G14+G26)</f>
         <v/>
       </c>
-      <c r="H27" s="405">
+      <c r="H27" s="406">
         <f>H17*(H14+H26)</f>
         <v/>
       </c>
-      <c r="I27" s="405">
+      <c r="I27" s="406">
         <f>I17*(I14+I26)</f>
         <v/>
       </c>
-      <c r="J27" s="405">
+      <c r="J27" s="406">
         <f>J17*(J14+J26)</f>
         <v/>
       </c>
-      <c r="K27" s="405">
+      <c r="K27" s="406">
         <f>K17*(K14+K26)</f>
         <v/>
       </c>
-      <c r="L27" s="405">
+      <c r="L27" s="406">
         <f>L17*(L14+L26)</f>
         <v/>
       </c>
-      <c r="M27" s="405">
+      <c r="M27" s="406">
         <f>M17*(M14+M26)</f>
         <v/>
       </c>
-      <c r="N27" s="405">
+      <c r="N27" s="406">
         <f>N17*(N14+N26)</f>
         <v/>
       </c>
-      <c r="O27" s="405">
+      <c r="O27" s="406">
         <f>O17*(O14+O26)</f>
         <v/>
       </c>
-      <c r="P27" s="405">
+      <c r="P27" s="406">
         <f>P17*(P14+P26)</f>
         <v/>
       </c>
-      <c r="Q27" s="405">
+      <c r="Q27" s="406">
         <f>Q17*(Q14+Q26)</f>
         <v/>
       </c>
-      <c r="R27" s="405">
+      <c r="R27" s="406">
         <f>R17*(R14+R26)</f>
         <v/>
       </c>
-      <c r="S27" s="405">
+      <c r="S27" s="406">
         <f>S17*(S14+S26)</f>
         <v/>
       </c>
-      <c r="T27" s="405">
+      <c r="T27" s="406">
         <f>T17*(T14+T26)</f>
         <v/>
       </c>
-      <c r="U27" s="405">
+      <c r="U27" s="406">
         <f>U17*(U14+U26)</f>
         <v/>
       </c>
-      <c r="V27" s="405">
+      <c r="V27" s="406">
         <f>V17*(V14+V26)</f>
         <v/>
       </c>
-      <c r="W27" s="405">
+      <c r="W27" s="406">
         <f>W17*(W14+W26)</f>
         <v/>
       </c>
-      <c r="X27" s="405">
+      <c r="X27" s="406">
         <f>X17*(X14+X26)</f>
         <v/>
       </c>
-      <c r="Y27" s="405">
+      <c r="Y27" s="406">
         <f>Y17*(Y14+Y26)</f>
         <v/>
       </c>
-      <c r="Z27" s="405">
+      <c r="Z27" s="406">
         <f>Z17*(Z14+Z26)</f>
         <v/>
       </c>
-      <c r="AA27" s="405">
+      <c r="AA27" s="406">
         <f>AA17*(AA14+AA26)</f>
         <v/>
       </c>
-      <c r="AB27" s="405">
+      <c r="AB27" s="406">
         <f>AB17*(AB14+AB26)</f>
         <v/>
       </c>
-      <c r="AC27" s="405">
+      <c r="AC27" s="406">
         <f>AC17*(AC14+AC26)</f>
         <v/>
       </c>
-      <c r="AD27" s="405">
+      <c r="AD27" s="406">
         <f>AD17*(AD14+AD26)</f>
         <v/>
       </c>
-      <c r="AE27" s="405">
+      <c r="AE27" s="406">
         <f>AE17*(AE14+AE26)</f>
         <v/>
       </c>
-      <c r="AF27" s="405">
+      <c r="AF27" s="406">
         <f>AF17*(AF14+AF26)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="12" customHeight="1" s="244">
       <c r="A28" s="261" t="n"/>
-      <c r="B28" s="402" t="n"/>
+      <c r="B28" s="403" t="n"/>
       <c r="C28" s="394" t="n"/>
       <c r="D28" s="261" t="n"/>
       <c r="E28" s="259" t="n"/>
-      <c r="F28" s="406">
+      <c r="F28" s="407">
         <f>F27/(1.163*F25)</f>
         <v/>
       </c>
-      <c r="G28" s="406">
+      <c r="G28" s="407">
         <f>G27/(1.163*G25)</f>
         <v/>
       </c>
-      <c r="H28" s="406">
+      <c r="H28" s="407">
         <f>H27/(1.163*H25)</f>
         <v/>
       </c>
-      <c r="I28" s="406">
+      <c r="I28" s="407">
         <f>I27/(1.163*I25)</f>
         <v/>
       </c>
-      <c r="J28" s="406">
+      <c r="J28" s="407">
         <f>J27/(1.163*J25)</f>
         <v/>
       </c>
-      <c r="K28" s="406">
+      <c r="K28" s="407">
         <f>K27/(1.163*K25)</f>
         <v/>
       </c>
-      <c r="L28" s="406">
+      <c r="L28" s="407">
         <f>L27/(1.163*L25)</f>
         <v/>
       </c>
-      <c r="M28" s="406">
+      <c r="M28" s="407">
         <f>M27/(1.163*M25)</f>
         <v/>
       </c>
-      <c r="N28" s="406">
+      <c r="N28" s="407">
         <f>N27/(1.163*N25)</f>
         <v/>
       </c>
-      <c r="O28" s="406">
+      <c r="O28" s="407">
         <f>O27/(1.163*O25)</f>
         <v/>
       </c>
-      <c r="P28" s="406">
+      <c r="P28" s="407">
         <f>P27/(1.163*P25)</f>
         <v/>
       </c>
-      <c r="Q28" s="406">
+      <c r="Q28" s="407">
         <f>Q27/(1.163*Q25)</f>
         <v/>
       </c>
-      <c r="R28" s="406">
+      <c r="R28" s="407">
         <f>R27/(1.163*R25)</f>
         <v/>
       </c>
-      <c r="S28" s="406">
+      <c r="S28" s="407">
         <f>S27/(1.163*S25)</f>
         <v/>
       </c>
-      <c r="T28" s="406">
+      <c r="T28" s="407">
         <f>T27/(1.163*T25)</f>
         <v/>
       </c>
-      <c r="U28" s="406">
+      <c r="U28" s="407">
         <f>U27/(1.163*U25)</f>
         <v/>
       </c>
-      <c r="V28" s="406">
+      <c r="V28" s="407">
         <f>V27/(1.163*V25)</f>
         <v/>
       </c>
-      <c r="W28" s="406">
+      <c r="W28" s="407">
         <f>W27/(1.163*W25)</f>
         <v/>
       </c>
-      <c r="X28" s="406">
+      <c r="X28" s="407">
         <f>X27/(1.163*X25)</f>
         <v/>
       </c>
-      <c r="Y28" s="406">
+      <c r="Y28" s="407">
         <f>Y27/(1.163*Y25)</f>
         <v/>
       </c>
-      <c r="Z28" s="406">
+      <c r="Z28" s="407">
         <f>Z27/(1.163*Z25)</f>
         <v/>
       </c>
-      <c r="AA28" s="406">
+      <c r="AA28" s="407">
         <f>AA27/(1.163*AA25)</f>
         <v/>
       </c>
-      <c r="AB28" s="406">
+      <c r="AB28" s="407">
         <f>AB27/(1.163*AB25)</f>
         <v/>
       </c>
-      <c r="AC28" s="406">
+      <c r="AC28" s="407">
         <f>AC27/(1.163*AC25)</f>
         <v/>
       </c>
-      <c r="AD28" s="406">
+      <c r="AD28" s="407">
         <f>AD27/(1.163*AD25)</f>
         <v/>
       </c>
-      <c r="AE28" s="406">
+      <c r="AE28" s="407">
         <f>AE27/(1.163*AE25)</f>
         <v/>
       </c>
-      <c r="AF28" s="406">
+      <c r="AF28" s="407">
         <f>AF27/(1.163*AF25)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="12" customHeight="1" s="244">
       <c r="A29" s="261" t="n"/>
-      <c r="B29" s="402" t="n"/>
+      <c r="B29" s="403" t="n"/>
       <c r="C29" s="394" t="n"/>
       <c r="D29" s="261" t="n"/>
       <c r="E29" s="259" t="n"/>
-      <c r="F29" s="407">
+      <c r="F29" s="408">
         <f>F17/(F22*0.01)</f>
         <v/>
       </c>
-      <c r="G29" s="407">
+      <c r="G29" s="408">
         <f>G17/(G22*0.01)</f>
         <v/>
       </c>
-      <c r="H29" s="407">
+      <c r="H29" s="408">
         <f>H17/(H22*0.01)</f>
         <v/>
       </c>
-      <c r="I29" s="407">
+      <c r="I29" s="408">
         <f>I17/(I22*0.01)</f>
         <v/>
       </c>
-      <c r="J29" s="407">
+      <c r="J29" s="408">
         <f>J17/(J22*0.01)</f>
         <v/>
       </c>
-      <c r="K29" s="407">
+      <c r="K29" s="408">
         <f>K17/(K22*0.01)</f>
         <v/>
       </c>
-      <c r="L29" s="407">
+      <c r="L29" s="408">
         <f>L17/(L22*0.01)</f>
         <v/>
       </c>
-      <c r="M29" s="407">
+      <c r="M29" s="408">
         <f>M17/(M22*0.01)</f>
         <v/>
       </c>
-      <c r="N29" s="407">
+      <c r="N29" s="408">
         <f>N17/(N22*0.01)</f>
         <v/>
       </c>
-      <c r="O29" s="407">
+      <c r="O29" s="408">
         <f>O17/(O22*0.01)</f>
         <v/>
       </c>
-      <c r="P29" s="407">
+      <c r="P29" s="408">
         <f>P17/(P22*0.01)</f>
         <v/>
       </c>
-      <c r="Q29" s="407">
+      <c r="Q29" s="408">
         <f>Q17/(Q22*0.01)</f>
         <v/>
       </c>
-      <c r="R29" s="407">
+      <c r="R29" s="408">
         <f>R17/(R22*0.01)</f>
         <v/>
       </c>
-      <c r="S29" s="407">
+      <c r="S29" s="408">
         <f>S17/(S22*0.01)</f>
         <v/>
       </c>
-      <c r="T29" s="407">
+      <c r="T29" s="408">
         <f>T17/(T22*0.01)</f>
         <v/>
       </c>
-      <c r="U29" s="407">
+      <c r="U29" s="408">
         <f>U17/(U22*0.01)</f>
         <v/>
       </c>
-      <c r="V29" s="407">
+      <c r="V29" s="408">
         <f>V17/(V22*0.01)</f>
         <v/>
       </c>
-      <c r="W29" s="407">
+      <c r="W29" s="408">
         <f>W17/(W22*0.01)</f>
         <v/>
       </c>
-      <c r="X29" s="407">
+      <c r="X29" s="408">
         <f>X17/(X22*0.01)</f>
         <v/>
       </c>
-      <c r="Y29" s="407">
+      <c r="Y29" s="408">
         <f>Y17/(Y22*0.01)</f>
         <v/>
       </c>
-      <c r="Z29" s="407">
+      <c r="Z29" s="408">
         <f>Z17/(Z22*0.01)</f>
         <v/>
       </c>
-      <c r="AA29" s="407">
+      <c r="AA29" s="408">
         <f>AA17/(AA22*0.01)</f>
         <v/>
       </c>
-      <c r="AB29" s="407">
+      <c r="AB29" s="408">
         <f>AB17/(AB22*0.01)</f>
         <v/>
       </c>
-      <c r="AC29" s="407">
+      <c r="AC29" s="408">
         <f>AC17/(AC22*0.01)</f>
         <v/>
       </c>
-      <c r="AD29" s="407">
+      <c r="AD29" s="408">
         <f>AD17/(AD22*0.01)</f>
         <v/>
       </c>
-      <c r="AE29" s="407">
+      <c r="AE29" s="408">
         <f>AE17/(AE22*0.01)</f>
         <v/>
       </c>
-      <c r="AF29" s="407">
+      <c r="AF29" s="408">
         <f>AF17/(AF22*0.01)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="12" customHeight="1" s="244">
       <c r="A30" s="261" t="n"/>
-      <c r="B30" s="402" t="n"/>
+      <c r="B30" s="403" t="n"/>
       <c r="C30" s="394" t="inlineStr">
         <is>
           <t>BAĞLANTI BORULARI</t>
@@ -15810,91 +15401,91 @@
         </is>
       </c>
       <c r="E30" s="259" t="n"/>
-      <c r="F30" s="408" t="n">
+      <c r="F30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="408" t="n">
+      <c r="G30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="408" t="n">
+      <c r="H30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="408" t="n">
+      <c r="I30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="408" t="n">
+      <c r="J30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="408" t="n">
+      <c r="K30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="408" t="n">
+      <c r="L30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="408" t="n">
+      <c r="M30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="408" t="n">
+      <c r="N30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="408" t="n">
+      <c r="O30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="408" t="n">
+      <c r="P30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="408" t="n">
+      <c r="Q30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="R30" s="408" t="n">
+      <c r="R30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="408" t="n">
+      <c r="S30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="408" t="n">
+      <c r="T30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="408" t="n">
+      <c r="U30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="408" t="n">
+      <c r="V30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="408" t="n">
+      <c r="W30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="X30" s="408" t="n">
+      <c r="X30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="Y30" s="408" t="n">
+      <c r="Y30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="408" t="n">
+      <c r="Z30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AA30" s="408" t="n">
+      <c r="AA30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AB30" s="408" t="n">
+      <c r="AB30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" s="408" t="n">
+      <c r="AC30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="408" t="n">
+      <c r="AD30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AE30" s="408" t="n">
+      <c r="AE30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AF30" s="408" t="n">
+      <c r="AF30" s="409" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" ht="12" customHeight="1" s="244">
       <c r="A31" s="261" t="n"/>
-      <c r="B31" s="402" t="n"/>
+      <c r="B31" s="403" t="n"/>
       <c r="C31" s="394" t="n"/>
       <c r="D31" s="261" t="n"/>
       <c r="E31" s="259" t="n"/>
@@ -16009,7 +15600,7 @@
     </row>
     <row r="32" ht="12" customHeight="1" s="244">
       <c r="A32" s="261" t="n"/>
-      <c r="B32" s="401" t="n"/>
+      <c r="B32" s="402" t="n"/>
       <c r="C32" s="394" t="inlineStr">
         <is>
           <t>DÜZ BORU BASINÇ KAYBI (5)</t>
@@ -16021,91 +15612,91 @@
         </is>
       </c>
       <c r="E32" s="259" t="n"/>
-      <c r="F32" s="407" t="n">
-        <v>2340</v>
-      </c>
-      <c r="G32" s="407" t="n">
-        <v>615</v>
-      </c>
-      <c r="H32" s="407" t="n">
-        <v>1519</v>
-      </c>
-      <c r="I32" s="407" t="n">
-        <v>1502</v>
-      </c>
-      <c r="J32" s="407" t="n">
-        <v>2107</v>
-      </c>
-      <c r="K32" s="407" t="n">
-        <v>2970</v>
-      </c>
-      <c r="L32" s="407" t="n">
-        <v>3467</v>
-      </c>
-      <c r="M32" s="407" t="n">
-        <v>2015</v>
-      </c>
-      <c r="N32" s="407" t="n">
-        <v>95</v>
-      </c>
-      <c r="O32" s="407" t="n">
-        <v>2718</v>
-      </c>
-      <c r="P32" s="407" t="n">
-        <v>572</v>
-      </c>
-      <c r="Q32" s="407" t="n">
-        <v>1332</v>
-      </c>
-      <c r="R32" s="407" t="n">
-        <v>1502</v>
-      </c>
-      <c r="S32" s="407" t="n">
-        <v>1881</v>
-      </c>
-      <c r="T32" s="407" t="n">
-        <v>4795</v>
-      </c>
-      <c r="U32" s="407" t="n">
-        <v>3467</v>
-      </c>
-      <c r="V32" s="407" t="n">
-        <v>2024</v>
-      </c>
-      <c r="W32" s="407" t="n">
-        <v>66</v>
-      </c>
-      <c r="X32" s="407" t="n">
-        <v>612</v>
-      </c>
-      <c r="Y32" s="407" t="n">
-        <v>398</v>
-      </c>
-      <c r="Z32" s="407" t="n">
-        <v>497</v>
-      </c>
-      <c r="AA32" s="407" t="n">
-        <v>1962</v>
-      </c>
-      <c r="AB32" s="407" t="n">
-        <v>3253</v>
-      </c>
-      <c r="AC32" s="407" t="n">
-        <v>2317</v>
-      </c>
-      <c r="AD32" s="407" t="n">
-        <v>1190</v>
-      </c>
-      <c r="AE32" s="407" t="n">
-        <v>2235</v>
-      </c>
-      <c r="AF32" s="407" t="n">
-        <v>27</v>
+      <c r="F32" s="408" t="n">
+        <v>9058</v>
+      </c>
+      <c r="G32" s="408" t="n">
+        <v>6556</v>
+      </c>
+      <c r="H32" s="408" t="n">
+        <v>5109</v>
+      </c>
+      <c r="I32" s="408" t="n">
+        <v>11661</v>
+      </c>
+      <c r="J32" s="408" t="n">
+        <v>11930</v>
+      </c>
+      <c r="K32" s="408" t="n">
+        <v>15862</v>
+      </c>
+      <c r="L32" s="408" t="n">
+        <v>18086</v>
+      </c>
+      <c r="M32" s="408" t="n">
+        <v>6816</v>
+      </c>
+      <c r="N32" s="408" t="n">
+        <v>517</v>
+      </c>
+      <c r="O32" s="408" t="n">
+        <v>9141</v>
+      </c>
+      <c r="P32" s="408" t="n">
+        <v>6076</v>
+      </c>
+      <c r="Q32" s="408" t="n">
+        <v>5253</v>
+      </c>
+      <c r="R32" s="408" t="n">
+        <v>11661</v>
+      </c>
+      <c r="S32" s="408" t="n">
+        <v>11832</v>
+      </c>
+      <c r="T32" s="408" t="n">
+        <v>16129</v>
+      </c>
+      <c r="U32" s="408" t="n">
+        <v>18086</v>
+      </c>
+      <c r="V32" s="408" t="n">
+        <v>6946</v>
+      </c>
+      <c r="W32" s="408" t="n">
+        <v>278</v>
+      </c>
+      <c r="X32" s="408" t="n">
+        <v>5105</v>
+      </c>
+      <c r="Y32" s="408" t="n">
+        <v>6946</v>
+      </c>
+      <c r="Z32" s="408" t="n">
+        <v>6527</v>
+      </c>
+      <c r="AA32" s="408" t="n">
+        <v>11807</v>
+      </c>
+      <c r="AB32" s="408" t="n">
+        <v>21236</v>
+      </c>
+      <c r="AC32" s="408" t="n">
+        <v>17288</v>
+      </c>
+      <c r="AD32" s="408" t="n">
+        <v>8072</v>
+      </c>
+      <c r="AE32" s="408" t="n">
+        <v>14409</v>
+      </c>
+      <c r="AF32" s="408" t="n">
+        <v>155</v>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1" s="244">
       <c r="A33" s="261" t="n"/>
-      <c r="B33" s="401" t="n"/>
+      <c r="B33" s="402" t="n"/>
       <c r="C33" s="394" t="n"/>
       <c r="D33" s="261" t="n"/>
       <c r="E33" s="259" t="n"/>
@@ -16220,7 +15811,7 @@
     </row>
     <row r="34" ht="12" customHeight="1" s="244">
       <c r="A34" s="261" t="n"/>
-      <c r="B34" s="401" t="n"/>
+      <c r="B34" s="402" t="n"/>
       <c r="C34" s="394" t="n"/>
       <c r="D34" s="261" t="n"/>
       <c r="E34" s="259" t="n"/>
@@ -16335,115 +15926,115 @@
     </row>
     <row r="35" ht="12" customHeight="1" s="244">
       <c r="A35" s="261" t="n"/>
-      <c r="B35" s="401" t="n"/>
+      <c r="B35" s="402" t="n"/>
       <c r="C35" s="282" t="n"/>
       <c r="D35" s="261" t="n"/>
       <c r="E35" s="259" t="n"/>
-      <c r="F35" s="409">
+      <c r="F35" s="410">
         <f>MAX(F34:AF34)-F34</f>
         <v/>
       </c>
-      <c r="G35" s="409">
+      <c r="G35" s="410">
         <f>MAX(F34:AF34)-G34</f>
         <v/>
       </c>
-      <c r="H35" s="409">
+      <c r="H35" s="410">
         <f>MAX(F34:AF34)-H34</f>
         <v/>
       </c>
-      <c r="I35" s="409">
+      <c r="I35" s="410">
         <f>MAX(F34:AF34)-I34</f>
         <v/>
       </c>
-      <c r="J35" s="409">
+      <c r="J35" s="410">
         <f>MAX(F34:AF34)-J34</f>
         <v/>
       </c>
-      <c r="K35" s="409">
+      <c r="K35" s="410">
         <f>MAX(F34:AF34)-K34</f>
         <v/>
       </c>
-      <c r="L35" s="409">
+      <c r="L35" s="410">
         <f>MAX(F34:AF34)-L34</f>
         <v/>
       </c>
-      <c r="M35" s="409">
+      <c r="M35" s="410">
         <f>MAX(F34:AF34)-M34</f>
         <v/>
       </c>
-      <c r="N35" s="409">
+      <c r="N35" s="410">
         <f>MAX(F34:AF34)-N34</f>
         <v/>
       </c>
-      <c r="O35" s="409">
+      <c r="O35" s="410">
         <f>MAX(F34:AF34)-O34</f>
         <v/>
       </c>
-      <c r="P35" s="409">
+      <c r="P35" s="410">
         <f>MAX(F34:AF34)-P34</f>
         <v/>
       </c>
-      <c r="Q35" s="409">
+      <c r="Q35" s="410">
         <f>MAX(F34:AF34)-Q34</f>
         <v/>
       </c>
-      <c r="R35" s="409">
+      <c r="R35" s="410">
         <f>MAX(F34:AF34)-R34</f>
         <v/>
       </c>
-      <c r="S35" s="409">
+      <c r="S35" s="410">
         <f>MAX(F34:AF34)-S34</f>
         <v/>
       </c>
-      <c r="T35" s="409">
+      <c r="T35" s="410">
         <f>MAX(F34:AF34)-T34</f>
         <v/>
       </c>
-      <c r="U35" s="409">
+      <c r="U35" s="410">
         <f>MAX(F34:AF34)-U34</f>
         <v/>
       </c>
-      <c r="V35" s="409">
+      <c r="V35" s="410">
         <f>MAX(F34:AF34)-V34</f>
         <v/>
       </c>
-      <c r="W35" s="409">
+      <c r="W35" s="410">
         <f>MAX(F34:AF34)-W34</f>
         <v/>
       </c>
-      <c r="X35" s="409">
+      <c r="X35" s="410">
         <f>MAX(F34:AF34)-X34</f>
         <v/>
       </c>
-      <c r="Y35" s="409">
+      <c r="Y35" s="410">
         <f>MAX(F34:AF34)-Y34</f>
         <v/>
       </c>
-      <c r="Z35" s="409">
+      <c r="Z35" s="410">
         <f>MAX(F34:AF34)-Z34</f>
         <v/>
       </c>
-      <c r="AA35" s="409">
+      <c r="AA35" s="410">
         <f>MAX(F34:AF34)-AA34</f>
         <v/>
       </c>
-      <c r="AB35" s="409">
+      <c r="AB35" s="410">
         <f>MAX(F34:AF34)-AB34</f>
         <v/>
       </c>
-      <c r="AC35" s="409">
+      <c r="AC35" s="410">
         <f>MAX(F34:AF34)-AC34</f>
         <v/>
       </c>
-      <c r="AD35" s="409">
+      <c r="AD35" s="410">
         <f>MAX(F34:AF34)-AD34</f>
         <v/>
       </c>
-      <c r="AE35" s="409">
+      <c r="AE35" s="410">
         <f>MAX(F34:AF34)-AE34</f>
         <v/>
       </c>
-      <c r="AF35" s="409">
+      <c r="AF35" s="410">
         <f>MAX(F34:AF34)-AF34</f>
         <v/>
       </c>
@@ -16460,21 +16051,31 @@
       <c r="H37" s="243" t="n"/>
     </row>
     <row r="38" ht="12.75" customHeight="1" s="244">
+      <c r="B38" s="411" t="inlineStr">
+        <is>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): Z01-1 (38.1 °C), Z02-2 (37.8 °C), Z02-3 (37.8 °C), Z03-4 (37.8 °C), Z04-5 (37.8 °C), Z05-6 (37.8 °C), Z05-7 (37.8 °C), Z06-8 (32.0 °C) ...</t>
+        </is>
+      </c>
       <c r="H38" s="243" t="n"/>
     </row>
     <row r="39" ht="12.75" customHeight="1" s="244">
-      <c r="H39" s="410" t="n"/>
-      <c r="I39" s="410" t="n"/>
-      <c r="J39" s="410" t="n"/>
-      <c r="K39" s="410" t="n"/>
-      <c r="L39" s="410" t="n"/>
-      <c r="M39" s="410" t="n"/>
-      <c r="N39" s="410" t="n"/>
-      <c r="O39" s="410" t="n"/>
-      <c r="P39" s="410" t="n"/>
+      <c r="B39" s="412" t="inlineStr">
+        <is>
+          <t>Sınır içinde kalmak için q" ≤ 100 W/m² (oturma) gerekir; 35 W/m ile bu, boru aralığı ≈ 35 cm demektir. Boru aralığı 15 cm (kullanıcı seçimi) değiştirilmemiştir — ısı kaybı ile qh girilmelidir.</t>
+        </is>
+      </c>
+      <c r="H39" s="413" t="n"/>
+      <c r="I39" s="413" t="n"/>
+      <c r="J39" s="413" t="n"/>
+      <c r="K39" s="413" t="n"/>
+      <c r="L39" s="413" t="n"/>
+      <c r="M39" s="413" t="n"/>
+      <c r="N39" s="413" t="n"/>
+      <c r="O39" s="413" t="n"/>
+      <c r="P39" s="413" t="n"/>
     </row>
     <row r="40" ht="12.75" customHeight="1" s="244">
-      <c r="A40" s="411" t="inlineStr">
+      <c r="A40" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (1)</t>
         </is>
@@ -16484,18 +16085,18 @@
           <t>Şek. 19.7.1 den seçilmiştir.</t>
         </is>
       </c>
-      <c r="H40" s="410" t="n"/>
-      <c r="I40" s="410" t="n"/>
-      <c r="J40" s="410" t="n"/>
-      <c r="K40" s="410" t="n"/>
-      <c r="L40" s="410" t="n"/>
-      <c r="M40" s="410" t="n"/>
-      <c r="N40" s="410" t="n"/>
-      <c r="O40" s="410" t="n"/>
-      <c r="P40" s="410" t="n"/>
+      <c r="H40" s="413" t="n"/>
+      <c r="I40" s="413" t="n"/>
+      <c r="J40" s="413" t="n"/>
+      <c r="K40" s="413" t="n"/>
+      <c r="L40" s="413" t="n"/>
+      <c r="M40" s="413" t="n"/>
+      <c r="N40" s="413" t="n"/>
+      <c r="O40" s="413" t="n"/>
+      <c r="P40" s="413" t="n"/>
     </row>
     <row r="41" ht="12.75" customHeight="1" s="244">
-      <c r="A41" s="411" t="inlineStr">
+      <c r="A41" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (2)</t>
         </is>
@@ -16505,18 +16106,18 @@
           <t>Kombi gidiş suyu sıcaklığı 45 °C, dönüş 35 °C seçilmiştir.</t>
         </is>
       </c>
-      <c r="H41" s="410" t="n"/>
-      <c r="I41" s="410" t="n"/>
-      <c r="J41" s="410" t="n"/>
-      <c r="K41" s="410" t="n"/>
-      <c r="L41" s="410" t="n"/>
-      <c r="M41" s="410" t="n"/>
-      <c r="N41" s="410" t="n"/>
-      <c r="O41" s="410" t="n"/>
-      <c r="P41" s="410" t="n"/>
+      <c r="H41" s="413" t="n"/>
+      <c r="I41" s="413" t="n"/>
+      <c r="J41" s="413" t="n"/>
+      <c r="K41" s="413" t="n"/>
+      <c r="L41" s="413" t="n"/>
+      <c r="M41" s="413" t="n"/>
+      <c r="N41" s="413" t="n"/>
+      <c r="O41" s="413" t="n"/>
+      <c r="P41" s="413" t="n"/>
     </row>
     <row r="42" ht="12.75" customHeight="1" s="244">
-      <c r="A42" s="411" t="inlineStr">
+      <c r="A42" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (3)</t>
         </is>
@@ -16528,19 +16129,19 @@
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1" s="244">
-      <c r="A43" s="411" t="inlineStr">
+      <c r="A43" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (4)</t>
         </is>
       </c>
       <c r="B43" s="243" t="inlineStr">
         <is>
-          <t>Alta geçen ısı 0,2 q" olarak alınmıştır. qh = 17,5 W/m × devre boyu (şablon birim verimi); ısı kaybı hesabı ayrıca yapılmalıdır.</t>
+          <t>Alta geçen ısı 0,2 q" olarak alınmıştır. qh = 35 W/m × devre boyu (plan etiketi ve kolon şeması ile aynı esas); ayrı ısı kaybı hesabı yapılmamıştır.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1" s="244">
-      <c r="A44" s="411" t="inlineStr">
+      <c r="A44" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (5)</t>
         </is>
@@ -16552,7 +16153,7 @@
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1" s="244">
-      <c r="A45" s="411" t="inlineStr">
+      <c r="A45" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (6)</t>
         </is>
@@ -16564,7 +16165,7 @@
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1" s="244">
-      <c r="A46" s="411" t="inlineStr">
+      <c r="A46" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (7)</t>
         </is>
@@ -16576,7 +16177,7 @@
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1" s="244">
-      <c r="A47" s="412" t="n"/>
+      <c r="A47" s="415" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -16641,16 +16242,16 @@
       <c r="M1" s="264" t="n"/>
       <c r="N1" s="264" t="n"/>
       <c r="O1" s="264" t="n"/>
-      <c r="P1" s="413" t="n"/>
-      <c r="Q1" s="414" t="n"/>
-      <c r="R1" s="414" t="n"/>
-      <c r="S1" s="414" t="n"/>
-      <c r="T1" s="414" t="n"/>
-      <c r="U1" s="414" t="n"/>
-      <c r="V1" s="414" t="n"/>
-      <c r="W1" s="414" t="n"/>
-      <c r="X1" s="415" t="n"/>
-      <c r="Y1" s="415" t="n"/>
+      <c r="P1" s="416" t="n"/>
+      <c r="Q1" s="417" t="n"/>
+      <c r="R1" s="417" t="n"/>
+      <c r="S1" s="417" t="n"/>
+      <c r="T1" s="417" t="n"/>
+      <c r="U1" s="417" t="n"/>
+      <c r="V1" s="417" t="n"/>
+      <c r="W1" s="417" t="n"/>
+      <c r="X1" s="418" t="n"/>
+      <c r="Y1" s="418" t="n"/>
     </row>
     <row r="2" ht="12.75" customFormat="1" customHeight="1" s="329">
       <c r="A2" s="380" t="inlineStr">
@@ -16671,7 +16272,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 18220 W</t>
+          <t>TOPLAM ISI = 43868 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -16705,12 +16306,12 @@
       <c r="C3" s="337" t="n"/>
       <c r="D3" s="385" t="inlineStr">
         <is>
-          <t>Isıtma Çevrim Sayısı : 28</t>
+          <t>Isıtma Çevrim Sayısı : 27</t>
         </is>
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 4942 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 19058 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -16786,19 +16387,19 @@
       <c r="J5" s="260" t="n"/>
       <c r="K5" s="331" t="n"/>
       <c r="L5" s="331" t="n"/>
-      <c r="M5" s="416" t="n"/>
-      <c r="N5" s="416" t="n"/>
-      <c r="O5" s="417" t="n"/>
-      <c r="P5" s="417" t="n"/>
-      <c r="Q5" s="417" t="n"/>
-      <c r="R5" s="417" t="n"/>
-      <c r="S5" s="417" t="n"/>
-      <c r="T5" s="417" t="n"/>
-      <c r="U5" s="417" t="n"/>
-      <c r="V5" s="417" t="n"/>
-      <c r="W5" s="417" t="n"/>
-      <c r="X5" s="418" t="n"/>
-      <c r="Y5" s="418" t="n"/>
+      <c r="M5" s="419" t="n"/>
+      <c r="N5" s="419" t="n"/>
+      <c r="O5" s="420" t="n"/>
+      <c r="P5" s="420" t="n"/>
+      <c r="Q5" s="420" t="n"/>
+      <c r="R5" s="420" t="n"/>
+      <c r="S5" s="420" t="n"/>
+      <c r="T5" s="420" t="n"/>
+      <c r="U5" s="420" t="n"/>
+      <c r="V5" s="420" t="n"/>
+      <c r="W5" s="420" t="n"/>
+      <c r="X5" s="421" t="n"/>
+      <c r="Y5" s="421" t="n"/>
       <c r="Z5" s="355" t="n"/>
       <c r="AA5" s="355" t="n"/>
       <c r="AB5" s="355" t="n"/>
@@ -16909,9 +16510,7 @@
       <c r="AF7" s="392" t="n">
         <v>27</v>
       </c>
-      <c r="AG7" s="392" t="n">
-        <v>28</v>
-      </c>
+      <c r="AG7" s="391" t="n"/>
       <c r="AH7" s="391" t="n"/>
       <c r="AI7" s="391" t="n"/>
       <c r="AJ7" s="391" t="n"/>
@@ -17070,11 +16669,7 @@
           <t>121</t>
         </is>
       </c>
-      <c r="AG8" s="393" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
+      <c r="AG8" s="391" t="n"/>
       <c r="AH8" s="391" t="n"/>
       <c r="AI8" s="391" t="n"/>
       <c r="AJ8" s="391" t="n"/>
@@ -17085,12 +16680,12 @@
       <c r="AO8" s="391" t="n"/>
       <c r="AP8" s="391" t="n"/>
       <c r="AQ8" s="391" t="n"/>
-      <c r="AR8" s="419" t="n"/>
+      <c r="AR8" s="422" t="n"/>
       <c r="AS8" s="391" t="n"/>
       <c r="AT8" s="391" t="n"/>
       <c r="AU8" s="391" t="n"/>
       <c r="AV8" s="391" t="n"/>
-      <c r="AW8" s="419" t="n"/>
+      <c r="AW8" s="422" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1" s="244">
       <c r="A9" s="261" t="n"/>
@@ -17230,30 +16825,26 @@
       </c>
       <c r="AF9" s="395" t="inlineStr">
         <is>
-          <t>D6 wc-duş</t>
-        </is>
-      </c>
-      <c r="AG9" s="395" t="inlineStr">
-        <is>
           <t>D6 banyo</t>
         </is>
       </c>
-      <c r="AH9" s="420" t="n"/>
-      <c r="AI9" s="420" t="n"/>
+      <c r="AG9" s="423" t="n"/>
+      <c r="AH9" s="423" t="n"/>
+      <c r="AI9" s="423" t="n"/>
       <c r="AJ9" s="391" t="n"/>
       <c r="AK9" s="391" t="n"/>
       <c r="AL9" s="391" t="n"/>
       <c r="AM9" s="391" t="n"/>
       <c r="AN9" s="391" t="n"/>
-      <c r="AO9" s="421" t="n"/>
-      <c r="AP9" s="421" t="n"/>
-      <c r="AQ9" s="421" t="n"/>
-      <c r="AR9" s="422" t="n"/>
-      <c r="AS9" s="422" t="n"/>
-      <c r="AT9" s="421" t="n"/>
-      <c r="AU9" s="421" t="n"/>
-      <c r="AV9" s="421" t="n"/>
-      <c r="AW9" s="421" t="n"/>
+      <c r="AO9" s="424" t="n"/>
+      <c r="AP9" s="424" t="n"/>
+      <c r="AQ9" s="424" t="n"/>
+      <c r="AR9" s="425" t="n"/>
+      <c r="AS9" s="425" t="n"/>
+      <c r="AT9" s="424" t="n"/>
+      <c r="AU9" s="424" t="n"/>
+      <c r="AV9" s="424" t="n"/>
+      <c r="AW9" s="424" t="n"/>
     </row>
     <row r="10" ht="12" customHeight="1" s="244">
       <c r="A10" s="261" t="n"/>
@@ -17342,9 +16933,7 @@
       <c r="AF10" s="396" t="n">
         <v>24</v>
       </c>
-      <c r="AG10" s="396" t="n">
-        <v>24</v>
-      </c>
+      <c r="AG10" s="259" t="n"/>
       <c r="AH10" s="259" t="n"/>
       <c r="AI10" s="259" t="n"/>
       <c r="AJ10" s="259" t="n"/>
@@ -17449,9 +17038,7 @@
       <c r="AF11" s="396" t="n">
         <v>20</v>
       </c>
-      <c r="AG11" s="396" t="n">
-        <v>20</v>
-      </c>
+      <c r="AG11" s="259" t="n"/>
       <c r="AH11" s="259" t="n"/>
       <c r="AI11" s="259" t="n"/>
       <c r="AJ11" s="259" t="n"/>
@@ -17481,209 +17068,213 @@
         <v>7.87</v>
       </c>
       <c r="G12" s="397" t="n">
-        <v>7.86</v>
+        <v>7.21</v>
       </c>
       <c r="H12" s="397" t="n">
-        <v>5.62</v>
+        <v>7.94</v>
       </c>
       <c r="I12" s="397" t="n">
-        <v>8.74</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="J12" s="397" t="n">
-        <v>8.789999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="K12" s="397" t="n">
-        <v>10.62</v>
+        <v>9.83</v>
       </c>
       <c r="L12" s="397" t="n">
-        <v>9.51</v>
+        <v>10.3</v>
       </c>
       <c r="M12" s="397" t="n">
-        <v>7.61</v>
+        <v>7.66</v>
       </c>
       <c r="N12" s="397" t="n">
         <v>3.28</v>
       </c>
       <c r="O12" s="397" t="n">
-        <v>6.43</v>
+        <v>7.11</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>6.55</v>
+        <v>7.24</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>7.54</v>
+        <v>7.07</v>
       </c>
       <c r="R12" s="397" t="n">
-        <v>8.619999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S12" s="397" t="n">
-        <v>10.99</v>
+        <v>10.38</v>
       </c>
       <c r="T12" s="397" t="n">
-        <v>9.76</v>
+        <v>10.55</v>
       </c>
       <c r="U12" s="397" t="n">
         <v>7.29</v>
       </c>
       <c r="V12" s="397" t="n">
-        <v>10.21</v>
+        <v>10.3</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>7.83</v>
       </c>
       <c r="Y12" s="397" t="n">
-        <v>6.31</v>
+        <v>7.12</v>
       </c>
       <c r="Z12" s="397" t="n">
-        <v>7.31</v>
+        <v>6.5</v>
       </c>
       <c r="AA12" s="397" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AB12" s="397" t="n">
-        <v>8.84</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AC12" s="397" t="n">
-        <v>9.789999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="AD12" s="397" t="n">
-        <v>10.35</v>
+        <v>10.31</v>
       </c>
       <c r="AE12" s="397" t="n">
         <v>7.61</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AG12" s="397" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AH12" s="423" t="n"/>
-      <c r="AI12" s="423" t="n"/>
-      <c r="AJ12" s="423" t="n"/>
-      <c r="AK12" s="424" t="n"/>
-      <c r="AL12" s="424" t="n"/>
-      <c r="AM12" s="424" t="n"/>
-      <c r="AN12" s="423" t="n"/>
-      <c r="AO12" s="423" t="n"/>
-      <c r="AP12" s="423" t="n"/>
-      <c r="AQ12" s="423" t="n"/>
-      <c r="AR12" s="423" t="n"/>
-      <c r="AS12" s="423" t="n"/>
-      <c r="AT12" s="423" t="n"/>
-      <c r="AU12" s="423" t="n"/>
-      <c r="AV12" s="423" t="n"/>
-      <c r="AW12" s="423" t="n"/>
+        <v>2.61</v>
+      </c>
+      <c r="AG12" s="426" t="n"/>
+      <c r="AH12" s="426" t="n"/>
+      <c r="AI12" s="426" t="n"/>
+      <c r="AJ12" s="426" t="n"/>
+      <c r="AK12" s="427" t="n"/>
+      <c r="AL12" s="427" t="n"/>
+      <c r="AM12" s="427" t="n"/>
+      <c r="AN12" s="426" t="n"/>
+      <c r="AO12" s="426" t="n"/>
+      <c r="AP12" s="426" t="n"/>
+      <c r="AQ12" s="426" t="n"/>
+      <c r="AR12" s="426" t="n"/>
+      <c r="AS12" s="426" t="n"/>
+      <c r="AT12" s="426" t="n"/>
+      <c r="AU12" s="426" t="n"/>
+      <c r="AV12" s="426" t="n"/>
+      <c r="AW12" s="426" t="n"/>
     </row>
     <row r="13" ht="12" customHeight="1" s="244">
       <c r="A13" s="261" t="n"/>
       <c r="B13" s="282" t="n"/>
-      <c r="C13" s="394" t="n"/>
-      <c r="D13" s="261" t="n"/>
+      <c r="C13" s="394" t="inlineStr">
+        <is>
+          <t>DEVRE ISIL GÜCÜ</t>
+        </is>
+      </c>
+      <c r="D13" s="261" t="inlineStr">
+        <is>
+          <t>35 W/m × L (planla aynı)</t>
+        </is>
+      </c>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>847.7</v>
+        <v>1695.4</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>740.2</v>
+        <v>1460.2</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>528.9</v>
+        <v>1609.3</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>682.7</v>
+        <v>1850.8</v>
       </c>
       <c r="J13" s="398" t="n">
-        <v>741</v>
+        <v>1860.6</v>
       </c>
       <c r="K13" s="398" t="n">
-        <v>1034.2</v>
+        <v>2068.5</v>
       </c>
       <c r="L13" s="398" t="n">
-        <v>925.4</v>
+        <v>2167.2</v>
       </c>
       <c r="M13" s="398" t="n">
-        <v>760.9</v>
+        <v>1533</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>192.5</v>
+        <v>560.7</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>588.3</v>
+        <v>1341.2</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>490.9</v>
+        <v>1533</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>565.2</v>
+        <v>1498.7</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>752.3</v>
+        <v>1859.2</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>854</v>
+        <v>2132.2</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>759.2</v>
+        <v>2167.6</v>
       </c>
       <c r="U13" s="398" t="n">
-        <v>543.4</v>
+        <v>1614.9</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>788.7</v>
+        <v>2005.1</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>124.9</v>
+        <v>419.7</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>844.2</v>
+        <v>1688.4</v>
       </c>
       <c r="Y13" s="398" t="n">
-        <v>592.5</v>
+        <v>1505.3</v>
       </c>
       <c r="Z13" s="398" t="n">
-        <v>686.2</v>
+        <v>1372.4</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>710.7</v>
+        <v>1856.4</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>749.7</v>
+        <v>1872.8</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>876.2</v>
+        <v>2072.7</v>
       </c>
       <c r="AD13" s="398" t="n">
-        <v>926.8</v>
+        <v>2173.8</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>759.7</v>
+        <v>1522.5</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG13" s="398" t="n">
-        <v>124.8</v>
-      </c>
-      <c r="AH13" s="425" t="n"/>
-      <c r="AI13" s="425" t="n"/>
-      <c r="AJ13" s="425" t="n"/>
-      <c r="AK13" s="425" t="n"/>
-      <c r="AL13" s="425" t="n"/>
-      <c r="AM13" s="425" t="n"/>
-      <c r="AN13" s="425" t="n"/>
-      <c r="AO13" s="425" t="n"/>
-      <c r="AP13" s="425" t="n"/>
-      <c r="AQ13" s="425" t="n"/>
-      <c r="AR13" s="425" t="n"/>
-      <c r="AS13" s="425" t="n"/>
-      <c r="AT13" s="425" t="n"/>
-      <c r="AU13" s="425" t="n"/>
-      <c r="AV13" s="425" t="n"/>
-      <c r="AW13" s="425" t="n"/>
+        <v>425.9</v>
+      </c>
+      <c r="AG13" s="428" t="n"/>
+      <c r="AH13" s="428" t="n"/>
+      <c r="AI13" s="428" t="n"/>
+      <c r="AJ13" s="428" t="n"/>
+      <c r="AK13" s="428" t="n"/>
+      <c r="AL13" s="428" t="n"/>
+      <c r="AM13" s="428" t="n"/>
+      <c r="AN13" s="428" t="n"/>
+      <c r="AO13" s="428" t="n"/>
+      <c r="AP13" s="428" t="n"/>
+      <c r="AQ13" s="428" t="n"/>
+      <c r="AR13" s="428" t="n"/>
+      <c r="AS13" s="428" t="n"/>
+      <c r="AT13" s="428" t="n"/>
+      <c r="AU13" s="428" t="n"/>
+      <c r="AV13" s="428" t="n"/>
+      <c r="AW13" s="428" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1" s="244">
       <c r="A14" s="261" t="n"/>
@@ -17799,26 +17390,23 @@
         <f>AF13/AF12</f>
         <v/>
       </c>
-      <c r="AG14" s="399">
-        <f>AG13/AG12</f>
-        <v/>
-      </c>
-      <c r="AH14" s="426" t="n"/>
-      <c r="AI14" s="426" t="n"/>
-      <c r="AJ14" s="426" t="n"/>
-      <c r="AK14" s="426" t="n"/>
-      <c r="AL14" s="426" t="n"/>
-      <c r="AM14" s="426" t="n"/>
-      <c r="AN14" s="426" t="n"/>
-      <c r="AO14" s="426" t="n"/>
-      <c r="AP14" s="426" t="n"/>
-      <c r="AQ14" s="426" t="n"/>
-      <c r="AR14" s="426" t="n"/>
-      <c r="AS14" s="426" t="n"/>
-      <c r="AT14" s="426" t="n"/>
-      <c r="AU14" s="426" t="n"/>
-      <c r="AV14" s="426" t="n"/>
-      <c r="AW14" s="426" t="n"/>
+      <c r="AG14" s="429" t="n"/>
+      <c r="AH14" s="429" t="n"/>
+      <c r="AI14" s="429" t="n"/>
+      <c r="AJ14" s="429" t="n"/>
+      <c r="AK14" s="429" t="n"/>
+      <c r="AL14" s="429" t="n"/>
+      <c r="AM14" s="429" t="n"/>
+      <c r="AN14" s="429" t="n"/>
+      <c r="AO14" s="429" t="n"/>
+      <c r="AP14" s="429" t="n"/>
+      <c r="AQ14" s="429" t="n"/>
+      <c r="AR14" s="429" t="n"/>
+      <c r="AS14" s="429" t="n"/>
+      <c r="AT14" s="429" t="n"/>
+      <c r="AU14" s="429" t="n"/>
+      <c r="AV14" s="429" t="n"/>
+      <c r="AW14" s="429" t="n"/>
     </row>
     <row r="15" ht="12" customHeight="1" s="244">
       <c r="A15" s="261" t="n"/>
@@ -17907,9 +17495,7 @@
       <c r="AF15" s="396" t="n">
         <v>0.012</v>
       </c>
-      <c r="AG15" s="396" t="n">
-        <v>0.012</v>
-      </c>
+      <c r="AG15" s="259" t="n"/>
       <c r="AH15" s="259" t="n"/>
       <c r="AI15" s="259" t="n"/>
       <c r="AJ15" s="259" t="n"/>
@@ -18014,25 +17600,23 @@
       <c r="AF16" s="397" t="n">
         <v>1</v>
       </c>
-      <c r="AG16" s="397" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH16" s="423" t="n"/>
-      <c r="AI16" s="423" t="n"/>
-      <c r="AJ16" s="423" t="n"/>
-      <c r="AK16" s="423" t="n"/>
-      <c r="AL16" s="423" t="n"/>
-      <c r="AM16" s="423" t="n"/>
-      <c r="AN16" s="423" t="n"/>
-      <c r="AO16" s="423" t="n"/>
-      <c r="AP16" s="423" t="n"/>
-      <c r="AQ16" s="423" t="n"/>
-      <c r="AR16" s="423" t="n"/>
-      <c r="AS16" s="423" t="n"/>
-      <c r="AT16" s="423" t="n"/>
-      <c r="AU16" s="423" t="n"/>
-      <c r="AV16" s="423" t="n"/>
-      <c r="AW16" s="423" t="n"/>
+      <c r="AG16" s="426" t="n"/>
+      <c r="AH16" s="426" t="n"/>
+      <c r="AI16" s="426" t="n"/>
+      <c r="AJ16" s="426" t="n"/>
+      <c r="AK16" s="426" t="n"/>
+      <c r="AL16" s="426" t="n"/>
+      <c r="AM16" s="426" t="n"/>
+      <c r="AN16" s="426" t="n"/>
+      <c r="AO16" s="426" t="n"/>
+      <c r="AP16" s="426" t="n"/>
+      <c r="AQ16" s="426" t="n"/>
+      <c r="AR16" s="426" t="n"/>
+      <c r="AS16" s="426" t="n"/>
+      <c r="AT16" s="426" t="n"/>
+      <c r="AU16" s="426" t="n"/>
+      <c r="AV16" s="426" t="n"/>
+      <c r="AW16" s="426" t="n"/>
     </row>
     <row r="17" ht="12" customHeight="1" s="244">
       <c r="A17" s="261" t="n"/>
@@ -18148,10 +17732,7 @@
         <f>AF12</f>
         <v/>
       </c>
-      <c r="AG17" s="396">
-        <f>AG12</f>
-        <v/>
-      </c>
+      <c r="AG17" s="259" t="n"/>
       <c r="AH17" s="259" t="n"/>
       <c r="AI17" s="259" t="n"/>
       <c r="AJ17" s="259" t="n"/>
@@ -18283,26 +17864,23 @@
         <f>AF13/AF17</f>
         <v/>
       </c>
-      <c r="AG18" s="400">
-        <f>AG13/AG17</f>
-        <v/>
-      </c>
-      <c r="AH18" s="427" t="n"/>
-      <c r="AI18" s="427" t="n"/>
-      <c r="AJ18" s="427" t="n"/>
-      <c r="AK18" s="427" t="n"/>
-      <c r="AL18" s="427" t="n"/>
-      <c r="AM18" s="427" t="n"/>
-      <c r="AN18" s="427" t="n"/>
-      <c r="AO18" s="427" t="n"/>
-      <c r="AP18" s="427" t="n"/>
-      <c r="AQ18" s="427" t="n"/>
-      <c r="AR18" s="427" t="n"/>
-      <c r="AS18" s="427" t="n"/>
-      <c r="AT18" s="427" t="n"/>
-      <c r="AU18" s="427" t="n"/>
-      <c r="AV18" s="427" t="n"/>
-      <c r="AW18" s="427" t="n"/>
+      <c r="AG18" s="430" t="n"/>
+      <c r="AH18" s="430" t="n"/>
+      <c r="AI18" s="430" t="n"/>
+      <c r="AJ18" s="430" t="n"/>
+      <c r="AK18" s="430" t="n"/>
+      <c r="AL18" s="430" t="n"/>
+      <c r="AM18" s="430" t="n"/>
+      <c r="AN18" s="430" t="n"/>
+      <c r="AO18" s="430" t="n"/>
+      <c r="AP18" s="430" t="n"/>
+      <c r="AQ18" s="430" t="n"/>
+      <c r="AR18" s="430" t="n"/>
+      <c r="AS18" s="430" t="n"/>
+      <c r="AT18" s="430" t="n"/>
+      <c r="AU18" s="430" t="n"/>
+      <c r="AV18" s="430" t="n"/>
+      <c r="AW18" s="430" t="n"/>
     </row>
     <row r="19" ht="19.5" customHeight="1" s="244">
       <c r="A19" s="261" t="n"/>
@@ -18310,134 +17888,131 @@
       <c r="C19" s="394" t="n"/>
       <c r="D19" s="261" t="n"/>
       <c r="E19" s="259" t="n"/>
-      <c r="F19" s="400">
+      <c r="F19" s="401">
         <f>F10+(F14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="G19" s="400">
+      <c r="G19" s="401">
         <f>G10+(G14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="H19" s="400">
+      <c r="H19" s="401">
         <f>H10+(H14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="I19" s="400">
+      <c r="I19" s="401">
         <f>I10+(I14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="J19" s="400">
+      <c r="J19" s="401">
         <f>J10+(J14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="K19" s="400">
+      <c r="K19" s="401">
         <f>K10+(K14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="L19" s="400">
+      <c r="L19" s="401">
         <f>L10+(L14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="M19" s="400">
+      <c r="M19" s="401">
         <f>M10+(M14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="N19" s="400">
+      <c r="N19" s="401">
         <f>N10+(N14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="O19" s="400">
+      <c r="O19" s="401">
         <f>O10+(O14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="P19" s="400">
+      <c r="P19" s="401">
         <f>P10+(P14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="Q19" s="400">
+      <c r="Q19" s="401">
         <f>Q10+(Q14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="R19" s="400">
+      <c r="R19" s="401">
         <f>R10+(R14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="S19" s="400">
+      <c r="S19" s="401">
         <f>S10+(S14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="T19" s="400">
+      <c r="T19" s="401">
         <f>T10+(T14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="U19" s="400">
+      <c r="U19" s="401">
         <f>U10+(U14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="V19" s="400">
+      <c r="V19" s="401">
         <f>V10+(V14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="W19" s="400">
+      <c r="W19" s="401">
         <f>W10+(W14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="X19" s="400">
+      <c r="X19" s="401">
         <f>X10+(X14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="Y19" s="400">
+      <c r="Y19" s="401">
         <f>Y10+(Y14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="Z19" s="400">
+      <c r="Z19" s="401">
         <f>Z10+(Z14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AA19" s="400">
+      <c r="AA19" s="401">
         <f>AA10+(AA14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AB19" s="400">
+      <c r="AB19" s="401">
         <f>AB10+(AB14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AC19" s="400">
+      <c r="AC19" s="401">
         <f>AC10+(AC14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AD19" s="400">
+      <c r="AD19" s="401">
         <f>AD10+(AD14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AE19" s="400">
+      <c r="AE19" s="401">
         <f>AE10+(AE14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AF19" s="400">
+      <c r="AF19" s="401">
         <f>AF10+(AF14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AG19" s="400">
-        <f>AG10+(AG14/8.92)^0.91</f>
-        <v/>
-      </c>
-      <c r="AH19" s="427" t="n"/>
-      <c r="AI19" s="427" t="n"/>
-      <c r="AJ19" s="427" t="n"/>
-      <c r="AK19" s="427" t="n"/>
-      <c r="AL19" s="427" t="n"/>
-      <c r="AM19" s="427" t="n"/>
-      <c r="AN19" s="427" t="n"/>
-      <c r="AO19" s="427" t="n"/>
-      <c r="AP19" s="427" t="n"/>
-      <c r="AQ19" s="427" t="n"/>
-      <c r="AR19" s="427" t="n"/>
-      <c r="AS19" s="427" t="n"/>
-      <c r="AT19" s="427" t="n"/>
-      <c r="AU19" s="427" t="n"/>
-      <c r="AV19" s="427" t="n"/>
-      <c r="AW19" s="427" t="n"/>
+      <c r="AG19" s="430" t="n"/>
+      <c r="AH19" s="430" t="n"/>
+      <c r="AI19" s="430" t="n"/>
+      <c r="AJ19" s="430" t="n"/>
+      <c r="AK19" s="430" t="n"/>
+      <c r="AL19" s="430" t="n"/>
+      <c r="AM19" s="430" t="n"/>
+      <c r="AN19" s="430" t="n"/>
+      <c r="AO19" s="430" t="n"/>
+      <c r="AP19" s="430" t="n"/>
+      <c r="AQ19" s="430" t="n"/>
+      <c r="AR19" s="430" t="n"/>
+      <c r="AS19" s="430" t="n"/>
+      <c r="AT19" s="430" t="n"/>
+      <c r="AU19" s="430" t="n"/>
+      <c r="AV19" s="430" t="n"/>
+      <c r="AW19" s="430" t="n"/>
     </row>
     <row r="20" ht="12" customHeight="1" s="244">
       <c r="A20" s="261" t="n"/>
@@ -18526,9 +18101,7 @@
       <c r="AF20" s="396" t="n">
         <v>45</v>
       </c>
-      <c r="AG20" s="396" t="n">
-        <v>45</v>
-      </c>
+      <c r="AG20" s="259" t="n"/>
       <c r="AH20" s="259" t="n"/>
       <c r="AI20" s="259" t="n"/>
       <c r="AJ20" s="259" t="n"/>
@@ -18548,7 +18121,7 @@
     </row>
     <row r="21" ht="12" customHeight="1" s="244">
       <c r="A21" s="261" t="n"/>
-      <c r="B21" s="401" t="n"/>
+      <c r="B21" s="402" t="n"/>
       <c r="C21" s="394" t="n"/>
       <c r="D21" s="261" t="n"/>
       <c r="E21" s="259" t="n"/>
@@ -18660,10 +18233,7 @@
         <f>AF20-AF10</f>
         <v/>
       </c>
-      <c r="AG21" s="396">
-        <f>AG20-AG10</f>
-        <v/>
-      </c>
+      <c r="AG21" s="259" t="n"/>
       <c r="AH21" s="259" t="n"/>
       <c r="AI21" s="259" t="n"/>
       <c r="AJ21" s="259" t="n"/>
@@ -18683,7 +18253,7 @@
     </row>
     <row r="22" ht="12" customHeight="1" s="244">
       <c r="A22" s="261" t="n"/>
-      <c r="B22" s="402" t="n"/>
+      <c r="B22" s="403" t="n"/>
       <c r="C22" s="394" t="n"/>
       <c r="D22" s="261" t="n"/>
       <c r="E22" s="259" t="n"/>
@@ -18768,9 +18338,7 @@
       <c r="AF22" s="396" t="n">
         <v>15</v>
       </c>
-      <c r="AG22" s="396" t="n">
-        <v>15</v>
-      </c>
+      <c r="AG22" s="259" t="n"/>
       <c r="AH22" s="259" t="n"/>
       <c r="AI22" s="259" t="n"/>
       <c r="AJ22" s="259" t="n"/>
@@ -18790,114 +18358,112 @@
     </row>
     <row r="23" ht="12" customHeight="1" s="244">
       <c r="A23" s="261" t="n"/>
-      <c r="B23" s="402" t="n"/>
+      <c r="B23" s="403" t="n"/>
       <c r="C23" s="394" t="n"/>
       <c r="D23" s="261" t="n"/>
       <c r="E23" s="259" t="n"/>
-      <c r="F23" s="403" t="n">
+      <c r="F23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="G23" s="403" t="n">
+      <c r="G23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="H23" s="403" t="n">
+      <c r="H23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="I23" s="403" t="n">
+      <c r="I23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="J23" s="403" t="n">
+      <c r="J23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="K23" s="403" t="n">
+      <c r="K23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="L23" s="403" t="n">
+      <c r="L23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="M23" s="403" t="n">
+      <c r="M23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="N23" s="403" t="n">
+      <c r="N23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="O23" s="403" t="n">
+      <c r="O23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="P23" s="403" t="n">
+      <c r="P23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="Q23" s="403" t="n">
+      <c r="Q23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="R23" s="403" t="n">
+      <c r="R23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="S23" s="403" t="n">
+      <c r="S23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="T23" s="403" t="n">
+      <c r="T23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="U23" s="403" t="n">
+      <c r="U23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="V23" s="403" t="n">
+      <c r="V23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="W23" s="403" t="n">
+      <c r="W23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="X23" s="403" t="n">
+      <c r="X23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="Y23" s="403" t="n">
+      <c r="Y23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="Z23" s="403" t="n">
+      <c r="Z23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AA23" s="403" t="n">
+      <c r="AA23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AB23" s="403" t="n">
+      <c r="AB23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AC23" s="403" t="n">
+      <c r="AC23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AD23" s="403" t="n">
+      <c r="AD23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AE23" s="403" t="n">
+      <c r="AE23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AF23" s="403" t="n">
+      <c r="AF23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AG23" s="403" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH23" s="428" t="n"/>
-      <c r="AI23" s="428" t="n"/>
-      <c r="AJ23" s="428" t="n"/>
-      <c r="AK23" s="428" t="n"/>
-      <c r="AL23" s="428" t="n"/>
-      <c r="AM23" s="428" t="n"/>
-      <c r="AN23" s="428" t="n"/>
-      <c r="AO23" s="428" t="n"/>
-      <c r="AP23" s="428" t="n"/>
-      <c r="AQ23" s="428" t="n"/>
-      <c r="AR23" s="428" t="n"/>
-      <c r="AS23" s="428" t="n"/>
-      <c r="AT23" s="428" t="n"/>
-      <c r="AU23" s="428" t="n"/>
-      <c r="AV23" s="428" t="n"/>
-      <c r="AW23" s="428" t="n"/>
+      <c r="AG23" s="431" t="n"/>
+      <c r="AH23" s="431" t="n"/>
+      <c r="AI23" s="431" t="n"/>
+      <c r="AJ23" s="431" t="n"/>
+      <c r="AK23" s="431" t="n"/>
+      <c r="AL23" s="431" t="n"/>
+      <c r="AM23" s="431" t="n"/>
+      <c r="AN23" s="431" t="n"/>
+      <c r="AO23" s="431" t="n"/>
+      <c r="AP23" s="431" t="n"/>
+      <c r="AQ23" s="431" t="n"/>
+      <c r="AR23" s="431" t="n"/>
+      <c r="AS23" s="431" t="n"/>
+      <c r="AT23" s="431" t="n"/>
+      <c r="AU23" s="431" t="n"/>
+      <c r="AV23" s="431" t="n"/>
+      <c r="AW23" s="431" t="n"/>
     </row>
     <row r="24" ht="12" customHeight="1" s="244">
       <c r="A24" s="261" t="n"/>
-      <c r="B24" s="401" t="n"/>
+      <c r="B24" s="402" t="n"/>
       <c r="C24" s="394" t="n"/>
       <c r="D24" s="261" t="n"/>
       <c r="E24" s="259" t="n"/>
@@ -19009,10 +18575,7 @@
         <f>AF23-AF10</f>
         <v/>
       </c>
-      <c r="AG24" s="396">
-        <f>AG23-AG10</f>
-        <v/>
-      </c>
+      <c r="AG24" s="259" t="n"/>
       <c r="AH24" s="259" t="n"/>
       <c r="AI24" s="259" t="n"/>
       <c r="AJ24" s="259" t="n"/>
@@ -19032,7 +18595,7 @@
     </row>
     <row r="25" ht="12" customHeight="1" s="244">
       <c r="A25" s="261" t="n"/>
-      <c r="B25" s="401" t="n"/>
+      <c r="B25" s="402" t="n"/>
       <c r="C25" s="394" t="n"/>
       <c r="D25" s="261" t="n"/>
       <c r="E25" s="259" t="n"/>
@@ -19144,10 +18707,7 @@
         <f>2*(AF21-AF24)</f>
         <v/>
       </c>
-      <c r="AG25" s="396">
-        <f>2*(AG21-AG24)</f>
-        <v/>
-      </c>
+      <c r="AG25" s="259" t="n"/>
       <c r="AH25" s="259" t="n"/>
       <c r="AI25" s="259" t="n"/>
       <c r="AJ25" s="259" t="n"/>
@@ -19167,9 +18727,9 @@
     </row>
     <row r="26" ht="12" customHeight="1" s="244">
       <c r="A26" s="261" t="n"/>
-      <c r="B26" s="402" t="n"/>
+      <c r="B26" s="403" t="n"/>
       <c r="C26" s="394" t="n"/>
-      <c r="D26" s="404" t="n"/>
+      <c r="D26" s="405" t="n"/>
       <c r="E26" s="259" t="n"/>
       <c r="F26" s="400">
         <f>0.2*F14</f>
@@ -19279,435 +18839,423 @@
         <f>0.2*AF14</f>
         <v/>
       </c>
-      <c r="AG26" s="400">
-        <f>0.2*AG14</f>
-        <v/>
-      </c>
-      <c r="AH26" s="427" t="n"/>
-      <c r="AI26" s="427" t="n"/>
-      <c r="AJ26" s="427" t="n"/>
-      <c r="AK26" s="427" t="n"/>
-      <c r="AL26" s="427" t="n"/>
-      <c r="AM26" s="427" t="n"/>
-      <c r="AN26" s="427" t="n"/>
-      <c r="AO26" s="427" t="n"/>
-      <c r="AP26" s="427" t="n"/>
-      <c r="AQ26" s="427" t="n"/>
-      <c r="AR26" s="427" t="n"/>
-      <c r="AS26" s="427" t="n"/>
-      <c r="AT26" s="427" t="n"/>
-      <c r="AU26" s="427" t="n"/>
-      <c r="AV26" s="427" t="n"/>
-      <c r="AW26" s="427" t="n"/>
+      <c r="AG26" s="430" t="n"/>
+      <c r="AH26" s="430" t="n"/>
+      <c r="AI26" s="430" t="n"/>
+      <c r="AJ26" s="430" t="n"/>
+      <c r="AK26" s="430" t="n"/>
+      <c r="AL26" s="430" t="n"/>
+      <c r="AM26" s="430" t="n"/>
+      <c r="AN26" s="430" t="n"/>
+      <c r="AO26" s="430" t="n"/>
+      <c r="AP26" s="430" t="n"/>
+      <c r="AQ26" s="430" t="n"/>
+      <c r="AR26" s="430" t="n"/>
+      <c r="AS26" s="430" t="n"/>
+      <c r="AT26" s="430" t="n"/>
+      <c r="AU26" s="430" t="n"/>
+      <c r="AV26" s="430" t="n"/>
+      <c r="AW26" s="430" t="n"/>
     </row>
     <row r="27" ht="12" customHeight="1" s="244">
       <c r="A27" s="261" t="n"/>
-      <c r="B27" s="402" t="n"/>
+      <c r="B27" s="403" t="n"/>
       <c r="C27" s="394" t="n"/>
       <c r="D27" s="261" t="n"/>
       <c r="E27" s="259" t="n"/>
-      <c r="F27" s="405">
+      <c r="F27" s="406">
         <f>F17*(F14+F26)</f>
         <v/>
       </c>
-      <c r="G27" s="405">
+      <c r="G27" s="406">
         <f>G17*(G14+G26)</f>
         <v/>
       </c>
-      <c r="H27" s="405">
+      <c r="H27" s="406">
         <f>H17*(H14+H26)</f>
         <v/>
       </c>
-      <c r="I27" s="405">
+      <c r="I27" s="406">
         <f>I17*(I14+I26)</f>
         <v/>
       </c>
-      <c r="J27" s="405">
+      <c r="J27" s="406">
         <f>J17*(J14+J26)</f>
         <v/>
       </c>
-      <c r="K27" s="405">
+      <c r="K27" s="406">
         <f>K17*(K14+K26)</f>
         <v/>
       </c>
-      <c r="L27" s="405">
+      <c r="L27" s="406">
         <f>L17*(L14+L26)</f>
         <v/>
       </c>
-      <c r="M27" s="405">
+      <c r="M27" s="406">
         <f>M17*(M14+M26)</f>
         <v/>
       </c>
-      <c r="N27" s="405">
+      <c r="N27" s="406">
         <f>N17*(N14+N26)</f>
         <v/>
       </c>
-      <c r="O27" s="405">
+      <c r="O27" s="406">
         <f>O17*(O14+O26)</f>
         <v/>
       </c>
-      <c r="P27" s="405">
+      <c r="P27" s="406">
         <f>P17*(P14+P26)</f>
         <v/>
       </c>
-      <c r="Q27" s="405">
+      <c r="Q27" s="406">
         <f>Q17*(Q14+Q26)</f>
         <v/>
       </c>
-      <c r="R27" s="405">
+      <c r="R27" s="406">
         <f>R17*(R14+R26)</f>
         <v/>
       </c>
-      <c r="S27" s="405">
+      <c r="S27" s="406">
         <f>S17*(S14+S26)</f>
         <v/>
       </c>
-      <c r="T27" s="405">
+      <c r="T27" s="406">
         <f>T17*(T14+T26)</f>
         <v/>
       </c>
-      <c r="U27" s="405">
+      <c r="U27" s="406">
         <f>U17*(U14+U26)</f>
         <v/>
       </c>
-      <c r="V27" s="405">
+      <c r="V27" s="406">
         <f>V17*(V14+V26)</f>
         <v/>
       </c>
-      <c r="W27" s="405">
+      <c r="W27" s="406">
         <f>W17*(W14+W26)</f>
         <v/>
       </c>
-      <c r="X27" s="405">
+      <c r="X27" s="406">
         <f>X17*(X14+X26)</f>
         <v/>
       </c>
-      <c r="Y27" s="405">
+      <c r="Y27" s="406">
         <f>Y17*(Y14+Y26)</f>
         <v/>
       </c>
-      <c r="Z27" s="405">
+      <c r="Z27" s="406">
         <f>Z17*(Z14+Z26)</f>
         <v/>
       </c>
-      <c r="AA27" s="405">
+      <c r="AA27" s="406">
         <f>AA17*(AA14+AA26)</f>
         <v/>
       </c>
-      <c r="AB27" s="405">
+      <c r="AB27" s="406">
         <f>AB17*(AB14+AB26)</f>
         <v/>
       </c>
-      <c r="AC27" s="405">
+      <c r="AC27" s="406">
         <f>AC17*(AC14+AC26)</f>
         <v/>
       </c>
-      <c r="AD27" s="405">
+      <c r="AD27" s="406">
         <f>AD17*(AD14+AD26)</f>
         <v/>
       </c>
-      <c r="AE27" s="405">
+      <c r="AE27" s="406">
         <f>AE17*(AE14+AE26)</f>
         <v/>
       </c>
-      <c r="AF27" s="405">
+      <c r="AF27" s="406">
         <f>AF17*(AF14+AF26)</f>
         <v/>
       </c>
-      <c r="AG27" s="405">
-        <f>AG17*(AG14+AG26)</f>
-        <v/>
-      </c>
-      <c r="AH27" s="429" t="n"/>
-      <c r="AI27" s="429" t="n"/>
-      <c r="AJ27" s="429" t="n"/>
-      <c r="AK27" s="429" t="n"/>
-      <c r="AL27" s="429" t="n"/>
-      <c r="AM27" s="429" t="n"/>
-      <c r="AN27" s="429" t="n"/>
-      <c r="AO27" s="429" t="n"/>
-      <c r="AP27" s="429" t="n"/>
-      <c r="AQ27" s="429" t="n"/>
-      <c r="AR27" s="429" t="n"/>
-      <c r="AS27" s="429" t="n"/>
-      <c r="AT27" s="429" t="n"/>
-      <c r="AU27" s="429" t="n"/>
-      <c r="AV27" s="429" t="n"/>
-      <c r="AW27" s="429" t="n"/>
+      <c r="AG27" s="432" t="n"/>
+      <c r="AH27" s="432" t="n"/>
+      <c r="AI27" s="432" t="n"/>
+      <c r="AJ27" s="432" t="n"/>
+      <c r="AK27" s="432" t="n"/>
+      <c r="AL27" s="432" t="n"/>
+      <c r="AM27" s="432" t="n"/>
+      <c r="AN27" s="432" t="n"/>
+      <c r="AO27" s="432" t="n"/>
+      <c r="AP27" s="432" t="n"/>
+      <c r="AQ27" s="432" t="n"/>
+      <c r="AR27" s="432" t="n"/>
+      <c r="AS27" s="432" t="n"/>
+      <c r="AT27" s="432" t="n"/>
+      <c r="AU27" s="432" t="n"/>
+      <c r="AV27" s="432" t="n"/>
+      <c r="AW27" s="432" t="n"/>
     </row>
     <row r="28" ht="12" customHeight="1" s="244">
       <c r="A28" s="261" t="n"/>
-      <c r="B28" s="402" t="n"/>
+      <c r="B28" s="403" t="n"/>
       <c r="C28" s="394" t="n"/>
       <c r="D28" s="261" t="n"/>
       <c r="E28" s="259" t="n"/>
-      <c r="F28" s="406">
+      <c r="F28" s="407">
         <f>F27/(1.163*F25)</f>
         <v/>
       </c>
-      <c r="G28" s="406">
+      <c r="G28" s="407">
         <f>G27/(1.163*G25)</f>
         <v/>
       </c>
-      <c r="H28" s="406">
+      <c r="H28" s="407">
         <f>H27/(1.163*H25)</f>
         <v/>
       </c>
-      <c r="I28" s="406">
+      <c r="I28" s="407">
         <f>I27/(1.163*I25)</f>
         <v/>
       </c>
-      <c r="J28" s="406">
+      <c r="J28" s="407">
         <f>J27/(1.163*J25)</f>
         <v/>
       </c>
-      <c r="K28" s="406">
+      <c r="K28" s="407">
         <f>K27/(1.163*K25)</f>
         <v/>
       </c>
-      <c r="L28" s="406">
+      <c r="L28" s="407">
         <f>L27/(1.163*L25)</f>
         <v/>
       </c>
-      <c r="M28" s="406">
+      <c r="M28" s="407">
         <f>M27/(1.163*M25)</f>
         <v/>
       </c>
-      <c r="N28" s="406">
+      <c r="N28" s="407">
         <f>N27/(1.163*N25)</f>
         <v/>
       </c>
-      <c r="O28" s="406">
+      <c r="O28" s="407">
         <f>O27/(1.163*O25)</f>
         <v/>
       </c>
-      <c r="P28" s="406">
+      <c r="P28" s="407">
         <f>P27/(1.163*P25)</f>
         <v/>
       </c>
-      <c r="Q28" s="406">
+      <c r="Q28" s="407">
         <f>Q27/(1.163*Q25)</f>
         <v/>
       </c>
-      <c r="R28" s="406">
+      <c r="R28" s="407">
         <f>R27/(1.163*R25)</f>
         <v/>
       </c>
-      <c r="S28" s="406">
+      <c r="S28" s="407">
         <f>S27/(1.163*S25)</f>
         <v/>
       </c>
-      <c r="T28" s="406">
+      <c r="T28" s="407">
         <f>T27/(1.163*T25)</f>
         <v/>
       </c>
-      <c r="U28" s="406">
+      <c r="U28" s="407">
         <f>U27/(1.163*U25)</f>
         <v/>
       </c>
-      <c r="V28" s="406">
+      <c r="V28" s="407">
         <f>V27/(1.163*V25)</f>
         <v/>
       </c>
-      <c r="W28" s="406">
+      <c r="W28" s="407">
         <f>W27/(1.163*W25)</f>
         <v/>
       </c>
-      <c r="X28" s="406">
+      <c r="X28" s="407">
         <f>X27/(1.163*X25)</f>
         <v/>
       </c>
-      <c r="Y28" s="406">
+      <c r="Y28" s="407">
         <f>Y27/(1.163*Y25)</f>
         <v/>
       </c>
-      <c r="Z28" s="406">
+      <c r="Z28" s="407">
         <f>Z27/(1.163*Z25)</f>
         <v/>
       </c>
-      <c r="AA28" s="406">
+      <c r="AA28" s="407">
         <f>AA27/(1.163*AA25)</f>
         <v/>
       </c>
-      <c r="AB28" s="406">
+      <c r="AB28" s="407">
         <f>AB27/(1.163*AB25)</f>
         <v/>
       </c>
-      <c r="AC28" s="406">
+      <c r="AC28" s="407">
         <f>AC27/(1.163*AC25)</f>
         <v/>
       </c>
-      <c r="AD28" s="406">
+      <c r="AD28" s="407">
         <f>AD27/(1.163*AD25)</f>
         <v/>
       </c>
-      <c r="AE28" s="406">
+      <c r="AE28" s="407">
         <f>AE27/(1.163*AE25)</f>
         <v/>
       </c>
-      <c r="AF28" s="406">
+      <c r="AF28" s="407">
         <f>AF27/(1.163*AF25)</f>
         <v/>
       </c>
-      <c r="AG28" s="406">
-        <f>AG27/(1.163*AG25)</f>
-        <v/>
-      </c>
-      <c r="AH28" s="430" t="n"/>
-      <c r="AI28" s="430" t="n"/>
-      <c r="AJ28" s="430" t="n"/>
-      <c r="AK28" s="430" t="n"/>
-      <c r="AL28" s="430" t="n"/>
-      <c r="AM28" s="430" t="n"/>
-      <c r="AN28" s="430" t="n"/>
-      <c r="AO28" s="430" t="n"/>
-      <c r="AP28" s="430" t="n"/>
-      <c r="AQ28" s="430" t="n"/>
-      <c r="AR28" s="430" t="n"/>
-      <c r="AS28" s="430" t="n"/>
-      <c r="AT28" s="430" t="n"/>
-      <c r="AU28" s="430" t="n"/>
-      <c r="AV28" s="430" t="n"/>
-      <c r="AW28" s="430" t="n"/>
+      <c r="AG28" s="433" t="n"/>
+      <c r="AH28" s="433" t="n"/>
+      <c r="AI28" s="433" t="n"/>
+      <c r="AJ28" s="433" t="n"/>
+      <c r="AK28" s="433" t="n"/>
+      <c r="AL28" s="433" t="n"/>
+      <c r="AM28" s="433" t="n"/>
+      <c r="AN28" s="433" t="n"/>
+      <c r="AO28" s="433" t="n"/>
+      <c r="AP28" s="433" t="n"/>
+      <c r="AQ28" s="433" t="n"/>
+      <c r="AR28" s="433" t="n"/>
+      <c r="AS28" s="433" t="n"/>
+      <c r="AT28" s="433" t="n"/>
+      <c r="AU28" s="433" t="n"/>
+      <c r="AV28" s="433" t="n"/>
+      <c r="AW28" s="433" t="n"/>
     </row>
     <row r="29" ht="12" customHeight="1" s="244">
       <c r="A29" s="261" t="n"/>
-      <c r="B29" s="402" t="n"/>
+      <c r="B29" s="403" t="n"/>
       <c r="C29" s="394" t="n"/>
       <c r="D29" s="261" t="n"/>
       <c r="E29" s="259" t="n"/>
-      <c r="F29" s="407">
+      <c r="F29" s="408">
         <f>F17/(F22*0.01)</f>
         <v/>
       </c>
-      <c r="G29" s="407">
+      <c r="G29" s="408">
         <f>G17/(G22*0.01)</f>
         <v/>
       </c>
-      <c r="H29" s="407">
+      <c r="H29" s="408">
         <f>H17/(H22*0.01)</f>
         <v/>
       </c>
-      <c r="I29" s="407">
+      <c r="I29" s="408">
         <f>I17/(I22*0.01)</f>
         <v/>
       </c>
-      <c r="J29" s="407">
+      <c r="J29" s="408">
         <f>J17/(J22*0.01)</f>
         <v/>
       </c>
-      <c r="K29" s="407">
+      <c r="K29" s="408">
         <f>K17/(K22*0.01)</f>
         <v/>
       </c>
-      <c r="L29" s="407">
+      <c r="L29" s="408">
         <f>L17/(L22*0.01)</f>
         <v/>
       </c>
-      <c r="M29" s="407">
+      <c r="M29" s="408">
         <f>M17/(M22*0.01)</f>
         <v/>
       </c>
-      <c r="N29" s="407">
+      <c r="N29" s="408">
         <f>N17/(N22*0.01)</f>
         <v/>
       </c>
-      <c r="O29" s="407">
+      <c r="O29" s="408">
         <f>O17/(O22*0.01)</f>
         <v/>
       </c>
-      <c r="P29" s="407">
+      <c r="P29" s="408">
         <f>P17/(P22*0.01)</f>
         <v/>
       </c>
-      <c r="Q29" s="407">
+      <c r="Q29" s="408">
         <f>Q17/(Q22*0.01)</f>
         <v/>
       </c>
-      <c r="R29" s="407">
+      <c r="R29" s="408">
         <f>R17/(R22*0.01)</f>
         <v/>
       </c>
-      <c r="S29" s="407">
+      <c r="S29" s="408">
         <f>S17/(S22*0.01)</f>
         <v/>
       </c>
-      <c r="T29" s="407">
+      <c r="T29" s="408">
         <f>T17/(T22*0.01)</f>
         <v/>
       </c>
-      <c r="U29" s="407">
+      <c r="U29" s="408">
         <f>U17/(U22*0.01)</f>
         <v/>
       </c>
-      <c r="V29" s="407">
+      <c r="V29" s="408">
         <f>V17/(V22*0.01)</f>
         <v/>
       </c>
-      <c r="W29" s="407">
+      <c r="W29" s="408">
         <f>W17/(W22*0.01)</f>
         <v/>
       </c>
-      <c r="X29" s="407">
+      <c r="X29" s="408">
         <f>X17/(X22*0.01)</f>
         <v/>
       </c>
-      <c r="Y29" s="407">
+      <c r="Y29" s="408">
         <f>Y17/(Y22*0.01)</f>
         <v/>
       </c>
-      <c r="Z29" s="407">
+      <c r="Z29" s="408">
         <f>Z17/(Z22*0.01)</f>
         <v/>
       </c>
-      <c r="AA29" s="407">
+      <c r="AA29" s="408">
         <f>AA17/(AA22*0.01)</f>
         <v/>
       </c>
-      <c r="AB29" s="407">
+      <c r="AB29" s="408">
         <f>AB17/(AB22*0.01)</f>
         <v/>
       </c>
-      <c r="AC29" s="407">
+      <c r="AC29" s="408">
         <f>AC17/(AC22*0.01)</f>
         <v/>
       </c>
-      <c r="AD29" s="407">
+      <c r="AD29" s="408">
         <f>AD17/(AD22*0.01)</f>
         <v/>
       </c>
-      <c r="AE29" s="407">
+      <c r="AE29" s="408">
         <f>AE17/(AE22*0.01)</f>
         <v/>
       </c>
-      <c r="AF29" s="407">
+      <c r="AF29" s="408">
         <f>AF17/(AF22*0.01)</f>
         <v/>
       </c>
-      <c r="AG29" s="407">
-        <f>AG17/(AG22*0.01)</f>
-        <v/>
-      </c>
-      <c r="AH29" s="431" t="n"/>
-      <c r="AI29" s="431" t="n"/>
-      <c r="AJ29" s="431" t="n"/>
-      <c r="AK29" s="431" t="n"/>
-      <c r="AL29" s="431" t="n"/>
-      <c r="AM29" s="431" t="n"/>
-      <c r="AN29" s="431" t="n"/>
-      <c r="AO29" s="431" t="n"/>
-      <c r="AP29" s="431" t="n"/>
-      <c r="AQ29" s="431" t="n"/>
-      <c r="AR29" s="431" t="n"/>
-      <c r="AS29" s="431" t="n"/>
-      <c r="AT29" s="431" t="n"/>
-      <c r="AU29" s="431" t="n"/>
-      <c r="AV29" s="431" t="n"/>
-      <c r="AW29" s="431" t="n"/>
+      <c r="AG29" s="434" t="n"/>
+      <c r="AH29" s="434" t="n"/>
+      <c r="AI29" s="434" t="n"/>
+      <c r="AJ29" s="434" t="n"/>
+      <c r="AK29" s="434" t="n"/>
+      <c r="AL29" s="434" t="n"/>
+      <c r="AM29" s="434" t="n"/>
+      <c r="AN29" s="434" t="n"/>
+      <c r="AO29" s="434" t="n"/>
+      <c r="AP29" s="434" t="n"/>
+      <c r="AQ29" s="434" t="n"/>
+      <c r="AR29" s="434" t="n"/>
+      <c r="AS29" s="434" t="n"/>
+      <c r="AT29" s="434" t="n"/>
+      <c r="AU29" s="434" t="n"/>
+      <c r="AV29" s="434" t="n"/>
+      <c r="AW29" s="434" t="n"/>
     </row>
     <row r="30" ht="12" customHeight="1" s="244">
       <c r="A30" s="261" t="n"/>
-      <c r="B30" s="402" t="n"/>
+      <c r="B30" s="403" t="n"/>
       <c r="C30" s="394" t="inlineStr">
         <is>
           <t>BAĞLANTI BORULARI</t>
@@ -19719,103 +19267,101 @@
         </is>
       </c>
       <c r="E30" s="259" t="n"/>
-      <c r="F30" s="408" t="n">
+      <c r="F30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="408" t="n">
+      <c r="G30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="408" t="n">
+      <c r="H30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="408" t="n">
+      <c r="I30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="408" t="n">
+      <c r="J30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="408" t="n">
+      <c r="K30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="408" t="n">
+      <c r="L30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="408" t="n">
+      <c r="M30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="408" t="n">
+      <c r="N30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="408" t="n">
+      <c r="O30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="408" t="n">
+      <c r="P30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="408" t="n">
+      <c r="Q30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="R30" s="408" t="n">
+      <c r="R30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="408" t="n">
+      <c r="S30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="408" t="n">
+      <c r="T30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="408" t="n">
+      <c r="U30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="408" t="n">
+      <c r="V30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="408" t="n">
+      <c r="W30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="X30" s="408" t="n">
+      <c r="X30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="Y30" s="408" t="n">
+      <c r="Y30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="408" t="n">
+      <c r="Z30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AA30" s="408" t="n">
+      <c r="AA30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AB30" s="408" t="n">
+      <c r="AB30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" s="408" t="n">
+      <c r="AC30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="408" t="n">
+      <c r="AD30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AE30" s="408" t="n">
+      <c r="AE30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AF30" s="408" t="n">
+      <c r="AF30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AG30" s="408" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="432" t="n"/>
-      <c r="AP30" s="432" t="n"/>
-      <c r="AQ30" s="432" t="n"/>
-      <c r="AR30" s="432" t="n"/>
-      <c r="AS30" s="432" t="n"/>
-      <c r="AT30" s="432" t="n"/>
-      <c r="AU30" s="432" t="n"/>
-      <c r="AV30" s="432" t="n"/>
-      <c r="AW30" s="432" t="n"/>
+      <c r="AG30" s="435" t="n"/>
+      <c r="AO30" s="435" t="n"/>
+      <c r="AP30" s="435" t="n"/>
+      <c r="AQ30" s="435" t="n"/>
+      <c r="AR30" s="435" t="n"/>
+      <c r="AS30" s="435" t="n"/>
+      <c r="AT30" s="435" t="n"/>
+      <c r="AU30" s="435" t="n"/>
+      <c r="AV30" s="435" t="n"/>
+      <c r="AW30" s="435" t="n"/>
     </row>
     <row r="31" ht="12" customHeight="1" s="244">
       <c r="A31" s="261" t="n"/>
-      <c r="B31" s="402" t="n"/>
+      <c r="B31" s="403" t="n"/>
       <c r="C31" s="394" t="n"/>
       <c r="D31" s="261" t="n"/>
       <c r="E31" s="259" t="n"/>
@@ -19927,10 +19473,7 @@
         <f>AF29+AF30</f>
         <v/>
       </c>
-      <c r="AG31" s="396">
-        <f>AG29+AG30</f>
-        <v/>
-      </c>
+      <c r="AG31" s="259" t="n"/>
       <c r="AH31" s="259" t="n"/>
       <c r="AI31" s="259" t="n"/>
       <c r="AJ31" s="259" t="n"/>
@@ -19950,7 +19493,7 @@
     </row>
     <row r="32" ht="12" customHeight="1" s="244">
       <c r="A32" s="261" t="n"/>
-      <c r="B32" s="401" t="n"/>
+      <c r="B32" s="402" t="n"/>
       <c r="C32" s="394" t="inlineStr">
         <is>
           <t>DÜZ BORU BASINÇ KAYBI (5)</t>
@@ -19962,110 +19505,108 @@
         </is>
       </c>
       <c r="E32" s="259" t="n"/>
-      <c r="F32" s="407" t="n">
-        <v>2724</v>
-      </c>
-      <c r="G32" s="407" t="n">
-        <v>1876</v>
-      </c>
-      <c r="H32" s="407" t="n">
-        <v>494</v>
-      </c>
-      <c r="I32" s="407" t="n">
-        <v>1502</v>
-      </c>
-      <c r="J32" s="407" t="n">
-        <v>1881</v>
-      </c>
-      <c r="K32" s="407" t="n">
-        <v>4707</v>
-      </c>
-      <c r="L32" s="407" t="n">
-        <v>3467</v>
-      </c>
-      <c r="M32" s="407" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N32" s="407" t="n">
-        <v>65</v>
-      </c>
-      <c r="O32" s="407" t="n">
-        <v>611</v>
-      </c>
-      <c r="P32" s="407" t="n">
-        <v>425</v>
-      </c>
-      <c r="Q32" s="407" t="n">
-        <v>564</v>
-      </c>
-      <c r="R32" s="407" t="n">
-        <v>1962</v>
-      </c>
-      <c r="S32" s="407" t="n">
-        <v>2780</v>
-      </c>
-      <c r="T32" s="407" t="n">
-        <v>2011</v>
-      </c>
-      <c r="U32" s="407" t="n">
-        <v>521</v>
-      </c>
-      <c r="V32" s="407" t="n">
-        <v>2234</v>
-      </c>
-      <c r="W32" s="407" t="n">
-        <v>28</v>
-      </c>
-      <c r="X32" s="407" t="n">
-        <v>2693</v>
-      </c>
-      <c r="Y32" s="407" t="n">
-        <v>1017</v>
-      </c>
-      <c r="Z32" s="407" t="n">
-        <v>1523</v>
-      </c>
-      <c r="AA32" s="407" t="n">
-        <v>1677</v>
-      </c>
-      <c r="AB32" s="407" t="n">
-        <v>1943</v>
-      </c>
-      <c r="AC32" s="407" t="n">
-        <v>2983</v>
-      </c>
-      <c r="AD32" s="407" t="n">
-        <v>3481</v>
-      </c>
-      <c r="AE32" s="407" t="n">
-        <v>2015</v>
-      </c>
-      <c r="AF32" s="407" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG32" s="407" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH32" s="431" t="n"/>
-      <c r="AI32" s="431" t="n"/>
-      <c r="AJ32" s="431" t="n"/>
-      <c r="AK32" s="431" t="n"/>
-      <c r="AL32" s="431" t="n"/>
-      <c r="AM32" s="431" t="n"/>
-      <c r="AN32" s="431" t="n"/>
-      <c r="AO32" s="431" t="n"/>
-      <c r="AP32" s="431" t="n"/>
-      <c r="AQ32" s="431" t="n"/>
-      <c r="AR32" s="431" t="n"/>
-      <c r="AS32" s="431" t="n"/>
-      <c r="AT32" s="431" t="n"/>
-      <c r="AU32" s="431" t="n"/>
-      <c r="AV32" s="431" t="n"/>
-      <c r="AW32" s="431" t="n"/>
+      <c r="F32" s="408" t="n">
+        <v>9162</v>
+      </c>
+      <c r="G32" s="408" t="n">
+        <v>6076</v>
+      </c>
+      <c r="H32" s="408" t="n">
+        <v>7939</v>
+      </c>
+      <c r="I32" s="408" t="n">
+        <v>11661</v>
+      </c>
+      <c r="J32" s="408" t="n">
+        <v>11832</v>
+      </c>
+      <c r="K32" s="408" t="n">
+        <v>15833</v>
+      </c>
+      <c r="L32" s="408" t="n">
+        <v>17998</v>
+      </c>
+      <c r="M32" s="408" t="n">
+        <v>6946</v>
+      </c>
+      <c r="N32" s="408" t="n">
+        <v>277</v>
+      </c>
+      <c r="O32" s="408" t="n">
+        <v>4810</v>
+      </c>
+      <c r="P32" s="408" t="n">
+        <v>6946</v>
+      </c>
+      <c r="Q32" s="408" t="n">
+        <v>6527</v>
+      </c>
+      <c r="R32" s="408" t="n">
+        <v>11807</v>
+      </c>
+      <c r="S32" s="408" t="n">
+        <v>17210</v>
+      </c>
+      <c r="T32" s="408" t="n">
+        <v>18006</v>
+      </c>
+      <c r="U32" s="408" t="n">
+        <v>8015</v>
+      </c>
+      <c r="V32" s="408" t="n">
+        <v>14535</v>
+      </c>
+      <c r="W32" s="408" t="n">
+        <v>155</v>
+      </c>
+      <c r="X32" s="408" t="n">
+        <v>9058</v>
+      </c>
+      <c r="Y32" s="408" t="n">
+        <v>6607</v>
+      </c>
+      <c r="Z32" s="408" t="n">
+        <v>5123</v>
+      </c>
+      <c r="AA32" s="408" t="n">
+        <v>11758</v>
+      </c>
+      <c r="AB32" s="408" t="n">
+        <v>12047</v>
+      </c>
+      <c r="AC32" s="408" t="n">
+        <v>15921</v>
+      </c>
+      <c r="AD32" s="408" t="n">
+        <v>18150</v>
+      </c>
+      <c r="AE32" s="408" t="n">
+        <v>6816</v>
+      </c>
+      <c r="AF32" s="408" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG32" s="434" t="n"/>
+      <c r="AH32" s="434" t="n"/>
+      <c r="AI32" s="434" t="n"/>
+      <c r="AJ32" s="434" t="n"/>
+      <c r="AK32" s="434" t="n"/>
+      <c r="AL32" s="434" t="n"/>
+      <c r="AM32" s="434" t="n"/>
+      <c r="AN32" s="434" t="n"/>
+      <c r="AO32" s="434" t="n"/>
+      <c r="AP32" s="434" t="n"/>
+      <c r="AQ32" s="434" t="n"/>
+      <c r="AR32" s="434" t="n"/>
+      <c r="AS32" s="434" t="n"/>
+      <c r="AT32" s="434" t="n"/>
+      <c r="AU32" s="434" t="n"/>
+      <c r="AV32" s="434" t="n"/>
+      <c r="AW32" s="434" t="n"/>
     </row>
     <row r="33" ht="12" customHeight="1" s="244">
       <c r="A33" s="261" t="n"/>
-      <c r="B33" s="401" t="n"/>
+      <c r="B33" s="402" t="n"/>
       <c r="C33" s="394" t="n"/>
       <c r="D33" s="261" t="n"/>
       <c r="E33" s="259" t="n"/>
@@ -20177,10 +19718,7 @@
         <f>AF32*0.05</f>
         <v/>
       </c>
-      <c r="AG33" s="396">
-        <f>AG32*0.05</f>
-        <v/>
-      </c>
+      <c r="AG33" s="259" t="n"/>
       <c r="AH33" s="259" t="n"/>
       <c r="AI33" s="259" t="n"/>
       <c r="AJ33" s="259" t="n"/>
@@ -20200,7 +19738,7 @@
     </row>
     <row r="34" ht="12" customHeight="1" s="244">
       <c r="A34" s="261" t="n"/>
-      <c r="B34" s="401" t="n"/>
+      <c r="B34" s="402" t="n"/>
       <c r="C34" s="394" t="n"/>
       <c r="D34" s="261" t="n"/>
       <c r="E34" s="259" t="n"/>
@@ -20312,10 +19850,7 @@
         <f>AF32+AF33</f>
         <v/>
       </c>
-      <c r="AG34" s="396">
-        <f>AG32+AG33</f>
-        <v/>
-      </c>
+      <c r="AG34" s="430" t="n"/>
       <c r="AH34" s="259" t="n"/>
       <c r="AI34" s="259" t="n"/>
       <c r="AJ34" s="259" t="n"/>
@@ -20335,138 +19870,135 @@
     </row>
     <row r="35" ht="12" customHeight="1" s="244">
       <c r="A35" s="261" t="n"/>
-      <c r="B35" s="401" t="n"/>
+      <c r="B35" s="402" t="n"/>
       <c r="C35" s="282" t="n"/>
       <c r="D35" s="261" t="n"/>
       <c r="E35" s="259" t="n"/>
-      <c r="F35" s="409">
-        <f>MAX(F34:AG34)-F34</f>
-        <v/>
-      </c>
-      <c r="G35" s="409">
-        <f>MAX(F34:AG34)-G34</f>
-        <v/>
-      </c>
-      <c r="H35" s="409">
-        <f>MAX(F34:AG34)-H34</f>
-        <v/>
-      </c>
-      <c r="I35" s="409">
-        <f>MAX(F34:AG34)-I34</f>
-        <v/>
-      </c>
-      <c r="J35" s="409">
-        <f>MAX(F34:AG34)-J34</f>
-        <v/>
-      </c>
-      <c r="K35" s="409">
-        <f>MAX(F34:AG34)-K34</f>
-        <v/>
-      </c>
-      <c r="L35" s="409">
-        <f>MAX(F34:AG34)-L34</f>
-        <v/>
-      </c>
-      <c r="M35" s="409">
-        <f>MAX(F34:AG34)-M34</f>
-        <v/>
-      </c>
-      <c r="N35" s="409">
-        <f>MAX(F34:AG34)-N34</f>
-        <v/>
-      </c>
-      <c r="O35" s="409">
-        <f>MAX(F34:AG34)-O34</f>
-        <v/>
-      </c>
-      <c r="P35" s="409">
-        <f>MAX(F34:AG34)-P34</f>
-        <v/>
-      </c>
-      <c r="Q35" s="409">
-        <f>MAX(F34:AG34)-Q34</f>
-        <v/>
-      </c>
-      <c r="R35" s="409">
-        <f>MAX(F34:AG34)-R34</f>
-        <v/>
-      </c>
-      <c r="S35" s="409">
-        <f>MAX(F34:AG34)-S34</f>
-        <v/>
-      </c>
-      <c r="T35" s="409">
-        <f>MAX(F34:AG34)-T34</f>
-        <v/>
-      </c>
-      <c r="U35" s="409">
-        <f>MAX(F34:AG34)-U34</f>
-        <v/>
-      </c>
-      <c r="V35" s="409">
-        <f>MAX(F34:AG34)-V34</f>
-        <v/>
-      </c>
-      <c r="W35" s="409">
-        <f>MAX(F34:AG34)-W34</f>
-        <v/>
-      </c>
-      <c r="X35" s="409">
-        <f>MAX(F34:AG34)-X34</f>
-        <v/>
-      </c>
-      <c r="Y35" s="409">
-        <f>MAX(F34:AG34)-Y34</f>
-        <v/>
-      </c>
-      <c r="Z35" s="409">
-        <f>MAX(F34:AG34)-Z34</f>
-        <v/>
-      </c>
-      <c r="AA35" s="409">
-        <f>MAX(F34:AG34)-AA34</f>
-        <v/>
-      </c>
-      <c r="AB35" s="409">
-        <f>MAX(F34:AG34)-AB34</f>
-        <v/>
-      </c>
-      <c r="AC35" s="409">
-        <f>MAX(F34:AG34)-AC34</f>
-        <v/>
-      </c>
-      <c r="AD35" s="409">
-        <f>MAX(F34:AG34)-AD34</f>
-        <v/>
-      </c>
-      <c r="AE35" s="409">
-        <f>MAX(F34:AG34)-AE34</f>
-        <v/>
-      </c>
-      <c r="AF35" s="409">
-        <f>MAX(F34:AG34)-AF34</f>
-        <v/>
-      </c>
-      <c r="AG35" s="409">
-        <f>MAX(F34:AG34)-AG34</f>
-        <v/>
-      </c>
-      <c r="AH35" s="433" t="n"/>
-      <c r="AI35" s="433" t="n"/>
-      <c r="AJ35" s="433" t="n"/>
-      <c r="AK35" s="433" t="n"/>
-      <c r="AL35" s="433" t="n"/>
-      <c r="AM35" s="433" t="n"/>
-      <c r="AN35" s="433" t="n"/>
-      <c r="AO35" s="433" t="n"/>
-      <c r="AP35" s="433" t="n"/>
-      <c r="AQ35" s="433" t="n"/>
-      <c r="AR35" s="433" t="n"/>
-      <c r="AS35" s="433" t="n"/>
-      <c r="AT35" s="433" t="n"/>
-      <c r="AU35" s="433" t="n"/>
-      <c r="AV35" s="433" t="n"/>
-      <c r="AW35" s="433" t="n"/>
+      <c r="F35" s="410">
+        <f>MAX(F34:AF34)-F34</f>
+        <v/>
+      </c>
+      <c r="G35" s="410">
+        <f>MAX(F34:AF34)-G34</f>
+        <v/>
+      </c>
+      <c r="H35" s="410">
+        <f>MAX(F34:AF34)-H34</f>
+        <v/>
+      </c>
+      <c r="I35" s="410">
+        <f>MAX(F34:AF34)-I34</f>
+        <v/>
+      </c>
+      <c r="J35" s="410">
+        <f>MAX(F34:AF34)-J34</f>
+        <v/>
+      </c>
+      <c r="K35" s="410">
+        <f>MAX(F34:AF34)-K34</f>
+        <v/>
+      </c>
+      <c r="L35" s="410">
+        <f>MAX(F34:AF34)-L34</f>
+        <v/>
+      </c>
+      <c r="M35" s="410">
+        <f>MAX(F34:AF34)-M34</f>
+        <v/>
+      </c>
+      <c r="N35" s="410">
+        <f>MAX(F34:AF34)-N34</f>
+        <v/>
+      </c>
+      <c r="O35" s="410">
+        <f>MAX(F34:AF34)-O34</f>
+        <v/>
+      </c>
+      <c r="P35" s="410">
+        <f>MAX(F34:AF34)-P34</f>
+        <v/>
+      </c>
+      <c r="Q35" s="410">
+        <f>MAX(F34:AF34)-Q34</f>
+        <v/>
+      </c>
+      <c r="R35" s="410">
+        <f>MAX(F34:AF34)-R34</f>
+        <v/>
+      </c>
+      <c r="S35" s="410">
+        <f>MAX(F34:AF34)-S34</f>
+        <v/>
+      </c>
+      <c r="T35" s="410">
+        <f>MAX(F34:AF34)-T34</f>
+        <v/>
+      </c>
+      <c r="U35" s="410">
+        <f>MAX(F34:AF34)-U34</f>
+        <v/>
+      </c>
+      <c r="V35" s="410">
+        <f>MAX(F34:AF34)-V34</f>
+        <v/>
+      </c>
+      <c r="W35" s="410">
+        <f>MAX(F34:AF34)-W34</f>
+        <v/>
+      </c>
+      <c r="X35" s="410">
+        <f>MAX(F34:AF34)-X34</f>
+        <v/>
+      </c>
+      <c r="Y35" s="410">
+        <f>MAX(F34:AF34)-Y34</f>
+        <v/>
+      </c>
+      <c r="Z35" s="410">
+        <f>MAX(F34:AF34)-Z34</f>
+        <v/>
+      </c>
+      <c r="AA35" s="410">
+        <f>MAX(F34:AF34)-AA34</f>
+        <v/>
+      </c>
+      <c r="AB35" s="410">
+        <f>MAX(F34:AF34)-AB34</f>
+        <v/>
+      </c>
+      <c r="AC35" s="410">
+        <f>MAX(F34:AF34)-AC34</f>
+        <v/>
+      </c>
+      <c r="AD35" s="410">
+        <f>MAX(F34:AF34)-AD34</f>
+        <v/>
+      </c>
+      <c r="AE35" s="410">
+        <f>MAX(F34:AF34)-AE34</f>
+        <v/>
+      </c>
+      <c r="AF35" s="410">
+        <f>MAX(F34:AF34)-AF34</f>
+        <v/>
+      </c>
+      <c r="AG35" s="436" t="n"/>
+      <c r="AH35" s="436" t="n"/>
+      <c r="AI35" s="436" t="n"/>
+      <c r="AJ35" s="436" t="n"/>
+      <c r="AK35" s="436" t="n"/>
+      <c r="AL35" s="436" t="n"/>
+      <c r="AM35" s="436" t="n"/>
+      <c r="AN35" s="436" t="n"/>
+      <c r="AO35" s="436" t="n"/>
+      <c r="AP35" s="436" t="n"/>
+      <c r="AQ35" s="436" t="n"/>
+      <c r="AR35" s="436" t="n"/>
+      <c r="AS35" s="436" t="n"/>
+      <c r="AT35" s="436" t="n"/>
+      <c r="AU35" s="436" t="n"/>
+      <c r="AV35" s="436" t="n"/>
+      <c r="AW35" s="436" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1" s="244">
       <c r="D36" s="266" t="inlineStr">
@@ -20488,6 +20020,11 @@
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1" s="244">
+      <c r="B38" s="411" t="inlineStr">
+        <is>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 101-1 (38.1 °C), 102-2 (37.1 °C), 102-3 (37.1 °C), 103-4 (37.8 °C), 104-5 (37.8 °C), 105-6 (37.7 °C), 105-7 (37.7 °C), 106-8 (32.0 °C) ...</t>
+        </is>
+      </c>
       <c r="F38" s="243" t="inlineStr">
         <is>
           <t>GÖRE AYARLANMALIDIR….</t>
@@ -20495,21 +20032,26 @@
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1" s="244">
-      <c r="F39" s="410" t="inlineStr">
+      <c r="B39" s="412" t="inlineStr">
+        <is>
+          <t>Sınır içinde kalmak için q" ≤ 100 W/m² (oturma) gerekir; 35 W/m ile bu, boru aralığı ≈ 35 cm demektir. Boru aralığı 15 cm (kullanıcı seçimi) değiştirilmemiştir — ısı kaybı ile qh girilmelidir.</t>
+        </is>
+      </c>
+      <c r="F39" s="413" t="inlineStr">
         <is>
           <t>Δpö</t>
         </is>
       </c>
-      <c r="G39" s="410" t="inlineStr">
+      <c r="G39" s="413" t="inlineStr">
         <is>
           <t>EK VI-14i Tablosundan q değeri m³/h çevrilir DN10 borusu için</t>
         </is>
       </c>
-      <c r="H39" s="410" t="n"/>
-      <c r="I39" s="410" t="n"/>
+      <c r="H39" s="413" t="n"/>
+      <c r="I39" s="413" t="n"/>
     </row>
     <row r="40" ht="12.75" customHeight="1" s="244">
-      <c r="A40" s="411" t="inlineStr">
+      <c r="A40" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (1)</t>
         </is>
@@ -20519,17 +20061,17 @@
           <t>Şek. 19.7.1 den seçilmiştir.</t>
         </is>
       </c>
-      <c r="F40" s="410" t="n"/>
-      <c r="G40" s="410" t="inlineStr">
+      <c r="F40" s="413" t="n"/>
+      <c r="G40" s="413" t="inlineStr">
         <is>
           <t>R (Pa/m) 1metre borudaki basın. Kaybı bulunur..</t>
         </is>
       </c>
-      <c r="H40" s="410" t="n"/>
-      <c r="I40" s="410" t="n"/>
+      <c r="H40" s="413" t="n"/>
+      <c r="I40" s="413" t="n"/>
     </row>
     <row r="41" ht="12.75" customHeight="1" s="244">
-      <c r="A41" s="411" t="inlineStr">
+      <c r="A41" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (2)</t>
         </is>
@@ -20539,17 +20081,17 @@
           <t>Kombi gidiş suyu sıcaklığı 45 °C, dönüş 35 °C seçilmiştir.</t>
         </is>
       </c>
-      <c r="F41" s="410" t="n"/>
-      <c r="G41" s="410" t="inlineStr">
+      <c r="F41" s="413" t="n"/>
+      <c r="G41" s="413" t="inlineStr">
         <is>
           <t xml:space="preserve">toplam boru boyu ile çarpımından Δpö (Pa) bulunur.  </t>
         </is>
       </c>
-      <c r="H41" s="410" t="n"/>
-      <c r="I41" s="410" t="n"/>
+      <c r="H41" s="413" t="n"/>
+      <c r="I41" s="413" t="n"/>
     </row>
     <row r="42" ht="12.75" customHeight="1" s="244">
-      <c r="A42" s="411" t="inlineStr">
+      <c r="A42" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (3)</t>
         </is>
@@ -20561,19 +20103,19 @@
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1" s="244">
-      <c r="A43" s="411" t="inlineStr">
+      <c r="A43" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (4)</t>
         </is>
       </c>
       <c r="B43" s="243" t="inlineStr">
         <is>
-          <t>Alta geçen ısı 0,2 q" olarak alınmıştır. qh = 17,5 W/m × devre boyu (şablon birim verimi); ısı kaybı hesabı ayrıca yapılmalıdır.</t>
+          <t>Alta geçen ısı 0,2 q" olarak alınmıştır. qh = 35 W/m × devre boyu (plan etiketi ve kolon şeması ile aynı esas); ayrı ısı kaybı hesabı yapılmamıştır.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1" s="244">
-      <c r="A44" s="411" t="inlineStr">
+      <c r="A44" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (5)</t>
         </is>
@@ -20585,7 +20127,7 @@
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1" s="244">
-      <c r="A45" s="411" t="inlineStr">
+      <c r="A45" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (6)</t>
         </is>
@@ -20597,7 +20139,7 @@
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1" s="244">
-      <c r="A46" s="411" t="inlineStr">
+      <c r="A46" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (7)</t>
         </is>
@@ -20609,7 +20151,7 @@
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1" s="244">
-      <c r="A47" s="412" t="n"/>
+      <c r="A47" s="415" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -20674,16 +20216,16 @@
       <c r="M1" s="264" t="n"/>
       <c r="N1" s="264" t="n"/>
       <c r="O1" s="264" t="n"/>
-      <c r="P1" s="413" t="n"/>
-      <c r="Q1" s="414" t="n"/>
-      <c r="R1" s="414" t="n"/>
-      <c r="S1" s="414" t="n"/>
-      <c r="T1" s="414" t="n"/>
-      <c r="U1" s="414" t="n"/>
-      <c r="V1" s="414" t="n"/>
-      <c r="W1" s="414" t="n"/>
-      <c r="X1" s="415" t="n"/>
-      <c r="Y1" s="415" t="n"/>
+      <c r="P1" s="416" t="n"/>
+      <c r="Q1" s="417" t="n"/>
+      <c r="R1" s="417" t="n"/>
+      <c r="S1" s="417" t="n"/>
+      <c r="T1" s="417" t="n"/>
+      <c r="U1" s="417" t="n"/>
+      <c r="V1" s="417" t="n"/>
+      <c r="W1" s="417" t="n"/>
+      <c r="X1" s="418" t="n"/>
+      <c r="Y1" s="418" t="n"/>
     </row>
     <row r="2" ht="12.75" customFormat="1" customHeight="1" s="329">
       <c r="A2" s="380" t="inlineStr">
@@ -20704,7 +20246,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 17851 W</t>
+          <t>TOPLAM ISI = 43759 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -20743,7 +20285,7 @@
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 3618 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 18806 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -20819,19 +20361,19 @@
       <c r="J5" s="260" t="n"/>
       <c r="K5" s="331" t="n"/>
       <c r="L5" s="331" t="n"/>
-      <c r="M5" s="416" t="n"/>
-      <c r="N5" s="416" t="n"/>
-      <c r="O5" s="417" t="n"/>
-      <c r="P5" s="417" t="n"/>
-      <c r="Q5" s="417" t="n"/>
-      <c r="R5" s="417" t="n"/>
-      <c r="S5" s="417" t="n"/>
-      <c r="T5" s="417" t="n"/>
-      <c r="U5" s="417" t="n"/>
-      <c r="V5" s="417" t="n"/>
-      <c r="W5" s="417" t="n"/>
-      <c r="X5" s="418" t="n"/>
-      <c r="Y5" s="418" t="n"/>
+      <c r="M5" s="419" t="n"/>
+      <c r="N5" s="419" t="n"/>
+      <c r="O5" s="420" t="n"/>
+      <c r="P5" s="420" t="n"/>
+      <c r="Q5" s="420" t="n"/>
+      <c r="R5" s="420" t="n"/>
+      <c r="S5" s="420" t="n"/>
+      <c r="T5" s="420" t="n"/>
+      <c r="U5" s="420" t="n"/>
+      <c r="V5" s="420" t="n"/>
+      <c r="W5" s="420" t="n"/>
+      <c r="X5" s="421" t="n"/>
+      <c r="Y5" s="421" t="n"/>
       <c r="Z5" s="355" t="n"/>
       <c r="AA5" s="355" t="n"/>
       <c r="AB5" s="355" t="n"/>
@@ -21112,12 +20654,12 @@
       <c r="AO8" s="391" t="n"/>
       <c r="AP8" s="391" t="n"/>
       <c r="AQ8" s="391" t="n"/>
-      <c r="AR8" s="419" t="n"/>
+      <c r="AR8" s="422" t="n"/>
       <c r="AS8" s="391" t="n"/>
       <c r="AT8" s="391" t="n"/>
       <c r="AU8" s="391" t="n"/>
       <c r="AV8" s="391" t="n"/>
-      <c r="AW8" s="419" t="n"/>
+      <c r="AW8" s="422" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1" s="244">
       <c r="A9" s="261" t="n"/>
@@ -21260,23 +20802,23 @@
           <t>D9 banyo</t>
         </is>
       </c>
-      <c r="AG9" s="420" t="n"/>
-      <c r="AH9" s="420" t="n"/>
-      <c r="AI9" s="420" t="n"/>
+      <c r="AG9" s="423" t="n"/>
+      <c r="AH9" s="423" t="n"/>
+      <c r="AI9" s="423" t="n"/>
       <c r="AJ9" s="391" t="n"/>
       <c r="AK9" s="391" t="n"/>
       <c r="AL9" s="391" t="n"/>
       <c r="AM9" s="391" t="n"/>
       <c r="AN9" s="391" t="n"/>
-      <c r="AO9" s="421" t="n"/>
-      <c r="AP9" s="421" t="n"/>
-      <c r="AQ9" s="421" t="n"/>
-      <c r="AR9" s="422" t="n"/>
-      <c r="AS9" s="422" t="n"/>
-      <c r="AT9" s="421" t="n"/>
-      <c r="AU9" s="421" t="n"/>
-      <c r="AV9" s="421" t="n"/>
-      <c r="AW9" s="421" t="n"/>
+      <c r="AO9" s="424" t="n"/>
+      <c r="AP9" s="424" t="n"/>
+      <c r="AQ9" s="424" t="n"/>
+      <c r="AR9" s="425" t="n"/>
+      <c r="AS9" s="425" t="n"/>
+      <c r="AT9" s="424" t="n"/>
+      <c r="AU9" s="424" t="n"/>
+      <c r="AV9" s="424" t="n"/>
+      <c r="AW9" s="424" t="n"/>
     </row>
     <row r="10" ht="12" customHeight="1" s="244">
       <c r="A10" s="261" t="n"/>
@@ -21500,25 +21042,25 @@
         <v>7.57</v>
       </c>
       <c r="G12" s="397" t="n">
-        <v>6.05</v>
+        <v>7.19</v>
       </c>
       <c r="H12" s="397" t="n">
-        <v>7.39</v>
+        <v>7.96</v>
       </c>
       <c r="I12" s="397" t="n">
-        <v>8.73</v>
+        <v>8.76</v>
       </c>
       <c r="J12" s="397" t="n">
-        <v>8.800000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="K12" s="397" t="n">
-        <v>9.69</v>
+        <v>9.75</v>
       </c>
       <c r="L12" s="397" t="n">
-        <v>10.34</v>
+        <v>10.28</v>
       </c>
       <c r="M12" s="397" t="n">
-        <v>7.57</v>
+        <v>7.64</v>
       </c>
       <c r="N12" s="397" t="n">
         <v>3.33</v>
@@ -21527,178 +21069,186 @@
         <v>6.92</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>7.39</v>
+        <v>7.03</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>6.63</v>
+        <v>7.18</v>
       </c>
       <c r="R12" s="397" t="n">
         <v>8.66</v>
       </c>
       <c r="S12" s="397" t="n">
-        <v>10.87</v>
+        <v>10.32</v>
       </c>
       <c r="T12" s="397" t="n">
-        <v>9.779999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="U12" s="397" t="n">
-        <v>7.11</v>
+        <v>7.28</v>
       </c>
       <c r="V12" s="397" t="n">
-        <v>10.43</v>
+        <v>10.51</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>7.8</v>
       </c>
       <c r="Y12" s="397" t="n">
-        <v>6.29</v>
+        <v>7.1</v>
       </c>
       <c r="Z12" s="397" t="n">
-        <v>7.29</v>
+        <v>6.48</v>
       </c>
       <c r="AA12" s="397" t="n">
-        <v>8.74</v>
+        <v>8.77</v>
       </c>
       <c r="AB12" s="397" t="n">
         <v>8.85</v>
       </c>
       <c r="AC12" s="397" t="n">
-        <v>9.619999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="AD12" s="397" t="n">
-        <v>10.36</v>
+        <v>10.3</v>
       </c>
       <c r="AE12" s="397" t="n">
-        <v>7.54</v>
+        <v>8.07</v>
       </c>
       <c r="AF12" s="397" t="n">
         <v>3.35</v>
       </c>
-      <c r="AG12" s="423" t="n"/>
-      <c r="AH12" s="423" t="n"/>
-      <c r="AI12" s="423" t="n"/>
-      <c r="AJ12" s="423" t="n"/>
-      <c r="AK12" s="424" t="n"/>
-      <c r="AL12" s="424" t="n"/>
-      <c r="AM12" s="424" t="n"/>
-      <c r="AN12" s="423" t="n"/>
-      <c r="AO12" s="423" t="n"/>
-      <c r="AP12" s="423" t="n"/>
-      <c r="AQ12" s="423" t="n"/>
-      <c r="AR12" s="423" t="n"/>
-      <c r="AS12" s="423" t="n"/>
-      <c r="AT12" s="423" t="n"/>
-      <c r="AU12" s="423" t="n"/>
-      <c r="AV12" s="423" t="n"/>
-      <c r="AW12" s="423" t="n"/>
+      <c r="AG12" s="426" t="n"/>
+      <c r="AH12" s="426" t="n"/>
+      <c r="AI12" s="426" t="n"/>
+      <c r="AJ12" s="426" t="n"/>
+      <c r="AK12" s="427" t="n"/>
+      <c r="AL12" s="427" t="n"/>
+      <c r="AM12" s="427" t="n"/>
+      <c r="AN12" s="426" t="n"/>
+      <c r="AO12" s="426" t="n"/>
+      <c r="AP12" s="426" t="n"/>
+      <c r="AQ12" s="426" t="n"/>
+      <c r="AR12" s="426" t="n"/>
+      <c r="AS12" s="426" t="n"/>
+      <c r="AT12" s="426" t="n"/>
+      <c r="AU12" s="426" t="n"/>
+      <c r="AV12" s="426" t="n"/>
+      <c r="AW12" s="426" t="n"/>
     </row>
     <row r="13" ht="12" customHeight="1" s="244">
       <c r="A13" s="261" t="n"/>
       <c r="B13" s="282" t="n"/>
-      <c r="C13" s="394" t="n"/>
-      <c r="D13" s="261" t="n"/>
+      <c r="C13" s="394" t="inlineStr">
+        <is>
+          <t>DEVRE ISIL GÜCÜ</t>
+        </is>
+      </c>
+      <c r="D13" s="261" t="inlineStr">
+        <is>
+          <t>35 W/m × L (planla aynı)</t>
+        </is>
+      </c>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>793.5</v>
+        <v>1597.8</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>550</v>
+        <v>1451.8</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>671.8</v>
+        <v>1605.4</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>680.6</v>
+        <v>1848</v>
       </c>
       <c r="J13" s="398" t="n">
-        <v>745.1</v>
+        <v>1859.2</v>
       </c>
       <c r="K13" s="398" t="n">
-        <v>865</v>
+        <v>2050.3</v>
       </c>
       <c r="L13" s="398" t="n">
-        <v>923.3</v>
+        <v>2163</v>
       </c>
       <c r="M13" s="398" t="n">
-        <v>752.7</v>
+        <v>1526.3</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>211.4</v>
+        <v>621.2</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>594.6</v>
+        <v>1288.4</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>491.6</v>
+        <v>1453.5</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>440.6</v>
+        <v>1483.7</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>769.5</v>
+        <v>1859.2</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>785.6</v>
+        <v>2125.2</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>707.2</v>
+        <v>2163.3</v>
       </c>
       <c r="U13" s="398" t="n">
-        <v>622.3</v>
+        <v>1610.7</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>787.9</v>
+        <v>2005.9</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>123.7</v>
+        <v>420.3</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>838.9</v>
+        <v>1679.7</v>
       </c>
       <c r="Y13" s="398" t="n">
-        <v>588.9</v>
+        <v>1498</v>
       </c>
       <c r="Z13" s="398" t="n">
-        <v>683.2</v>
+        <v>1366.4</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>686.2</v>
+        <v>1848</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>771.4</v>
+        <v>1864.8</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>856.6</v>
+        <v>2033.5</v>
       </c>
       <c r="AD13" s="398" t="n">
-        <v>923.3</v>
+        <v>2163</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>752.9</v>
+        <v>1545.2</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>233.4</v>
-      </c>
-      <c r="AG13" s="425" t="n"/>
-      <c r="AH13" s="425" t="n"/>
-      <c r="AI13" s="425" t="n"/>
-      <c r="AJ13" s="425" t="n"/>
-      <c r="AK13" s="425" t="n"/>
-      <c r="AL13" s="425" t="n"/>
-      <c r="AM13" s="425" t="n"/>
-      <c r="AN13" s="425" t="n"/>
-      <c r="AO13" s="425" t="n"/>
-      <c r="AP13" s="425" t="n"/>
-      <c r="AQ13" s="425" t="n"/>
-      <c r="AR13" s="425" t="n"/>
-      <c r="AS13" s="425" t="n"/>
-      <c r="AT13" s="425" t="n"/>
-      <c r="AU13" s="425" t="n"/>
-      <c r="AV13" s="425" t="n"/>
-      <c r="AW13" s="425" t="n"/>
+        <v>627.5</v>
+      </c>
+      <c r="AG13" s="428" t="n"/>
+      <c r="AH13" s="428" t="n"/>
+      <c r="AI13" s="428" t="n"/>
+      <c r="AJ13" s="428" t="n"/>
+      <c r="AK13" s="428" t="n"/>
+      <c r="AL13" s="428" t="n"/>
+      <c r="AM13" s="428" t="n"/>
+      <c r="AN13" s="428" t="n"/>
+      <c r="AO13" s="428" t="n"/>
+      <c r="AP13" s="428" t="n"/>
+      <c r="AQ13" s="428" t="n"/>
+      <c r="AR13" s="428" t="n"/>
+      <c r="AS13" s="428" t="n"/>
+      <c r="AT13" s="428" t="n"/>
+      <c r="AU13" s="428" t="n"/>
+      <c r="AV13" s="428" t="n"/>
+      <c r="AW13" s="428" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1" s="244">
       <c r="A14" s="261" t="n"/>
@@ -21814,23 +21364,23 @@
         <f>AF13/AF12</f>
         <v/>
       </c>
-      <c r="AG14" s="426" t="n"/>
-      <c r="AH14" s="426" t="n"/>
-      <c r="AI14" s="426" t="n"/>
-      <c r="AJ14" s="426" t="n"/>
-      <c r="AK14" s="426" t="n"/>
-      <c r="AL14" s="426" t="n"/>
-      <c r="AM14" s="426" t="n"/>
-      <c r="AN14" s="426" t="n"/>
-      <c r="AO14" s="426" t="n"/>
-      <c r="AP14" s="426" t="n"/>
-      <c r="AQ14" s="426" t="n"/>
-      <c r="AR14" s="426" t="n"/>
-      <c r="AS14" s="426" t="n"/>
-      <c r="AT14" s="426" t="n"/>
-      <c r="AU14" s="426" t="n"/>
-      <c r="AV14" s="426" t="n"/>
-      <c r="AW14" s="426" t="n"/>
+      <c r="AG14" s="429" t="n"/>
+      <c r="AH14" s="429" t="n"/>
+      <c r="AI14" s="429" t="n"/>
+      <c r="AJ14" s="429" t="n"/>
+      <c r="AK14" s="429" t="n"/>
+      <c r="AL14" s="429" t="n"/>
+      <c r="AM14" s="429" t="n"/>
+      <c r="AN14" s="429" t="n"/>
+      <c r="AO14" s="429" t="n"/>
+      <c r="AP14" s="429" t="n"/>
+      <c r="AQ14" s="429" t="n"/>
+      <c r="AR14" s="429" t="n"/>
+      <c r="AS14" s="429" t="n"/>
+      <c r="AT14" s="429" t="n"/>
+      <c r="AU14" s="429" t="n"/>
+      <c r="AV14" s="429" t="n"/>
+      <c r="AW14" s="429" t="n"/>
     </row>
     <row r="15" ht="12" customHeight="1" s="244">
       <c r="A15" s="261" t="n"/>
@@ -22024,23 +21574,23 @@
       <c r="AF16" s="397" t="n">
         <v>1</v>
       </c>
-      <c r="AG16" s="423" t="n"/>
-      <c r="AH16" s="423" t="n"/>
-      <c r="AI16" s="423" t="n"/>
-      <c r="AJ16" s="423" t="n"/>
-      <c r="AK16" s="423" t="n"/>
-      <c r="AL16" s="423" t="n"/>
-      <c r="AM16" s="423" t="n"/>
-      <c r="AN16" s="423" t="n"/>
-      <c r="AO16" s="423" t="n"/>
-      <c r="AP16" s="423" t="n"/>
-      <c r="AQ16" s="423" t="n"/>
-      <c r="AR16" s="423" t="n"/>
-      <c r="AS16" s="423" t="n"/>
-      <c r="AT16" s="423" t="n"/>
-      <c r="AU16" s="423" t="n"/>
-      <c r="AV16" s="423" t="n"/>
-      <c r="AW16" s="423" t="n"/>
+      <c r="AG16" s="426" t="n"/>
+      <c r="AH16" s="426" t="n"/>
+      <c r="AI16" s="426" t="n"/>
+      <c r="AJ16" s="426" t="n"/>
+      <c r="AK16" s="426" t="n"/>
+      <c r="AL16" s="426" t="n"/>
+      <c r="AM16" s="426" t="n"/>
+      <c r="AN16" s="426" t="n"/>
+      <c r="AO16" s="426" t="n"/>
+      <c r="AP16" s="426" t="n"/>
+      <c r="AQ16" s="426" t="n"/>
+      <c r="AR16" s="426" t="n"/>
+      <c r="AS16" s="426" t="n"/>
+      <c r="AT16" s="426" t="n"/>
+      <c r="AU16" s="426" t="n"/>
+      <c r="AV16" s="426" t="n"/>
+      <c r="AW16" s="426" t="n"/>
     </row>
     <row r="17" ht="12" customHeight="1" s="244">
       <c r="A17" s="261" t="n"/>
@@ -22288,23 +21838,23 @@
         <f>AF13/AF17</f>
         <v/>
       </c>
-      <c r="AG18" s="427" t="n"/>
-      <c r="AH18" s="427" t="n"/>
-      <c r="AI18" s="427" t="n"/>
-      <c r="AJ18" s="427" t="n"/>
-      <c r="AK18" s="427" t="n"/>
-      <c r="AL18" s="427" t="n"/>
-      <c r="AM18" s="427" t="n"/>
-      <c r="AN18" s="427" t="n"/>
-      <c r="AO18" s="427" t="n"/>
-      <c r="AP18" s="427" t="n"/>
-      <c r="AQ18" s="427" t="n"/>
-      <c r="AR18" s="427" t="n"/>
-      <c r="AS18" s="427" t="n"/>
-      <c r="AT18" s="427" t="n"/>
-      <c r="AU18" s="427" t="n"/>
-      <c r="AV18" s="427" t="n"/>
-      <c r="AW18" s="427" t="n"/>
+      <c r="AG18" s="430" t="n"/>
+      <c r="AH18" s="430" t="n"/>
+      <c r="AI18" s="430" t="n"/>
+      <c r="AJ18" s="430" t="n"/>
+      <c r="AK18" s="430" t="n"/>
+      <c r="AL18" s="430" t="n"/>
+      <c r="AM18" s="430" t="n"/>
+      <c r="AN18" s="430" t="n"/>
+      <c r="AO18" s="430" t="n"/>
+      <c r="AP18" s="430" t="n"/>
+      <c r="AQ18" s="430" t="n"/>
+      <c r="AR18" s="430" t="n"/>
+      <c r="AS18" s="430" t="n"/>
+      <c r="AT18" s="430" t="n"/>
+      <c r="AU18" s="430" t="n"/>
+      <c r="AV18" s="430" t="n"/>
+      <c r="AW18" s="430" t="n"/>
     </row>
     <row r="19" ht="19.5" customHeight="1" s="244">
       <c r="A19" s="261" t="n"/>
@@ -22312,131 +21862,131 @@
       <c r="C19" s="394" t="n"/>
       <c r="D19" s="261" t="n"/>
       <c r="E19" s="259" t="n"/>
-      <c r="F19" s="400">
+      <c r="F19" s="401">
         <f>F10+(F14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="G19" s="400">
+      <c r="G19" s="401">
         <f>G10+(G14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="H19" s="400">
+      <c r="H19" s="401">
         <f>H10+(H14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="I19" s="400">
+      <c r="I19" s="401">
         <f>I10+(I14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="J19" s="400">
+      <c r="J19" s="401">
         <f>J10+(J14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="K19" s="400">
+      <c r="K19" s="401">
         <f>K10+(K14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="L19" s="400">
+      <c r="L19" s="401">
         <f>L10+(L14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="M19" s="400">
+      <c r="M19" s="401">
         <f>M10+(M14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="N19" s="400">
+      <c r="N19" s="401">
         <f>N10+(N14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="O19" s="400">
+      <c r="O19" s="401">
         <f>O10+(O14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="P19" s="400">
+      <c r="P19" s="401">
         <f>P10+(P14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="Q19" s="400">
+      <c r="Q19" s="401">
         <f>Q10+(Q14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="R19" s="400">
+      <c r="R19" s="401">
         <f>R10+(R14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="S19" s="400">
+      <c r="S19" s="401">
         <f>S10+(S14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="T19" s="400">
+      <c r="T19" s="401">
         <f>T10+(T14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="U19" s="400">
+      <c r="U19" s="401">
         <f>U10+(U14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="V19" s="400">
+      <c r="V19" s="401">
         <f>V10+(V14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="W19" s="400">
+      <c r="W19" s="401">
         <f>W10+(W14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="X19" s="400">
+      <c r="X19" s="401">
         <f>X10+(X14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="Y19" s="400">
+      <c r="Y19" s="401">
         <f>Y10+(Y14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="Z19" s="400">
+      <c r="Z19" s="401">
         <f>Z10+(Z14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AA19" s="400">
+      <c r="AA19" s="401">
         <f>AA10+(AA14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AB19" s="400">
+      <c r="AB19" s="401">
         <f>AB10+(AB14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AC19" s="400">
+      <c r="AC19" s="401">
         <f>AC10+(AC14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AD19" s="400">
+      <c r="AD19" s="401">
         <f>AD10+(AD14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AE19" s="400">
+      <c r="AE19" s="401">
         <f>AE10+(AE14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AF19" s="400">
+      <c r="AF19" s="401">
         <f>AF10+(AF14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AG19" s="427" t="n"/>
-      <c r="AH19" s="427" t="n"/>
-      <c r="AI19" s="427" t="n"/>
-      <c r="AJ19" s="427" t="n"/>
-      <c r="AK19" s="427" t="n"/>
-      <c r="AL19" s="427" t="n"/>
-      <c r="AM19" s="427" t="n"/>
-      <c r="AN19" s="427" t="n"/>
-      <c r="AO19" s="427" t="n"/>
-      <c r="AP19" s="427" t="n"/>
-      <c r="AQ19" s="427" t="n"/>
-      <c r="AR19" s="427" t="n"/>
-      <c r="AS19" s="427" t="n"/>
-      <c r="AT19" s="427" t="n"/>
-      <c r="AU19" s="427" t="n"/>
-      <c r="AV19" s="427" t="n"/>
-      <c r="AW19" s="427" t="n"/>
+      <c r="AG19" s="430" t="n"/>
+      <c r="AH19" s="430" t="n"/>
+      <c r="AI19" s="430" t="n"/>
+      <c r="AJ19" s="430" t="n"/>
+      <c r="AK19" s="430" t="n"/>
+      <c r="AL19" s="430" t="n"/>
+      <c r="AM19" s="430" t="n"/>
+      <c r="AN19" s="430" t="n"/>
+      <c r="AO19" s="430" t="n"/>
+      <c r="AP19" s="430" t="n"/>
+      <c r="AQ19" s="430" t="n"/>
+      <c r="AR19" s="430" t="n"/>
+      <c r="AS19" s="430" t="n"/>
+      <c r="AT19" s="430" t="n"/>
+      <c r="AU19" s="430" t="n"/>
+      <c r="AV19" s="430" t="n"/>
+      <c r="AW19" s="430" t="n"/>
     </row>
     <row r="20" ht="12" customHeight="1" s="244">
       <c r="A20" s="261" t="n"/>
@@ -22545,7 +22095,7 @@
     </row>
     <row r="21" ht="12" customHeight="1" s="244">
       <c r="A21" s="261" t="n"/>
-      <c r="B21" s="401" t="n"/>
+      <c r="B21" s="402" t="n"/>
       <c r="C21" s="394" t="n"/>
       <c r="D21" s="261" t="n"/>
       <c r="E21" s="259" t="n"/>
@@ -22677,7 +22227,7 @@
     </row>
     <row r="22" ht="12" customHeight="1" s="244">
       <c r="A22" s="261" t="n"/>
-      <c r="B22" s="402" t="n"/>
+      <c r="B22" s="403" t="n"/>
       <c r="C22" s="394" t="n"/>
       <c r="D22" s="261" t="n"/>
       <c r="E22" s="259" t="n"/>
@@ -22782,112 +22332,112 @@
     </row>
     <row r="23" ht="12" customHeight="1" s="244">
       <c r="A23" s="261" t="n"/>
-      <c r="B23" s="402" t="n"/>
+      <c r="B23" s="403" t="n"/>
       <c r="C23" s="394" t="n"/>
       <c r="D23" s="261" t="n"/>
       <c r="E23" s="259" t="n"/>
-      <c r="F23" s="403" t="n">
+      <c r="F23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="G23" s="403" t="n">
+      <c r="G23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="H23" s="403" t="n">
+      <c r="H23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="I23" s="403" t="n">
+      <c r="I23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="J23" s="403" t="n">
+      <c r="J23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="K23" s="403" t="n">
+      <c r="K23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="L23" s="403" t="n">
+      <c r="L23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="M23" s="403" t="n">
+      <c r="M23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="N23" s="403" t="n">
+      <c r="N23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="O23" s="403" t="n">
+      <c r="O23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="P23" s="403" t="n">
+      <c r="P23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="Q23" s="403" t="n">
+      <c r="Q23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="R23" s="403" t="n">
+      <c r="R23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="S23" s="403" t="n">
+      <c r="S23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="T23" s="403" t="n">
+      <c r="T23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="U23" s="403" t="n">
+      <c r="U23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="V23" s="403" t="n">
+      <c r="V23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="W23" s="403" t="n">
+      <c r="W23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="X23" s="403" t="n">
+      <c r="X23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="Y23" s="403" t="n">
+      <c r="Y23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="Z23" s="403" t="n">
+      <c r="Z23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AA23" s="403" t="n">
+      <c r="AA23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AB23" s="403" t="n">
+      <c r="AB23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AC23" s="403" t="n">
+      <c r="AC23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AD23" s="403" t="n">
+      <c r="AD23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AE23" s="403" t="n">
+      <c r="AE23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AF23" s="403" t="n">
+      <c r="AF23" s="404" t="n">
         <v>40</v>
       </c>
-      <c r="AG23" s="428" t="n"/>
-      <c r="AH23" s="428" t="n"/>
-      <c r="AI23" s="428" t="n"/>
-      <c r="AJ23" s="428" t="n"/>
-      <c r="AK23" s="428" t="n"/>
-      <c r="AL23" s="428" t="n"/>
-      <c r="AM23" s="428" t="n"/>
-      <c r="AN23" s="428" t="n"/>
-      <c r="AO23" s="428" t="n"/>
-      <c r="AP23" s="428" t="n"/>
-      <c r="AQ23" s="428" t="n"/>
-      <c r="AR23" s="428" t="n"/>
-      <c r="AS23" s="428" t="n"/>
-      <c r="AT23" s="428" t="n"/>
-      <c r="AU23" s="428" t="n"/>
-      <c r="AV23" s="428" t="n"/>
-      <c r="AW23" s="428" t="n"/>
+      <c r="AG23" s="431" t="n"/>
+      <c r="AH23" s="431" t="n"/>
+      <c r="AI23" s="431" t="n"/>
+      <c r="AJ23" s="431" t="n"/>
+      <c r="AK23" s="431" t="n"/>
+      <c r="AL23" s="431" t="n"/>
+      <c r="AM23" s="431" t="n"/>
+      <c r="AN23" s="431" t="n"/>
+      <c r="AO23" s="431" t="n"/>
+      <c r="AP23" s="431" t="n"/>
+      <c r="AQ23" s="431" t="n"/>
+      <c r="AR23" s="431" t="n"/>
+      <c r="AS23" s="431" t="n"/>
+      <c r="AT23" s="431" t="n"/>
+      <c r="AU23" s="431" t="n"/>
+      <c r="AV23" s="431" t="n"/>
+      <c r="AW23" s="431" t="n"/>
     </row>
     <row r="24" ht="12" customHeight="1" s="244">
       <c r="A24" s="261" t="n"/>
-      <c r="B24" s="401" t="n"/>
+      <c r="B24" s="402" t="n"/>
       <c r="C24" s="394" t="n"/>
       <c r="D24" s="261" t="n"/>
       <c r="E24" s="259" t="n"/>
@@ -23019,7 +22569,7 @@
     </row>
     <row r="25" ht="12" customHeight="1" s="244">
       <c r="A25" s="261" t="n"/>
-      <c r="B25" s="401" t="n"/>
+      <c r="B25" s="402" t="n"/>
       <c r="C25" s="394" t="n"/>
       <c r="D25" s="261" t="n"/>
       <c r="E25" s="259" t="n"/>
@@ -23151,9 +22701,9 @@
     </row>
     <row r="26" ht="12" customHeight="1" s="244">
       <c r="A26" s="261" t="n"/>
-      <c r="B26" s="402" t="n"/>
+      <c r="B26" s="403" t="n"/>
       <c r="C26" s="394" t="n"/>
-      <c r="D26" s="404" t="n"/>
+      <c r="D26" s="405" t="n"/>
       <c r="E26" s="259" t="n"/>
       <c r="F26" s="400">
         <f>0.2*F14</f>
@@ -23263,423 +22813,423 @@
         <f>0.2*AF14</f>
         <v/>
       </c>
-      <c r="AG26" s="427" t="n"/>
-      <c r="AH26" s="427" t="n"/>
-      <c r="AI26" s="427" t="n"/>
-      <c r="AJ26" s="427" t="n"/>
-      <c r="AK26" s="427" t="n"/>
-      <c r="AL26" s="427" t="n"/>
-      <c r="AM26" s="427" t="n"/>
-      <c r="AN26" s="427" t="n"/>
-      <c r="AO26" s="427" t="n"/>
-      <c r="AP26" s="427" t="n"/>
-      <c r="AQ26" s="427" t="n"/>
-      <c r="AR26" s="427" t="n"/>
-      <c r="AS26" s="427" t="n"/>
-      <c r="AT26" s="427" t="n"/>
-      <c r="AU26" s="427" t="n"/>
-      <c r="AV26" s="427" t="n"/>
-      <c r="AW26" s="427" t="n"/>
+      <c r="AG26" s="430" t="n"/>
+      <c r="AH26" s="430" t="n"/>
+      <c r="AI26" s="430" t="n"/>
+      <c r="AJ26" s="430" t="n"/>
+      <c r="AK26" s="430" t="n"/>
+      <c r="AL26" s="430" t="n"/>
+      <c r="AM26" s="430" t="n"/>
+      <c r="AN26" s="430" t="n"/>
+      <c r="AO26" s="430" t="n"/>
+      <c r="AP26" s="430" t="n"/>
+      <c r="AQ26" s="430" t="n"/>
+      <c r="AR26" s="430" t="n"/>
+      <c r="AS26" s="430" t="n"/>
+      <c r="AT26" s="430" t="n"/>
+      <c r="AU26" s="430" t="n"/>
+      <c r="AV26" s="430" t="n"/>
+      <c r="AW26" s="430" t="n"/>
     </row>
     <row r="27" ht="12" customHeight="1" s="244">
       <c r="A27" s="261" t="n"/>
-      <c r="B27" s="402" t="n"/>
+      <c r="B27" s="403" t="n"/>
       <c r="C27" s="394" t="n"/>
       <c r="D27" s="261" t="n"/>
       <c r="E27" s="259" t="n"/>
-      <c r="F27" s="405">
+      <c r="F27" s="406">
         <f>F17*(F14+F26)</f>
         <v/>
       </c>
-      <c r="G27" s="405">
+      <c r="G27" s="406">
         <f>G17*(G14+G26)</f>
         <v/>
       </c>
-      <c r="H27" s="405">
+      <c r="H27" s="406">
         <f>H17*(H14+H26)</f>
         <v/>
       </c>
-      <c r="I27" s="405">
+      <c r="I27" s="406">
         <f>I17*(I14+I26)</f>
         <v/>
       </c>
-      <c r="J27" s="405">
+      <c r="J27" s="406">
         <f>J17*(J14+J26)</f>
         <v/>
       </c>
-      <c r="K27" s="405">
+      <c r="K27" s="406">
         <f>K17*(K14+K26)</f>
         <v/>
       </c>
-      <c r="L27" s="405">
+      <c r="L27" s="406">
         <f>L17*(L14+L26)</f>
         <v/>
       </c>
-      <c r="M27" s="405">
+      <c r="M27" s="406">
         <f>M17*(M14+M26)</f>
         <v/>
       </c>
-      <c r="N27" s="405">
+      <c r="N27" s="406">
         <f>N17*(N14+N26)</f>
         <v/>
       </c>
-      <c r="O27" s="405">
+      <c r="O27" s="406">
         <f>O17*(O14+O26)</f>
         <v/>
       </c>
-      <c r="P27" s="405">
+      <c r="P27" s="406">
         <f>P17*(P14+P26)</f>
         <v/>
       </c>
-      <c r="Q27" s="405">
+      <c r="Q27" s="406">
         <f>Q17*(Q14+Q26)</f>
         <v/>
       </c>
-      <c r="R27" s="405">
+      <c r="R27" s="406">
         <f>R17*(R14+R26)</f>
         <v/>
       </c>
-      <c r="S27" s="405">
+      <c r="S27" s="406">
         <f>S17*(S14+S26)</f>
         <v/>
       </c>
-      <c r="T27" s="405">
+      <c r="T27" s="406">
         <f>T17*(T14+T26)</f>
         <v/>
       </c>
-      <c r="U27" s="405">
+      <c r="U27" s="406">
         <f>U17*(U14+U26)</f>
         <v/>
       </c>
-      <c r="V27" s="405">
+      <c r="V27" s="406">
         <f>V17*(V14+V26)</f>
         <v/>
       </c>
-      <c r="W27" s="405">
+      <c r="W27" s="406">
         <f>W17*(W14+W26)</f>
         <v/>
       </c>
-      <c r="X27" s="405">
+      <c r="X27" s="406">
         <f>X17*(X14+X26)</f>
         <v/>
       </c>
-      <c r="Y27" s="405">
+      <c r="Y27" s="406">
         <f>Y17*(Y14+Y26)</f>
         <v/>
       </c>
-      <c r="Z27" s="405">
+      <c r="Z27" s="406">
         <f>Z17*(Z14+Z26)</f>
         <v/>
       </c>
-      <c r="AA27" s="405">
+      <c r="AA27" s="406">
         <f>AA17*(AA14+AA26)</f>
         <v/>
       </c>
-      <c r="AB27" s="405">
+      <c r="AB27" s="406">
         <f>AB17*(AB14+AB26)</f>
         <v/>
       </c>
-      <c r="AC27" s="405">
+      <c r="AC27" s="406">
         <f>AC17*(AC14+AC26)</f>
         <v/>
       </c>
-      <c r="AD27" s="405">
+      <c r="AD27" s="406">
         <f>AD17*(AD14+AD26)</f>
         <v/>
       </c>
-      <c r="AE27" s="405">
+      <c r="AE27" s="406">
         <f>AE17*(AE14+AE26)</f>
         <v/>
       </c>
-      <c r="AF27" s="405">
+      <c r="AF27" s="406">
         <f>AF17*(AF14+AF26)</f>
         <v/>
       </c>
-      <c r="AG27" s="429" t="n"/>
-      <c r="AH27" s="429" t="n"/>
-      <c r="AI27" s="429" t="n"/>
-      <c r="AJ27" s="429" t="n"/>
-      <c r="AK27" s="429" t="n"/>
-      <c r="AL27" s="429" t="n"/>
-      <c r="AM27" s="429" t="n"/>
-      <c r="AN27" s="429" t="n"/>
-      <c r="AO27" s="429" t="n"/>
-      <c r="AP27" s="429" t="n"/>
-      <c r="AQ27" s="429" t="n"/>
-      <c r="AR27" s="429" t="n"/>
-      <c r="AS27" s="429" t="n"/>
-      <c r="AT27" s="429" t="n"/>
-      <c r="AU27" s="429" t="n"/>
-      <c r="AV27" s="429" t="n"/>
-      <c r="AW27" s="429" t="n"/>
+      <c r="AG27" s="432" t="n"/>
+      <c r="AH27" s="432" t="n"/>
+      <c r="AI27" s="432" t="n"/>
+      <c r="AJ27" s="432" t="n"/>
+      <c r="AK27" s="432" t="n"/>
+      <c r="AL27" s="432" t="n"/>
+      <c r="AM27" s="432" t="n"/>
+      <c r="AN27" s="432" t="n"/>
+      <c r="AO27" s="432" t="n"/>
+      <c r="AP27" s="432" t="n"/>
+      <c r="AQ27" s="432" t="n"/>
+      <c r="AR27" s="432" t="n"/>
+      <c r="AS27" s="432" t="n"/>
+      <c r="AT27" s="432" t="n"/>
+      <c r="AU27" s="432" t="n"/>
+      <c r="AV27" s="432" t="n"/>
+      <c r="AW27" s="432" t="n"/>
     </row>
     <row r="28" ht="12" customHeight="1" s="244">
       <c r="A28" s="261" t="n"/>
-      <c r="B28" s="402" t="n"/>
+      <c r="B28" s="403" t="n"/>
       <c r="C28" s="394" t="n"/>
       <c r="D28" s="261" t="n"/>
       <c r="E28" s="259" t="n"/>
-      <c r="F28" s="406">
+      <c r="F28" s="407">
         <f>F27/(1.163*F25)</f>
         <v/>
       </c>
-      <c r="G28" s="406">
+      <c r="G28" s="407">
         <f>G27/(1.163*G25)</f>
         <v/>
       </c>
-      <c r="H28" s="406">
+      <c r="H28" s="407">
         <f>H27/(1.163*H25)</f>
         <v/>
       </c>
-      <c r="I28" s="406">
+      <c r="I28" s="407">
         <f>I27/(1.163*I25)</f>
         <v/>
       </c>
-      <c r="J28" s="406">
+      <c r="J28" s="407">
         <f>J27/(1.163*J25)</f>
         <v/>
       </c>
-      <c r="K28" s="406">
+      <c r="K28" s="407">
         <f>K27/(1.163*K25)</f>
         <v/>
       </c>
-      <c r="L28" s="406">
+      <c r="L28" s="407">
         <f>L27/(1.163*L25)</f>
         <v/>
       </c>
-      <c r="M28" s="406">
+      <c r="M28" s="407">
         <f>M27/(1.163*M25)</f>
         <v/>
       </c>
-      <c r="N28" s="406">
+      <c r="N28" s="407">
         <f>N27/(1.163*N25)</f>
         <v/>
       </c>
-      <c r="O28" s="406">
+      <c r="O28" s="407">
         <f>O27/(1.163*O25)</f>
         <v/>
       </c>
-      <c r="P28" s="406">
+      <c r="P28" s="407">
         <f>P27/(1.163*P25)</f>
         <v/>
       </c>
-      <c r="Q28" s="406">
+      <c r="Q28" s="407">
         <f>Q27/(1.163*Q25)</f>
         <v/>
       </c>
-      <c r="R28" s="406">
+      <c r="R28" s="407">
         <f>R27/(1.163*R25)</f>
         <v/>
       </c>
-      <c r="S28" s="406">
+      <c r="S28" s="407">
         <f>S27/(1.163*S25)</f>
         <v/>
       </c>
-      <c r="T28" s="406">
+      <c r="T28" s="407">
         <f>T27/(1.163*T25)</f>
         <v/>
       </c>
-      <c r="U28" s="406">
+      <c r="U28" s="407">
         <f>U27/(1.163*U25)</f>
         <v/>
       </c>
-      <c r="V28" s="406">
+      <c r="V28" s="407">
         <f>V27/(1.163*V25)</f>
         <v/>
       </c>
-      <c r="W28" s="406">
+      <c r="W28" s="407">
         <f>W27/(1.163*W25)</f>
         <v/>
       </c>
-      <c r="X28" s="406">
+      <c r="X28" s="407">
         <f>X27/(1.163*X25)</f>
         <v/>
       </c>
-      <c r="Y28" s="406">
+      <c r="Y28" s="407">
         <f>Y27/(1.163*Y25)</f>
         <v/>
       </c>
-      <c r="Z28" s="406">
+      <c r="Z28" s="407">
         <f>Z27/(1.163*Z25)</f>
         <v/>
       </c>
-      <c r="AA28" s="406">
+      <c r="AA28" s="407">
         <f>AA27/(1.163*AA25)</f>
         <v/>
       </c>
-      <c r="AB28" s="406">
+      <c r="AB28" s="407">
         <f>AB27/(1.163*AB25)</f>
         <v/>
       </c>
-      <c r="AC28" s="406">
+      <c r="AC28" s="407">
         <f>AC27/(1.163*AC25)</f>
         <v/>
       </c>
-      <c r="AD28" s="406">
+      <c r="AD28" s="407">
         <f>AD27/(1.163*AD25)</f>
         <v/>
       </c>
-      <c r="AE28" s="406">
+      <c r="AE28" s="407">
         <f>AE27/(1.163*AE25)</f>
         <v/>
       </c>
-      <c r="AF28" s="406">
+      <c r="AF28" s="407">
         <f>AF27/(1.163*AF25)</f>
         <v/>
       </c>
-      <c r="AG28" s="430" t="n"/>
-      <c r="AH28" s="430" t="n"/>
-      <c r="AI28" s="430" t="n"/>
-      <c r="AJ28" s="430" t="n"/>
-      <c r="AK28" s="430" t="n"/>
-      <c r="AL28" s="430" t="n"/>
-      <c r="AM28" s="430" t="n"/>
-      <c r="AN28" s="430" t="n"/>
-      <c r="AO28" s="430" t="n"/>
-      <c r="AP28" s="430" t="n"/>
-      <c r="AQ28" s="430" t="n"/>
-      <c r="AR28" s="430" t="n"/>
-      <c r="AS28" s="430" t="n"/>
-      <c r="AT28" s="430" t="n"/>
-      <c r="AU28" s="430" t="n"/>
-      <c r="AV28" s="430" t="n"/>
-      <c r="AW28" s="430" t="n"/>
+      <c r="AG28" s="433" t="n"/>
+      <c r="AH28" s="433" t="n"/>
+      <c r="AI28" s="433" t="n"/>
+      <c r="AJ28" s="433" t="n"/>
+      <c r="AK28" s="433" t="n"/>
+      <c r="AL28" s="433" t="n"/>
+      <c r="AM28" s="433" t="n"/>
+      <c r="AN28" s="433" t="n"/>
+      <c r="AO28" s="433" t="n"/>
+      <c r="AP28" s="433" t="n"/>
+      <c r="AQ28" s="433" t="n"/>
+      <c r="AR28" s="433" t="n"/>
+      <c r="AS28" s="433" t="n"/>
+      <c r="AT28" s="433" t="n"/>
+      <c r="AU28" s="433" t="n"/>
+      <c r="AV28" s="433" t="n"/>
+      <c r="AW28" s="433" t="n"/>
     </row>
     <row r="29" ht="12" customHeight="1" s="244">
       <c r="A29" s="261" t="n"/>
-      <c r="B29" s="402" t="n"/>
+      <c r="B29" s="403" t="n"/>
       <c r="C29" s="394" t="n"/>
       <c r="D29" s="261" t="n"/>
       <c r="E29" s="259" t="n"/>
-      <c r="F29" s="407">
+      <c r="F29" s="408">
         <f>F17/(F22*0.01)</f>
         <v/>
       </c>
-      <c r="G29" s="407">
+      <c r="G29" s="408">
         <f>G17/(G22*0.01)</f>
         <v/>
       </c>
-      <c r="H29" s="407">
+      <c r="H29" s="408">
         <f>H17/(H22*0.01)</f>
         <v/>
       </c>
-      <c r="I29" s="407">
+      <c r="I29" s="408">
         <f>I17/(I22*0.01)</f>
         <v/>
       </c>
-      <c r="J29" s="407">
+      <c r="J29" s="408">
         <f>J17/(J22*0.01)</f>
         <v/>
       </c>
-      <c r="K29" s="407">
+      <c r="K29" s="408">
         <f>K17/(K22*0.01)</f>
         <v/>
       </c>
-      <c r="L29" s="407">
+      <c r="L29" s="408">
         <f>L17/(L22*0.01)</f>
         <v/>
       </c>
-      <c r="M29" s="407">
+      <c r="M29" s="408">
         <f>M17/(M22*0.01)</f>
         <v/>
       </c>
-      <c r="N29" s="407">
+      <c r="N29" s="408">
         <f>N17/(N22*0.01)</f>
         <v/>
       </c>
-      <c r="O29" s="407">
+      <c r="O29" s="408">
         <f>O17/(O22*0.01)</f>
         <v/>
       </c>
-      <c r="P29" s="407">
+      <c r="P29" s="408">
         <f>P17/(P22*0.01)</f>
         <v/>
       </c>
-      <c r="Q29" s="407">
+      <c r="Q29" s="408">
         <f>Q17/(Q22*0.01)</f>
         <v/>
       </c>
-      <c r="R29" s="407">
+      <c r="R29" s="408">
         <f>R17/(R22*0.01)</f>
         <v/>
       </c>
-      <c r="S29" s="407">
+      <c r="S29" s="408">
         <f>S17/(S22*0.01)</f>
         <v/>
       </c>
-      <c r="T29" s="407">
+      <c r="T29" s="408">
         <f>T17/(T22*0.01)</f>
         <v/>
       </c>
-      <c r="U29" s="407">
+      <c r="U29" s="408">
         <f>U17/(U22*0.01)</f>
         <v/>
       </c>
-      <c r="V29" s="407">
+      <c r="V29" s="408">
         <f>V17/(V22*0.01)</f>
         <v/>
       </c>
-      <c r="W29" s="407">
+      <c r="W29" s="408">
         <f>W17/(W22*0.01)</f>
         <v/>
       </c>
-      <c r="X29" s="407">
+      <c r="X29" s="408">
         <f>X17/(X22*0.01)</f>
         <v/>
       </c>
-      <c r="Y29" s="407">
+      <c r="Y29" s="408">
         <f>Y17/(Y22*0.01)</f>
         <v/>
       </c>
-      <c r="Z29" s="407">
+      <c r="Z29" s="408">
         <f>Z17/(Z22*0.01)</f>
         <v/>
       </c>
-      <c r="AA29" s="407">
+      <c r="AA29" s="408">
         <f>AA17/(AA22*0.01)</f>
         <v/>
       </c>
-      <c r="AB29" s="407">
+      <c r="AB29" s="408">
         <f>AB17/(AB22*0.01)</f>
         <v/>
       </c>
-      <c r="AC29" s="407">
+      <c r="AC29" s="408">
         <f>AC17/(AC22*0.01)</f>
         <v/>
       </c>
-      <c r="AD29" s="407">
+      <c r="AD29" s="408">
         <f>AD17/(AD22*0.01)</f>
         <v/>
       </c>
-      <c r="AE29" s="407">
+      <c r="AE29" s="408">
         <f>AE17/(AE22*0.01)</f>
         <v/>
       </c>
-      <c r="AF29" s="407">
+      <c r="AF29" s="408">
         <f>AF17/(AF22*0.01)</f>
         <v/>
       </c>
-      <c r="AG29" s="431" t="n"/>
-      <c r="AH29" s="431" t="n"/>
-      <c r="AI29" s="431" t="n"/>
-      <c r="AJ29" s="431" t="n"/>
-      <c r="AK29" s="431" t="n"/>
-      <c r="AL29" s="431" t="n"/>
-      <c r="AM29" s="431" t="n"/>
-      <c r="AN29" s="431" t="n"/>
-      <c r="AO29" s="431" t="n"/>
-      <c r="AP29" s="431" t="n"/>
-      <c r="AQ29" s="431" t="n"/>
-      <c r="AR29" s="431" t="n"/>
-      <c r="AS29" s="431" t="n"/>
-      <c r="AT29" s="431" t="n"/>
-      <c r="AU29" s="431" t="n"/>
-      <c r="AV29" s="431" t="n"/>
-      <c r="AW29" s="431" t="n"/>
+      <c r="AG29" s="434" t="n"/>
+      <c r="AH29" s="434" t="n"/>
+      <c r="AI29" s="434" t="n"/>
+      <c r="AJ29" s="434" t="n"/>
+      <c r="AK29" s="434" t="n"/>
+      <c r="AL29" s="434" t="n"/>
+      <c r="AM29" s="434" t="n"/>
+      <c r="AN29" s="434" t="n"/>
+      <c r="AO29" s="434" t="n"/>
+      <c r="AP29" s="434" t="n"/>
+      <c r="AQ29" s="434" t="n"/>
+      <c r="AR29" s="434" t="n"/>
+      <c r="AS29" s="434" t="n"/>
+      <c r="AT29" s="434" t="n"/>
+      <c r="AU29" s="434" t="n"/>
+      <c r="AV29" s="434" t="n"/>
+      <c r="AW29" s="434" t="n"/>
     </row>
     <row r="30" ht="12" customHeight="1" s="244">
       <c r="A30" s="261" t="n"/>
-      <c r="B30" s="402" t="n"/>
+      <c r="B30" s="403" t="n"/>
       <c r="C30" s="394" t="inlineStr">
         <is>
           <t>BAĞLANTI BORULARI</t>
@@ -23691,101 +23241,101 @@
         </is>
       </c>
       <c r="E30" s="259" t="n"/>
-      <c r="F30" s="408" t="n">
+      <c r="F30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="408" t="n">
+      <c r="G30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="408" t="n">
+      <c r="H30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="408" t="n">
+      <c r="I30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="J30" s="408" t="n">
+      <c r="J30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="408" t="n">
+      <c r="K30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="L30" s="408" t="n">
+      <c r="L30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="408" t="n">
+      <c r="M30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="408" t="n">
+      <c r="N30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="408" t="n">
+      <c r="O30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="P30" s="408" t="n">
+      <c r="P30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="408" t="n">
+      <c r="Q30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="R30" s="408" t="n">
+      <c r="R30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="408" t="n">
+      <c r="S30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="T30" s="408" t="n">
+      <c r="T30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="408" t="n">
+      <c r="U30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="408" t="n">
+      <c r="V30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="408" t="n">
+      <c r="W30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="X30" s="408" t="n">
+      <c r="X30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="Y30" s="408" t="n">
+      <c r="Y30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="Z30" s="408" t="n">
+      <c r="Z30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AA30" s="408" t="n">
+      <c r="AA30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AB30" s="408" t="n">
+      <c r="AB30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" s="408" t="n">
+      <c r="AC30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="408" t="n">
+      <c r="AD30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AE30" s="408" t="n">
+      <c r="AE30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AF30" s="408" t="n">
+      <c r="AF30" s="409" t="n">
         <v>0</v>
       </c>
-      <c r="AG30" s="432" t="n"/>
-      <c r="AO30" s="432" t="n"/>
-      <c r="AP30" s="432" t="n"/>
-      <c r="AQ30" s="432" t="n"/>
-      <c r="AR30" s="432" t="n"/>
-      <c r="AS30" s="432" t="n"/>
-      <c r="AT30" s="432" t="n"/>
-      <c r="AU30" s="432" t="n"/>
-      <c r="AV30" s="432" t="n"/>
-      <c r="AW30" s="432" t="n"/>
+      <c r="AG30" s="435" t="n"/>
+      <c r="AO30" s="435" t="n"/>
+      <c r="AP30" s="435" t="n"/>
+      <c r="AQ30" s="435" t="n"/>
+      <c r="AR30" s="435" t="n"/>
+      <c r="AS30" s="435" t="n"/>
+      <c r="AT30" s="435" t="n"/>
+      <c r="AU30" s="435" t="n"/>
+      <c r="AV30" s="435" t="n"/>
+      <c r="AW30" s="435" t="n"/>
     </row>
     <row r="31" ht="12" customHeight="1" s="244">
       <c r="A31" s="261" t="n"/>
-      <c r="B31" s="402" t="n"/>
+      <c r="B31" s="403" t="n"/>
       <c r="C31" s="394" t="n"/>
       <c r="D31" s="261" t="n"/>
       <c r="E31" s="259" t="n"/>
@@ -23917,7 +23467,7 @@
     </row>
     <row r="32" ht="12" customHeight="1" s="244">
       <c r="A32" s="261" t="n"/>
-      <c r="B32" s="401" t="n"/>
+      <c r="B32" s="402" t="n"/>
       <c r="C32" s="394" t="inlineStr">
         <is>
           <t>DÜZ BORU BASINÇ KAYBI (5)</t>
@@ -23929,108 +23479,108 @@
         </is>
       </c>
       <c r="E32" s="259" t="n"/>
-      <c r="F32" s="407" t="n">
-        <v>2271</v>
-      </c>
-      <c r="G32" s="407" t="n">
-        <v>534</v>
-      </c>
-      <c r="H32" s="407" t="n">
-        <v>1437</v>
-      </c>
-      <c r="I32" s="407" t="n">
-        <v>1489</v>
-      </c>
-      <c r="J32" s="407" t="n">
-        <v>1911</v>
-      </c>
-      <c r="K32" s="407" t="n">
-        <v>2880</v>
-      </c>
-      <c r="L32" s="407" t="n">
-        <v>3445</v>
-      </c>
-      <c r="M32" s="407" t="n">
-        <v>1964</v>
-      </c>
-      <c r="N32" s="407" t="n">
-        <v>79</v>
-      </c>
-      <c r="O32" s="407" t="n">
-        <v>1027</v>
-      </c>
-      <c r="P32" s="407" t="n">
-        <v>426</v>
-      </c>
-      <c r="Q32" s="407" t="n">
-        <v>343</v>
-      </c>
-      <c r="R32" s="407" t="n">
-        <v>2087</v>
-      </c>
-      <c r="S32" s="407" t="n">
-        <v>2210</v>
-      </c>
-      <c r="T32" s="407" t="n">
-        <v>1655</v>
-      </c>
-      <c r="U32" s="407" t="n">
-        <v>1164</v>
-      </c>
-      <c r="V32" s="407" t="n">
-        <v>2227</v>
-      </c>
-      <c r="W32" s="407" t="n">
-        <v>27</v>
-      </c>
-      <c r="X32" s="407" t="n">
-        <v>2647</v>
-      </c>
-      <c r="Y32" s="407" t="n">
-        <v>612</v>
-      </c>
-      <c r="Z32" s="407" t="n">
-        <v>1505</v>
-      </c>
-      <c r="AA32" s="407" t="n">
-        <v>1523</v>
-      </c>
-      <c r="AB32" s="407" t="n">
-        <v>2102</v>
-      </c>
-      <c r="AC32" s="407" t="n">
-        <v>2804</v>
-      </c>
-      <c r="AD32" s="407" t="n">
-        <v>3445</v>
-      </c>
-      <c r="AE32" s="407" t="n">
-        <v>1966</v>
-      </c>
-      <c r="AF32" s="407" t="n">
-        <v>96</v>
-      </c>
-      <c r="AG32" s="431" t="n"/>
-      <c r="AH32" s="431" t="n"/>
-      <c r="AI32" s="431" t="n"/>
-      <c r="AJ32" s="431" t="n"/>
-      <c r="AK32" s="431" t="n"/>
-      <c r="AL32" s="431" t="n"/>
-      <c r="AM32" s="431" t="n"/>
-      <c r="AN32" s="431" t="n"/>
-      <c r="AO32" s="431" t="n"/>
-      <c r="AP32" s="431" t="n"/>
-      <c r="AQ32" s="431" t="n"/>
-      <c r="AR32" s="431" t="n"/>
-      <c r="AS32" s="431" t="n"/>
-      <c r="AT32" s="431" t="n"/>
-      <c r="AU32" s="431" t="n"/>
-      <c r="AV32" s="431" t="n"/>
-      <c r="AW32" s="431" t="n"/>
+      <c r="F32" s="408" t="n">
+        <v>7783</v>
+      </c>
+      <c r="G32" s="408" t="n">
+        <v>5981</v>
+      </c>
+      <c r="H32" s="408" t="n">
+        <v>7887</v>
+      </c>
+      <c r="I32" s="408" t="n">
+        <v>11613</v>
+      </c>
+      <c r="J32" s="408" t="n">
+        <v>11807</v>
+      </c>
+      <c r="K32" s="408" t="n">
+        <v>15452</v>
+      </c>
+      <c r="L32" s="408" t="n">
+        <v>17902</v>
+      </c>
+      <c r="M32" s="408" t="n">
+        <v>6864</v>
+      </c>
+      <c r="N32" s="408" t="n">
+        <v>579</v>
+      </c>
+      <c r="O32" s="408" t="n">
+        <v>4306</v>
+      </c>
+      <c r="P32" s="408" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Q32" s="408" t="n">
+        <v>6348</v>
+      </c>
+      <c r="R32" s="408" t="n">
+        <v>11807</v>
+      </c>
+      <c r="S32" s="408" t="n">
+        <v>17055</v>
+      </c>
+      <c r="T32" s="408" t="n">
+        <v>17910</v>
+      </c>
+      <c r="U32" s="408" t="n">
+        <v>7958</v>
+      </c>
+      <c r="V32" s="408" t="n">
+        <v>14549</v>
+      </c>
+      <c r="W32" s="408" t="n">
+        <v>156</v>
+      </c>
+      <c r="X32" s="408" t="n">
+        <v>8930</v>
+      </c>
+      <c r="Y32" s="408" t="n">
+        <v>6519</v>
+      </c>
+      <c r="Z32" s="408" t="n">
+        <v>5062</v>
+      </c>
+      <c r="AA32" s="408" t="n">
+        <v>11613</v>
+      </c>
+      <c r="AB32" s="408" t="n">
+        <v>11905</v>
+      </c>
+      <c r="AC32" s="408" t="n">
+        <v>15107</v>
+      </c>
+      <c r="AD32" s="408" t="n">
+        <v>17902</v>
+      </c>
+      <c r="AE32" s="408" t="n">
+        <v>7100</v>
+      </c>
+      <c r="AF32" s="408" t="n">
+        <v>596</v>
+      </c>
+      <c r="AG32" s="434" t="n"/>
+      <c r="AH32" s="434" t="n"/>
+      <c r="AI32" s="434" t="n"/>
+      <c r="AJ32" s="434" t="n"/>
+      <c r="AK32" s="434" t="n"/>
+      <c r="AL32" s="434" t="n"/>
+      <c r="AM32" s="434" t="n"/>
+      <c r="AN32" s="434" t="n"/>
+      <c r="AO32" s="434" t="n"/>
+      <c r="AP32" s="434" t="n"/>
+      <c r="AQ32" s="434" t="n"/>
+      <c r="AR32" s="434" t="n"/>
+      <c r="AS32" s="434" t="n"/>
+      <c r="AT32" s="434" t="n"/>
+      <c r="AU32" s="434" t="n"/>
+      <c r="AV32" s="434" t="n"/>
+      <c r="AW32" s="434" t="n"/>
     </row>
     <row r="33" ht="12" customHeight="1" s="244">
       <c r="A33" s="261" t="n"/>
-      <c r="B33" s="401" t="n"/>
+      <c r="B33" s="402" t="n"/>
       <c r="C33" s="394" t="n"/>
       <c r="D33" s="261" t="n"/>
       <c r="E33" s="259" t="n"/>
@@ -24162,7 +23712,7 @@
     </row>
     <row r="34" ht="12" customHeight="1" s="244">
       <c r="A34" s="261" t="n"/>
-      <c r="B34" s="401" t="n"/>
+      <c r="B34" s="402" t="n"/>
       <c r="C34" s="394" t="n"/>
       <c r="D34" s="261" t="n"/>
       <c r="E34" s="259" t="n"/>
@@ -24274,7 +23824,7 @@
         <f>AF32+AF33</f>
         <v/>
       </c>
-      <c r="AG34" s="427" t="n"/>
+      <c r="AG34" s="430" t="n"/>
       <c r="AH34" s="259" t="n"/>
       <c r="AI34" s="259" t="n"/>
       <c r="AJ34" s="259" t="n"/>
@@ -24294,135 +23844,135 @@
     </row>
     <row r="35" ht="12" customHeight="1" s="244">
       <c r="A35" s="261" t="n"/>
-      <c r="B35" s="401" t="n"/>
+      <c r="B35" s="402" t="n"/>
       <c r="C35" s="282" t="n"/>
       <c r="D35" s="261" t="n"/>
       <c r="E35" s="259" t="n"/>
-      <c r="F35" s="409">
+      <c r="F35" s="410">
         <f>MAX(F34:AF34)-F34</f>
         <v/>
       </c>
-      <c r="G35" s="409">
+      <c r="G35" s="410">
         <f>MAX(F34:AF34)-G34</f>
         <v/>
       </c>
-      <c r="H35" s="409">
+      <c r="H35" s="410">
         <f>MAX(F34:AF34)-H34</f>
         <v/>
       </c>
-      <c r="I35" s="409">
+      <c r="I35" s="410">
         <f>MAX(F34:AF34)-I34</f>
         <v/>
       </c>
-      <c r="J35" s="409">
+      <c r="J35" s="410">
         <f>MAX(F34:AF34)-J34</f>
         <v/>
       </c>
-      <c r="K35" s="409">
+      <c r="K35" s="410">
         <f>MAX(F34:AF34)-K34</f>
         <v/>
       </c>
-      <c r="L35" s="409">
+      <c r="L35" s="410">
         <f>MAX(F34:AF34)-L34</f>
         <v/>
       </c>
-      <c r="M35" s="409">
+      <c r="M35" s="410">
         <f>MAX(F34:AF34)-M34</f>
         <v/>
       </c>
-      <c r="N35" s="409">
+      <c r="N35" s="410">
         <f>MAX(F34:AF34)-N34</f>
         <v/>
       </c>
-      <c r="O35" s="409">
+      <c r="O35" s="410">
         <f>MAX(F34:AF34)-O34</f>
         <v/>
       </c>
-      <c r="P35" s="409">
+      <c r="P35" s="410">
         <f>MAX(F34:AF34)-P34</f>
         <v/>
       </c>
-      <c r="Q35" s="409">
+      <c r="Q35" s="410">
         <f>MAX(F34:AF34)-Q34</f>
         <v/>
       </c>
-      <c r="R35" s="409">
+      <c r="R35" s="410">
         <f>MAX(F34:AF34)-R34</f>
         <v/>
       </c>
-      <c r="S35" s="409">
+      <c r="S35" s="410">
         <f>MAX(F34:AF34)-S34</f>
         <v/>
       </c>
-      <c r="T35" s="409">
+      <c r="T35" s="410">
         <f>MAX(F34:AF34)-T34</f>
         <v/>
       </c>
-      <c r="U35" s="409">
+      <c r="U35" s="410">
         <f>MAX(F34:AF34)-U34</f>
         <v/>
       </c>
-      <c r="V35" s="409">
+      <c r="V35" s="410">
         <f>MAX(F34:AF34)-V34</f>
         <v/>
       </c>
-      <c r="W35" s="409">
+      <c r="W35" s="410">
         <f>MAX(F34:AF34)-W34</f>
         <v/>
       </c>
-      <c r="X35" s="409">
+      <c r="X35" s="410">
         <f>MAX(F34:AF34)-X34</f>
         <v/>
       </c>
-      <c r="Y35" s="409">
+      <c r="Y35" s="410">
         <f>MAX(F34:AF34)-Y34</f>
         <v/>
       </c>
-      <c r="Z35" s="409">
+      <c r="Z35" s="410">
         <f>MAX(F34:AF34)-Z34</f>
         <v/>
       </c>
-      <c r="AA35" s="409">
+      <c r="AA35" s="410">
         <f>MAX(F34:AF34)-AA34</f>
         <v/>
       </c>
-      <c r="AB35" s="409">
+      <c r="AB35" s="410">
         <f>MAX(F34:AF34)-AB34</f>
         <v/>
       </c>
-      <c r="AC35" s="409">
+      <c r="AC35" s="410">
         <f>MAX(F34:AF34)-AC34</f>
         <v/>
       </c>
-      <c r="AD35" s="409">
+      <c r="AD35" s="410">
         <f>MAX(F34:AF34)-AD34</f>
         <v/>
       </c>
-      <c r="AE35" s="409">
+      <c r="AE35" s="410">
         <f>MAX(F34:AF34)-AE34</f>
         <v/>
       </c>
-      <c r="AF35" s="409">
+      <c r="AF35" s="410">
         <f>MAX(F34:AF34)-AF34</f>
         <v/>
       </c>
-      <c r="AG35" s="433" t="n"/>
-      <c r="AH35" s="433" t="n"/>
-      <c r="AI35" s="433" t="n"/>
-      <c r="AJ35" s="433" t="n"/>
-      <c r="AK35" s="433" t="n"/>
-      <c r="AL35" s="433" t="n"/>
-      <c r="AM35" s="433" t="n"/>
-      <c r="AN35" s="433" t="n"/>
-      <c r="AO35" s="433" t="n"/>
-      <c r="AP35" s="433" t="n"/>
-      <c r="AQ35" s="433" t="n"/>
-      <c r="AR35" s="433" t="n"/>
-      <c r="AS35" s="433" t="n"/>
-      <c r="AT35" s="433" t="n"/>
-      <c r="AU35" s="433" t="n"/>
-      <c r="AV35" s="433" t="n"/>
-      <c r="AW35" s="433" t="n"/>
+      <c r="AG35" s="436" t="n"/>
+      <c r="AH35" s="436" t="n"/>
+      <c r="AI35" s="436" t="n"/>
+      <c r="AJ35" s="436" t="n"/>
+      <c r="AK35" s="436" t="n"/>
+      <c r="AL35" s="436" t="n"/>
+      <c r="AM35" s="436" t="n"/>
+      <c r="AN35" s="436" t="n"/>
+      <c r="AO35" s="436" t="n"/>
+      <c r="AP35" s="436" t="n"/>
+      <c r="AQ35" s="436" t="n"/>
+      <c r="AR35" s="436" t="n"/>
+      <c r="AS35" s="436" t="n"/>
+      <c r="AT35" s="436" t="n"/>
+      <c r="AU35" s="436" t="n"/>
+      <c r="AV35" s="436" t="n"/>
+      <c r="AW35" s="436" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1" s="244">
       <c r="D36" s="266" t="inlineStr">
@@ -24444,6 +23994,11 @@
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1" s="244">
+      <c r="B38" s="411" t="inlineStr">
+        <is>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 201-1 (37.8 °C), 202-2 (37.1 °C), 202-3 (37.1 °C), 203-4 (37.8 °C), 204-5 (37.8 °C), 205-6 (37.7 °C), 205-7 (37.7 °C), 206-8 (31.9 °C) ...</t>
+        </is>
+      </c>
       <c r="F38" s="243" t="inlineStr">
         <is>
           <t>GÖRE AYARLANMALIDIR….</t>
@@ -24451,21 +24006,26 @@
       </c>
     </row>
     <row r="39" ht="12.75" customHeight="1" s="244">
-      <c r="F39" s="410" t="inlineStr">
+      <c r="B39" s="412" t="inlineStr">
+        <is>
+          <t>Sınır içinde kalmak için q" ≤ 100 W/m² (oturma) gerekir; 35 W/m ile bu, boru aralığı ≈ 35 cm demektir. Boru aralığı 15 cm (kullanıcı seçimi) değiştirilmemiştir — ısı kaybı ile qh girilmelidir.</t>
+        </is>
+      </c>
+      <c r="F39" s="413" t="inlineStr">
         <is>
           <t>Δpö</t>
         </is>
       </c>
-      <c r="G39" s="410" t="inlineStr">
+      <c r="G39" s="413" t="inlineStr">
         <is>
           <t>EK VI-14i Tablosundan q değeri m³/h çevrilir DN10 borusu için</t>
         </is>
       </c>
-      <c r="H39" s="410" t="n"/>
-      <c r="I39" s="410" t="n"/>
+      <c r="H39" s="413" t="n"/>
+      <c r="I39" s="413" t="n"/>
     </row>
     <row r="40" ht="12.75" customHeight="1" s="244">
-      <c r="A40" s="411" t="inlineStr">
+      <c r="A40" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (1)</t>
         </is>
@@ -24475,17 +24035,17 @@
           <t>Şek. 19.7.1 den seçilmiştir.</t>
         </is>
       </c>
-      <c r="F40" s="410" t="n"/>
-      <c r="G40" s="410" t="inlineStr">
+      <c r="F40" s="413" t="n"/>
+      <c r="G40" s="413" t="inlineStr">
         <is>
           <t>R (Pa/m) 1metre borudaki basın. Kaybı bulunur..</t>
         </is>
       </c>
-      <c r="H40" s="410" t="n"/>
-      <c r="I40" s="410" t="n"/>
+      <c r="H40" s="413" t="n"/>
+      <c r="I40" s="413" t="n"/>
     </row>
     <row r="41" ht="12.75" customHeight="1" s="244">
-      <c r="A41" s="411" t="inlineStr">
+      <c r="A41" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (2)</t>
         </is>
@@ -24495,17 +24055,17 @@
           <t>Kombi gidiş suyu sıcaklığı 45 °C, dönüş 35 °C seçilmiştir.</t>
         </is>
       </c>
-      <c r="F41" s="410" t="n"/>
-      <c r="G41" s="410" t="inlineStr">
+      <c r="F41" s="413" t="n"/>
+      <c r="G41" s="413" t="inlineStr">
         <is>
           <t xml:space="preserve">toplam boru boyu ile çarpımından Δpö (Pa) bulunur.  </t>
         </is>
       </c>
-      <c r="H41" s="410" t="n"/>
-      <c r="I41" s="410" t="n"/>
+      <c r="H41" s="413" t="n"/>
+      <c r="I41" s="413" t="n"/>
     </row>
     <row r="42" ht="12.75" customHeight="1" s="244">
-      <c r="A42" s="411" t="inlineStr">
+      <c r="A42" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (3)</t>
         </is>
@@ -24517,19 +24077,19 @@
       </c>
     </row>
     <row r="43" ht="12.75" customHeight="1" s="244">
-      <c r="A43" s="411" t="inlineStr">
+      <c r="A43" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (4)</t>
         </is>
       </c>
       <c r="B43" s="243" t="inlineStr">
         <is>
-          <t>Alta geçen ısı 0,2 q" olarak alınmıştır. qh = 17,5 W/m × devre boyu (şablon birim verimi); ısı kaybı hesabı ayrıca yapılmalıdır.</t>
+          <t>Alta geçen ısı 0,2 q" olarak alınmıştır. qh = 35 W/m × devre boyu (plan etiketi ve kolon şeması ile aynı esas); ayrı ısı kaybı hesabı yapılmamıştır.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="12.75" customHeight="1" s="244">
-      <c r="A44" s="411" t="inlineStr">
+      <c r="A44" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (5)</t>
         </is>
@@ -24541,7 +24101,7 @@
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1" s="244">
-      <c r="A45" s="411" t="inlineStr">
+      <c r="A45" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (6)</t>
         </is>
@@ -24553,7 +24113,7 @@
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1" s="244">
-      <c r="A46" s="411" t="inlineStr">
+      <c r="A46" s="414" t="inlineStr">
         <is>
           <t xml:space="preserve"> (7)</t>
         </is>
@@ -24565,7 +24125,7 @@
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1" s="244">
-      <c r="A47" s="412" t="n"/>
+      <c r="A47" s="415" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="D16" s="343" t="n">
-        <v>596.1</v>
+        <v>602.4</v>
       </c>
       <c r="E16" s="344" t="n">
         <v>35</v>
@@ -4662,7 +4662,7 @@
         <v/>
       </c>
       <c r="G16" s="340" t="n">
-        <v>17.03</v>
+        <v>17.21</v>
       </c>
       <c r="H16" s="340" t="n">
         <v>1</v>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="D18" s="343" t="n">
-        <v>2845.1</v>
+        <v>2889.9</v>
       </c>
       <c r="E18" s="344" t="n">
         <v>35</v>
@@ -4752,7 +4752,7 @@
         <v/>
       </c>
       <c r="G18" s="340" t="n">
-        <v>81.29000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="H18" s="340" t="n">
         <v>2</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="D23" s="343" t="n">
-        <v>561.1</v>
+        <v>611.4</v>
       </c>
       <c r="E23" s="344" t="n">
         <v>35</v>
@@ -4977,7 +4977,7 @@
         <v/>
       </c>
       <c r="G23" s="340" t="n">
-        <v>16.03</v>
+        <v>17.47</v>
       </c>
       <c r="H23" s="340" t="n">
         <v>1</v>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="D30" s="348" t="n">
-        <v>419.7</v>
+        <v>349</v>
       </c>
       <c r="E30" s="349" t="n">
         <v>35</v>
@@ -5292,7 +5292,7 @@
         <v/>
       </c>
       <c r="G30" s="345" t="n">
-        <v>11.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H30" s="345" t="n">
         <v>1</v>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="D33" s="348" t="n">
-        <v>3069.5</v>
+        <v>2889.9</v>
       </c>
       <c r="E33" s="349" t="n">
         <v>35</v>
@@ -5415,7 +5415,7 @@
         <v/>
       </c>
       <c r="G33" s="345" t="n">
-        <v>87.7</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="H33" s="345" t="n">
         <v>2</v>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="D38" s="348" t="n">
-        <v>560.7</v>
+        <v>582</v>
       </c>
       <c r="E38" s="349" t="n">
         <v>35</v>
@@ -5640,7 +5640,7 @@
         <v/>
       </c>
       <c r="G38" s="345" t="n">
-        <v>16.02</v>
+        <v>16.63</v>
       </c>
       <c r="H38" s="345" t="n">
         <v>1</v>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="D45" s="348" t="n">
-        <v>419.7</v>
+        <v>349.3</v>
       </c>
       <c r="E45" s="349" t="n">
         <v>35</v>
@@ -5955,7 +5955,7 @@
         <v/>
       </c>
       <c r="G45" s="345" t="n">
-        <v>11.99</v>
+        <v>9.98</v>
       </c>
       <c r="H45" s="345" t="n">
         <v>1</v>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="D52" s="348" t="n">
-        <v>425.9</v>
+        <v>524.6</v>
       </c>
       <c r="E52" s="349" t="n">
         <v>35</v>
@@ -6270,7 +6270,7 @@
         <v/>
       </c>
       <c r="G52" s="345" t="n">
-        <v>12.17</v>
+        <v>14.99</v>
       </c>
       <c r="H52" s="345" t="n">
         <v>1</v>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="D55" s="348" t="n">
-        <v>3057.2</v>
+        <v>2867.2</v>
       </c>
       <c r="E55" s="349" t="n">
         <v>35</v>
@@ -6393,7 +6393,7 @@
         <v/>
       </c>
       <c r="G55" s="345" t="n">
-        <v>87.34999999999999</v>
+        <v>81.92</v>
       </c>
       <c r="H55" s="345" t="n">
         <v>2</v>
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="D60" s="348" t="n">
-        <v>621.2</v>
+        <v>627.5</v>
       </c>
       <c r="E60" s="349" t="n">
         <v>35</v>
@@ -6618,7 +6618,7 @@
         <v/>
       </c>
       <c r="G60" s="345" t="n">
-        <v>17.75</v>
+        <v>17.93</v>
       </c>
       <c r="H60" s="345" t="n">
         <v>1</v>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="D67" s="348" t="n">
-        <v>420.3</v>
+        <v>344.1</v>
       </c>
       <c r="E67" s="349" t="n">
         <v>35</v>
@@ -6933,7 +6933,7 @@
         <v/>
       </c>
       <c r="G67" s="345" t="n">
-        <v>12.01</v>
+        <v>9.83</v>
       </c>
       <c r="H67" s="345" t="n">
         <v>1</v>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="D74" s="348" t="n">
-        <v>627.5</v>
+        <v>646.8</v>
       </c>
       <c r="E74" s="349" t="n">
         <v>35</v>
@@ -7248,7 +7248,7 @@
         <v/>
       </c>
       <c r="G74" s="345" t="n">
-        <v>17.93</v>
+        <v>18.48</v>
       </c>
       <c r="H74" s="345" t="n">
         <v>1</v>
@@ -12824,7 +12824,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 43972 W</t>
+          <t>TOPLAM ISI = 44002 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -13529,16 +13529,16 @@
         <v>7.61</v>
       </c>
       <c r="N12" s="397" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="O12" s="397" t="n">
         <v>7.87</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>7.1</v>
+        <v>6.98</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>6.74</v>
+        <v>6.49</v>
       </c>
       <c r="R12" s="397" t="n">
         <v>8.76</v>
@@ -13556,7 +13556,7 @@
         <v>7.67</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>3.29</v>
+        <v>3.44</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>7.23</v>
@@ -13583,7 +13583,7 @@
         <v>10.28</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="244">
@@ -13625,16 +13625,16 @@
         <v>1522.5</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>596.1</v>
+        <v>602.4</v>
       </c>
       <c r="O13" s="398" t="n">
         <v>1694</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>1460.2</v>
+        <v>1498</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>1385</v>
+        <v>1392</v>
       </c>
       <c r="R13" s="398" t="n">
         <v>1850.8</v>
@@ -13652,7 +13652,7 @@
         <v>1533</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>561.1</v>
+        <v>611.4</v>
       </c>
       <c r="X13" s="398" t="n">
         <v>1370.6</v>
@@ -13679,7 +13679,7 @@
         <v>1998.8</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>419.7</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1" s="244">
@@ -15637,16 +15637,16 @@
         <v>6816</v>
       </c>
       <c r="N32" s="408" t="n">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="O32" s="408" t="n">
         <v>9141</v>
       </c>
       <c r="P32" s="408" t="n">
-        <v>6076</v>
+        <v>6519</v>
       </c>
       <c r="Q32" s="408" t="n">
-        <v>5253</v>
+        <v>5327</v>
       </c>
       <c r="R32" s="408" t="n">
         <v>11661</v>
@@ -15664,7 +15664,7 @@
         <v>6946</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>278</v>
+        <v>555</v>
       </c>
       <c r="X32" s="408" t="n">
         <v>5105</v>
@@ -15691,7 +15691,7 @@
         <v>14409</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>155</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1" s="244">
@@ -16272,7 +16272,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 43868 W</t>
+          <t>TOPLAM ISI = 43738 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -17068,10 +17068,10 @@
         <v>7.87</v>
       </c>
       <c r="G12" s="397" t="n">
-        <v>7.21</v>
+        <v>6.98</v>
       </c>
       <c r="H12" s="397" t="n">
-        <v>7.94</v>
+        <v>6.49</v>
       </c>
       <c r="I12" s="397" t="n">
         <v>8.779999999999999</v>
@@ -17089,7 +17089,7 @@
         <v>7.66</v>
       </c>
       <c r="N12" s="397" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="O12" s="397" t="n">
         <v>7.11</v>
@@ -17116,7 +17116,7 @@
         <v>10.3</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>7.83</v>
@@ -17143,7 +17143,7 @@
         <v>7.61</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="AG12" s="426" t="n"/>
       <c r="AH12" s="426" t="n"/>
@@ -17181,10 +17181,10 @@
         <v>1695.4</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>1460.2</v>
+        <v>1498</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>1609.3</v>
+        <v>1392</v>
       </c>
       <c r="I13" s="398" t="n">
         <v>1850.8</v>
@@ -17202,7 +17202,7 @@
         <v>1533</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>560.7</v>
+        <v>582</v>
       </c>
       <c r="O13" s="398" t="n">
         <v>1341.2</v>
@@ -17229,7 +17229,7 @@
         <v>2005.1</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>419.7</v>
+        <v>349.3</v>
       </c>
       <c r="X13" s="398" t="n">
         <v>1688.4</v>
@@ -17256,7 +17256,7 @@
         <v>1522.5</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>425.9</v>
+        <v>524.6</v>
       </c>
       <c r="AG13" s="428" t="n"/>
       <c r="AH13" s="428" t="n"/>
@@ -19509,10 +19509,10 @@
         <v>9162</v>
       </c>
       <c r="G32" s="408" t="n">
-        <v>6076</v>
+        <v>6519</v>
       </c>
       <c r="H32" s="408" t="n">
-        <v>7939</v>
+        <v>5327</v>
       </c>
       <c r="I32" s="408" t="n">
         <v>11661</v>
@@ -19530,7 +19530,7 @@
         <v>6946</v>
       </c>
       <c r="N32" s="408" t="n">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="O32" s="408" t="n">
         <v>4810</v>
@@ -19557,7 +19557,7 @@
         <v>14535</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="X32" s="408" t="n">
         <v>9058</v>
@@ -19584,7 +19584,7 @@
         <v>6816</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>160</v>
+        <v>243</v>
       </c>
       <c r="AG32" s="434" t="n"/>
       <c r="AH32" s="434" t="n"/>
@@ -20022,7 +20022,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 101-1 (38.1 °C), 102-2 (37.1 °C), 102-3 (37.1 °C), 103-4 (37.8 °C), 104-5 (37.8 °C), 105-6 (37.7 °C), 105-7 (37.7 °C), 106-8 (32.0 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 101-1 (38.1 °C), 102-2 (38.1 °C), 102-3 (38.1 °C), 103-4 (37.8 °C), 104-5 (37.8 °C), 105-6 (37.7 °C), 105-7 (37.7 °C), 106-8 (32.0 °C) ...</t>
         </is>
       </c>
       <c r="F38" s="243" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 43759 W</t>
+          <t>TOPLAM ISI = 43519 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -21042,10 +21042,10 @@
         <v>7.57</v>
       </c>
       <c r="G12" s="397" t="n">
-        <v>7.19</v>
+        <v>6.98</v>
       </c>
       <c r="H12" s="397" t="n">
-        <v>7.96</v>
+        <v>6.46</v>
       </c>
       <c r="I12" s="397" t="n">
         <v>8.76</v>
@@ -21063,7 +21063,7 @@
         <v>7.64</v>
       </c>
       <c r="N12" s="397" t="n">
-        <v>3.33</v>
+        <v>3.49</v>
       </c>
       <c r="O12" s="397" t="n">
         <v>6.92</v>
@@ -21090,7 +21090,7 @@
         <v>10.51</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>7.8</v>
@@ -21117,7 +21117,7 @@
         <v>8.07</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="AG12" s="426" t="n"/>
       <c r="AH12" s="426" t="n"/>
@@ -21155,10 +21155,10 @@
         <v>1597.8</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>1451.8</v>
+        <v>1488.9</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>1605.4</v>
+        <v>1378.3</v>
       </c>
       <c r="I13" s="398" t="n">
         <v>1848</v>
@@ -21176,7 +21176,7 @@
         <v>1526.3</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>621.2</v>
+        <v>627.5</v>
       </c>
       <c r="O13" s="398" t="n">
         <v>1288.4</v>
@@ -21203,7 +21203,7 @@
         <v>2005.9</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>420.3</v>
+        <v>344.1</v>
       </c>
       <c r="X13" s="398" t="n">
         <v>1679.7</v>
@@ -21230,7 +21230,7 @@
         <v>1545.2</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>627.5</v>
+        <v>646.8</v>
       </c>
       <c r="AG13" s="428" t="n"/>
       <c r="AH13" s="428" t="n"/>
@@ -23483,10 +23483,10 @@
         <v>7783</v>
       </c>
       <c r="G32" s="408" t="n">
-        <v>5981</v>
+        <v>6410</v>
       </c>
       <c r="H32" s="408" t="n">
-        <v>7887</v>
+        <v>5184</v>
       </c>
       <c r="I32" s="408" t="n">
         <v>11613</v>
@@ -23504,7 +23504,7 @@
         <v>6864</v>
       </c>
       <c r="N32" s="408" t="n">
-        <v>579</v>
+        <v>596</v>
       </c>
       <c r="O32" s="408" t="n">
         <v>4306</v>
@@ -23531,7 +23531,7 @@
         <v>14549</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="X32" s="408" t="n">
         <v>8930</v>
@@ -23558,7 +23558,7 @@
         <v>7100</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>596</v>
+        <v>647</v>
       </c>
       <c r="AG32" s="434" t="n"/>
       <c r="AH32" s="434" t="n"/>
@@ -23996,7 +23996,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 201-1 (37.8 °C), 202-2 (37.1 °C), 202-3 (37.1 °C), 203-4 (37.8 °C), 204-5 (37.8 °C), 205-6 (37.7 °C), 205-7 (37.7 °C), 206-8 (31.9 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 201-1 (37.8 °C), 202-2 (38.0 °C), 202-3 (38.0 °C), 203-4 (37.8 °C), 204-5 (37.8 °C), 205-6 (37.7 °C), 205-7 (37.7 °C), 206-8 (31.9 °C) ...</t>
         </is>
       </c>
       <c r="F38" s="243" t="inlineStr">

--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'kapak'!$A$1:$I$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'TEKNİK RAPOR'!$A$1:$H$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'TEKNİK RAPOR'!$A$1:$H$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'PETEK LİST'!$A$1:$P$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'YERDEN ISITMA'!$A$1:$N$76</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'MMO YERDEN ISITMA'!$A$1:$AF$47</definedName>
@@ -3829,7 +3829,7 @@
       <c r="A38" s="310" t="n"/>
       <c r="B38" s="313" t="inlineStr">
         <is>
-          <t>Boru PEX 16 x 2,0, boru aralığı 15 cm, duvardan kenar mesafesi 7,5 cm; devre boyu en çok 80 m.</t>
+          <t>Boru PEX 16 x 2,0, boru aralığı 15 cm, duvardan kenar mesafesi 7,5 cm (dar ıslak hacimlerde 5-6 cm); devre boyu en çok 80 m.</t>
         </is>
       </c>
       <c r="E38" s="243" t="n"/>
@@ -3858,8 +3858,16 @@
       <c r="H40" s="280" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="244">
-      <c r="A41" s="310" t="n"/>
-      <c r="B41" s="313" t="n"/>
+      <c r="A41" s="310" t="inlineStr">
+        <is>
+          <t>1.4.</t>
+        </is>
+      </c>
+      <c r="B41" s="313" t="inlineStr">
+        <is>
+          <t>Not — "YERDEN ISITMA" (modülasyon) sayfasındaki negatif değerler:</t>
+        </is>
+      </c>
       <c r="E41" s="243" t="n"/>
       <c r="F41" s="317" t="n"/>
       <c r="G41" s="323" t="n"/>
@@ -3875,7 +3883,11 @@
     </row>
     <row r="43" ht="15" customHeight="1" s="244">
       <c r="A43" s="310" t="n"/>
-      <c r="B43" s="313" t="n"/>
+      <c r="B43" s="313" t="inlineStr">
+        <is>
+          <t>Sayfadaki G sütunu (MODÜL) şablon formülüdür: G = 76,263 − 0,539 × F, F = q = Q / A (W/m²). Şablon 17,5 W/m esası için kurulmuştur;</t>
+        </is>
+      </c>
       <c r="E43" s="243" t="n"/>
       <c r="F43" s="317" t="n"/>
       <c r="G43" s="323" t="n"/>
@@ -3883,7 +3895,11 @@
     </row>
     <row r="44" ht="15" customHeight="1" s="244">
       <c r="A44" s="310" t="n"/>
-      <c r="B44" s="313" t="n"/>
+      <c r="B44" s="313" t="inlineStr">
+        <is>
+          <t>q &gt; 141,5 W/m² olduğunda G negatif çıkar. Bu projede Q = 35 W/m × L ve boru yoğunluğu ≈ 6 m/m² olduğundan q ≈ 200-215 W/m² olur;</t>
+        </is>
+      </c>
       <c r="E44" s="243" t="n"/>
       <c r="F44" s="317" t="n"/>
       <c r="G44" s="323" t="n"/>
@@ -3891,7 +3907,11 @@
     </row>
     <row r="45" ht="15" customHeight="1" s="244">
       <c r="A45" s="310" t="n"/>
-      <c r="B45" s="313" t="n"/>
+      <c r="B45" s="313" t="inlineStr">
+        <is>
+          <t>bu yüzden G (MODÜL) ve H = D / G (m²) sütunlarında negatif değerler görünür. Bunlar bir ölçü değildir, yalnız formülün geçerlilik aralığı dışında olunduğunu gösterir.</t>
+        </is>
+      </c>
       <c r="E45" s="243" t="n"/>
       <c r="F45" s="317" t="n"/>
       <c r="G45" s="323" t="n"/>
@@ -3899,7 +3919,11 @@
     </row>
     <row r="46" ht="15" customHeight="1" s="244">
       <c r="A46" s="310" t="n"/>
-      <c r="B46" s="313" t="n"/>
+      <c r="B46" s="313" t="inlineStr">
+        <is>
+          <t>Formüller bozulmadan bırakılmıştır. Aynı esasla MMO sayfasında yüzey sıcaklığı ≈ 37,8 °C ve devre basınç kaybı Δpmax üstünde çıkar (sayfadaki uyarı satırları).</t>
+        </is>
+      </c>
       <c r="C46" s="324" t="n"/>
       <c r="D46" s="323" t="n"/>
       <c r="E46" s="243" t="n"/>
@@ -3909,7 +3933,11 @@
     </row>
     <row r="47" ht="15" customHeight="1" s="244">
       <c r="A47" s="310" t="n"/>
-      <c r="B47" s="313" t="n"/>
+      <c r="B47" s="313" t="inlineStr">
+        <is>
+          <t>Devre gücü esası (35 W/m × L, plan etiketleriyle aynı) proje sahibinin kararına bırakılmıştır; 17,5 W/m ya da ısı kaybı esasına geçilirse bu değerler olağan aralığa döner.</t>
+        </is>
+      </c>
       <c r="C47" s="324" t="n"/>
       <c r="D47" s="323" t="n"/>
       <c r="E47" s="243" t="n"/>

--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="D16" s="343" t="n">
-        <v>602.4</v>
+        <v>661.1</v>
       </c>
       <c r="E16" s="344" t="n">
         <v>35</v>
@@ -4690,7 +4690,7 @@
         <v/>
       </c>
       <c r="G16" s="340" t="n">
-        <v>17.21</v>
+        <v>18.89</v>
       </c>
       <c r="H16" s="340" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="D23" s="343" t="n">
-        <v>611.4</v>
+        <v>671</v>
       </c>
       <c r="E23" s="344" t="n">
         <v>35</v>
@@ -5005,7 +5005,7 @@
         <v/>
       </c>
       <c r="G23" s="340" t="n">
-        <v>17.47</v>
+        <v>19.17</v>
       </c>
       <c r="H23" s="340" t="n">
         <v>1</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="D30" s="348" t="n">
-        <v>349</v>
+        <v>465.1</v>
       </c>
       <c r="E30" s="349" t="n">
         <v>35</v>
@@ -5320,7 +5320,7 @@
         <v/>
       </c>
       <c r="G30" s="345" t="n">
-        <v>9.970000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="H30" s="345" t="n">
         <v>1</v>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="D38" s="348" t="n">
-        <v>582</v>
+        <v>670.2</v>
       </c>
       <c r="E38" s="349" t="n">
         <v>35</v>
@@ -5668,7 +5668,7 @@
         <v/>
       </c>
       <c r="G38" s="345" t="n">
-        <v>16.63</v>
+        <v>19.15</v>
       </c>
       <c r="H38" s="345" t="n">
         <v>1</v>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="D45" s="348" t="n">
-        <v>349.3</v>
+        <v>465.1</v>
       </c>
       <c r="E45" s="349" t="n">
         <v>35</v>
@@ -5983,7 +5983,7 @@
         <v/>
       </c>
       <c r="G45" s="345" t="n">
-        <v>9.98</v>
+        <v>13.29</v>
       </c>
       <c r="H45" s="345" t="n">
         <v>1</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="D52" s="348" t="n">
-        <v>524.6</v>
+        <v>560</v>
       </c>
       <c r="E52" s="349" t="n">
         <v>35</v>
@@ -6298,7 +6298,7 @@
         <v/>
       </c>
       <c r="G52" s="345" t="n">
-        <v>14.99</v>
+        <v>16</v>
       </c>
       <c r="H52" s="345" t="n">
         <v>1</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="D60" s="348" t="n">
-        <v>627.5</v>
+        <v>695.8</v>
       </c>
       <c r="E60" s="349" t="n">
         <v>35</v>
@@ -6646,7 +6646,7 @@
         <v/>
       </c>
       <c r="G60" s="345" t="n">
-        <v>17.93</v>
+        <v>19.88</v>
       </c>
       <c r="H60" s="345" t="n">
         <v>1</v>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="D67" s="348" t="n">
-        <v>344.1</v>
+        <v>460.2</v>
       </c>
       <c r="E67" s="349" t="n">
         <v>35</v>
@@ -6961,7 +6961,7 @@
         <v/>
       </c>
       <c r="G67" s="345" t="n">
-        <v>9.83</v>
+        <v>13.15</v>
       </c>
       <c r="H67" s="345" t="n">
         <v>1</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="D74" s="348" t="n">
-        <v>646.8</v>
+        <v>704.2</v>
       </c>
       <c r="E74" s="349" t="n">
         <v>35</v>
@@ -7276,7 +7276,7 @@
         <v/>
       </c>
       <c r="G74" s="345" t="n">
-        <v>18.48</v>
+        <v>20.12</v>
       </c>
       <c r="H74" s="345" t="n">
         <v>1</v>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 44002 W</t>
+          <t>TOPLAM ISI = 44237 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -13557,7 +13557,7 @@
         <v>7.61</v>
       </c>
       <c r="N12" s="397" t="n">
-        <v>3.39</v>
+        <v>3.54</v>
       </c>
       <c r="O12" s="397" t="n">
         <v>7.87</v>
@@ -13584,7 +13584,7 @@
         <v>7.67</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>7.23</v>
@@ -13611,7 +13611,7 @@
         <v>10.28</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="244">
@@ -13653,7 +13653,7 @@
         <v>1522.5</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>602.4</v>
+        <v>661.1</v>
       </c>
       <c r="O13" s="398" t="n">
         <v>1694</v>
@@ -13680,7 +13680,7 @@
         <v>1533</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>611.4</v>
+        <v>671</v>
       </c>
       <c r="X13" s="398" t="n">
         <v>1370.6</v>
@@ -13707,7 +13707,7 @@
         <v>1998.8</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>349</v>
+        <v>465.1</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1" s="244">
@@ -15665,7 +15665,7 @@
         <v>6816</v>
       </c>
       <c r="N32" s="408" t="n">
-        <v>532</v>
+        <v>688</v>
       </c>
       <c r="O32" s="408" t="n">
         <v>9141</v>
@@ -15692,7 +15692,7 @@
         <v>6946</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>555</v>
+        <v>716</v>
       </c>
       <c r="X32" s="408" t="n">
         <v>5105</v>
@@ -15719,7 +15719,7 @@
         <v>14409</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>107</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1" s="244">
@@ -16300,7 +16300,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 43738 W</t>
+          <t>TOPLAM ISI = 43977 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -17117,7 +17117,7 @@
         <v>7.66</v>
       </c>
       <c r="N12" s="397" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="O12" s="397" t="n">
         <v>7.11</v>
@@ -17144,7 +17144,7 @@
         <v>10.3</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>7.83</v>
@@ -17171,7 +17171,7 @@
         <v>7.61</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="AG12" s="426" t="n"/>
       <c r="AH12" s="426" t="n"/>
@@ -17230,7 +17230,7 @@
         <v>1533</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>582</v>
+        <v>670.2</v>
       </c>
       <c r="O13" s="398" t="n">
         <v>1341.2</v>
@@ -17257,7 +17257,7 @@
         <v>2005.1</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>349.3</v>
+        <v>465.1</v>
       </c>
       <c r="X13" s="398" t="n">
         <v>1688.4</v>
@@ -17284,7 +17284,7 @@
         <v>1522.5</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>524.6</v>
+        <v>560</v>
       </c>
       <c r="AG13" s="428" t="n"/>
       <c r="AH13" s="428" t="n"/>
@@ -19558,7 +19558,7 @@
         <v>6946</v>
       </c>
       <c r="N32" s="408" t="n">
-        <v>299</v>
+        <v>714</v>
       </c>
       <c r="O32" s="408" t="n">
         <v>4810</v>
@@ -19585,7 +19585,7 @@
         <v>14535</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="X32" s="408" t="n">
         <v>9058</v>
@@ -19612,7 +19612,7 @@
         <v>6816</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="AG32" s="434" t="n"/>
       <c r="AH32" s="434" t="n"/>
@@ -20274,7 +20274,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 43519 W</t>
+          <t>TOPLAM ISI = 43760 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -21091,7 +21091,7 @@
         <v>7.64</v>
       </c>
       <c r="N12" s="397" t="n">
-        <v>3.49</v>
+        <v>3.64</v>
       </c>
       <c r="O12" s="397" t="n">
         <v>6.92</v>
@@ -21118,7 +21118,7 @@
         <v>10.51</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>7.8</v>
@@ -21145,7 +21145,7 @@
         <v>8.07</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>3.52</v>
+        <v>3.67</v>
       </c>
       <c r="AG12" s="426" t="n"/>
       <c r="AH12" s="426" t="n"/>
@@ -21204,7 +21204,7 @@
         <v>1526.3</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>627.5</v>
+        <v>695.8</v>
       </c>
       <c r="O13" s="398" t="n">
         <v>1288.4</v>
@@ -21231,7 +21231,7 @@
         <v>2005.9</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>344.1</v>
+        <v>460.2</v>
       </c>
       <c r="X13" s="398" t="n">
         <v>1679.7</v>
@@ -21258,7 +21258,7 @@
         <v>1545.2</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>646.8</v>
+        <v>704.2</v>
       </c>
       <c r="AG13" s="428" t="n"/>
       <c r="AH13" s="428" t="n"/>
@@ -23532,7 +23532,7 @@
         <v>6864</v>
       </c>
       <c r="N32" s="408" t="n">
-        <v>596</v>
+        <v>791</v>
       </c>
       <c r="O32" s="408" t="n">
         <v>4306</v>
@@ -23559,7 +23559,7 @@
         <v>14549</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>104</v>
+        <v>187</v>
       </c>
       <c r="X32" s="408" t="n">
         <v>8930</v>
@@ -23586,7 +23586,7 @@
         <v>7100</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>647</v>
+        <v>818</v>
       </c>
       <c r="AG32" s="434" t="n"/>
       <c r="AH32" s="434" t="n"/>

--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="D10" s="343" t="n">
-        <v>1688.4</v>
+        <v>1649.2</v>
       </c>
       <c r="E10" s="344" t="n">
         <v>35</v>
@@ -4420,7 +4420,7 @@
         <v/>
       </c>
       <c r="G10" s="340" t="n">
-        <v>48.24</v>
+        <v>47.12</v>
       </c>
       <c r="H10" s="340" t="n">
         <v>1</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="D11" s="343" t="n">
-        <v>2872.1</v>
+        <v>3369.8</v>
       </c>
       <c r="E11" s="344" t="n">
         <v>35</v>
@@ -4465,7 +4465,7 @@
         <v/>
       </c>
       <c r="G11" s="340" t="n">
-        <v>82.06</v>
+        <v>96.28</v>
       </c>
       <c r="H11" s="340" t="n">
         <v>2</v>
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="D12" s="343" t="n">
-        <v>1850.8</v>
+        <v>2001</v>
       </c>
       <c r="E12" s="344" t="n">
         <v>35</v>
@@ -4510,7 +4510,7 @@
         <v/>
       </c>
       <c r="G12" s="340" t="n">
-        <v>52.88</v>
+        <v>57.17</v>
       </c>
       <c r="H12" s="340" t="n">
         <v>1</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="D13" s="343" t="n">
-        <v>1866.2</v>
+        <v>2088.8</v>
       </c>
       <c r="E13" s="344" t="n">
         <v>35</v>
@@ -4555,7 +4555,7 @@
         <v/>
       </c>
       <c r="G13" s="340" t="n">
-        <v>53.32</v>
+        <v>59.68</v>
       </c>
       <c r="H13" s="340" t="n">
         <v>1</v>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="D14" s="343" t="n">
-        <v>4240.9</v>
+        <v>4620.7</v>
       </c>
       <c r="E14" s="344" t="n">
         <v>35</v>
@@ -4600,7 +4600,7 @@
         <v/>
       </c>
       <c r="G14" s="340" t="n">
-        <v>121.17</v>
+        <v>132.02</v>
       </c>
       <c r="H14" s="340" t="n">
         <v>2</v>
@@ -4635,7 +4635,7 @@
         </is>
       </c>
       <c r="D15" s="343" t="n">
-        <v>1522.5</v>
+        <v>202.3</v>
       </c>
       <c r="E15" s="344" t="n">
         <v>35</v>
@@ -4645,7 +4645,7 @@
         <v/>
       </c>
       <c r="G15" s="340" t="n">
-        <v>43.5</v>
+        <v>5.78</v>
       </c>
       <c r="H15" s="340" t="n">
         <v>1</v>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="D16" s="343" t="n">
-        <v>661.1</v>
+        <v>854</v>
       </c>
       <c r="E16" s="344" t="n">
         <v>35</v>
@@ -4690,7 +4690,7 @@
         <v/>
       </c>
       <c r="G16" s="340" t="n">
-        <v>18.89</v>
+        <v>24.4</v>
       </c>
       <c r="H16" s="340" t="n">
         <v>1</v>
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="D17" s="343" t="n">
-        <v>1694</v>
+        <v>1374.1</v>
       </c>
       <c r="E17" s="344" t="n">
         <v>35</v>
@@ -4735,7 +4735,7 @@
         <v/>
       </c>
       <c r="G17" s="340" t="n">
-        <v>48.4</v>
+        <v>39.26</v>
       </c>
       <c r="H17" s="340" t="n">
         <v>1</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="D18" s="343" t="n">
-        <v>2889.9</v>
+        <v>3396.8</v>
       </c>
       <c r="E18" s="344" t="n">
         <v>35</v>
@@ -4780,7 +4780,7 @@
         <v/>
       </c>
       <c r="G18" s="340" t="n">
-        <v>82.56999999999999</v>
+        <v>97.05</v>
       </c>
       <c r="H18" s="340" t="n">
         <v>2</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="D19" s="343" t="n">
-        <v>1850.8</v>
+        <v>2002.4</v>
       </c>
       <c r="E19" s="344" t="n">
         <v>35</v>
@@ -4825,7 +4825,7 @@
         <v/>
       </c>
       <c r="G19" s="340" t="n">
-        <v>52.88</v>
+        <v>57.21</v>
       </c>
       <c r="H19" s="340" t="n">
         <v>1</v>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="D20" s="343" t="n">
-        <v>1860.6</v>
+        <v>2072</v>
       </c>
       <c r="E20" s="344" t="n">
         <v>35</v>
@@ -4870,7 +4870,7 @@
         <v/>
       </c>
       <c r="G20" s="340" t="n">
-        <v>53.16</v>
+        <v>59.2</v>
       </c>
       <c r="H20" s="340" t="n">
         <v>1</v>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="D21" s="343" t="n">
-        <v>4253.6</v>
+        <v>4647.3</v>
       </c>
       <c r="E21" s="344" t="n">
         <v>35</v>
@@ -4915,7 +4915,7 @@
         <v/>
       </c>
       <c r="G21" s="340" t="n">
-        <v>121.53</v>
+        <v>132.78</v>
       </c>
       <c r="H21" s="340" t="n">
         <v>2</v>
@@ -4950,7 +4950,7 @@
         </is>
       </c>
       <c r="D22" s="343" t="n">
-        <v>1533</v>
+        <v>183.4</v>
       </c>
       <c r="E22" s="344" t="n">
         <v>35</v>
@@ -4960,7 +4960,7 @@
         <v/>
       </c>
       <c r="G22" s="340" t="n">
-        <v>43.8</v>
+        <v>5.24</v>
       </c>
       <c r="H22" s="340" t="n">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="D23" s="343" t="n">
-        <v>671</v>
+        <v>872.9</v>
       </c>
       <c r="E23" s="344" t="n">
         <v>35</v>
@@ -5005,7 +5005,7 @@
         <v/>
       </c>
       <c r="G23" s="340" t="n">
-        <v>19.17</v>
+        <v>24.94</v>
       </c>
       <c r="H23" s="340" t="n">
         <v>1</v>
@@ -5040,7 +5040,7 @@
         </is>
       </c>
       <c r="D24" s="343" t="n">
-        <v>1370.6</v>
+        <v>1010.1</v>
       </c>
       <c r="E24" s="344" t="n">
         <v>35</v>
@@ -5050,7 +5050,7 @@
         <v/>
       </c>
       <c r="G24" s="340" t="n">
-        <v>39.16</v>
+        <v>28.86</v>
       </c>
       <c r="H24" s="340" t="n">
         <v>1</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="D25" s="348" t="n">
-        <v>3031.7</v>
+        <v>3711.4</v>
       </c>
       <c r="E25" s="349" t="n">
         <v>35</v>
@@ -5095,7 +5095,7 @@
         <v/>
       </c>
       <c r="G25" s="345" t="n">
-        <v>86.62</v>
+        <v>106.04</v>
       </c>
       <c r="H25" s="345" t="n">
         <v>2</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="D26" s="348" t="n">
-        <v>1859.2</v>
+        <v>2216.9</v>
       </c>
       <c r="E26" s="349" t="n">
         <v>35</v>
@@ -5140,7 +5140,7 @@
         <v/>
       </c>
       <c r="G26" s="345" t="n">
-        <v>53.12</v>
+        <v>63.34</v>
       </c>
       <c r="H26" s="345" t="n">
         <v>1</v>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="D27" s="348" t="n">
-        <v>4437.3</v>
+        <v>4299.1</v>
       </c>
       <c r="E27" s="349" t="n">
         <v>35</v>
@@ -5185,7 +5185,7 @@
         <v/>
       </c>
       <c r="G27" s="345" t="n">
-        <v>126.78</v>
+        <v>122.83</v>
       </c>
       <c r="H27" s="345" t="n">
         <v>2</v>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="D28" s="348" t="n">
-        <v>1619.1</v>
+        <v>2157.1</v>
       </c>
       <c r="E28" s="349" t="n">
         <v>35</v>
@@ -5230,7 +5230,7 @@
         <v/>
       </c>
       <c r="G28" s="345" t="n">
-        <v>46.26</v>
+        <v>61.63</v>
       </c>
       <c r="H28" s="345" t="n">
         <v>1</v>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="D29" s="348" t="n">
-        <v>1998.8</v>
+        <v>915.6</v>
       </c>
       <c r="E29" s="349" t="n">
         <v>35</v>
@@ -5275,7 +5275,7 @@
         <v/>
       </c>
       <c r="G29" s="345" t="n">
-        <v>57.11</v>
+        <v>26.16</v>
       </c>
       <c r="H29" s="345" t="n">
         <v>1</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="D30" s="348" t="n">
-        <v>465.1</v>
+        <v>798.7</v>
       </c>
       <c r="E30" s="349" t="n">
         <v>35</v>
@@ -5320,7 +5320,7 @@
         <v/>
       </c>
       <c r="G30" s="345" t="n">
-        <v>13.29</v>
+        <v>22.82</v>
       </c>
       <c r="H30" s="345" t="n">
         <v>1</v>
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="D32" s="348" t="n">
-        <v>1695.4</v>
+        <v>1375.5</v>
       </c>
       <c r="E32" s="349" t="n">
         <v>35</v>
@@ -5398,7 +5398,7 @@
         <v/>
       </c>
       <c r="G32" s="345" t="n">
-        <v>48.44</v>
+        <v>39.3</v>
       </c>
       <c r="H32" s="345" t="n">
         <v>1</v>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="D33" s="348" t="n">
-        <v>2889.9</v>
+        <v>3396.8</v>
       </c>
       <c r="E33" s="349" t="n">
         <v>35</v>
@@ -5443,7 +5443,7 @@
         <v/>
       </c>
       <c r="G33" s="345" t="n">
-        <v>82.56999999999999</v>
+        <v>97.05</v>
       </c>
       <c r="H33" s="345" t="n">
         <v>2</v>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="D34" s="348" t="n">
-        <v>1850.8</v>
+        <v>2002.4</v>
       </c>
       <c r="E34" s="349" t="n">
         <v>35</v>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="G34" s="345" t="n">
-        <v>52.88</v>
+        <v>57.21</v>
       </c>
       <c r="H34" s="345" t="n">
         <v>1</v>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="D35" s="348" t="n">
-        <v>1860.6</v>
+        <v>2072</v>
       </c>
       <c r="E35" s="349" t="n">
         <v>35</v>
@@ -5533,7 +5533,7 @@
         <v/>
       </c>
       <c r="G35" s="345" t="n">
-        <v>53.16</v>
+        <v>59.2</v>
       </c>
       <c r="H35" s="345" t="n">
         <v>1</v>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="D36" s="348" t="n">
-        <v>4235.7</v>
+        <v>4634</v>
       </c>
       <c r="E36" s="349" t="n">
         <v>35</v>
@@ -5578,7 +5578,7 @@
         <v/>
       </c>
       <c r="G36" s="345" t="n">
-        <v>121.02</v>
+        <v>132.4</v>
       </c>
       <c r="H36" s="345" t="n">
         <v>2</v>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="D37" s="348" t="n">
-        <v>1533</v>
+        <v>183.4</v>
       </c>
       <c r="E37" s="349" t="n">
         <v>35</v>
@@ -5623,7 +5623,7 @@
         <v/>
       </c>
       <c r="G37" s="345" t="n">
-        <v>43.8</v>
+        <v>5.24</v>
       </c>
       <c r="H37" s="345" t="n">
         <v>1</v>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="D38" s="348" t="n">
-        <v>670.2</v>
+        <v>872.2</v>
       </c>
       <c r="E38" s="349" t="n">
         <v>35</v>
@@ -5668,7 +5668,7 @@
         <v/>
       </c>
       <c r="G38" s="345" t="n">
-        <v>19.15</v>
+        <v>24.92</v>
       </c>
       <c r="H38" s="345" t="n">
         <v>1</v>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="D39" s="348" t="n">
-        <v>1341.2</v>
+        <v>1271.2</v>
       </c>
       <c r="E39" s="349" t="n">
         <v>35</v>
@@ -5713,7 +5713,7 @@
         <v/>
       </c>
       <c r="G39" s="345" t="n">
-        <v>38.32</v>
+        <v>36.32</v>
       </c>
       <c r="H39" s="345" t="n">
         <v>1</v>
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="D40" s="348" t="n">
-        <v>3031.7</v>
+        <v>3266.2</v>
       </c>
       <c r="E40" s="349" t="n">
         <v>35</v>
@@ -5758,7 +5758,7 @@
         <v/>
       </c>
       <c r="G40" s="345" t="n">
-        <v>86.62</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="H40" s="345" t="n">
         <v>2</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="D41" s="348" t="n">
-        <v>1859.2</v>
+        <v>1985.9</v>
       </c>
       <c r="E41" s="349" t="n">
         <v>35</v>
@@ -5803,7 +5803,7 @@
         <v/>
       </c>
       <c r="G41" s="345" t="n">
-        <v>53.12</v>
+        <v>56.74</v>
       </c>
       <c r="H41" s="345" t="n">
         <v>1</v>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="D42" s="348" t="n">
-        <v>4299.8</v>
+        <v>4719.4</v>
       </c>
       <c r="E42" s="349" t="n">
         <v>35</v>
@@ -5848,7 +5848,7 @@
         <v/>
       </c>
       <c r="G42" s="345" t="n">
-        <v>122.85</v>
+        <v>134.84</v>
       </c>
       <c r="H42" s="345" t="n">
         <v>2</v>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="D43" s="348" t="n">
-        <v>1614.9</v>
+        <v>1931.3</v>
       </c>
       <c r="E43" s="349" t="n">
         <v>35</v>
@@ -5893,7 +5893,7 @@
         <v/>
       </c>
       <c r="G43" s="345" t="n">
-        <v>46.14</v>
+        <v>55.18</v>
       </c>
       <c r="H43" s="345" t="n">
         <v>1</v>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="D44" s="348" t="n">
-        <v>2005.1</v>
+        <v>449.4</v>
       </c>
       <c r="E44" s="349" t="n">
         <v>35</v>
@@ -5938,7 +5938,7 @@
         <v/>
       </c>
       <c r="G44" s="345" t="n">
-        <v>57.29</v>
+        <v>12.84</v>
       </c>
       <c r="H44" s="345" t="n">
         <v>1</v>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="D45" s="348" t="n">
-        <v>465.1</v>
+        <v>539</v>
       </c>
       <c r="E45" s="349" t="n">
         <v>35</v>
@@ -5983,7 +5983,7 @@
         <v/>
       </c>
       <c r="G45" s="345" t="n">
-        <v>13.29</v>
+        <v>15.4</v>
       </c>
       <c r="H45" s="345" t="n">
         <v>1</v>
@@ -6018,7 +6018,7 @@
         </is>
       </c>
       <c r="D46" s="348" t="n">
-        <v>1688.4</v>
+        <v>1653</v>
       </c>
       <c r="E46" s="349" t="n">
         <v>35</v>
@@ -6028,7 +6028,7 @@
         <v/>
       </c>
       <c r="G46" s="345" t="n">
-        <v>48.24</v>
+        <v>47.23</v>
       </c>
       <c r="H46" s="345" t="n">
         <v>1</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="D47" s="348" t="n">
-        <v>2877.7</v>
+        <v>3375.4</v>
       </c>
       <c r="E47" s="349" t="n">
         <v>35</v>
@@ -6073,7 +6073,7 @@
         <v/>
       </c>
       <c r="G47" s="345" t="n">
-        <v>82.22</v>
+        <v>96.44</v>
       </c>
       <c r="H47" s="345" t="n">
         <v>2</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="D48" s="348" t="n">
-        <v>1856.4</v>
+        <v>2006.5</v>
       </c>
       <c r="E48" s="349" t="n">
         <v>35</v>
@@ -6118,7 +6118,7 @@
         <v/>
       </c>
       <c r="G48" s="345" t="n">
-        <v>53.04</v>
+        <v>57.33</v>
       </c>
       <c r="H48" s="345" t="n">
         <v>1</v>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="D49" s="348" t="n">
-        <v>1872.8</v>
+        <v>2095.4</v>
       </c>
       <c r="E49" s="349" t="n">
         <v>35</v>
@@ -6163,7 +6163,7 @@
         <v/>
       </c>
       <c r="G49" s="345" t="n">
-        <v>53.51</v>
+        <v>59.87</v>
       </c>
       <c r="H49" s="345" t="n">
         <v>1</v>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="D50" s="348" t="n">
-        <v>4246.6</v>
+        <v>4626.3</v>
       </c>
       <c r="E50" s="349" t="n">
         <v>35</v>
@@ -6208,7 +6208,7 @@
         <v/>
       </c>
       <c r="G50" s="345" t="n">
-        <v>121.33</v>
+        <v>132.18</v>
       </c>
       <c r="H50" s="345" t="n">
         <v>2</v>
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="D51" s="348" t="n">
-        <v>1522.5</v>
+        <v>202.3</v>
       </c>
       <c r="E51" s="349" t="n">
         <v>35</v>
@@ -6253,7 +6253,7 @@
         <v/>
       </c>
       <c r="G51" s="345" t="n">
-        <v>43.5</v>
+        <v>5.78</v>
       </c>
       <c r="H51" s="345" t="n">
         <v>1</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="D52" s="348" t="n">
-        <v>560</v>
+        <v>690.9</v>
       </c>
       <c r="E52" s="349" t="n">
         <v>35</v>
@@ -6298,7 +6298,7 @@
         <v/>
       </c>
       <c r="G52" s="345" t="n">
-        <v>16</v>
+        <v>19.74</v>
       </c>
       <c r="H52" s="345" t="n">
         <v>1</v>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="D54" s="348" t="n">
-        <v>1597.8</v>
+        <v>1760.5</v>
       </c>
       <c r="E54" s="349" t="n">
         <v>35</v>
@@ -6376,7 +6376,7 @@
         <v/>
       </c>
       <c r="G54" s="345" t="n">
-        <v>45.65</v>
+        <v>50.3</v>
       </c>
       <c r="H54" s="345" t="n">
         <v>1</v>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="D55" s="348" t="n">
-        <v>2867.2</v>
+        <v>3383.5</v>
       </c>
       <c r="E55" s="349" t="n">
         <v>35</v>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="G55" s="345" t="n">
-        <v>81.92</v>
+        <v>96.67</v>
       </c>
       <c r="H55" s="345" t="n">
         <v>2</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="D56" s="348" t="n">
-        <v>1848</v>
+        <v>1999.6</v>
       </c>
       <c r="E56" s="349" t="n">
         <v>35</v>
@@ -6466,7 +6466,7 @@
         <v/>
       </c>
       <c r="G56" s="345" t="n">
-        <v>52.8</v>
+        <v>57.13</v>
       </c>
       <c r="H56" s="345" t="n">
         <v>1</v>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="D57" s="348" t="n">
-        <v>1859.2</v>
+        <v>2075.8</v>
       </c>
       <c r="E57" s="349" t="n">
         <v>35</v>
@@ -6511,7 +6511,7 @@
         <v/>
       </c>
       <c r="G57" s="345" t="n">
-        <v>53.12</v>
+        <v>59.31</v>
       </c>
       <c r="H57" s="345" t="n">
         <v>1</v>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="D58" s="348" t="n">
-        <v>4213.3</v>
+        <v>4611.6</v>
       </c>
       <c r="E58" s="349" t="n">
         <v>35</v>
@@ -6556,7 +6556,7 @@
         <v/>
       </c>
       <c r="G58" s="345" t="n">
-        <v>120.38</v>
+        <v>131.76</v>
       </c>
       <c r="H58" s="345" t="n">
         <v>2</v>
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="D59" s="348" t="n">
-        <v>1526.3</v>
+        <v>255.8</v>
       </c>
       <c r="E59" s="349" t="n">
         <v>35</v>
@@ -6601,7 +6601,7 @@
         <v/>
       </c>
       <c r="G59" s="345" t="n">
-        <v>43.61</v>
+        <v>7.31</v>
       </c>
       <c r="H59" s="345" t="n">
         <v>1</v>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="D60" s="348" t="n">
-        <v>695.8</v>
+        <v>897.8</v>
       </c>
       <c r="E60" s="349" t="n">
         <v>35</v>
@@ -6646,7 +6646,7 @@
         <v/>
       </c>
       <c r="G60" s="345" t="n">
-        <v>19.88</v>
+        <v>25.65</v>
       </c>
       <c r="H60" s="345" t="n">
         <v>1</v>
@@ -6681,7 +6681,7 @@
         </is>
       </c>
       <c r="D61" s="348" t="n">
-        <v>1288.4</v>
+        <v>1253</v>
       </c>
       <c r="E61" s="349" t="n">
         <v>35</v>
@@ -6691,7 +6691,7 @@
         <v/>
       </c>
       <c r="G61" s="345" t="n">
-        <v>36.81</v>
+        <v>35.8</v>
       </c>
       <c r="H61" s="345" t="n">
         <v>1</v>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="D62" s="348" t="n">
-        <v>2937.2</v>
+        <v>3260.9</v>
       </c>
       <c r="E62" s="349" t="n">
         <v>35</v>
@@ -6736,7 +6736,7 @@
         <v/>
       </c>
       <c r="G62" s="345" t="n">
-        <v>83.92</v>
+        <v>93.17</v>
       </c>
       <c r="H62" s="345" t="n">
         <v>2</v>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="D63" s="348" t="n">
-        <v>1859.2</v>
+        <v>1982.4</v>
       </c>
       <c r="E63" s="349" t="n">
         <v>35</v>
@@ -6781,7 +6781,7 @@
         <v/>
       </c>
       <c r="G63" s="345" t="n">
-        <v>53.12</v>
+        <v>56.64</v>
       </c>
       <c r="H63" s="345" t="n">
         <v>1</v>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="D64" s="348" t="n">
-        <v>4288.6</v>
+        <v>4714.5</v>
       </c>
       <c r="E64" s="349" t="n">
         <v>35</v>
@@ -6826,7 +6826,7 @@
         <v/>
       </c>
       <c r="G64" s="345" t="n">
-        <v>122.53</v>
+        <v>134.7</v>
       </c>
       <c r="H64" s="345" t="n">
         <v>2</v>
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="D65" s="348" t="n">
-        <v>1610.7</v>
+        <v>1927.1</v>
       </c>
       <c r="E65" s="349" t="n">
         <v>35</v>
@@ -6871,7 +6871,7 @@
         <v/>
       </c>
       <c r="G65" s="345" t="n">
-        <v>46.02</v>
+        <v>55.06</v>
       </c>
       <c r="H65" s="345" t="n">
         <v>1</v>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="D66" s="348" t="n">
-        <v>2005.9</v>
+        <v>450.8</v>
       </c>
       <c r="E66" s="349" t="n">
         <v>35</v>
@@ -6916,7 +6916,7 @@
         <v/>
       </c>
       <c r="G66" s="345" t="n">
-        <v>57.31</v>
+        <v>12.88</v>
       </c>
       <c r="H66" s="345" t="n">
         <v>1</v>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="D67" s="348" t="n">
-        <v>460.2</v>
+        <v>528.9</v>
       </c>
       <c r="E67" s="349" t="n">
         <v>35</v>
@@ -6961,7 +6961,7 @@
         <v/>
       </c>
       <c r="G67" s="345" t="n">
-        <v>13.15</v>
+        <v>15.11</v>
       </c>
       <c r="H67" s="345" t="n">
         <v>1</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="D68" s="348" t="n">
-        <v>1679.7</v>
+        <v>1660</v>
       </c>
       <c r="E68" s="349" t="n">
         <v>35</v>
@@ -7006,7 +7006,7 @@
         <v/>
       </c>
       <c r="G68" s="345" t="n">
-        <v>47.99</v>
+        <v>47.43</v>
       </c>
       <c r="H68" s="345" t="n">
         <v>1</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="D69" s="348" t="n">
-        <v>2864.4</v>
+        <v>3370.1</v>
       </c>
       <c r="E69" s="349" t="n">
         <v>35</v>
@@ -7051,7 +7051,7 @@
         <v/>
       </c>
       <c r="G69" s="345" t="n">
-        <v>81.84</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="H69" s="345" t="n">
         <v>2</v>
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="D70" s="348" t="n">
-        <v>1848</v>
+        <v>2006.9</v>
       </c>
       <c r="E70" s="349" t="n">
         <v>35</v>
@@ -7096,7 +7096,7 @@
         <v/>
       </c>
       <c r="G70" s="345" t="n">
-        <v>52.8</v>
+        <v>57.34</v>
       </c>
       <c r="H70" s="345" t="n">
         <v>1</v>
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="D71" s="348" t="n">
-        <v>1864.8</v>
+        <v>2088.8</v>
       </c>
       <c r="E71" s="349" t="n">
         <v>35</v>
@@ -7141,7 +7141,7 @@
         <v/>
       </c>
       <c r="G71" s="345" t="n">
-        <v>53.28</v>
+        <v>59.68</v>
       </c>
       <c r="H71" s="345" t="n">
         <v>1</v>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="D72" s="348" t="n">
-        <v>4196.5</v>
+        <v>4603.9</v>
       </c>
       <c r="E72" s="349" t="n">
         <v>35</v>
@@ -7186,7 +7186,7 @@
         <v/>
       </c>
       <c r="G72" s="345" t="n">
-        <v>119.9</v>
+        <v>131.54</v>
       </c>
       <c r="H72" s="345" t="n">
         <v>2</v>
@@ -7221,7 +7221,7 @@
         </is>
       </c>
       <c r="D73" s="348" t="n">
-        <v>1545.2</v>
+        <v>174.3</v>
       </c>
       <c r="E73" s="349" t="n">
         <v>35</v>
@@ -7231,7 +7231,7 @@
         <v/>
       </c>
       <c r="G73" s="345" t="n">
-        <v>44.15</v>
+        <v>4.98</v>
       </c>
       <c r="H73" s="345" t="n">
         <v>1</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="D74" s="348" t="n">
-        <v>704.2</v>
+        <v>904</v>
       </c>
       <c r="E74" s="349" t="n">
         <v>35</v>
@@ -7276,7 +7276,7 @@
         <v/>
       </c>
       <c r="G74" s="345" t="n">
-        <v>20.12</v>
+        <v>25.83</v>
       </c>
       <c r="H74" s="345" t="n">
         <v>1</v>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 44237 W</t>
+          <t>TOPLAM ISI = 44443 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 22298 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 23920 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -13533,85 +13533,85 @@
       <c r="D12" s="261" t="n"/>
       <c r="E12" s="259" t="n"/>
       <c r="F12" s="397" t="n">
-        <v>7.83</v>
+        <v>6.92</v>
       </c>
       <c r="G12" s="397" t="n">
-        <v>7.11</v>
+        <v>6.47</v>
       </c>
       <c r="H12" s="397" t="n">
-        <v>6.49</v>
+        <v>6.97</v>
       </c>
       <c r="I12" s="397" t="n">
-        <v>8.779999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="J12" s="397" t="n">
         <v>8.84</v>
       </c>
       <c r="K12" s="397" t="n">
-        <v>9.81</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L12" s="397" t="n">
-        <v>10.29</v>
+        <v>10.24</v>
       </c>
       <c r="M12" s="397" t="n">
-        <v>7.61</v>
+        <v>1.17</v>
       </c>
       <c r="N12" s="397" t="n">
         <v>3.54</v>
       </c>
       <c r="O12" s="397" t="n">
-        <v>7.87</v>
+        <v>5.75</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>6.98</v>
+        <v>6.37</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>6.49</v>
+        <v>6.96</v>
       </c>
       <c r="R12" s="397" t="n">
-        <v>8.76</v>
+        <v>8.43</v>
       </c>
       <c r="S12" s="397" t="n">
         <v>8.83</v>
       </c>
       <c r="T12" s="397" t="n">
-        <v>9.880000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="U12" s="397" t="n">
-        <v>10.29</v>
+        <v>10.25</v>
       </c>
       <c r="V12" s="397" t="n">
-        <v>7.67</v>
+        <v>1.12</v>
       </c>
       <c r="W12" s="397" t="n">
         <v>3.6</v>
       </c>
       <c r="X12" s="397" t="n">
-        <v>7.23</v>
+        <v>4.26</v>
       </c>
       <c r="Y12" s="397" t="n">
-        <v>7.24</v>
+        <v>6.8</v>
       </c>
       <c r="Z12" s="397" t="n">
-        <v>7.08</v>
+        <v>7.31</v>
       </c>
       <c r="AA12" s="397" t="n">
         <v>8.640000000000001</v>
       </c>
       <c r="AB12" s="397" t="n">
-        <v>10.87</v>
+        <v>10.14</v>
       </c>
       <c r="AC12" s="397" t="n">
-        <v>10.08</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AD12" s="397" t="n">
         <v>7.31</v>
       </c>
       <c r="AE12" s="397" t="n">
-        <v>10.28</v>
+        <v>4.95</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>2.41</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="244">
@@ -13629,85 +13629,85 @@
       </c>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>1688.4</v>
+        <v>1649.2</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>1501.2</v>
+        <v>1621.2</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>1371</v>
+        <v>1748.6</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>1850.8</v>
+        <v>2001</v>
       </c>
       <c r="J13" s="398" t="n">
-        <v>1866.2</v>
+        <v>2088.8</v>
       </c>
       <c r="K13" s="398" t="n">
-        <v>2069.9</v>
+        <v>2266.6</v>
       </c>
       <c r="L13" s="398" t="n">
-        <v>2171.1</v>
+        <v>2354.1</v>
       </c>
       <c r="M13" s="398" t="n">
-        <v>1522.5</v>
+        <v>202.3</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>661.1</v>
+        <v>854</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>1694</v>
+        <v>1374.1</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>1498</v>
+        <v>1622.6</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>1392</v>
+        <v>1774.1</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>1850.8</v>
+        <v>2002.4</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>1860.6</v>
+        <v>2072</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>2082.5</v>
+        <v>2286.2</v>
       </c>
       <c r="U13" s="398" t="n">
-        <v>2171.1</v>
+        <v>2361.1</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>1533</v>
+        <v>183.4</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>671</v>
+        <v>872.9</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>1370.6</v>
+        <v>1010.1</v>
       </c>
       <c r="Y13" s="398" t="n">
-        <v>1533</v>
+        <v>1789.6</v>
       </c>
       <c r="Z13" s="398" t="n">
-        <v>1498.7</v>
+        <v>1921.8</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>1859.2</v>
+        <v>2216.9</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>2301.6</v>
+        <v>2303</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>2135.7</v>
+        <v>1996</v>
       </c>
       <c r="AD13" s="398" t="n">
-        <v>1619.1</v>
+        <v>2157.1</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>1998.8</v>
+        <v>915.6</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>465.1</v>
+        <v>798.7</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1" s="244">
@@ -15641,85 +15641,85 @@
       </c>
       <c r="E32" s="259" t="n"/>
       <c r="F32" s="408" t="n">
-        <v>9058</v>
+        <v>8492</v>
       </c>
       <c r="G32" s="408" t="n">
-        <v>6556</v>
+        <v>8101</v>
       </c>
       <c r="H32" s="408" t="n">
-        <v>5109</v>
+        <v>9975</v>
       </c>
       <c r="I32" s="408" t="n">
-        <v>11661</v>
+        <v>14451</v>
       </c>
       <c r="J32" s="408" t="n">
-        <v>11930</v>
+        <v>16264</v>
       </c>
       <c r="K32" s="408" t="n">
-        <v>15862</v>
+        <v>20360</v>
       </c>
       <c r="L32" s="408" t="n">
-        <v>18086</v>
+        <v>22595</v>
       </c>
       <c r="M32" s="408" t="n">
-        <v>6816</v>
+        <v>36</v>
       </c>
       <c r="N32" s="408" t="n">
-        <v>688</v>
+        <v>1390</v>
       </c>
       <c r="O32" s="408" t="n">
-        <v>9141</v>
+        <v>5141</v>
       </c>
       <c r="P32" s="408" t="n">
-        <v>6519</v>
+        <v>8120</v>
       </c>
       <c r="Q32" s="408" t="n">
-        <v>5327</v>
+        <v>10381</v>
       </c>
       <c r="R32" s="408" t="n">
-        <v>11661</v>
+        <v>14479</v>
       </c>
       <c r="S32" s="408" t="n">
-        <v>11832</v>
+        <v>15906</v>
       </c>
       <c r="T32" s="408" t="n">
-        <v>16129</v>
+        <v>20848</v>
       </c>
       <c r="U32" s="408" t="n">
-        <v>18086</v>
+        <v>22781</v>
       </c>
       <c r="V32" s="408" t="n">
-        <v>6946</v>
+        <v>30</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>716</v>
+        <v>1476</v>
       </c>
       <c r="X32" s="408" t="n">
-        <v>5105</v>
+        <v>2205</v>
       </c>
       <c r="Y32" s="408" t="n">
-        <v>6946</v>
+        <v>10630</v>
       </c>
       <c r="Z32" s="408" t="n">
-        <v>6527</v>
+        <v>12934</v>
       </c>
       <c r="AA32" s="408" t="n">
-        <v>11807</v>
+        <v>19156</v>
       </c>
       <c r="AB32" s="408" t="n">
-        <v>21236</v>
+        <v>21272</v>
       </c>
       <c r="AC32" s="408" t="n">
-        <v>17288</v>
+        <v>14354</v>
       </c>
       <c r="AD32" s="408" t="n">
-        <v>8072</v>
+        <v>17767</v>
       </c>
       <c r="AE32" s="408" t="n">
-        <v>14409</v>
+        <v>1683</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>191</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1" s="244">
@@ -16081,7 +16081,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): Z01-1 (38.1 °C), Z02-2 (37.8 °C), Z02-3 (37.8 °C), Z03-4 (37.8 °C), Z04-5 (37.8 °C), Z05-6 (37.8 °C), Z05-7 (37.8 °C), Z06-8 (32.0 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): Z01-1 (39.9 °C), Z02-2 (40.8 °C), Z02-3 (40.8 °C), Z03-4 (39.7 °C), Z04-5 (39.7 °C), Z05-6 (39.2 °C), Z05-7 (39.2 °C), Z06-8 (29.8 °C) ...</t>
         </is>
       </c>
       <c r="H38" s="243" t="n"/>
@@ -16300,7 +16300,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 43977 W</t>
+          <t>TOPLAM ISI = 43349 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 19058 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 27181 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -17093,85 +17093,85 @@
       <c r="D12" s="261" t="n"/>
       <c r="E12" s="259" t="n"/>
       <c r="F12" s="397" t="n">
-        <v>7.87</v>
+        <v>5.76</v>
       </c>
       <c r="G12" s="397" t="n">
-        <v>6.98</v>
+        <v>6.37</v>
       </c>
       <c r="H12" s="397" t="n">
-        <v>6.49</v>
+        <v>6.96</v>
       </c>
       <c r="I12" s="397" t="n">
-        <v>8.779999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="J12" s="397" t="n">
         <v>8.83</v>
       </c>
       <c r="K12" s="397" t="n">
-        <v>9.83</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L12" s="397" t="n">
-        <v>10.3</v>
+        <v>10.25</v>
       </c>
       <c r="M12" s="397" t="n">
-        <v>7.66</v>
+        <v>1.12</v>
       </c>
       <c r="N12" s="397" t="n">
         <v>3.59</v>
       </c>
       <c r="O12" s="397" t="n">
-        <v>7.11</v>
+        <v>5.54</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>7.24</v>
+        <v>6.78</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>7.07</v>
+        <v>7.33</v>
       </c>
       <c r="R12" s="397" t="n">
         <v>8.640000000000001</v>
       </c>
       <c r="S12" s="397" t="n">
-        <v>10.38</v>
+        <v>9.85</v>
       </c>
       <c r="T12" s="397" t="n">
-        <v>10.55</v>
+        <v>10.84</v>
       </c>
       <c r="U12" s="397" t="n">
         <v>7.29</v>
       </c>
       <c r="V12" s="397" t="n">
-        <v>10.3</v>
+        <v>2.64</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>2.41</v>
+        <v>1.14</v>
       </c>
       <c r="X12" s="397" t="n">
-        <v>7.83</v>
+        <v>6.9</v>
       </c>
       <c r="Y12" s="397" t="n">
-        <v>7.12</v>
+        <v>6.49</v>
       </c>
       <c r="Z12" s="397" t="n">
-        <v>6.5</v>
+        <v>6.98</v>
       </c>
       <c r="AA12" s="397" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AB12" s="397" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="AC12" s="397" t="n">
-        <v>9.83</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AD12" s="397" t="n">
-        <v>10.31</v>
+        <v>10.26</v>
       </c>
       <c r="AE12" s="397" t="n">
-        <v>7.61</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>2.93</v>
+        <v>2.58</v>
       </c>
       <c r="AG12" s="426" t="n"/>
       <c r="AH12" s="426" t="n"/>
@@ -17206,85 +17206,85 @@
       </c>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>1695.4</v>
+        <v>1375.5</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>1498</v>
+        <v>1622.6</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>1392</v>
+        <v>1774.1</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>1850.8</v>
+        <v>2002.4</v>
       </c>
       <c r="J13" s="398" t="n">
-        <v>1860.6</v>
+        <v>2072</v>
       </c>
       <c r="K13" s="398" t="n">
-        <v>2068.5</v>
+        <v>2274.6</v>
       </c>
       <c r="L13" s="398" t="n">
-        <v>2167.2</v>
+        <v>2359.3</v>
       </c>
       <c r="M13" s="398" t="n">
-        <v>1533</v>
+        <v>183.4</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>670.2</v>
+        <v>872.2</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>1341.2</v>
+        <v>1271.2</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>1533</v>
+        <v>1569</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>1498.7</v>
+        <v>1697.2</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>1859.2</v>
+        <v>1985.9</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>2132.2</v>
+        <v>2246</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>2167.6</v>
+        <v>2473.5</v>
       </c>
       <c r="U13" s="398" t="n">
-        <v>1614.9</v>
+        <v>1931.3</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>2005.1</v>
+        <v>449.4</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>465.1</v>
+        <v>539</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>1688.4</v>
+        <v>1653</v>
       </c>
       <c r="Y13" s="398" t="n">
-        <v>1505.3</v>
+        <v>1625.4</v>
       </c>
       <c r="Z13" s="398" t="n">
-        <v>1372.4</v>
+        <v>1750</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>1856.4</v>
+        <v>2006.5</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>1872.8</v>
+        <v>2095.4</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>2072.7</v>
+        <v>2269.4</v>
       </c>
       <c r="AD13" s="398" t="n">
-        <v>2173.8</v>
+        <v>2356.9</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>1522.5</v>
+        <v>202.3</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>560</v>
+        <v>690.9</v>
       </c>
       <c r="AG13" s="428" t="n"/>
       <c r="AH13" s="428" t="n"/>
@@ -19534,85 +19534,85 @@
       </c>
       <c r="E32" s="259" t="n"/>
       <c r="F32" s="408" t="n">
-        <v>9162</v>
+        <v>5155</v>
       </c>
       <c r="G32" s="408" t="n">
-        <v>6519</v>
+        <v>8120</v>
       </c>
       <c r="H32" s="408" t="n">
-        <v>5327</v>
+        <v>10381</v>
       </c>
       <c r="I32" s="408" t="n">
-        <v>11661</v>
+        <v>14479</v>
       </c>
       <c r="J32" s="408" t="n">
-        <v>11832</v>
+        <v>15906</v>
       </c>
       <c r="K32" s="408" t="n">
-        <v>15833</v>
+        <v>20560</v>
       </c>
       <c r="L32" s="408" t="n">
-        <v>17998</v>
+        <v>22734</v>
       </c>
       <c r="M32" s="408" t="n">
-        <v>6946</v>
+        <v>30</v>
       </c>
       <c r="N32" s="408" t="n">
-        <v>714</v>
+        <v>1473</v>
       </c>
       <c r="O32" s="408" t="n">
-        <v>4810</v>
+        <v>4150</v>
       </c>
       <c r="P32" s="408" t="n">
-        <v>6946</v>
+        <v>7405</v>
       </c>
       <c r="Q32" s="408" t="n">
-        <v>6527</v>
+        <v>9188</v>
       </c>
       <c r="R32" s="408" t="n">
-        <v>11807</v>
+        <v>14154</v>
       </c>
       <c r="S32" s="408" t="n">
-        <v>17210</v>
+        <v>19854</v>
       </c>
       <c r="T32" s="408" t="n">
-        <v>18006</v>
+        <v>25887</v>
       </c>
       <c r="U32" s="408" t="n">
-        <v>8015</v>
+        <v>13109</v>
       </c>
       <c r="V32" s="408" t="n">
-        <v>14535</v>
+        <v>178</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="X32" s="408" t="n">
-        <v>9058</v>
+        <v>8546</v>
       </c>
       <c r="Y32" s="408" t="n">
-        <v>6607</v>
+        <v>8159</v>
       </c>
       <c r="Z32" s="408" t="n">
-        <v>5123</v>
+        <v>9997</v>
       </c>
       <c r="AA32" s="408" t="n">
-        <v>11758</v>
+        <v>14563</v>
       </c>
       <c r="AB32" s="408" t="n">
-        <v>12047</v>
+        <v>16406</v>
       </c>
       <c r="AC32" s="408" t="n">
-        <v>15921</v>
+        <v>20429</v>
       </c>
       <c r="AD32" s="408" t="n">
-        <v>18150</v>
+        <v>22669</v>
       </c>
       <c r="AE32" s="408" t="n">
-        <v>6816</v>
+        <v>36</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>277</v>
+        <v>776</v>
       </c>
       <c r="AG32" s="434" t="n"/>
       <c r="AH32" s="434" t="n"/>
@@ -20050,7 +20050,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 101-1 (38.1 °C), 102-2 (38.1 °C), 102-3 (38.1 °C), 103-4 (37.8 °C), 104-5 (37.8 °C), 105-6 (37.7 °C), 105-7 (37.7 °C), 106-8 (32.0 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 101-1 (39.9 °C), 102-2 (41.1 °C), 102-3 (41.1 °C), 103-4 (39.8 °C), 104-5 (39.6 °C), 105-6 (39.3 °C), 105-7 (39.3 °C), 106-8 (29.1 °C) ...</t>
         </is>
       </c>
       <c r="F38" s="243" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 43760 W</t>
+          <t>TOPLAM ISI = 43910 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -20313,7 +20313,7 @@
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 18806 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 28470 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -21070,79 +21070,79 @@
         <v>7.57</v>
       </c>
       <c r="G12" s="397" t="n">
-        <v>6.98</v>
+        <v>6.35</v>
       </c>
       <c r="H12" s="397" t="n">
-        <v>6.46</v>
+        <v>6.95</v>
       </c>
       <c r="I12" s="397" t="n">
-        <v>8.76</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J12" s="397" t="n">
         <v>8.83</v>
       </c>
       <c r="K12" s="397" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L12" s="397" t="n">
-        <v>10.28</v>
+        <v>10.23</v>
       </c>
       <c r="M12" s="397" t="n">
-        <v>7.64</v>
+        <v>1.24</v>
       </c>
       <c r="N12" s="397" t="n">
         <v>3.64</v>
       </c>
       <c r="O12" s="397" t="n">
-        <v>6.92</v>
+        <v>5.7</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>7.03</v>
+        <v>6.78</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>7.18</v>
+        <v>7.38</v>
       </c>
       <c r="R12" s="397" t="n">
         <v>8.66</v>
       </c>
       <c r="S12" s="397" t="n">
-        <v>10.32</v>
+        <v>11.08</v>
       </c>
       <c r="T12" s="397" t="n">
-        <v>10.5</v>
+        <v>9.68</v>
       </c>
       <c r="U12" s="397" t="n">
         <v>7.28</v>
       </c>
       <c r="V12" s="397" t="n">
-        <v>10.51</v>
+        <v>2.81</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>2.37</v>
+        <v>2.06</v>
       </c>
       <c r="X12" s="397" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="Y12" s="397" t="n">
-        <v>7.1</v>
+        <v>6.47</v>
       </c>
       <c r="Z12" s="397" t="n">
-        <v>6.48</v>
+        <v>6.96</v>
       </c>
       <c r="AA12" s="397" t="n">
-        <v>8.77</v>
+        <v>8.51</v>
       </c>
       <c r="AB12" s="397" t="n">
         <v>8.85</v>
       </c>
       <c r="AC12" s="397" t="n">
-        <v>9.68</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AD12" s="397" t="n">
-        <v>10.3</v>
+        <v>10.26</v>
       </c>
       <c r="AE12" s="397" t="n">
-        <v>8.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" s="397" t="n">
         <v>3.67</v>
@@ -21180,85 +21180,85 @@
       </c>
       <c r="E13" s="259" t="n"/>
       <c r="F13" s="398" t="n">
-        <v>1597.8</v>
+        <v>1760.5</v>
       </c>
       <c r="G13" s="398" t="n">
-        <v>1488.9</v>
+        <v>1616</v>
       </c>
       <c r="H13" s="398" t="n">
-        <v>1378.3</v>
+        <v>1767.5</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>1848</v>
+        <v>1999.6</v>
       </c>
       <c r="J13" s="398" t="n">
-        <v>1859.2</v>
+        <v>2075.8</v>
       </c>
       <c r="K13" s="398" t="n">
-        <v>2050.3</v>
+        <v>2256.4</v>
       </c>
       <c r="L13" s="398" t="n">
-        <v>2163</v>
+        <v>2355.2</v>
       </c>
       <c r="M13" s="398" t="n">
-        <v>1526.3</v>
+        <v>255.8</v>
       </c>
       <c r="N13" s="398" t="n">
-        <v>695.8</v>
+        <v>897.8</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>1288.4</v>
+        <v>1253</v>
       </c>
       <c r="P13" s="398" t="n">
-        <v>1453.5</v>
+        <v>1561.7</v>
       </c>
       <c r="Q13" s="398" t="n">
-        <v>1483.7</v>
+        <v>1699.2</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>1859.2</v>
+        <v>1982.4</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>2125.2</v>
+        <v>2515.5</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>2163.3</v>
+        <v>2199</v>
       </c>
       <c r="U13" s="398" t="n">
-        <v>1610.7</v>
+        <v>1927.1</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>2005.9</v>
+        <v>450.8</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>460.2</v>
+        <v>528.9</v>
       </c>
       <c r="X13" s="398" t="n">
-        <v>1679.7</v>
+        <v>1660</v>
       </c>
       <c r="Y13" s="398" t="n">
-        <v>1498</v>
+        <v>1622.6</v>
       </c>
       <c r="Z13" s="398" t="n">
-        <v>1366.4</v>
+        <v>1747.5</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>1848</v>
+        <v>2006.9</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>1864.8</v>
+        <v>2088.8</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>2033.5</v>
+        <v>2239.7</v>
       </c>
       <c r="AD13" s="398" t="n">
-        <v>2163</v>
+        <v>2364.2</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>1545.2</v>
+        <v>174.3</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>704.2</v>
+        <v>904</v>
       </c>
       <c r="AG13" s="428" t="n"/>
       <c r="AH13" s="428" t="n"/>
@@ -21954,7 +21954,7 @@
         <f>U10+(U14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="V19" s="401">
+      <c r="V19" s="400">
         <f>V10+(V14/8.92)^0.91</f>
         <v/>
       </c>
@@ -21990,7 +21990,7 @@
         <f>AD10+(AD14/8.92)^0.91</f>
         <v/>
       </c>
-      <c r="AE19" s="401">
+      <c r="AE19" s="400">
         <f>AE10+(AE14/8.92)^0.91</f>
         <v/>
       </c>
@@ -23508,85 +23508,85 @@
       </c>
       <c r="E32" s="259" t="n"/>
       <c r="F32" s="408" t="n">
-        <v>7783</v>
+        <v>10162</v>
       </c>
       <c r="G32" s="408" t="n">
-        <v>6410</v>
+        <v>8029</v>
       </c>
       <c r="H32" s="408" t="n">
-        <v>5184</v>
+        <v>10274</v>
       </c>
       <c r="I32" s="408" t="n">
-        <v>11613</v>
+        <v>14423</v>
       </c>
       <c r="J32" s="408" t="n">
-        <v>11807</v>
+        <v>15988</v>
       </c>
       <c r="K32" s="408" t="n">
-        <v>15452</v>
+        <v>20110</v>
       </c>
       <c r="L32" s="408" t="n">
-        <v>17902</v>
+        <v>22623</v>
       </c>
       <c r="M32" s="408" t="n">
-        <v>6864</v>
+        <v>58</v>
       </c>
       <c r="N32" s="408" t="n">
-        <v>791</v>
+        <v>1595</v>
       </c>
       <c r="O32" s="408" t="n">
-        <v>4306</v>
+        <v>3989</v>
       </c>
       <c r="P32" s="408" t="n">
-        <v>6000</v>
+        <v>7310</v>
       </c>
       <c r="Q32" s="408" t="n">
-        <v>6348</v>
+        <v>9219</v>
       </c>
       <c r="R32" s="408" t="n">
-        <v>11807</v>
+        <v>14086</v>
       </c>
       <c r="S32" s="408" t="n">
-        <v>17055</v>
+        <v>27114</v>
       </c>
       <c r="T32" s="408" t="n">
-        <v>17910</v>
+        <v>18735</v>
       </c>
       <c r="U32" s="408" t="n">
-        <v>7958</v>
+        <v>13031</v>
       </c>
       <c r="V32" s="408" t="n">
-        <v>14549</v>
+        <v>179</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="X32" s="408" t="n">
-        <v>8930</v>
+        <v>8646</v>
       </c>
       <c r="Y32" s="408" t="n">
-        <v>6519</v>
+        <v>8120</v>
       </c>
       <c r="Z32" s="408" t="n">
-        <v>5062</v>
+        <v>9958</v>
       </c>
       <c r="AA32" s="408" t="n">
-        <v>11613</v>
+        <v>14570</v>
       </c>
       <c r="AB32" s="408" t="n">
-        <v>11905</v>
+        <v>16264</v>
       </c>
       <c r="AC32" s="408" t="n">
-        <v>15107</v>
+        <v>19701</v>
       </c>
       <c r="AD32" s="408" t="n">
-        <v>17902</v>
+        <v>22864</v>
       </c>
       <c r="AE32" s="408" t="n">
-        <v>7100</v>
+        <v>27</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>818</v>
+        <v>1626</v>
       </c>
       <c r="AG32" s="434" t="n"/>
       <c r="AH32" s="434" t="n"/>
@@ -24024,7 +24024,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 201-1 (37.8 °C), 202-2 (38.0 °C), 202-3 (38.0 °C), 203-4 (37.8 °C), 204-5 (37.8 °C), 205-6 (37.7 °C), 205-7 (37.7 °C), 206-8 (31.9 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (25 devre): 201-1 (39.4 °C), 202-2 (41.1 °C), 202-3 (41.1 °C), 203-4 (39.8 °C), 204-5 (39.6 °C), 205-6 (39.3 °C), 205-7 (39.3 °C), 206-8 (32.4 °C) ...</t>
         </is>
       </c>
       <c r="F38" s="243" t="inlineStr">

--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -4500,7 +4500,7 @@
         </is>
       </c>
       <c r="D12" s="343" t="n">
-        <v>2001</v>
+        <v>2084.2</v>
       </c>
       <c r="E12" s="344" t="n">
         <v>35</v>
@@ -4510,7 +4510,7 @@
         <v/>
       </c>
       <c r="G12" s="340" t="n">
-        <v>57.17</v>
+        <v>59.55</v>
       </c>
       <c r="H12" s="340" t="n">
         <v>1</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="D19" s="343" t="n">
-        <v>2002.4</v>
+        <v>2090.5</v>
       </c>
       <c r="E19" s="344" t="n">
         <v>35</v>
@@ -4825,7 +4825,7 @@
         <v/>
       </c>
       <c r="G19" s="340" t="n">
-        <v>57.21</v>
+        <v>59.73</v>
       </c>
       <c r="H19" s="340" t="n">
         <v>1</v>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="D27" s="348" t="n">
-        <v>4299.1</v>
+        <v>4301.5</v>
       </c>
       <c r="E27" s="349" t="n">
         <v>35</v>
@@ -5185,7 +5185,7 @@
         <v/>
       </c>
       <c r="G27" s="345" t="n">
-        <v>122.83</v>
+        <v>122.9</v>
       </c>
       <c r="H27" s="345" t="n">
         <v>2</v>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
       <c r="D29" s="348" t="n">
-        <v>915.6</v>
+        <v>869.8</v>
       </c>
       <c r="E29" s="349" t="n">
         <v>35</v>
@@ -5275,7 +5275,7 @@
         <v/>
       </c>
       <c r="G29" s="345" t="n">
-        <v>26.16</v>
+        <v>24.85</v>
       </c>
       <c r="H29" s="345" t="n">
         <v>1</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="D30" s="348" t="n">
-        <v>798.7</v>
+        <v>1053.8</v>
       </c>
       <c r="E30" s="349" t="n">
         <v>35</v>
@@ -5320,7 +5320,7 @@
         <v/>
       </c>
       <c r="G30" s="345" t="n">
-        <v>22.82</v>
+        <v>30.11</v>
       </c>
       <c r="H30" s="345" t="n">
         <v>1</v>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="D34" s="348" t="n">
-        <v>2002.4</v>
+        <v>2090.5</v>
       </c>
       <c r="E34" s="349" t="n">
         <v>35</v>
@@ -5488,7 +5488,7 @@
         <v/>
       </c>
       <c r="G34" s="345" t="n">
-        <v>57.21</v>
+        <v>59.73</v>
       </c>
       <c r="H34" s="345" t="n">
         <v>1</v>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="D39" s="348" t="n">
-        <v>1271.2</v>
+        <v>1285.2</v>
       </c>
       <c r="E39" s="349" t="n">
         <v>35</v>
@@ -5713,7 +5713,7 @@
         <v/>
       </c>
       <c r="G39" s="345" t="n">
-        <v>36.32</v>
+        <v>36.72</v>
       </c>
       <c r="H39" s="345" t="n">
         <v>1</v>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="D42" s="348" t="n">
-        <v>4719.4</v>
+        <v>4733.4</v>
       </c>
       <c r="E42" s="349" t="n">
         <v>35</v>
@@ -5848,7 +5848,7 @@
         <v/>
       </c>
       <c r="G42" s="345" t="n">
-        <v>134.84</v>
+        <v>135.24</v>
       </c>
       <c r="H42" s="345" t="n">
         <v>2</v>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="D44" s="348" t="n">
-        <v>449.4</v>
+        <v>641.5</v>
       </c>
       <c r="E44" s="349" t="n">
         <v>35</v>
@@ -5938,7 +5938,7 @@
         <v/>
       </c>
       <c r="G44" s="345" t="n">
-        <v>12.84</v>
+        <v>18.33</v>
       </c>
       <c r="H44" s="345" t="n">
         <v>1</v>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="D45" s="348" t="n">
-        <v>539</v>
+        <v>791.7</v>
       </c>
       <c r="E45" s="349" t="n">
         <v>35</v>
@@ -5983,7 +5983,7 @@
         <v/>
       </c>
       <c r="G45" s="345" t="n">
-        <v>15.4</v>
+        <v>22.62</v>
       </c>
       <c r="H45" s="345" t="n">
         <v>1</v>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="D48" s="348" t="n">
-        <v>2006.5</v>
+        <v>2089.8</v>
       </c>
       <c r="E48" s="349" t="n">
         <v>35</v>
@@ -6118,7 +6118,7 @@
         <v/>
       </c>
       <c r="G48" s="345" t="n">
-        <v>57.33</v>
+        <v>59.71</v>
       </c>
       <c r="H48" s="345" t="n">
         <v>1</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="D52" s="348" t="n">
-        <v>690.9</v>
+        <v>731.1</v>
       </c>
       <c r="E52" s="349" t="n">
         <v>35</v>
@@ -6298,7 +6298,7 @@
         <v/>
       </c>
       <c r="G52" s="345" t="n">
-        <v>19.74</v>
+        <v>20.89</v>
       </c>
       <c r="H52" s="345" t="n">
         <v>1</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="D56" s="348" t="n">
-        <v>1999.6</v>
+        <v>2087.8</v>
       </c>
       <c r="E56" s="349" t="n">
         <v>35</v>
@@ -6466,7 +6466,7 @@
         <v/>
       </c>
       <c r="G56" s="345" t="n">
-        <v>57.13</v>
+        <v>59.65</v>
       </c>
       <c r="H56" s="345" t="n">
         <v>1</v>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="D67" s="348" t="n">
-        <v>528.9</v>
+        <v>786.4</v>
       </c>
       <c r="E67" s="349" t="n">
         <v>35</v>
@@ -6961,7 +6961,7 @@
         <v/>
       </c>
       <c r="G67" s="345" t="n">
-        <v>15.11</v>
+        <v>22.47</v>
       </c>
       <c r="H67" s="345" t="n">
         <v>1</v>
@@ -7086,7 +7086,7 @@
         </is>
       </c>
       <c r="D70" s="348" t="n">
-        <v>2006.9</v>
+        <v>2094.8</v>
       </c>
       <c r="E70" s="349" t="n">
         <v>35</v>
@@ -7096,7 +7096,7 @@
         <v/>
       </c>
       <c r="G70" s="345" t="n">
-        <v>57.34</v>
+        <v>59.85</v>
       </c>
       <c r="H70" s="345" t="n">
         <v>1</v>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 44443 W</t>
+          <t>TOPLAM ISI = 44827 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -13542,7 +13542,7 @@
         <v>6.97</v>
       </c>
       <c r="I12" s="397" t="n">
-        <v>8.48</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="J12" s="397" t="n">
         <v>8.84</v>
@@ -13569,7 +13569,7 @@
         <v>6.96</v>
       </c>
       <c r="R12" s="397" t="n">
-        <v>8.43</v>
+        <v>8.76</v>
       </c>
       <c r="S12" s="397" t="n">
         <v>8.83</v>
@@ -13590,28 +13590,28 @@
         <v>4.26</v>
       </c>
       <c r="Y12" s="397" t="n">
-        <v>6.8</v>
+        <v>6.82</v>
       </c>
       <c r="Z12" s="397" t="n">
-        <v>7.31</v>
+        <v>7.33</v>
       </c>
       <c r="AA12" s="397" t="n">
         <v>8.640000000000001</v>
       </c>
       <c r="AB12" s="397" t="n">
-        <v>10.14</v>
+        <v>11.14</v>
       </c>
       <c r="AC12" s="397" t="n">
-        <v>8.789999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="AD12" s="397" t="n">
         <v>7.31</v>
       </c>
       <c r="AE12" s="397" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>1.12</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="13" ht="12" customHeight="1" s="244">
@@ -13638,7 +13638,7 @@
         <v>1748.6</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>2001</v>
+        <v>2084.2</v>
       </c>
       <c r="J13" s="398" t="n">
         <v>2088.8</v>
@@ -13665,7 +13665,7 @@
         <v>1774.1</v>
       </c>
       <c r="R13" s="398" t="n">
-        <v>2002.4</v>
+        <v>2090.5</v>
       </c>
       <c r="S13" s="398" t="n">
         <v>2072</v>
@@ -13695,19 +13695,19 @@
         <v>2216.9</v>
       </c>
       <c r="AB13" s="398" t="n">
-        <v>2303</v>
+        <v>2306.8</v>
       </c>
       <c r="AC13" s="398" t="n">
-        <v>1996</v>
+        <v>1994.7</v>
       </c>
       <c r="AD13" s="398" t="n">
         <v>2157.1</v>
       </c>
       <c r="AE13" s="398" t="n">
-        <v>915.6</v>
+        <v>869.8</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>798.7</v>
+        <v>1053.8</v>
       </c>
     </row>
     <row r="14" ht="12" customHeight="1" s="244">
@@ -15650,7 +15650,7 @@
         <v>9975</v>
       </c>
       <c r="I32" s="408" t="n">
-        <v>14451</v>
+        <v>16166</v>
       </c>
       <c r="J32" s="408" t="n">
         <v>16264</v>
@@ -15677,7 +15677,7 @@
         <v>10381</v>
       </c>
       <c r="R32" s="408" t="n">
-        <v>14479</v>
+        <v>16301</v>
       </c>
       <c r="S32" s="408" t="n">
         <v>15906</v>
@@ -15707,19 +15707,19 @@
         <v>19156</v>
       </c>
       <c r="AB32" s="408" t="n">
-        <v>21272</v>
+        <v>21370</v>
       </c>
       <c r="AC32" s="408" t="n">
-        <v>14354</v>
+        <v>14326</v>
       </c>
       <c r="AD32" s="408" t="n">
         <v>17767</v>
       </c>
       <c r="AE32" s="408" t="n">
-        <v>1683</v>
+        <v>1462</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>1156</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1" s="244">
@@ -16081,7 +16081,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): Z01-1 (39.9 °C), Z02-2 (40.8 °C), Z02-3 (40.8 °C), Z03-4 (39.7 °C), Z04-5 (39.7 °C), Z05-6 (39.2 °C), Z05-7 (39.2 °C), Z06-8 (29.8 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): Z01-1 (39.9 °C), Z02-2 (40.8 °C), Z02-3 (40.8 °C), Z03-4 (39.8 °C), Z04-5 (39.7 °C), Z05-6 (39.2 °C), Z05-7 (39.2 °C), Z06-8 (29.8 °C) ...</t>
         </is>
       </c>
       <c r="H38" s="243" t="n"/>
@@ -16300,7 +16300,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 43349 W</t>
+          <t>TOPLAM ISI = 44033 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="E3" s="383" t="inlineStr">
         <is>
-          <t>MAX. BASINÇ KAYBI = 27181 Pa</t>
+          <t>MAX. BASINÇ KAYBI = 27393 Pa</t>
         </is>
       </c>
       <c r="F3" s="250" t="n"/>
@@ -17102,7 +17102,7 @@
         <v>6.96</v>
       </c>
       <c r="I12" s="397" t="n">
-        <v>8.460000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="J12" s="397" t="n">
         <v>8.83</v>
@@ -17123,28 +17123,28 @@
         <v>5.54</v>
       </c>
       <c r="P12" s="397" t="n">
-        <v>6.78</v>
+        <v>6.79</v>
       </c>
       <c r="Q12" s="397" t="n">
-        <v>7.33</v>
+        <v>7.35</v>
       </c>
       <c r="R12" s="397" t="n">
         <v>8.640000000000001</v>
       </c>
       <c r="S12" s="397" t="n">
-        <v>9.85</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="T12" s="397" t="n">
-        <v>10.84</v>
+        <v>10.87</v>
       </c>
       <c r="U12" s="397" t="n">
         <v>7.29</v>
       </c>
       <c r="V12" s="397" t="n">
-        <v>2.64</v>
+        <v>2.07</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>1.14</v>
+        <v>2.41</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>6.9</v>
@@ -17156,7 +17156,7 @@
         <v>6.98</v>
       </c>
       <c r="AA12" s="397" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB12" s="397" t="n">
         <v>8.880000000000001</v>
@@ -17171,7 +17171,7 @@
         <v>1.17</v>
       </c>
       <c r="AF12" s="397" t="n">
-        <v>2.58</v>
+        <v>2.93</v>
       </c>
       <c r="AG12" s="426" t="n"/>
       <c r="AH12" s="426" t="n"/>
@@ -17215,7 +17215,7 @@
         <v>1774.1</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>2002.4</v>
+        <v>2090.5</v>
       </c>
       <c r="J13" s="398" t="n">
         <v>2072</v>
@@ -17233,7 +17233,7 @@
         <v>872.2</v>
       </c>
       <c r="O13" s="398" t="n">
-        <v>1271.2</v>
+        <v>1285.2</v>
       </c>
       <c r="P13" s="398" t="n">
         <v>1569</v>
@@ -17245,19 +17245,19 @@
         <v>1985.9</v>
       </c>
       <c r="S13" s="398" t="n">
-        <v>2246</v>
+        <v>2253</v>
       </c>
       <c r="T13" s="398" t="n">
-        <v>2473.5</v>
+        <v>2480.5</v>
       </c>
       <c r="U13" s="398" t="n">
         <v>1931.3</v>
       </c>
       <c r="V13" s="398" t="n">
-        <v>449.4</v>
+        <v>641.5</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>539</v>
+        <v>791.7</v>
       </c>
       <c r="X13" s="398" t="n">
         <v>1653</v>
@@ -17269,7 +17269,7 @@
         <v>1750</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>2006.5</v>
+        <v>2089.8</v>
       </c>
       <c r="AB13" s="398" t="n">
         <v>2095.4</v>
@@ -17284,7 +17284,7 @@
         <v>202.3</v>
       </c>
       <c r="AF13" s="398" t="n">
-        <v>690.9</v>
+        <v>731.1</v>
       </c>
       <c r="AG13" s="428" t="n"/>
       <c r="AH13" s="428" t="n"/>
@@ -19543,7 +19543,7 @@
         <v>10381</v>
       </c>
       <c r="I32" s="408" t="n">
-        <v>14479</v>
+        <v>16301</v>
       </c>
       <c r="J32" s="408" t="n">
         <v>15906</v>
@@ -19561,7 +19561,7 @@
         <v>1473</v>
       </c>
       <c r="O32" s="408" t="n">
-        <v>4150</v>
+        <v>4277</v>
       </c>
       <c r="P32" s="408" t="n">
         <v>7405</v>
@@ -19573,19 +19573,19 @@
         <v>14154</v>
       </c>
       <c r="S32" s="408" t="n">
-        <v>19854</v>
+        <v>20025</v>
       </c>
       <c r="T32" s="408" t="n">
-        <v>25887</v>
+        <v>26089</v>
       </c>
       <c r="U32" s="408" t="n">
         <v>13109</v>
       </c>
       <c r="V32" s="408" t="n">
-        <v>178</v>
+        <v>633</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>256</v>
+        <v>1129</v>
       </c>
       <c r="X32" s="408" t="n">
         <v>8546</v>
@@ -19597,7 +19597,7 @@
         <v>9997</v>
       </c>
       <c r="AA32" s="408" t="n">
-        <v>14563</v>
+        <v>16286</v>
       </c>
       <c r="AB32" s="408" t="n">
         <v>16406</v>
@@ -19612,7 +19612,7 @@
         <v>36</v>
       </c>
       <c r="AF32" s="408" t="n">
-        <v>776</v>
+        <v>907</v>
       </c>
       <c r="AG32" s="434" t="n"/>
       <c r="AH32" s="434" t="n"/>
@@ -20050,7 +20050,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 101-1 (39.9 °C), 102-2 (41.1 °C), 102-3 (41.1 °C), 103-4 (39.8 °C), 104-5 (39.6 °C), 105-6 (39.3 °C), 105-7 (39.3 °C), 106-8 (29.1 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 101-1 (39.9 °C), 102-2 (41.1 °C), 102-3 (41.1 °C), 103-4 (39.9 °C), 104-5 (39.6 °C), 105-6 (39.3 °C), 105-7 (39.3 °C), 106-8 (29.1 °C) ...</t>
         </is>
       </c>
       <c r="F38" s="243" t="inlineStr">
@@ -20274,7 +20274,7 @@
       </c>
       <c r="E2" s="383" t="inlineStr">
         <is>
-          <t>TOPLAM ISI = 43910 W</t>
+          <t>TOPLAM ISI = 44344 W</t>
         </is>
       </c>
       <c r="F2" s="264" t="n"/>
@@ -21076,7 +21076,7 @@
         <v>6.95</v>
       </c>
       <c r="I12" s="397" t="n">
-        <v>8.449999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="J12" s="397" t="n">
         <v>8.83</v>
@@ -21118,7 +21118,7 @@
         <v>2.81</v>
       </c>
       <c r="W12" s="397" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="X12" s="397" t="n">
         <v>6.9</v>
@@ -21130,7 +21130,7 @@
         <v>6.96</v>
       </c>
       <c r="AA12" s="397" t="n">
-        <v>8.51</v>
+        <v>8.77</v>
       </c>
       <c r="AB12" s="397" t="n">
         <v>8.85</v>
@@ -21189,7 +21189,7 @@
         <v>1767.5</v>
       </c>
       <c r="I13" s="398" t="n">
-        <v>1999.6</v>
+        <v>2087.8</v>
       </c>
       <c r="J13" s="398" t="n">
         <v>2075.8</v>
@@ -21231,7 +21231,7 @@
         <v>450.8</v>
       </c>
       <c r="W13" s="398" t="n">
-        <v>528.9</v>
+        <v>786.4</v>
       </c>
       <c r="X13" s="398" t="n">
         <v>1660</v>
@@ -21243,7 +21243,7 @@
         <v>1747.5</v>
       </c>
       <c r="AA13" s="398" t="n">
-        <v>2006.9</v>
+        <v>2094.8</v>
       </c>
       <c r="AB13" s="398" t="n">
         <v>2088.8</v>
@@ -23517,7 +23517,7 @@
         <v>10274</v>
       </c>
       <c r="I32" s="408" t="n">
-        <v>14423</v>
+        <v>16241</v>
       </c>
       <c r="J32" s="408" t="n">
         <v>15988</v>
@@ -23559,7 +23559,7 @@
         <v>179</v>
       </c>
       <c r="W32" s="408" t="n">
-        <v>247</v>
+        <v>1108</v>
       </c>
       <c r="X32" s="408" t="n">
         <v>8646</v>
@@ -23571,7 +23571,7 @@
         <v>9958</v>
       </c>
       <c r="AA32" s="408" t="n">
-        <v>14570</v>
+        <v>16391</v>
       </c>
       <c r="AB32" s="408" t="n">
         <v>16264</v>
@@ -24024,7 +24024,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (25 devre): 201-1 (39.4 °C), 202-2 (41.1 °C), 202-3 (41.1 °C), 203-4 (39.8 °C), 204-5 (39.6 °C), 205-6 (39.3 °C), 205-7 (39.3 °C), 206-8 (32.4 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (25 devre): 201-1 (39.4 °C), 202-2 (41.1 °C), 202-3 (41.1 °C), 203-4 (39.9 °C), 204-5 (39.6 °C), 205-6 (39.3 °C), 205-7 (39.3 °C), 206-8 (32.4 °C) ...</t>
         </is>
       </c>
       <c r="F38" s="243" t="inlineStr">

--- a/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
+++ b/proje/denemeler/yerden2/NB_YERDEN_ISITMA.xlsx
@@ -12983,40 +12983,40 @@
       <c r="D7" s="389" t="n"/>
       <c r="E7" s="391" t="n"/>
       <c r="F7" s="392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="392" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H7" s="392" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I7" s="392" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" s="392" t="n">
         <v>5</v>
       </c>
       <c r="K7" s="392" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L7" s="392" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M7" s="392" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N7" s="392" t="n">
         <v>9</v>
       </c>
       <c r="O7" s="392" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P7" s="392" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="392" t="n">
         <v>11</v>
-      </c>
-      <c r="Q7" s="392" t="n">
-        <v>12</v>
       </c>
       <c r="R7" s="392" t="n">
         <v>13</v>
@@ -13031,37 +13031,37 @@
         <v>16</v>
       </c>
       <c r="V7" s="392" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W7" s="392" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="X7" s="392" t="n">
         <v>19</v>
       </c>
       <c r="Y7" s="392" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z7" s="392" t="n">
         <v>21</v>
       </c>
       <c r="AA7" s="392" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AB7" s="392" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC7" s="392" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD7" s="392" t="n">
         <v>23</v>
       </c>
-      <c r="AC7" s="392" t="n">
+      <c r="AE7" s="392" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF7" s="392" t="n">
         <v>24</v>
-      </c>
-      <c r="AD7" s="392" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE7" s="392" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF7" s="392" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="8" ht="12" customHeight="1" s="244">
@@ -16081,7 +16081,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): Z01-1 (39.9 °C), Z02-2 (40.8 °C), Z02-3 (40.8 °C), Z03-4 (39.8 °C), Z04-5 (39.7 °C), Z05-6 (39.2 °C), Z05-7 (39.2 °C), Z06-8 (29.8 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): Z01-2 (39.9 °C), Z02-7 (40.8 °C), Z02-8 (40.8 °C), Z03-6 (39.8 °C), Z04-5 (39.7 °C), Z05-4 (39.2 °C), Z05-3 (39.2 °C), Z06-1 (29.8 °C) ...</t>
         </is>
       </c>
       <c r="H38" s="243" t="n"/>
@@ -16458,13 +16458,13 @@
       <c r="D7" s="389" t="n"/>
       <c r="E7" s="391" t="n"/>
       <c r="F7" s="392" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G7" s="392" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="392" t="n">
         <v>2</v>
-      </c>
-      <c r="H7" s="392" t="n">
-        <v>3</v>
       </c>
       <c r="I7" s="392" t="n">
         <v>4</v>
@@ -16479,61 +16479,61 @@
         <v>7</v>
       </c>
       <c r="M7" s="392" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="392" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O7" s="392" t="n">
+        <v>18</v>
+      </c>
+      <c r="P7" s="392" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="392" t="n">
+        <v>11</v>
+      </c>
+      <c r="R7" s="392" t="n">
         <v>10</v>
       </c>
-      <c r="P7" s="392" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q7" s="392" t="n">
-        <v>12</v>
-      </c>
-      <c r="R7" s="392" t="n">
+      <c r="S7" s="392" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" s="392" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" s="392" t="n">
         <v>13</v>
-      </c>
-      <c r="S7" s="392" t="n">
-        <v>14</v>
-      </c>
-      <c r="T7" s="392" t="n">
-        <v>15</v>
-      </c>
-      <c r="U7" s="392" t="n">
-        <v>16</v>
       </c>
       <c r="V7" s="392" t="n">
         <v>17</v>
       </c>
       <c r="W7" s="392" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="X7" s="392" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y7" s="392" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Z7" s="392" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AA7" s="392" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB7" s="392" t="n">
         <v>23</v>
       </c>
       <c r="AC7" s="392" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AD7" s="392" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE7" s="392" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AF7" s="392" t="n">
         <v>27</v>
@@ -20050,7 +20050,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 101-1 (39.9 °C), 102-2 (41.1 °C), 102-3 (41.1 °C), 103-4 (39.9 °C), 104-5 (39.6 °C), 105-6 (39.3 °C), 105-7 (39.3 °C), 106-8 (29.1 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (27 devre): 101-8 (39.9 °C), 102-3 (41.1 °C), 102-2 (41.1 °C), 103-4 (39.9 °C), 104-5 (39.6 °C), 105-6 (39.3 °C), 105-7 (39.3 °C), 106-9 (29.1 °C) ...</t>
         </is>
       </c>
       <c r="F38" s="243" t="inlineStr">
@@ -20432,13 +20432,13 @@
       <c r="D7" s="389" t="n"/>
       <c r="E7" s="391" t="n"/>
       <c r="F7" s="392" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G7" s="392" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="392" t="n">
         <v>2</v>
-      </c>
-      <c r="H7" s="392" t="n">
-        <v>3</v>
       </c>
       <c r="I7" s="392" t="n">
         <v>4</v>
@@ -20453,61 +20453,61 @@
         <v>7</v>
       </c>
       <c r="M7" s="392" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N7" s="392" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O7" s="392" t="n">
+        <v>18</v>
+      </c>
+      <c r="P7" s="392" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="392" t="n">
+        <v>11</v>
+      </c>
+      <c r="R7" s="392" t="n">
         <v>10</v>
       </c>
-      <c r="P7" s="392" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q7" s="392" t="n">
-        <v>12</v>
-      </c>
-      <c r="R7" s="392" t="n">
+      <c r="S7" s="392" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" s="392" t="n">
+        <v>17</v>
+      </c>
+      <c r="U7" s="392" t="n">
         <v>13</v>
       </c>
-      <c r="S7" s="392" t="n">
+      <c r="V7" s="392" t="n">
+        <v>15</v>
+      </c>
+      <c r="W7" s="392" t="n">
         <v>14</v>
       </c>
-      <c r="T7" s="392" t="n">
-        <v>15</v>
-      </c>
-      <c r="U7" s="392" t="n">
-        <v>16</v>
-      </c>
-      <c r="V7" s="392" t="n">
-        <v>17</v>
-      </c>
-      <c r="W7" s="392" t="n">
-        <v>18</v>
-      </c>
       <c r="X7" s="392" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y7" s="392" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Z7" s="392" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AA7" s="392" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB7" s="392" t="n">
         <v>23</v>
       </c>
       <c r="AC7" s="392" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AD7" s="392" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AE7" s="392" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AF7" s="392" t="n">
         <v>27</v>
@@ -24024,7 +24024,7 @@
     <row r="38" ht="12.75" customHeight="1" s="244">
       <c r="B38" s="411" t="inlineStr">
         <is>
-          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (25 devre): 201-1 (39.4 °C), 202-2 (41.1 °C), 202-3 (41.1 °C), 203-4 (39.9 °C), 204-5 (39.6 °C), 205-6 (39.3 °C), 205-7 (39.3 °C), 206-8 (32.4 °C) ...</t>
+          <t>UYARI: 35 W/m × L esasında döşeme yüzey sıcaklığı sınırı aşılıyor (25 devre): 201-8 (39.4 °C), 202-3 (41.1 °C), 202-2 (41.1 °C), 203-4 (39.9 °C), 204-5 (39.6 °C), 205-6 (39.3 °C), 205-7 (39.3 °C), 206-9 (32.4 °C) ...</t>
         </is>
       </c>
       <c r="F38" s="243" t="inlineStr">
